--- a/source/2026 - 2027 FEE.xlsx
+++ b/source/2026 - 2027 FEE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\KBI\ACCOUNTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E74E945-2CD0-43F7-8B64-DC4CAD2F27EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB9888DF-3D94-470D-B6B1-86121ACF596C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="781" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="254">
   <si>
     <t>LAST NAME</t>
   </si>
@@ -797,6 +797,9 @@
   <si>
     <t>DAVID OLUWADARASIMI</t>
   </si>
+  <si>
+    <t>CRECHE</t>
+  </si>
 </sst>
 </file>
 
@@ -1419,13 +1422,13 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
-        <v>34</v>
+        <v>143</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>197</v>
+        <v>241</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>36</v>
+        <v>253</v>
       </c>
       <c r="D2" s="16">
         <v>0.25</v>
@@ -1434,16 +1437,16 @@
         <v>0</v>
       </c>
       <c r="F2" s="17">
-        <v>33000</v>
+        <v>26000</v>
       </c>
       <c r="G2" s="17">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="H2" s="17">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="I2" s="17">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="J2" s="17">
         <f>(1-$D2)*E2</f>
@@ -1451,25 +1454,25 @@
       </c>
       <c r="K2" s="17">
         <f>(1-$D2)*F2</f>
-        <v>24750</v>
+        <v>19500</v>
       </c>
       <c r="L2" s="17">
         <f>G2</f>
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="M2" s="17">
         <f>(1-$D2)*H2</f>
-        <v>1500</v>
+        <v>750</v>
       </c>
       <c r="N2" s="17">
         <f>(1-$D2)*I2</f>
-        <v>4500</v>
+        <v>0</v>
       </c>
       <c r="O2" s="17">
-        <v>19560</v>
+        <v>0</v>
       </c>
       <c r="P2" s="17">
-        <v>14330</v>
+        <v>3050</v>
       </c>
       <c r="Q2" s="17">
         <v>0</v>
@@ -1481,7 +1484,7 @@
         <v>0</v>
       </c>
       <c r="T2" s="17">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="U2" s="17">
         <v>0</v>
@@ -1496,18 +1499,18 @@
         <v>0</v>
       </c>
       <c r="Y2" s="17">
-        <v>750</v>
+        <v>0</v>
       </c>
       <c r="Z2" s="17">
         <f>SUM(J2:Y2)</f>
-        <v>78390</v>
+        <v>27300</v>
       </c>
       <c r="AA2" s="17">
         <v>0</v>
       </c>
       <c r="AB2" s="14">
         <f>Z2-AA2</f>
-        <v>78390</v>
+        <v>27300</v>
       </c>
       <c r="AC2" s="17" t="str">
         <f>IF(AND($T2=6000, ($T2+$W2-$AB2)&gt;=6000),T2,"")</f>
@@ -1524,31 +1527,31 @@
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>53</v>
+        <v>242</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>36</v>
+        <v>253</v>
       </c>
       <c r="D3" s="16">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="E3" s="17">
         <v>0</v>
       </c>
       <c r="F3" s="17">
-        <v>33000</v>
+        <v>26000</v>
       </c>
       <c r="G3" s="17">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="H3" s="17">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="I3" s="17">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="J3" s="17">
         <f>(1-$D3)*E3</f>
@@ -1556,25 +1559,25 @@
       </c>
       <c r="K3" s="17">
         <f>(1-$D3)*F3</f>
-        <v>23100</v>
+        <v>26000</v>
       </c>
       <c r="L3" s="17">
         <f>G3</f>
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="M3" s="17">
         <f>(1-$D3)*H3</f>
-        <v>1400</v>
+        <v>1000</v>
       </c>
       <c r="N3" s="17">
         <f>(1-$D3)*I3</f>
-        <v>4200</v>
+        <v>0</v>
       </c>
       <c r="O3" s="17">
-        <v>19560</v>
+        <v>0</v>
       </c>
       <c r="P3" s="17">
-        <v>14330</v>
+        <v>3050</v>
       </c>
       <c r="Q3" s="17">
         <v>0</v>
@@ -1605,14 +1608,14 @@
       </c>
       <c r="Z3" s="17">
         <f>SUM(J3:Y3)</f>
-        <v>67590</v>
+        <v>34050</v>
       </c>
       <c r="AA3" s="17">
         <v>0</v>
       </c>
       <c r="AB3" s="14">
         <f>Z3-AA3</f>
-        <v>67590</v>
+        <v>34050</v>
       </c>
       <c r="AC3" s="17" t="str">
         <f>IF(AND($T3=6000, ($T3+$W3-$AB3)&gt;=6000),T3,"")</f>
@@ -1629,13 +1632,13 @@
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
-        <v>57</v>
+        <v>121</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>179</v>
+        <v>243</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>36</v>
+        <v>253</v>
       </c>
       <c r="D4" s="16">
         <v>0.25</v>
@@ -1644,16 +1647,16 @@
         <v>0</v>
       </c>
       <c r="F4" s="17">
-        <v>33000</v>
+        <v>26000</v>
       </c>
       <c r="G4" s="17">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="H4" s="17">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="I4" s="17">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="J4" s="17">
         <f>(1-$D4)*E4</f>
@@ -1661,25 +1664,25 @@
       </c>
       <c r="K4" s="17">
         <f>(1-$D4)*F4</f>
-        <v>24750</v>
+        <v>19500</v>
       </c>
       <c r="L4" s="17">
         <f>G4</f>
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="M4" s="17">
         <f>(1-$D4)*H4</f>
-        <v>1500</v>
+        <v>750</v>
       </c>
       <c r="N4" s="17">
         <f>(1-$D4)*I4</f>
-        <v>4500</v>
+        <v>0</v>
       </c>
       <c r="O4" s="17">
-        <v>19560</v>
+        <v>0</v>
       </c>
       <c r="P4" s="17">
-        <v>14330</v>
+        <v>3050</v>
       </c>
       <c r="Q4" s="17">
         <v>0</v>
@@ -1710,14 +1713,14 @@
       </c>
       <c r="Z4" s="17">
         <f>SUM(J4:Y4)</f>
-        <v>69640</v>
+        <v>27300</v>
       </c>
       <c r="AA4" s="17">
         <v>0</v>
       </c>
       <c r="AB4" s="14">
         <f>Z4-AA4</f>
-        <v>69640</v>
+        <v>27300</v>
       </c>
       <c r="AC4" s="17" t="str">
         <f>IF(AND($T4=6000, ($T4+$W4-$AB4)&gt;=6000),T4,"")</f>
@@ -1734,16 +1737,16 @@
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
-        <v>195</v>
+        <v>34</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C5" s="15" t="s">
         <v>36</v>
       </c>
       <c r="D5" s="16">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E5" s="17">
         <v>0</v>
@@ -1766,7 +1769,7 @@
       </c>
       <c r="K5" s="17">
         <f>(1-$D5)*F5</f>
-        <v>33000</v>
+        <v>24750</v>
       </c>
       <c r="L5" s="17">
         <f>G5</f>
@@ -1774,11 +1777,11 @@
       </c>
       <c r="M5" s="17">
         <f>(1-$D5)*H5</f>
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="N5" s="17">
         <f>(1-$D5)*I5</f>
-        <v>6000</v>
+        <v>4500</v>
       </c>
       <c r="O5" s="17">
         <v>19560</v>
@@ -1796,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="T5" s="17">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="U5" s="17">
         <v>0</v>
@@ -1811,18 +1814,18 @@
         <v>0</v>
       </c>
       <c r="Y5" s="17">
-        <v>0</v>
+        <v>750</v>
       </c>
       <c r="Z5" s="17">
         <f>SUM(J5:Y5)</f>
-        <v>79890</v>
+        <v>78390</v>
       </c>
       <c r="AA5" s="17">
         <v>0</v>
       </c>
       <c r="AB5" s="14">
         <f>Z5-AA5</f>
-        <v>79890</v>
+        <v>78390</v>
       </c>
       <c r="AC5" s="17" t="str">
         <f>IF(AND($T5=6000, ($T5+$W5-$AB5)&gt;=6000),T5,"")</f>
@@ -1839,10 +1842,10 @@
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
-        <v>89</v>
+        <v>53</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>92</v>
+        <v>56</v>
       </c>
       <c r="C6" s="15" t="s">
         <v>36</v>
@@ -1944,16 +1947,16 @@
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>51</v>
+        <v>179</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="D7" s="16">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="E7" s="17">
         <v>0</v>
@@ -1976,7 +1979,7 @@
       </c>
       <c r="K7" s="17">
         <f>(1-$D7)*F7</f>
-        <v>16500</v>
+        <v>24750</v>
       </c>
       <c r="L7" s="17">
         <f>G7</f>
@@ -1984,14 +1987,14 @@
       </c>
       <c r="M7" s="17">
         <f>(1-$D7)*H7</f>
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="N7" s="17">
         <f>(1-$D7)*I7</f>
-        <v>3000</v>
+        <v>4500</v>
       </c>
       <c r="O7" s="17">
-        <v>22580</v>
+        <v>19560</v>
       </c>
       <c r="P7" s="17">
         <v>14330</v>
@@ -2025,14 +2028,14 @@
       </c>
       <c r="Z7" s="17">
         <f>SUM(J7:Y7)</f>
-        <v>62410</v>
+        <v>69640</v>
       </c>
       <c r="AA7" s="17">
         <v>0</v>
       </c>
       <c r="AB7" s="14">
         <f>Z7-AA7</f>
-        <v>62410</v>
+        <v>69640</v>
       </c>
       <c r="AC7" s="17" t="str">
         <f>IF(AND($T7=6000, ($T7+$W7-$AB7)&gt;=6000),T7,"")</f>
@@ -2049,16 +2052,16 @@
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
-        <v>57</v>
+        <v>195</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>58</v>
+        <v>196</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="D8" s="16">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E8" s="17">
         <v>0</v>
@@ -2081,7 +2084,7 @@
       </c>
       <c r="K8" s="17">
         <f>(1-$D8)*F8</f>
-        <v>16500</v>
+        <v>33000</v>
       </c>
       <c r="L8" s="17">
         <f>G8</f>
@@ -2089,14 +2092,14 @@
       </c>
       <c r="M8" s="17">
         <f>(1-$D8)*H8</f>
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="N8" s="17">
         <f>(1-$D8)*I8</f>
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="O8" s="17">
-        <v>22580</v>
+        <v>19560</v>
       </c>
       <c r="P8" s="17">
         <v>14330</v>
@@ -2130,14 +2133,14 @@
       </c>
       <c r="Z8" s="17">
         <f>SUM(J8:Y8)</f>
-        <v>62410</v>
+        <v>79890</v>
       </c>
       <c r="AA8" s="17">
         <v>0</v>
       </c>
       <c r="AB8" s="14">
         <f>Z8-AA8</f>
-        <v>62410</v>
+        <v>79890</v>
       </c>
       <c r="AC8" s="17" t="str">
         <f>IF(AND($T8=6000, ($T8+$W8-$AB8)&gt;=6000),T8,"")</f>
@@ -2154,16 +2157,16 @@
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A9" s="15" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="D9" s="16">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="E9" s="17">
         <v>0</v>
@@ -2186,7 +2189,7 @@
       </c>
       <c r="K9" s="17">
         <f>(1-$D9)*F9</f>
-        <v>16500</v>
+        <v>23100</v>
       </c>
       <c r="L9" s="17">
         <f>G9</f>
@@ -2194,14 +2197,14 @@
       </c>
       <c r="M9" s="17">
         <f>(1-$D9)*H9</f>
-        <v>1000</v>
+        <v>1400</v>
       </c>
       <c r="N9" s="17">
         <f>(1-$D9)*I9</f>
-        <v>3000</v>
+        <v>4200</v>
       </c>
       <c r="O9" s="17">
-        <v>22580</v>
+        <v>19560</v>
       </c>
       <c r="P9" s="17">
         <v>14330</v>
@@ -2216,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="T9" s="17">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="U9" s="17">
         <v>0</v>
@@ -2231,18 +2234,18 @@
         <v>0</v>
       </c>
       <c r="Y9" s="17">
-        <v>-30</v>
+        <v>0</v>
       </c>
       <c r="Z9" s="17">
         <f>SUM(J9:Y9)</f>
-        <v>70380</v>
+        <v>67590</v>
       </c>
       <c r="AA9" s="17">
         <v>0</v>
       </c>
       <c r="AB9" s="14">
         <f>Z9-AA9</f>
-        <v>70380</v>
+        <v>67590</v>
       </c>
       <c r="AC9" s="17" t="str">
         <f>IF(AND($T9=6000, ($T9+$W9-$AB9)&gt;=6000),T9,"")</f>
@@ -2259,16 +2262,16 @@
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="C10" s="15" t="s">
         <v>67</v>
       </c>
       <c r="D10" s="16">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E10" s="17">
         <v>0</v>
@@ -2291,7 +2294,7 @@
       </c>
       <c r="K10" s="17">
         <f>(1-$D10)*F10</f>
-        <v>33000</v>
+        <v>16500</v>
       </c>
       <c r="L10" s="17">
         <f>G10</f>
@@ -2299,11 +2302,11 @@
       </c>
       <c r="M10" s="17">
         <f>(1-$D10)*H10</f>
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="N10" s="17">
         <f>(1-$D10)*I10</f>
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="O10" s="17">
         <v>22580</v>
@@ -2336,18 +2339,18 @@
         <v>0</v>
       </c>
       <c r="Y10" s="17">
-        <v>-8970</v>
+        <v>0</v>
       </c>
       <c r="Z10" s="17">
         <f>SUM(J10:Y10)</f>
-        <v>73940</v>
+        <v>62410</v>
       </c>
       <c r="AA10" s="17">
         <v>0</v>
       </c>
       <c r="AB10" s="14">
         <f>Z10-AA10</f>
-        <v>73940</v>
+        <v>62410</v>
       </c>
       <c r="AC10" s="17" t="str">
         <f>IF(AND($T10=6000, ($T10+$W10-$AB10)&gt;=6000),T10,"")</f>
@@ -2364,10 +2367,10 @@
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="C11" s="15" t="s">
         <v>67</v>
@@ -2441,18 +2444,18 @@
         <v>0</v>
       </c>
       <c r="Y11" s="17">
-        <v>480</v>
+        <v>0</v>
       </c>
       <c r="Z11" s="17">
         <f>SUM(J11:Y11)</f>
-        <v>62890</v>
+        <v>62410</v>
       </c>
       <c r="AA11" s="17">
         <v>0</v>
       </c>
       <c r="AB11" s="14">
         <f>Z11-AA11</f>
-        <v>62890</v>
+        <v>62410</v>
       </c>
       <c r="AC11" s="17" t="str">
         <f>IF(AND($T11=6000, ($T11+$W11-$AB11)&gt;=6000),T11,"")</f>
@@ -2469,16 +2472,16 @@
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
-        <v>191</v>
+        <v>65</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>199</v>
+        <v>66</v>
       </c>
       <c r="C12" s="15" t="s">
         <v>67</v>
       </c>
       <c r="D12" s="16">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E12" s="17">
         <v>0</v>
@@ -2501,7 +2504,7 @@
       </c>
       <c r="K12" s="17">
         <f>(1-$D12)*F12</f>
-        <v>24750</v>
+        <v>16500</v>
       </c>
       <c r="L12" s="17">
         <f>G12</f>
@@ -2509,11 +2512,11 @@
       </c>
       <c r="M12" s="17">
         <f>(1-$D12)*H12</f>
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="N12" s="17">
         <f>(1-$D12)*I12</f>
-        <v>4500</v>
+        <v>3000</v>
       </c>
       <c r="O12" s="17">
         <v>22580</v>
@@ -2531,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="T12" s="17">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="U12" s="17">
         <v>0</v>
@@ -2546,18 +2549,18 @@
         <v>0</v>
       </c>
       <c r="Y12" s="17">
-        <v>0</v>
+        <v>-30</v>
       </c>
       <c r="Z12" s="17">
         <f>SUM(J12:Y12)</f>
-        <v>72660</v>
+        <v>70380</v>
       </c>
       <c r="AA12" s="17">
         <v>0</v>
       </c>
       <c r="AB12" s="14">
         <f>Z12-AA12</f>
-        <v>72660</v>
+        <v>70380</v>
       </c>
       <c r="AC12" s="17" t="str">
         <f>IF(AND($T12=6000, ($T12+$W12-$AB12)&gt;=6000),T12,"")</f>
@@ -2574,16 +2577,16 @@
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C13" s="15" t="s">
         <v>67</v>
       </c>
       <c r="D13" s="16">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E13" s="17">
         <v>0</v>
@@ -2606,7 +2609,7 @@
       </c>
       <c r="K13" s="17">
         <f>(1-$D13)*F13</f>
-        <v>16500</v>
+        <v>33000</v>
       </c>
       <c r="L13" s="17">
         <f>G13</f>
@@ -2614,11 +2617,11 @@
       </c>
       <c r="M13" s="17">
         <f>(1-$D13)*H13</f>
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="N13" s="17">
         <f>(1-$D13)*I13</f>
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="O13" s="17">
         <v>22580</v>
@@ -2651,18 +2654,18 @@
         <v>0</v>
       </c>
       <c r="Y13" s="17">
-        <v>500</v>
+        <v>-8970</v>
       </c>
       <c r="Z13" s="17">
         <f>SUM(J13:Y13)</f>
-        <v>62910</v>
+        <v>73940</v>
       </c>
       <c r="AA13" s="17">
         <v>0</v>
       </c>
       <c r="AB13" s="14">
         <f>Z13-AA13</f>
-        <v>62910</v>
+        <v>73940</v>
       </c>
       <c r="AC13" s="17" t="str">
         <f>IF(AND($T13=6000, ($T13+$W13-$AB13)&gt;=6000),T13,"")</f>
@@ -2679,10 +2682,10 @@
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="C14" s="15" t="s">
         <v>67</v>
@@ -2756,18 +2759,18 @@
         <v>0</v>
       </c>
       <c r="Y14" s="17">
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="Z14" s="17">
         <f>SUM(J14:Y14)</f>
-        <v>62410</v>
+        <v>62890</v>
       </c>
       <c r="AA14" s="17">
         <v>0</v>
       </c>
       <c r="AB14" s="14">
         <f>Z14-AA14</f>
-        <v>62410</v>
+        <v>62890</v>
       </c>
       <c r="AC14" s="17" t="str">
         <f>IF(AND($T14=6000, ($T14+$W14-$AB14)&gt;=6000),T14,"")</f>
@@ -2784,16 +2787,16 @@
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A15" s="15" t="s">
-        <v>111</v>
+        <v>191</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>112</v>
+        <v>199</v>
       </c>
       <c r="C15" s="15" t="s">
         <v>67</v>
       </c>
       <c r="D15" s="16">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="E15" s="17">
         <v>0</v>
@@ -2816,7 +2819,7 @@
       </c>
       <c r="K15" s="17">
         <f>(1-$D15)*F15</f>
-        <v>23100</v>
+        <v>24750</v>
       </c>
       <c r="L15" s="17">
         <f>G15</f>
@@ -2824,11 +2827,11 @@
       </c>
       <c r="M15" s="17">
         <f>(1-$D15)*H15</f>
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="N15" s="17">
         <f>(1-$D15)*I15</f>
-        <v>4200</v>
+        <v>4500</v>
       </c>
       <c r="O15" s="17">
         <v>22580</v>
@@ -2865,14 +2868,14 @@
       </c>
       <c r="Z15" s="17">
         <f>SUM(J15:Y15)</f>
-        <v>70610</v>
+        <v>72660</v>
       </c>
       <c r="AA15" s="17">
         <v>0</v>
       </c>
       <c r="AB15" s="14">
         <f>Z15-AA15</f>
-        <v>70610</v>
+        <v>72660</v>
       </c>
       <c r="AC15" s="17" t="str">
         <f>IF(AND($T15=6000, ($T15+$W15-$AB15)&gt;=6000),T15,"")</f>
@@ -2889,10 +2892,10 @@
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
-        <v>116</v>
+        <v>55</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="C16" s="15" t="s">
         <v>67</v>
@@ -2951,7 +2954,7 @@
         <v>0</v>
       </c>
       <c r="T16" s="17">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="U16" s="17">
         <v>0</v>
@@ -2966,18 +2969,18 @@
         <v>0</v>
       </c>
       <c r="Y16" s="17">
-        <v>-3145</v>
+        <v>500</v>
       </c>
       <c r="Z16" s="17">
         <f>SUM(J16:Y16)</f>
-        <v>67265</v>
+        <v>62910</v>
       </c>
       <c r="AA16" s="17">
         <v>0</v>
       </c>
       <c r="AB16" s="14">
         <f>Z16-AA16</f>
-        <v>67265</v>
+        <v>62910</v>
       </c>
       <c r="AC16" s="17" t="str">
         <f>IF(AND($T16=6000, ($T16+$W16-$AB16)&gt;=6000),T16,"")</f>
@@ -2994,16 +2997,16 @@
     </row>
     <row r="17" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A17" s="15" t="s">
-        <v>130</v>
+        <v>85</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>131</v>
+        <v>86</v>
       </c>
       <c r="C17" s="15" t="s">
         <v>67</v>
       </c>
       <c r="D17" s="16">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="E17" s="17">
         <v>0</v>
@@ -3026,7 +3029,7 @@
       </c>
       <c r="K17" s="17">
         <f>(1-$D17)*F17</f>
-        <v>23100</v>
+        <v>16500</v>
       </c>
       <c r="L17" s="17">
         <f>G17</f>
@@ -3034,11 +3037,11 @@
       </c>
       <c r="M17" s="17">
         <f>(1-$D17)*H17</f>
-        <v>1400</v>
+        <v>1000</v>
       </c>
       <c r="N17" s="17">
         <f>(1-$D17)*I17</f>
-        <v>4200</v>
+        <v>3000</v>
       </c>
       <c r="O17" s="17">
         <v>22580</v>
@@ -3056,7 +3059,7 @@
         <v>0</v>
       </c>
       <c r="T17" s="17">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="U17" s="17">
         <v>0</v>
@@ -3075,14 +3078,14 @@
       </c>
       <c r="Z17" s="17">
         <f>SUM(J17:Y17)</f>
-        <v>78610</v>
+        <v>62410</v>
       </c>
       <c r="AA17" s="17">
         <v>0</v>
       </c>
       <c r="AB17" s="14">
         <f>Z17-AA17</f>
-        <v>78610</v>
+        <v>62410</v>
       </c>
       <c r="AC17" s="17" t="str">
         <f>IF(AND($T17=6000, ($T17+$W17-$AB17)&gt;=6000),T17,"")</f>
@@ -3099,31 +3102,31 @@
     </row>
     <row r="18" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A18" s="15" t="s">
-        <v>236</v>
+        <v>111</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>240</v>
+        <v>112</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="D18" s="16">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="E18" s="17">
         <v>0</v>
       </c>
       <c r="F18" s="17">
-        <v>26000</v>
+        <v>33000</v>
       </c>
       <c r="G18" s="17">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="H18" s="17">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I18" s="17">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="J18" s="17">
         <f>(1-$D18)*E18</f>
@@ -3131,25 +3134,25 @@
       </c>
       <c r="K18" s="17">
         <f>(1-$D18)*F18</f>
-        <v>19500</v>
+        <v>23100</v>
       </c>
       <c r="L18" s="17">
         <f>G18</f>
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="M18" s="17">
         <f>(1-$D18)*H18</f>
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="N18" s="17">
         <f>(1-$D18)*I18</f>
-        <v>0</v>
+        <v>4200</v>
       </c>
       <c r="O18" s="17">
-        <v>13080</v>
+        <v>22580</v>
       </c>
       <c r="P18" s="17">
-        <v>7550</v>
+        <v>14330</v>
       </c>
       <c r="Q18" s="17">
         <v>0</v>
@@ -3161,7 +3164,7 @@
         <v>0</v>
       </c>
       <c r="T18" s="17">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="U18" s="17">
         <v>0</v>
@@ -3176,18 +3179,18 @@
         <v>0</v>
       </c>
       <c r="Y18" s="17">
-        <v>750</v>
+        <v>0</v>
       </c>
       <c r="Z18" s="17">
         <f>SUM(J18:Y18)</f>
-        <v>50880</v>
+        <v>70610</v>
       </c>
       <c r="AA18" s="17">
         <v>0</v>
       </c>
       <c r="AB18" s="14">
         <f>Z18-AA18</f>
-        <v>50880</v>
+        <v>70610</v>
       </c>
       <c r="AC18" s="17" t="str">
         <f>IF(AND($T18=6000, ($T18+$W18-$AB18)&gt;=6000),T18,"")</f>
@@ -3204,31 +3207,31 @@
     </row>
     <row r="19" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A19" s="15" t="s">
-        <v>182</v>
+        <v>116</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>209</v>
+        <v>117</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="D19" s="16">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E19" s="17">
         <v>0</v>
       </c>
       <c r="F19" s="17">
-        <v>26000</v>
+        <v>33000</v>
       </c>
       <c r="G19" s="17">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="H19" s="17">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I19" s="17">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="J19" s="17">
         <f>(1-$D19)*E19</f>
@@ -3236,25 +3239,25 @@
       </c>
       <c r="K19" s="17">
         <f>(1-$D19)*F19</f>
-        <v>19500</v>
+        <v>16500</v>
       </c>
       <c r="L19" s="17">
         <f>G19</f>
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="M19" s="17">
         <f>(1-$D19)*H19</f>
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="N19" s="17">
         <f>(1-$D19)*I19</f>
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="O19" s="17">
-        <v>13080</v>
+        <v>22580</v>
       </c>
       <c r="P19" s="17">
-        <v>7550</v>
+        <v>14330</v>
       </c>
       <c r="Q19" s="17">
         <v>0</v>
@@ -3266,7 +3269,7 @@
         <v>0</v>
       </c>
       <c r="T19" s="17">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="U19" s="17">
         <v>0</v>
@@ -3281,18 +3284,18 @@
         <v>0</v>
       </c>
       <c r="Y19" s="17">
-        <v>0</v>
+        <v>-3145</v>
       </c>
       <c r="Z19" s="17">
         <f>SUM(J19:Y19)</f>
-        <v>44130</v>
+        <v>67265</v>
       </c>
       <c r="AA19" s="17">
         <v>0</v>
       </c>
       <c r="AB19" s="14">
         <f>Z19-AA19</f>
-        <v>44130</v>
+        <v>67265</v>
       </c>
       <c r="AC19" s="17" t="str">
         <f>IF(AND($T19=6000, ($T19+$W19-$AB19)&gt;=6000),T19,"")</f>
@@ -3309,31 +3312,31 @@
     </row>
     <row r="20" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="D20" s="16">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="E20" s="17">
         <v>0</v>
       </c>
       <c r="F20" s="17">
-        <v>26000</v>
+        <v>33000</v>
       </c>
       <c r="G20" s="17">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="H20" s="17">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I20" s="17">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="J20" s="17">
         <f>(1-$D20)*E20</f>
@@ -3341,25 +3344,25 @@
       </c>
       <c r="K20" s="17">
         <f>(1-$D20)*F20</f>
-        <v>19500</v>
+        <v>23100</v>
       </c>
       <c r="L20" s="17">
         <f>G20</f>
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="M20" s="17">
         <f>(1-$D20)*H20</f>
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="N20" s="17">
         <f>(1-$D20)*I20</f>
-        <v>0</v>
+        <v>4200</v>
       </c>
       <c r="O20" s="17">
-        <v>13080</v>
+        <v>22580</v>
       </c>
       <c r="P20" s="17">
-        <v>7550</v>
+        <v>14330</v>
       </c>
       <c r="Q20" s="17">
         <v>0</v>
@@ -3371,7 +3374,7 @@
         <v>0</v>
       </c>
       <c r="T20" s="17">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="U20" s="17">
         <v>0</v>
@@ -3390,14 +3393,14 @@
       </c>
       <c r="Z20" s="17">
         <f>SUM(J20:Y20)</f>
-        <v>50130</v>
+        <v>78610</v>
       </c>
       <c r="AA20" s="17">
         <v>0</v>
       </c>
       <c r="AB20" s="14">
         <f>Z20-AA20</f>
-        <v>50130</v>
+        <v>78610</v>
       </c>
       <c r="AC20" s="17" t="str">
         <f>IF(AND($T20=6000, ($T20+$W20-$AB20)&gt;=6000),T20,"")</f>
@@ -3414,16 +3417,16 @@
     </row>
     <row r="21" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A21" s="15" t="s">
-        <v>63</v>
+        <v>236</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>54</v>
+        <v>240</v>
       </c>
       <c r="C21" s="15" t="s">
         <v>44</v>
       </c>
       <c r="D21" s="16">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E21" s="17">
         <v>0</v>
@@ -3446,7 +3449,7 @@
       </c>
       <c r="K21" s="17">
         <f>(1-$D21)*F21</f>
-        <v>26000</v>
+        <v>19500</v>
       </c>
       <c r="L21" s="17">
         <f>G21</f>
@@ -3491,18 +3494,18 @@
         <v>0</v>
       </c>
       <c r="Y21" s="17">
-        <v>0</v>
+        <v>750</v>
       </c>
       <c r="Z21" s="17">
         <f>SUM(J21:Y21)</f>
-        <v>56630</v>
+        <v>50880</v>
       </c>
       <c r="AA21" s="17">
         <v>0</v>
       </c>
       <c r="AB21" s="14">
         <f>Z21-AA21</f>
-        <v>56630</v>
+        <v>50880</v>
       </c>
       <c r="AC21" s="17" t="str">
         <f>IF(AND($T21=6000, ($T21+$W21-$AB21)&gt;=6000),T21,"")</f>
@@ -3519,16 +3522,16 @@
     </row>
     <row r="22" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
-        <v>155</v>
+        <v>182</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>156</v>
+        <v>209</v>
       </c>
       <c r="C22" s="15" t="s">
         <v>44</v>
       </c>
       <c r="D22" s="16">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E22" s="17">
         <v>0</v>
@@ -3551,7 +3554,7 @@
       </c>
       <c r="K22" s="17">
         <f>(1-$D22)*F22</f>
-        <v>26000</v>
+        <v>19500</v>
       </c>
       <c r="L22" s="17">
         <f>G22</f>
@@ -3581,7 +3584,7 @@
         <v>0</v>
       </c>
       <c r="T22" s="17">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="U22" s="17">
         <v>0</v>
@@ -3600,14 +3603,14 @@
       </c>
       <c r="Z22" s="17">
         <f>SUM(J22:Y22)</f>
-        <v>56630</v>
+        <v>44130</v>
       </c>
       <c r="AA22" s="17">
         <v>0</v>
       </c>
       <c r="AB22" s="14">
         <f>Z22-AA22</f>
-        <v>56630</v>
+        <v>44130</v>
       </c>
       <c r="AC22" s="17" t="str">
         <f>IF(AND($T22=6000, ($T22+$W22-$AB22)&gt;=6000),T22,"")</f>
@@ -3624,16 +3627,16 @@
     </row>
     <row r="23" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A23" s="15" t="s">
-        <v>177</v>
+        <v>143</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>178</v>
+        <v>144</v>
       </c>
       <c r="C23" s="15" t="s">
         <v>44</v>
       </c>
       <c r="D23" s="16">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E23" s="17">
         <v>0</v>
@@ -3656,7 +3659,7 @@
       </c>
       <c r="K23" s="17">
         <f>(1-$D23)*F23</f>
-        <v>26000</v>
+        <v>19500</v>
       </c>
       <c r="L23" s="17">
         <f>G23</f>
@@ -3686,7 +3689,7 @@
         <v>0</v>
       </c>
       <c r="T23" s="17">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="U23" s="17">
         <v>0</v>
@@ -3705,14 +3708,14 @@
       </c>
       <c r="Z23" s="17">
         <f>SUM(J23:Y23)</f>
-        <v>50630</v>
+        <v>50130</v>
       </c>
       <c r="AA23" s="17">
         <v>0</v>
       </c>
       <c r="AB23" s="14">
         <f>Z23-AA23</f>
-        <v>50630</v>
+        <v>50130</v>
       </c>
       <c r="AC23" s="17" t="str">
         <f>IF(AND($T23=6000, ($T23+$W23-$AB23)&gt;=6000),T23,"")</f>
@@ -3729,10 +3732,10 @@
     </row>
     <row r="24" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A24" s="15" t="s">
-        <v>234</v>
+        <v>63</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>235</v>
+        <v>54</v>
       </c>
       <c r="C24" s="15" t="s">
         <v>44</v>
@@ -3806,18 +3809,18 @@
         <v>0</v>
       </c>
       <c r="Y24" s="17">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z24" s="17">
         <f>SUM(J24:Y24)</f>
-        <v>57630</v>
+        <v>56630</v>
       </c>
       <c r="AA24" s="17">
         <v>0</v>
       </c>
       <c r="AB24" s="14">
         <f>Z24-AA24</f>
-        <v>57630</v>
+        <v>56630</v>
       </c>
       <c r="AC24" s="17" t="str">
         <f>IF(AND($T24=6000, ($T24+$W24-$AB24)&gt;=6000),T24,"")</f>
@@ -3834,16 +3837,16 @@
     </row>
     <row r="25" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A25" s="15" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>73</v>
+        <v>156</v>
       </c>
       <c r="C25" s="15" t="s">
         <v>44</v>
       </c>
       <c r="D25" s="16">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E25" s="17">
         <v>0</v>
@@ -3866,7 +3869,7 @@
       </c>
       <c r="K25" s="17">
         <f>(1-$D25)*F25</f>
-        <v>13000</v>
+        <v>26000</v>
       </c>
       <c r="L25" s="17">
         <f>G25</f>
@@ -3896,7 +3899,7 @@
         <v>0</v>
       </c>
       <c r="T25" s="17">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="U25" s="17">
         <v>0</v>
@@ -3911,18 +3914,18 @@
         <v>0</v>
       </c>
       <c r="Y25" s="17">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="Z25" s="17">
         <f>SUM(J25:Y25)</f>
-        <v>45630</v>
+        <v>56630</v>
       </c>
       <c r="AA25" s="17">
         <v>0</v>
       </c>
       <c r="AB25" s="14">
         <f>Z25-AA25</f>
-        <v>45630</v>
+        <v>56630</v>
       </c>
       <c r="AC25" s="17" t="str">
         <f>IF(AND($T25=6000, ($T25+$W25-$AB25)&gt;=6000),T25,"")</f>
@@ -3939,16 +3942,16 @@
     </row>
     <row r="26" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
-        <v>157</v>
+        <v>177</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="C26" s="15" t="s">
         <v>44</v>
       </c>
       <c r="D26" s="16">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E26" s="17">
         <v>0</v>
@@ -3971,7 +3974,7 @@
       </c>
       <c r="K26" s="17">
         <f>(1-$D26)*F26</f>
-        <v>13000</v>
+        <v>26000</v>
       </c>
       <c r="L26" s="17">
         <f>G26</f>
@@ -4016,18 +4019,18 @@
         <v>0</v>
       </c>
       <c r="Y26" s="17">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="Z26" s="17">
         <f>SUM(J26:Y26)</f>
-        <v>45630</v>
+        <v>50630</v>
       </c>
       <c r="AA26" s="17">
         <v>0</v>
       </c>
       <c r="AB26" s="14">
         <f>Z26-AA26</f>
-        <v>45630</v>
+        <v>50630</v>
       </c>
       <c r="AC26" s="17" t="str">
         <f>IF(AND($T26=6000, ($T26+$W26-$AB26)&gt;=6000),T26,"")</f>
@@ -4044,16 +4047,16 @@
     </row>
     <row r="27" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A27" s="15" t="s">
-        <v>159</v>
+        <v>234</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>160</v>
+        <v>235</v>
       </c>
       <c r="C27" s="15" t="s">
         <v>44</v>
       </c>
       <c r="D27" s="16">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="E27" s="17">
         <v>0</v>
@@ -4076,7 +4079,7 @@
       </c>
       <c r="K27" s="17">
         <f>(1-$D27)*F27</f>
-        <v>19500</v>
+        <v>26000</v>
       </c>
       <c r="L27" s="17">
         <f>G27</f>
@@ -4121,18 +4124,18 @@
         <v>0</v>
       </c>
       <c r="Y27" s="17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z27" s="17">
         <f>SUM(J27:Y27)</f>
-        <v>50130</v>
+        <v>57630</v>
       </c>
       <c r="AA27" s="17">
         <v>0</v>
       </c>
       <c r="AB27" s="14">
         <f>Z27-AA27</f>
-        <v>50130</v>
+        <v>57630</v>
       </c>
       <c r="AC27" s="17" t="str">
         <f>IF(AND($T27=6000, ($T27+$W27-$AB27)&gt;=6000),T27,"")</f>
@@ -4149,16 +4152,16 @@
     </row>
     <row r="28" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A28" s="15" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>163</v>
+        <v>73</v>
       </c>
       <c r="C28" s="15" t="s">
         <v>44</v>
       </c>
       <c r="D28" s="16">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E28" s="17">
         <v>0</v>
@@ -4181,7 +4184,7 @@
       </c>
       <c r="K28" s="17">
         <f>(1-$D28)*F28</f>
-        <v>19500</v>
+        <v>13000</v>
       </c>
       <c r="L28" s="17">
         <f>G28</f>
@@ -4211,7 +4214,7 @@
         <v>0</v>
       </c>
       <c r="T28" s="17">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="U28" s="17">
         <v>0</v>
@@ -4226,18 +4229,18 @@
         <v>0</v>
       </c>
       <c r="Y28" s="17">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="Z28" s="17">
         <f>SUM(J28:Y28)</f>
-        <v>50130</v>
+        <v>45630</v>
       </c>
       <c r="AA28" s="17">
         <v>0</v>
       </c>
       <c r="AB28" s="14">
         <f>Z28-AA28</f>
-        <v>50130</v>
+        <v>45630</v>
       </c>
       <c r="AC28" s="17" t="str">
         <f>IF(AND($T28=6000, ($T28+$W28-$AB28)&gt;=6000),T28,"")</f>
@@ -4254,16 +4257,16 @@
     </row>
     <row r="29" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>238</v>
+        <v>157</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>239</v>
+        <v>158</v>
       </c>
       <c r="C29" s="15" t="s">
         <v>44</v>
       </c>
       <c r="D29" s="16">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E29" s="17">
         <v>0</v>
@@ -4286,7 +4289,7 @@
       </c>
       <c r="K29" s="17">
         <f>(1-$D29)*F29</f>
-        <v>26000</v>
+        <v>13000</v>
       </c>
       <c r="L29" s="17">
         <f>G29</f>
@@ -4331,18 +4334,18 @@
         <v>0</v>
       </c>
       <c r="Y29" s="17">
-        <v>14000</v>
+        <v>8000</v>
       </c>
       <c r="Z29" s="17">
         <f>SUM(J29:Y29)</f>
-        <v>64630</v>
+        <v>45630</v>
       </c>
       <c r="AA29" s="17">
         <v>0</v>
       </c>
       <c r="AB29" s="14">
         <f>Z29-AA29</f>
-        <v>64630</v>
+        <v>45630</v>
       </c>
       <c r="AC29" s="17" t="str">
         <f>IF(AND($T29=6000, ($T29+$W29-$AB29)&gt;=6000),T29,"")</f>
@@ -4359,16 +4362,16 @@
     </row>
     <row r="30" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A30" s="15" t="s">
-        <v>93</v>
+        <v>159</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>94</v>
+        <v>160</v>
       </c>
       <c r="C30" s="15" t="s">
         <v>44</v>
       </c>
       <c r="D30" s="16">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E30" s="17">
         <v>0</v>
@@ -4391,7 +4394,7 @@
       </c>
       <c r="K30" s="17">
         <f>(1-$D30)*F30</f>
-        <v>26000</v>
+        <v>19500</v>
       </c>
       <c r="L30" s="17">
         <f>G30</f>
@@ -4421,7 +4424,7 @@
         <v>0</v>
       </c>
       <c r="T30" s="17">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="U30" s="17">
         <v>0</v>
@@ -4436,18 +4439,18 @@
         <v>0</v>
       </c>
       <c r="Y30" s="17">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="Z30" s="17">
         <f>SUM(J30:Y30)</f>
-        <v>57630</v>
+        <v>50130</v>
       </c>
       <c r="AA30" s="17">
         <v>0</v>
       </c>
       <c r="AB30" s="14">
         <f>Z30-AA30</f>
-        <v>57630</v>
+        <v>50130</v>
       </c>
       <c r="AC30" s="17" t="str">
         <f>IF(AND($T30=6000, ($T30+$W30-$AB30)&gt;=6000),T30,"")</f>
@@ -4464,16 +4467,16 @@
     </row>
     <row r="31" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A31" s="15" t="s">
-        <v>100</v>
+        <v>161</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>101</v>
+        <v>163</v>
       </c>
       <c r="C31" s="15" t="s">
         <v>44</v>
       </c>
       <c r="D31" s="16">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E31" s="17">
         <v>0</v>
@@ -4496,7 +4499,7 @@
       </c>
       <c r="K31" s="17">
         <f>(1-$D31)*F31</f>
-        <v>26000</v>
+        <v>19500</v>
       </c>
       <c r="L31" s="17">
         <f>G31</f>
@@ -4526,7 +4529,7 @@
         <v>0</v>
       </c>
       <c r="T31" s="17">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="U31" s="17">
         <v>0</v>
@@ -4541,18 +4544,18 @@
         <v>0</v>
       </c>
       <c r="Y31" s="17">
-        <v>-3030</v>
+        <v>0</v>
       </c>
       <c r="Z31" s="17">
         <f>SUM(J31:Y31)</f>
-        <v>47600</v>
+        <v>50130</v>
       </c>
       <c r="AA31" s="17">
         <v>0</v>
       </c>
       <c r="AB31" s="14">
         <f>Z31-AA31</f>
-        <v>47600</v>
+        <v>50130</v>
       </c>
       <c r="AC31" s="17" t="str">
         <f>IF(AND($T31=6000, ($T31+$W31-$AB31)&gt;=6000),T31,"")</f>
@@ -4569,10 +4572,10 @@
     </row>
     <row r="32" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A32" s="15" t="s">
-        <v>146</v>
+        <v>238</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>147</v>
+        <v>239</v>
       </c>
       <c r="C32" s="15" t="s">
         <v>44</v>
@@ -4631,7 +4634,7 @@
         <v>0</v>
       </c>
       <c r="T32" s="17">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="U32" s="17">
         <v>0</v>
@@ -4646,18 +4649,18 @@
         <v>0</v>
       </c>
       <c r="Y32" s="17">
-        <v>0</v>
+        <v>14000</v>
       </c>
       <c r="Z32" s="17">
         <f>SUM(J32:Y32)</f>
-        <v>56630</v>
+        <v>64630</v>
       </c>
       <c r="AA32" s="17">
         <v>0</v>
       </c>
       <c r="AB32" s="14">
         <f>Z32-AA32</f>
-        <v>56630</v>
+        <v>64630</v>
       </c>
       <c r="AC32" s="17" t="str">
         <f>IF(AND($T32=6000, ($T32+$W32-$AB32)&gt;=6000),T32,"")</f>
@@ -4674,16 +4677,16 @@
     </row>
     <row r="33" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A33" s="15" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="C33" s="15" t="s">
         <v>44</v>
       </c>
       <c r="D33" s="16">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="E33" s="17">
         <v>0</v>
@@ -4706,7 +4709,7 @@
       </c>
       <c r="K33" s="17">
         <f>(1-$D33)*F33</f>
-        <v>19500</v>
+        <v>26000</v>
       </c>
       <c r="L33" s="17">
         <f>G33</f>
@@ -4736,7 +4739,7 @@
         <v>0</v>
       </c>
       <c r="T33" s="17">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="U33" s="17">
         <v>0</v>
@@ -4751,18 +4754,18 @@
         <v>0</v>
       </c>
       <c r="Y33" s="17">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="Z33" s="17">
         <f>SUM(J33:Y33)</f>
-        <v>50130</v>
+        <v>57630</v>
       </c>
       <c r="AA33" s="17">
         <v>0</v>
       </c>
       <c r="AB33" s="14">
         <f>Z33-AA33</f>
-        <v>50130</v>
+        <v>57630</v>
       </c>
       <c r="AC33" s="17" t="str">
         <f>IF(AND($T33=6000, ($T33+$W33-$AB33)&gt;=6000),T33,"")</f>
@@ -4779,16 +4782,16 @@
     </row>
     <row r="34" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A34" s="15" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="B34" s="15" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="C34" s="15" t="s">
         <v>44</v>
       </c>
       <c r="D34" s="16">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E34" s="17">
         <v>0</v>
@@ -4811,7 +4814,7 @@
       </c>
       <c r="K34" s="17">
         <f>(1-$D34)*F34</f>
-        <v>13000</v>
+        <v>26000</v>
       </c>
       <c r="L34" s="17">
         <f>G34</f>
@@ -4856,18 +4859,18 @@
         <v>0</v>
       </c>
       <c r="Y34" s="17">
-        <v>8000</v>
+        <v>-3030</v>
       </c>
       <c r="Z34" s="17">
         <f>SUM(J34:Y34)</f>
-        <v>45630</v>
+        <v>47600</v>
       </c>
       <c r="AA34" s="17">
         <v>0</v>
       </c>
       <c r="AB34" s="14">
         <f>Z34-AA34</f>
-        <v>45630</v>
+        <v>47600</v>
       </c>
       <c r="AC34" s="17" t="str">
         <f>IF(AND($T34=6000, ($T34+$W34-$AB34)&gt;=6000),T34,"")</f>
@@ -4884,16 +4887,16 @@
     </row>
     <row r="35" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A35" s="15" t="s">
-        <v>118</v>
+        <v>146</v>
       </c>
       <c r="B35" s="15" t="s">
-        <v>119</v>
+        <v>147</v>
       </c>
       <c r="C35" s="15" t="s">
         <v>44</v>
       </c>
       <c r="D35" s="16">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="E35" s="17">
         <v>0</v>
@@ -4916,7 +4919,7 @@
       </c>
       <c r="K35" s="17">
         <f>(1-$D35)*F35</f>
-        <v>19500</v>
+        <v>26000</v>
       </c>
       <c r="L35" s="17">
         <f>G35</f>
@@ -4946,7 +4949,7 @@
         <v>0</v>
       </c>
       <c r="T35" s="17">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="U35" s="17">
         <v>0</v>
@@ -4965,14 +4968,14 @@
       </c>
       <c r="Z35" s="17">
         <f>SUM(J35:Y35)</f>
-        <v>44130</v>
+        <v>56630</v>
       </c>
       <c r="AA35" s="17">
         <v>0</v>
       </c>
       <c r="AB35" s="14">
         <f>Z35-AA35</f>
-        <v>44130</v>
+        <v>56630</v>
       </c>
       <c r="AC35" s="17" t="str">
         <f>IF(AND($T35=6000, ($T35+$W35-$AB35)&gt;=6000),T35,"")</f>
@@ -4989,10 +4992,10 @@
     </row>
     <row r="36" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A36" s="15" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="B36" s="15" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="C36" s="15" t="s">
         <v>44</v>
@@ -5051,7 +5054,7 @@
         <v>0</v>
       </c>
       <c r="T36" s="17">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="U36" s="17">
         <v>0</v>
@@ -5070,14 +5073,14 @@
       </c>
       <c r="Z36" s="17">
         <f>SUM(J36:Y36)</f>
-        <v>44130</v>
+        <v>50130</v>
       </c>
       <c r="AA36" s="17">
         <v>0</v>
       </c>
       <c r="AB36" s="14">
         <f>Z36-AA36</f>
-        <v>44130</v>
+        <v>50130</v>
       </c>
       <c r="AC36" s="17" t="str">
         <f>IF(AND($T36=6000, ($T36+$W36-$AB36)&gt;=6000),T36,"")</f>
@@ -5094,16 +5097,16 @@
     </row>
     <row r="37" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A37" s="15" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="B37" s="15" t="s">
-        <v>138</v>
+        <v>115</v>
       </c>
       <c r="C37" s="15" t="s">
         <v>44</v>
       </c>
       <c r="D37" s="16">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E37" s="17">
         <v>0</v>
@@ -5126,7 +5129,7 @@
       </c>
       <c r="K37" s="17">
         <f>(1-$D37)*F37</f>
-        <v>26000</v>
+        <v>13000</v>
       </c>
       <c r="L37" s="17">
         <f>G37</f>
@@ -5171,18 +5174,18 @@
         <v>0</v>
       </c>
       <c r="Y37" s="17">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="Z37" s="17">
         <f>SUM(J37:Y37)</f>
-        <v>50630</v>
+        <v>45630</v>
       </c>
       <c r="AA37" s="17">
         <v>0</v>
       </c>
       <c r="AB37" s="14">
         <f>Z37-AA37</f>
-        <v>50630</v>
+        <v>45630</v>
       </c>
       <c r="AC37" s="17" t="str">
         <f>IF(AND($T37=6000, ($T37+$W37-$AB37)&gt;=6000),T37,"")</f>
@@ -5199,13 +5202,13 @@
     </row>
     <row r="38" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A38" s="15" t="s">
-        <v>28</v>
+        <v>118</v>
       </c>
       <c r="B38" s="15" t="s">
-        <v>29</v>
+        <v>119</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D38" s="16">
         <v>0.25</v>
@@ -5246,10 +5249,10 @@
         <v>0</v>
       </c>
       <c r="O38" s="17">
-        <v>24870</v>
+        <v>13080</v>
       </c>
       <c r="P38" s="17">
-        <v>10730</v>
+        <v>7550</v>
       </c>
       <c r="Q38" s="17">
         <v>0</v>
@@ -5280,14 +5283,14 @@
       </c>
       <c r="Z38" s="17">
         <f>SUM(J38:Y38)</f>
-        <v>59100</v>
+        <v>44130</v>
       </c>
       <c r="AA38" s="17">
         <v>0</v>
       </c>
       <c r="AB38" s="14">
         <f>Z38-AA38</f>
-        <v>59100</v>
+        <v>44130</v>
       </c>
       <c r="AC38" s="17" t="str">
         <f>IF(AND($T38=6000, ($T38+$W38-$AB38)&gt;=6000),T38,"")</f>
@@ -5304,16 +5307,16 @@
     </row>
     <row r="39" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A39" s="15" t="s">
-        <v>37</v>
+        <v>125</v>
       </c>
       <c r="B39" s="15" t="s">
-        <v>38</v>
+        <v>128</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D39" s="16">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="E39" s="17">
         <v>0</v>
@@ -5336,7 +5339,7 @@
       </c>
       <c r="K39" s="17">
         <f>(1-$D39)*F39</f>
-        <v>13000</v>
+        <v>19500</v>
       </c>
       <c r="L39" s="17">
         <f>G39</f>
@@ -5351,10 +5354,10 @@
         <v>0</v>
       </c>
       <c r="O39" s="17">
-        <v>24870</v>
+        <v>13080</v>
       </c>
       <c r="P39" s="17">
-        <v>10730</v>
+        <v>7550</v>
       </c>
       <c r="Q39" s="17">
         <v>0</v>
@@ -5385,14 +5388,14 @@
       </c>
       <c r="Z39" s="17">
         <f>SUM(J39:Y39)</f>
-        <v>52600</v>
+        <v>44130</v>
       </c>
       <c r="AA39" s="17">
         <v>0</v>
       </c>
       <c r="AB39" s="14">
         <f>Z39-AA39</f>
-        <v>52600</v>
+        <v>44130</v>
       </c>
       <c r="AC39" s="17" t="str">
         <f>IF(AND($T39=6000, ($T39+$W39-$AB39)&gt;=6000),T39,"")</f>
@@ -5409,16 +5412,16 @@
     </row>
     <row r="40" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A40" s="15" t="s">
-        <v>40</v>
+        <v>137</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>41</v>
+        <v>138</v>
       </c>
       <c r="C40" s="15" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D40" s="16">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="E40" s="17">
         <v>0</v>
@@ -5441,7 +5444,7 @@
       </c>
       <c r="K40" s="17">
         <f>(1-$D40)*F40</f>
-        <v>19500</v>
+        <v>26000</v>
       </c>
       <c r="L40" s="17">
         <f>G40</f>
@@ -5456,10 +5459,10 @@
         <v>0</v>
       </c>
       <c r="O40" s="17">
-        <v>24870</v>
+        <v>13080</v>
       </c>
       <c r="P40" s="17">
-        <v>10730</v>
+        <v>7550</v>
       </c>
       <c r="Q40" s="17">
         <v>0</v>
@@ -5490,14 +5493,14 @@
       </c>
       <c r="Z40" s="17">
         <f>SUM(J40:Y40)</f>
-        <v>59100</v>
+        <v>50630</v>
       </c>
       <c r="AA40" s="17">
         <v>0</v>
       </c>
       <c r="AB40" s="14">
         <f>Z40-AA40</f>
-        <v>59100</v>
+        <v>50630</v>
       </c>
       <c r="AC40" s="17" t="str">
         <f>IF(AND($T40=6000, ($T40+$W40-$AB40)&gt;=6000),T40,"")</f>
@@ -5514,10 +5517,10 @@
     </row>
     <row r="41" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A41" s="15" t="s">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="B41" s="15" t="s">
-        <v>62</v>
+        <v>29</v>
       </c>
       <c r="C41" s="15" t="s">
         <v>47</v>
@@ -5576,7 +5579,7 @@
         <v>0</v>
       </c>
       <c r="T41" s="17">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="U41" s="17">
         <v>0</v>
@@ -5595,14 +5598,14 @@
       </c>
       <c r="Z41" s="17">
         <f>SUM(J41:Y41)</f>
-        <v>65100</v>
+        <v>59100</v>
       </c>
       <c r="AA41" s="17">
         <v>0</v>
       </c>
       <c r="AB41" s="14">
         <f>Z41-AA41</f>
-        <v>65100</v>
+        <v>59100</v>
       </c>
       <c r="AC41" s="17" t="str">
         <f>IF(AND($T41=6000, ($T41+$W41-$AB41)&gt;=6000),T41,"")</f>
@@ -5619,16 +5622,16 @@
     </row>
     <row r="42" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A42" s="15" t="s">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="B42" s="15" t="s">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="C42" s="15" t="s">
         <v>47</v>
       </c>
       <c r="D42" s="16">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E42" s="17">
         <v>0</v>
@@ -5651,7 +5654,7 @@
       </c>
       <c r="K42" s="17">
         <f>(1-$D42)*F42</f>
-        <v>19500</v>
+        <v>13000</v>
       </c>
       <c r="L42" s="17">
         <f>G42</f>
@@ -5681,7 +5684,7 @@
         <v>0</v>
       </c>
       <c r="T42" s="17">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="U42" s="17">
         <v>0</v>
@@ -5696,18 +5699,18 @@
         <v>0</v>
       </c>
       <c r="Y42" s="17">
-        <v>18500</v>
+        <v>0</v>
       </c>
       <c r="Z42" s="17">
         <f>SUM(J42:Y42)</f>
-        <v>83600</v>
+        <v>52600</v>
       </c>
       <c r="AA42" s="17">
-        <v>48000</v>
+        <v>0</v>
       </c>
       <c r="AB42" s="14">
         <f>Z42-AA42</f>
-        <v>35600</v>
+        <v>52600</v>
       </c>
       <c r="AC42" s="17" t="str">
         <f>IF(AND($T42=6000, ($T42+$W42-$AB42)&gt;=6000),T42,"")</f>
@@ -5724,10 +5727,10 @@
     </row>
     <row r="43" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A43" s="15" t="s">
-        <v>88</v>
+        <v>40</v>
       </c>
       <c r="B43" s="15" t="s">
-        <v>206</v>
+        <v>41</v>
       </c>
       <c r="C43" s="15" t="s">
         <v>47</v>
@@ -5786,7 +5789,7 @@
         <v>0</v>
       </c>
       <c r="T43" s="17">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="U43" s="17">
         <v>0</v>
@@ -5805,14 +5808,14 @@
       </c>
       <c r="Z43" s="17">
         <f>SUM(J43:Y43)</f>
-        <v>65100</v>
+        <v>59100</v>
       </c>
       <c r="AA43" s="17">
         <v>0</v>
       </c>
       <c r="AB43" s="14">
         <f>Z43-AA43</f>
-        <v>65100</v>
+        <v>59100</v>
       </c>
       <c r="AC43" s="17" t="str">
         <f>IF(AND($T43=6000, ($T43+$W43-$AB43)&gt;=6000),T43,"")</f>
@@ -5829,10 +5832,10 @@
     </row>
     <row r="44" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A44" s="15" t="s">
-        <v>198</v>
+        <v>60</v>
       </c>
       <c r="B44" s="15" t="s">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="C44" s="15" t="s">
         <v>47</v>
@@ -5934,10 +5937,10 @@
     </row>
     <row r="45" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A45" s="15" t="s">
-        <v>121</v>
+        <v>64</v>
       </c>
       <c r="B45" s="15" t="s">
-        <v>122</v>
+        <v>76</v>
       </c>
       <c r="C45" s="15" t="s">
         <v>47</v>
@@ -6011,18 +6014,18 @@
         <v>0</v>
       </c>
       <c r="Y45" s="17">
-        <v>0</v>
+        <v>18500</v>
       </c>
       <c r="Z45" s="17">
         <f>SUM(J45:Y45)</f>
-        <v>65100</v>
+        <v>83600</v>
       </c>
       <c r="AA45" s="17">
-        <v>0</v>
+        <v>48000</v>
       </c>
       <c r="AB45" s="14">
         <f>Z45-AA45</f>
-        <v>65100</v>
+        <v>35600</v>
       </c>
       <c r="AC45" s="17" t="str">
         <f>IF(AND($T45=6000, ($T45+$W45-$AB45)&gt;=6000),T45,"")</f>
@@ -6039,16 +6042,16 @@
     </row>
     <row r="46" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A46" s="15" t="s">
-        <v>123</v>
+        <v>88</v>
       </c>
       <c r="B46" s="15" t="s">
-        <v>124</v>
+        <v>206</v>
       </c>
       <c r="C46" s="15" t="s">
         <v>47</v>
       </c>
       <c r="D46" s="16">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E46" s="17">
         <v>0</v>
@@ -6071,7 +6074,7 @@
       </c>
       <c r="K46" s="17">
         <f>(1-$D46)*F46</f>
-        <v>26000</v>
+        <v>19500</v>
       </c>
       <c r="L46" s="17">
         <f>G46</f>
@@ -6116,18 +6119,18 @@
         <v>0</v>
       </c>
       <c r="Y46" s="17">
-        <v>14240</v>
+        <v>0</v>
       </c>
       <c r="Z46" s="17">
         <f>SUM(J46:Y46)</f>
-        <v>85840</v>
+        <v>65100</v>
       </c>
       <c r="AA46" s="17">
         <v>0</v>
       </c>
       <c r="AB46" s="14">
         <f>Z46-AA46</f>
-        <v>85840</v>
+        <v>65100</v>
       </c>
       <c r="AC46" s="17" t="str">
         <f>IF(AND($T46=6000, ($T46+$W46-$AB46)&gt;=6000),T46,"")</f>
@@ -6144,16 +6147,16 @@
     </row>
     <row r="47" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A47" s="15" t="s">
-        <v>151</v>
+        <v>198</v>
       </c>
       <c r="B47" s="15" t="s">
-        <v>152</v>
+        <v>31</v>
       </c>
       <c r="C47" s="15" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D47" s="16">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E47" s="17">
         <v>0</v>
@@ -6165,7 +6168,7 @@
         <v>4000</v>
       </c>
       <c r="H47" s="17">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="I47" s="17">
         <v>0</v>
@@ -6176,7 +6179,7 @@
       </c>
       <c r="K47" s="17">
         <f>(1-$D47)*F47</f>
-        <v>26000</v>
+        <v>19500</v>
       </c>
       <c r="L47" s="17">
         <f>G47</f>
@@ -6184,29 +6187,29 @@
       </c>
       <c r="M47" s="17">
         <f>(1-$D47)*H47</f>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="N47" s="17">
         <f>(1-$D47)*I47</f>
         <v>0</v>
       </c>
       <c r="O47" s="17">
-        <v>8040</v>
+        <v>24870</v>
       </c>
       <c r="P47" s="17">
-        <v>5300</v>
+        <v>10730</v>
       </c>
       <c r="Q47" s="17">
-        <v>16000</v>
+        <v>0</v>
       </c>
       <c r="R47" s="17">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="S47" s="17">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="T47" s="17">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="U47" s="17">
         <v>0</v>
@@ -6221,18 +6224,18 @@
         <v>0</v>
       </c>
       <c r="Y47" s="17">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="Z47" s="17">
         <f>SUM(J47:Y47)</f>
-        <v>74340</v>
+        <v>65100</v>
       </c>
       <c r="AA47" s="17">
         <v>0</v>
       </c>
       <c r="AB47" s="14">
         <f>Z47-AA47</f>
-        <v>74340</v>
+        <v>65100</v>
       </c>
       <c r="AC47" s="17" t="str">
         <f>IF(AND($T47=6000, ($T47+$W47-$AB47)&gt;=6000),T47,"")</f>
@@ -6249,16 +6252,16 @@
     </row>
     <row r="48" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A48" s="15" t="s">
-        <v>203</v>
+        <v>121</v>
       </c>
       <c r="B48" s="15" t="s">
-        <v>214</v>
+        <v>122</v>
       </c>
       <c r="C48" s="15" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D48" s="16">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E48" s="17">
         <v>0</v>
@@ -6270,7 +6273,7 @@
         <v>4000</v>
       </c>
       <c r="H48" s="17">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="I48" s="17">
         <v>0</v>
@@ -6281,7 +6284,7 @@
       </c>
       <c r="K48" s="17">
         <f>(1-$D48)*F48</f>
-        <v>26000</v>
+        <v>19500</v>
       </c>
       <c r="L48" s="17">
         <f>G48</f>
@@ -6289,29 +6292,29 @@
       </c>
       <c r="M48" s="17">
         <f>(1-$D48)*H48</f>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="N48" s="17">
         <f>(1-$D48)*I48</f>
         <v>0</v>
       </c>
       <c r="O48" s="17">
-        <v>8040</v>
+        <v>24870</v>
       </c>
       <c r="P48" s="17">
-        <v>5300</v>
+        <v>10730</v>
       </c>
       <c r="Q48" s="17">
-        <v>16000</v>
+        <v>0</v>
       </c>
       <c r="R48" s="17">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="S48" s="17">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="T48" s="17">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="U48" s="17">
         <v>0</v>
@@ -6330,14 +6333,14 @@
       </c>
       <c r="Z48" s="17">
         <f>SUM(J48:Y48)</f>
-        <v>75340</v>
+        <v>65100</v>
       </c>
       <c r="AA48" s="17">
         <v>0</v>
       </c>
       <c r="AB48" s="14">
         <f>Z48-AA48</f>
-        <v>75340</v>
+        <v>65100</v>
       </c>
       <c r="AC48" s="17" t="str">
         <f>IF(AND($T48=6000, ($T48+$W48-$AB48)&gt;=6000),T48,"")</f>
@@ -6354,13 +6357,13 @@
     </row>
     <row r="49" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A49" s="15" t="s">
-        <v>188</v>
+        <v>123</v>
       </c>
       <c r="B49" s="15" t="s">
-        <v>190</v>
+        <v>124</v>
       </c>
       <c r="C49" s="15" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D49" s="16">
         <v>0</v>
@@ -6375,7 +6378,7 @@
         <v>4000</v>
       </c>
       <c r="H49" s="17">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="I49" s="17">
         <v>0</v>
@@ -6394,29 +6397,29 @@
       </c>
       <c r="M49" s="17">
         <f>(1-$D49)*H49</f>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="N49" s="17">
         <f>(1-$D49)*I49</f>
         <v>0</v>
       </c>
       <c r="O49" s="17">
-        <v>8040</v>
+        <v>24870</v>
       </c>
       <c r="P49" s="17">
-        <v>5300</v>
+        <v>10730</v>
       </c>
       <c r="Q49" s="17">
-        <v>16000</v>
+        <v>0</v>
       </c>
       <c r="R49" s="17">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="S49" s="17">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="T49" s="17">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="U49" s="17">
         <v>0</v>
@@ -6431,18 +6434,18 @@
         <v>0</v>
       </c>
       <c r="Y49" s="17">
-        <v>0</v>
+        <v>14240</v>
       </c>
       <c r="Z49" s="17">
         <f>SUM(J49:Y49)</f>
-        <v>75340</v>
+        <v>85840</v>
       </c>
       <c r="AA49" s="17">
         <v>0</v>
       </c>
       <c r="AB49" s="14">
         <f>Z49-AA49</f>
-        <v>75340</v>
+        <v>85840</v>
       </c>
       <c r="AC49" s="17" t="str">
         <f>IF(AND($T49=6000, ($T49+$W49-$AB49)&gt;=6000),T49,"")</f>
@@ -6459,16 +6462,16 @@
     </row>
     <row r="50" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A50" s="15" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="B50" s="15" t="s">
-        <v>241</v>
+        <v>152</v>
       </c>
       <c r="C50" s="15" t="s">
         <v>49</v>
       </c>
       <c r="D50" s="16">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="E50" s="17">
         <v>0</v>
@@ -6491,7 +6494,7 @@
       </c>
       <c r="K50" s="17">
         <f>(1-$D50)*F50</f>
-        <v>19500</v>
+        <v>26000</v>
       </c>
       <c r="L50" s="17">
         <f>G50</f>
@@ -6499,7 +6502,7 @@
       </c>
       <c r="M50" s="17">
         <f>(1-$D50)*H50</f>
-        <v>750</v>
+        <v>1000</v>
       </c>
       <c r="N50" s="17">
         <f>(1-$D50)*I50</f>
@@ -6536,18 +6539,18 @@
         <v>0</v>
       </c>
       <c r="Y50" s="17">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="Z50" s="17">
         <f>SUM(J50:Y50)</f>
-        <v>68590</v>
+        <v>74340</v>
       </c>
       <c r="AA50" s="17">
         <v>0</v>
       </c>
       <c r="AB50" s="14">
         <f>Z50-AA50</f>
-        <v>68590</v>
+        <v>74340</v>
       </c>
       <c r="AC50" s="17" t="str">
         <f>IF(AND($T50=6000, ($T50+$W50-$AB50)&gt;=6000),T50,"")</f>
@@ -6564,10 +6567,10 @@
     </row>
     <row r="51" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A51" s="15" t="s">
-        <v>187</v>
+        <v>203</v>
       </c>
       <c r="B51" s="15" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="C51" s="15" t="s">
         <v>49</v>
@@ -6669,10 +6672,10 @@
     </row>
     <row r="52" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A52" s="15" t="s">
-        <v>242</v>
+        <v>188</v>
       </c>
       <c r="B52" s="15" t="s">
-        <v>50</v>
+        <v>190</v>
       </c>
       <c r="C52" s="15" t="s">
         <v>49</v>
@@ -6774,10 +6777,10 @@
     </row>
     <row r="53" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A53" s="15" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="B53" s="15" t="s">
-        <v>174</v>
+        <v>201</v>
       </c>
       <c r="C53" s="15" t="s">
         <v>49</v>
@@ -6879,10 +6882,10 @@
     </row>
     <row r="54" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A54" s="15" t="s">
-        <v>244</v>
+        <v>173</v>
       </c>
       <c r="B54" s="15" t="s">
-        <v>245</v>
+        <v>174</v>
       </c>
       <c r="C54" s="15" t="s">
         <v>49</v>
@@ -6984,10 +6987,10 @@
     </row>
     <row r="55" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A55" s="15" t="s">
-        <v>175</v>
+        <v>244</v>
       </c>
       <c r="B55" s="15" t="s">
-        <v>176</v>
+        <v>245</v>
       </c>
       <c r="C55" s="15" t="s">
         <v>49</v>
@@ -7061,18 +7064,18 @@
         <v>0</v>
       </c>
       <c r="Y55" s="17">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="Z55" s="17">
         <f>SUM(J55:Y55)</f>
-        <v>77340</v>
+        <v>75340</v>
       </c>
       <c r="AA55" s="17">
         <v>0</v>
       </c>
       <c r="AB55" s="14">
         <f>Z55-AA55</f>
-        <v>77340</v>
+        <v>75340</v>
       </c>
       <c r="AC55" s="17" t="str">
         <f>IF(AND($T55=6000, ($T55+$W55-$AB55)&gt;=6000),T55,"")</f>
@@ -7089,16 +7092,16 @@
     </row>
     <row r="56" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A56" s="15" t="s">
-        <v>213</v>
+        <v>175</v>
       </c>
       <c r="B56" s="15" t="s">
-        <v>223</v>
+        <v>176</v>
       </c>
       <c r="C56" s="15" t="s">
         <v>49</v>
       </c>
       <c r="D56" s="16">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E56" s="17">
         <v>0</v>
@@ -7121,7 +7124,7 @@
       </c>
       <c r="K56" s="17">
         <f>(1-$D56)*F56</f>
-        <v>13000</v>
+        <v>26000</v>
       </c>
       <c r="L56" s="17">
         <f>G56</f>
@@ -7129,7 +7132,7 @@
       </c>
       <c r="M56" s="17">
         <f>(1-$D56)*H56</f>
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="N56" s="17">
         <f>(1-$D56)*I56</f>
@@ -7166,18 +7169,18 @@
         <v>0</v>
       </c>
       <c r="Y56" s="17">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="Z56" s="17">
         <f>SUM(J56:Y56)</f>
-        <v>61840</v>
+        <v>77340</v>
       </c>
       <c r="AA56" s="17">
         <v>0</v>
       </c>
       <c r="AB56" s="14">
         <f>Z56-AA56</f>
-        <v>61840</v>
+        <v>77340</v>
       </c>
       <c r="AC56" s="17" t="str">
         <f>IF(AND($T56=6000, ($T56+$W56-$AB56)&gt;=6000),T56,"")</f>
@@ -7194,16 +7197,16 @@
     </row>
     <row r="57" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A57" s="15" t="s">
-        <v>171</v>
+        <v>213</v>
       </c>
       <c r="B57" s="15" t="s">
-        <v>172</v>
+        <v>223</v>
       </c>
       <c r="C57" s="15" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="16">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E57" s="17">
         <v>0</v>
@@ -7226,7 +7229,7 @@
       </c>
       <c r="K57" s="17">
         <f>(1-$D57)*F57</f>
-        <v>26000</v>
+        <v>13000</v>
       </c>
       <c r="L57" s="17">
         <f>G57</f>
@@ -7234,7 +7237,7 @@
       </c>
       <c r="M57" s="17">
         <f>(1-$D57)*H57</f>
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="N57" s="17">
         <f>(1-$D57)*I57</f>
@@ -7275,14 +7278,14 @@
       </c>
       <c r="Z57" s="17">
         <f>SUM(J57:Y57)</f>
-        <v>75340</v>
+        <v>61840</v>
       </c>
       <c r="AA57" s="17">
         <v>0</v>
       </c>
       <c r="AB57" s="14">
         <f>Z57-AA57</f>
-        <v>75340</v>
+        <v>61840</v>
       </c>
       <c r="AC57" s="17" t="str">
         <f>IF(AND($T57=6000, ($T57+$W57-$AB57)&gt;=6000),T57,"")</f>
@@ -7299,16 +7302,16 @@
     </row>
     <row r="58" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A58" s="15" t="s">
-        <v>88</v>
+        <v>171</v>
       </c>
       <c r="B58" s="15" t="s">
-        <v>219</v>
+        <v>172</v>
       </c>
       <c r="C58" s="15" t="s">
         <v>49</v>
       </c>
       <c r="D58" s="16">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="E58" s="17">
         <v>0</v>
@@ -7331,7 +7334,7 @@
       </c>
       <c r="K58" s="17">
         <f>(1-$D58)*F58</f>
-        <v>19500</v>
+        <v>26000</v>
       </c>
       <c r="L58" s="17">
         <f>G58</f>
@@ -7339,7 +7342,7 @@
       </c>
       <c r="M58" s="17">
         <f>(1-$D58)*H58</f>
-        <v>750</v>
+        <v>1000</v>
       </c>
       <c r="N58" s="17">
         <f>(1-$D58)*I58</f>
@@ -7376,18 +7379,18 @@
         <v>0</v>
       </c>
       <c r="Y58" s="17">
-        <v>-500</v>
+        <v>0</v>
       </c>
       <c r="Z58" s="17">
         <f>SUM(J58:Y58)</f>
-        <v>68090</v>
+        <v>75340</v>
       </c>
       <c r="AA58" s="17">
         <v>0</v>
       </c>
       <c r="AB58" s="14">
         <f>Z58-AA58</f>
-        <v>68090</v>
+        <v>75340</v>
       </c>
       <c r="AC58" s="17" t="str">
         <f>IF(AND($T58=6000, ($T58+$W58-$AB58)&gt;=6000),T58,"")</f>
@@ -7404,10 +7407,10 @@
     </row>
     <row r="59" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A59" s="15" t="s">
-        <v>159</v>
+        <v>88</v>
       </c>
       <c r="B59" s="15" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C59" s="15" t="s">
         <v>49</v>
@@ -7481,18 +7484,18 @@
         <v>0</v>
       </c>
       <c r="Y59" s="17">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="Z59" s="17">
         <f>SUM(J59:Y59)</f>
-        <v>68590</v>
+        <v>68090</v>
       </c>
       <c r="AA59" s="17">
         <v>0</v>
       </c>
       <c r="AB59" s="14">
         <f>Z59-AA59</f>
-        <v>68590</v>
+        <v>68090</v>
       </c>
       <c r="AC59" s="17" t="str">
         <f>IF(AND($T59=6000, ($T59+$W59-$AB59)&gt;=6000),T59,"")</f>
@@ -7509,10 +7512,10 @@
     </row>
     <row r="60" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A60" s="15" t="s">
-        <v>207</v>
+        <v>159</v>
       </c>
       <c r="B60" s="15" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C60" s="15" t="s">
         <v>49</v>
@@ -7586,18 +7589,18 @@
         <v>0</v>
       </c>
       <c r="Y60" s="17">
-        <v>19200</v>
+        <v>0</v>
       </c>
       <c r="Z60" s="17">
         <f>SUM(J60:Y60)</f>
-        <v>87790</v>
+        <v>68590</v>
       </c>
       <c r="AA60" s="17">
         <v>0</v>
       </c>
       <c r="AB60" s="14">
         <f>Z60-AA60</f>
-        <v>87790</v>
+        <v>68590</v>
       </c>
       <c r="AC60" s="17" t="str">
         <f>IF(AND($T60=6000, ($T60+$W60-$AB60)&gt;=6000),T60,"")</f>
@@ -7617,7 +7620,7 @@
         <v>207</v>
       </c>
       <c r="B61" s="15" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C61" s="15" t="s">
         <v>49</v>
@@ -7719,10 +7722,10 @@
     </row>
     <row r="62" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A62" s="15" t="s">
-        <v>98</v>
+        <v>207</v>
       </c>
       <c r="B62" s="15" t="s">
-        <v>145</v>
+        <v>216</v>
       </c>
       <c r="C62" s="15" t="s">
         <v>49</v>
@@ -7796,18 +7799,18 @@
         <v>0</v>
       </c>
       <c r="Y62" s="17">
-        <v>0</v>
+        <v>19200</v>
       </c>
       <c r="Z62" s="17">
         <f>SUM(J62:Y62)</f>
-        <v>68590</v>
+        <v>87790</v>
       </c>
       <c r="AA62" s="17">
         <v>0</v>
       </c>
       <c r="AB62" s="14">
         <f>Z62-AA62</f>
-        <v>68590</v>
+        <v>87790</v>
       </c>
       <c r="AC62" s="17" t="str">
         <f>IF(AND($T62=6000, ($T62+$W62-$AB62)&gt;=6000),T62,"")</f>
@@ -7824,10 +7827,10 @@
     </row>
     <row r="63" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A63" s="15" t="s">
-        <v>204</v>
+        <v>98</v>
       </c>
       <c r="B63" s="15" t="s">
-        <v>205</v>
+        <v>145</v>
       </c>
       <c r="C63" s="15" t="s">
         <v>49</v>
@@ -7901,18 +7904,18 @@
         <v>0</v>
       </c>
       <c r="Y63" s="17">
-        <v>3500</v>
+        <v>0</v>
       </c>
       <c r="Z63" s="17">
         <f>SUM(J63:Y63)</f>
-        <v>72090</v>
+        <v>68590</v>
       </c>
       <c r="AA63" s="17">
         <v>0</v>
       </c>
       <c r="AB63" s="14">
         <f>Z63-AA63</f>
-        <v>72090</v>
+        <v>68590</v>
       </c>
       <c r="AC63" s="17" t="str">
         <f>IF(AND($T63=6000, ($T63+$W63-$AB63)&gt;=6000),T63,"")</f>
@@ -7929,16 +7932,16 @@
     </row>
     <row r="64" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A64" s="15" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="B64" s="15" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="C64" s="15" t="s">
         <v>49</v>
       </c>
       <c r="D64" s="16">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E64" s="17">
         <v>0</v>
@@ -7961,7 +7964,7 @@
       </c>
       <c r="K64" s="17">
         <f>(1-$D64)*F64</f>
-        <v>26000</v>
+        <v>19500</v>
       </c>
       <c r="L64" s="17">
         <f>G64</f>
@@ -7969,7 +7972,7 @@
       </c>
       <c r="M64" s="17">
         <f>(1-$D64)*H64</f>
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="N64" s="17">
         <f>(1-$D64)*I64</f>
@@ -8006,18 +8009,18 @@
         <v>0</v>
       </c>
       <c r="Y64" s="17">
-        <v>-10000</v>
+        <v>3500</v>
       </c>
       <c r="Z64" s="17">
         <f>SUM(J64:Y64)</f>
-        <v>65340</v>
+        <v>72090</v>
       </c>
       <c r="AA64" s="17">
         <v>0</v>
       </c>
       <c r="AB64" s="14">
         <f>Z64-AA64</f>
-        <v>65340</v>
+        <v>72090</v>
       </c>
       <c r="AC64" s="17" t="str">
         <f>IF(AND($T64=6000, ($T64+$W64-$AB64)&gt;=6000),T64,"")</f>
@@ -8034,16 +8037,16 @@
     </row>
     <row r="65" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A65" s="15" t="s">
-        <v>121</v>
+        <v>211</v>
       </c>
       <c r="B65" s="15" t="s">
-        <v>243</v>
+        <v>212</v>
       </c>
       <c r="C65" s="15" t="s">
         <v>49</v>
       </c>
       <c r="D65" s="16">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="E65" s="17">
         <v>0</v>
@@ -8066,7 +8069,7 @@
       </c>
       <c r="K65" s="17">
         <f>(1-$D65)*F65</f>
-        <v>19500</v>
+        <v>26000</v>
       </c>
       <c r="L65" s="17">
         <f>G65</f>
@@ -8074,7 +8077,7 @@
       </c>
       <c r="M65" s="17">
         <f>(1-$D65)*H65</f>
-        <v>750</v>
+        <v>1000</v>
       </c>
       <c r="N65" s="17">
         <f>(1-$D65)*I65</f>
@@ -8111,18 +8114,18 @@
         <v>0</v>
       </c>
       <c r="Y65" s="17">
-        <v>0</v>
+        <v>-10000</v>
       </c>
       <c r="Z65" s="17">
         <f>SUM(J65:Y65)</f>
-        <v>68590</v>
+        <v>65340</v>
       </c>
       <c r="AA65" s="17">
         <v>0</v>
       </c>
       <c r="AB65" s="14">
         <f>Z65-AA65</f>
-        <v>68590</v>
+        <v>65340</v>
       </c>
       <c r="AC65" s="17" t="str">
         <f>IF(AND($T65=6000, ($T65+$W65-$AB65)&gt;=6000),T65,"")</f>
@@ -13943,7 +13946,7 @@
       </c>
       <c r="Z121" s="29">
         <f>SUM(Z2:Z120)</f>
-        <v>7931310</v>
+        <v>7807440</v>
       </c>
       <c r="AA121" s="29">
         <f>SUM(AA2:AA120)</f>
@@ -13951,7 +13954,7 @@
       </c>
       <c r="AB121" s="29">
         <f>SUM(AB2:AB120)</f>
-        <v>7883310</v>
+        <v>7759440</v>
       </c>
       <c r="AC121" s="29">
         <f>SUM(AC2:AC120)</f>

--- a/source/2026 - 2027 FEE.xlsx
+++ b/source/2026 - 2027 FEE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\KBI\ACCOUNTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB9888DF-3D94-470D-B6B1-86121ACF596C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92E5169D-9DFC-4670-935A-B3C180C94B00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="781" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1449,23 +1449,23 @@
         <v>0</v>
       </c>
       <c r="J2" s="17">
-        <f>(1-$D2)*E2</f>
+        <f t="shared" ref="J2:J33" si="0">(1-$D2)*E2</f>
         <v>0</v>
       </c>
       <c r="K2" s="17">
-        <f>(1-$D2)*F2</f>
+        <f t="shared" ref="K2:K33" si="1">(1-$D2)*F2</f>
         <v>19500</v>
       </c>
       <c r="L2" s="17">
-        <f>G2</f>
+        <f t="shared" ref="L2:L33" si="2">G2</f>
         <v>4000</v>
       </c>
       <c r="M2" s="17">
-        <f>(1-$D2)*H2</f>
+        <f t="shared" ref="M2:M33" si="3">(1-$D2)*H2</f>
         <v>750</v>
       </c>
       <c r="N2" s="17">
-        <f>(1-$D2)*I2</f>
+        <f t="shared" ref="N2:N33" si="4">(1-$D2)*I2</f>
         <v>0</v>
       </c>
       <c r="O2" s="17">
@@ -1502,26 +1502,26 @@
         <v>0</v>
       </c>
       <c r="Z2" s="17">
-        <f>SUM(J2:Y2)</f>
+        <f t="shared" ref="Z2:Z33" si="5">SUM(J2:Y2)</f>
         <v>27300</v>
       </c>
       <c r="AA2" s="17">
         <v>0</v>
       </c>
       <c r="AB2" s="14">
-        <f>Z2-AA2</f>
+        <f t="shared" ref="AB2:AB33" si="6">Z2-AA2</f>
         <v>27300</v>
       </c>
       <c r="AC2" s="17" t="str">
-        <f>IF(AND($T2=6000, ($T2+$W2-$AB2)&gt;=6000),T2,"")</f>
+        <f t="shared" ref="AC2:AC33" si="7">IF(AND($T2=6000, ($T2+$W2-$AB2)&gt;=6000),T2,"")</f>
         <v/>
       </c>
       <c r="AD2" s="17" t="str">
-        <f>IF(AND($T2=8000, ($T2+$W2-$AB2)&gt;=8000),T2,"")</f>
+        <f t="shared" ref="AD2:AD33" si="8">IF(AND($T2=8000, ($T2+$W2-$AB2)&gt;=8000),T2,"")</f>
         <v/>
       </c>
       <c r="AE2" s="17" t="str">
-        <f>IF(($T2+$W2-$AB2)&gt;=$T2+8000,W2,"")</f>
+        <f t="shared" ref="AE2:AE33" si="9">IF(($T2+$W2-$AB2)&gt;=$T2+8000,W2,"")</f>
         <v/>
       </c>
     </row>
@@ -1554,23 +1554,23 @@
         <v>0</v>
       </c>
       <c r="J3" s="17">
-        <f>(1-$D3)*E3</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K3" s="17">
-        <f>(1-$D3)*F3</f>
+        <f t="shared" si="1"/>
         <v>26000</v>
       </c>
       <c r="L3" s="17">
-        <f>G3</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M3" s="17">
-        <f>(1-$D3)*H3</f>
+        <f t="shared" si="3"/>
         <v>1000</v>
       </c>
       <c r="N3" s="17">
-        <f>(1-$D3)*I3</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O3" s="17">
@@ -1607,26 +1607,26 @@
         <v>0</v>
       </c>
       <c r="Z3" s="17">
-        <f>SUM(J3:Y3)</f>
+        <f t="shared" si="5"/>
         <v>34050</v>
       </c>
       <c r="AA3" s="17">
         <v>0</v>
       </c>
       <c r="AB3" s="14">
-        <f>Z3-AA3</f>
+        <f t="shared" si="6"/>
         <v>34050</v>
       </c>
       <c r="AC3" s="17" t="str">
-        <f>IF(AND($T3=6000, ($T3+$W3-$AB3)&gt;=6000),T3,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD3" s="17" t="str">
-        <f>IF(AND($T3=8000, ($T3+$W3-$AB3)&gt;=8000),T3,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE3" s="17" t="str">
-        <f>IF(($T3+$W3-$AB3)&gt;=$T3+8000,W3,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -1659,23 +1659,23 @@
         <v>0</v>
       </c>
       <c r="J4" s="17">
-        <f>(1-$D4)*E4</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K4" s="17">
-        <f>(1-$D4)*F4</f>
+        <f t="shared" si="1"/>
         <v>19500</v>
       </c>
       <c r="L4" s="17">
-        <f>G4</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M4" s="17">
-        <f>(1-$D4)*H4</f>
+        <f t="shared" si="3"/>
         <v>750</v>
       </c>
       <c r="N4" s="17">
-        <f>(1-$D4)*I4</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O4" s="17">
@@ -1712,26 +1712,26 @@
         <v>0</v>
       </c>
       <c r="Z4" s="17">
-        <f>SUM(J4:Y4)</f>
+        <f t="shared" si="5"/>
         <v>27300</v>
       </c>
       <c r="AA4" s="17">
         <v>0</v>
       </c>
       <c r="AB4" s="14">
-        <f>Z4-AA4</f>
+        <f t="shared" si="6"/>
         <v>27300</v>
       </c>
       <c r="AC4" s="17" t="str">
-        <f>IF(AND($T4=6000, ($T4+$W4-$AB4)&gt;=6000),T4,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD4" s="17" t="str">
-        <f>IF(AND($T4=8000, ($T4+$W4-$AB4)&gt;=8000),T4,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE4" s="17" t="str">
-        <f>IF(($T4+$W4-$AB4)&gt;=$T4+8000,W4,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -1764,23 +1764,23 @@
         <v>6000</v>
       </c>
       <c r="J5" s="17">
-        <f>(1-$D5)*E5</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K5" s="17">
-        <f>(1-$D5)*F5</f>
+        <f t="shared" si="1"/>
         <v>24750</v>
       </c>
       <c r="L5" s="17">
-        <f>G5</f>
+        <f t="shared" si="2"/>
         <v>5000</v>
       </c>
       <c r="M5" s="17">
-        <f>(1-$D5)*H5</f>
+        <f t="shared" si="3"/>
         <v>1500</v>
       </c>
       <c r="N5" s="17">
-        <f>(1-$D5)*I5</f>
+        <f t="shared" si="4"/>
         <v>4500</v>
       </c>
       <c r="O5" s="17">
@@ -1817,26 +1817,26 @@
         <v>750</v>
       </c>
       <c r="Z5" s="17">
-        <f>SUM(J5:Y5)</f>
+        <f t="shared" si="5"/>
         <v>78390</v>
       </c>
       <c r="AA5" s="17">
         <v>0</v>
       </c>
       <c r="AB5" s="14">
-        <f>Z5-AA5</f>
+        <f t="shared" si="6"/>
         <v>78390</v>
       </c>
       <c r="AC5" s="17" t="str">
-        <f>IF(AND($T5=6000, ($T5+$W5-$AB5)&gt;=6000),T5,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD5" s="17" t="str">
-        <f>IF(AND($T5=8000, ($T5+$W5-$AB5)&gt;=8000),T5,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE5" s="17" t="str">
-        <f>IF(($T5+$W5-$AB5)&gt;=$T5+8000,W5,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -1869,23 +1869,23 @@
         <v>6000</v>
       </c>
       <c r="J6" s="17">
-        <f>(1-$D6)*E6</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K6" s="17">
-        <f>(1-$D6)*F6</f>
+        <f t="shared" si="1"/>
         <v>23100</v>
       </c>
       <c r="L6" s="17">
-        <f>G6</f>
+        <f t="shared" si="2"/>
         <v>5000</v>
       </c>
       <c r="M6" s="17">
-        <f>(1-$D6)*H6</f>
+        <f t="shared" si="3"/>
         <v>1400</v>
       </c>
       <c r="N6" s="17">
-        <f>(1-$D6)*I6</f>
+        <f t="shared" si="4"/>
         <v>4200</v>
       </c>
       <c r="O6" s="17">
@@ -1922,26 +1922,26 @@
         <v>0</v>
       </c>
       <c r="Z6" s="17">
-        <f>SUM(J6:Y6)</f>
+        <f t="shared" si="5"/>
         <v>67590</v>
       </c>
       <c r="AA6" s="17">
         <v>0</v>
       </c>
       <c r="AB6" s="14">
-        <f>Z6-AA6</f>
+        <f t="shared" si="6"/>
         <v>67590</v>
       </c>
       <c r="AC6" s="17" t="str">
-        <f>IF(AND($T6=6000, ($T6+$W6-$AB6)&gt;=6000),T6,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD6" s="17" t="str">
-        <f>IF(AND($T6=8000, ($T6+$W6-$AB6)&gt;=8000),T6,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE6" s="17" t="str">
-        <f>IF(($T6+$W6-$AB6)&gt;=$T6+8000,W6,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -1974,23 +1974,23 @@
         <v>6000</v>
       </c>
       <c r="J7" s="17">
-        <f>(1-$D7)*E7</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K7" s="17">
-        <f>(1-$D7)*F7</f>
+        <f t="shared" si="1"/>
         <v>24750</v>
       </c>
       <c r="L7" s="17">
-        <f>G7</f>
+        <f t="shared" si="2"/>
         <v>5000</v>
       </c>
       <c r="M7" s="17">
-        <f>(1-$D7)*H7</f>
+        <f t="shared" si="3"/>
         <v>1500</v>
       </c>
       <c r="N7" s="17">
-        <f>(1-$D7)*I7</f>
+        <f t="shared" si="4"/>
         <v>4500</v>
       </c>
       <c r="O7" s="17">
@@ -2027,26 +2027,26 @@
         <v>0</v>
       </c>
       <c r="Z7" s="17">
-        <f>SUM(J7:Y7)</f>
+        <f t="shared" si="5"/>
         <v>69640</v>
       </c>
       <c r="AA7" s="17">
         <v>0</v>
       </c>
       <c r="AB7" s="14">
-        <f>Z7-AA7</f>
+        <f t="shared" si="6"/>
         <v>69640</v>
       </c>
       <c r="AC7" s="17" t="str">
-        <f>IF(AND($T7=6000, ($T7+$W7-$AB7)&gt;=6000),T7,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD7" s="17" t="str">
-        <f>IF(AND($T7=8000, ($T7+$W7-$AB7)&gt;=8000),T7,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE7" s="17" t="str">
-        <f>IF(($T7+$W7-$AB7)&gt;=$T7+8000,W7,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -2079,23 +2079,23 @@
         <v>6000</v>
       </c>
       <c r="J8" s="17">
-        <f>(1-$D8)*E8</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K8" s="17">
-        <f>(1-$D8)*F8</f>
+        <f t="shared" si="1"/>
         <v>33000</v>
       </c>
       <c r="L8" s="17">
-        <f>G8</f>
+        <f t="shared" si="2"/>
         <v>5000</v>
       </c>
       <c r="M8" s="17">
-        <f>(1-$D8)*H8</f>
+        <f t="shared" si="3"/>
         <v>2000</v>
       </c>
       <c r="N8" s="17">
-        <f>(1-$D8)*I8</f>
+        <f t="shared" si="4"/>
         <v>6000</v>
       </c>
       <c r="O8" s="17">
@@ -2132,26 +2132,26 @@
         <v>0</v>
       </c>
       <c r="Z8" s="17">
-        <f>SUM(J8:Y8)</f>
+        <f t="shared" si="5"/>
         <v>79890</v>
       </c>
       <c r="AA8" s="17">
         <v>0</v>
       </c>
       <c r="AB8" s="14">
-        <f>Z8-AA8</f>
+        <f t="shared" si="6"/>
         <v>79890</v>
       </c>
       <c r="AC8" s="17" t="str">
-        <f>IF(AND($T8=6000, ($T8+$W8-$AB8)&gt;=6000),T8,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD8" s="17" t="str">
-        <f>IF(AND($T8=8000, ($T8+$W8-$AB8)&gt;=8000),T8,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE8" s="17" t="str">
-        <f>IF(($T8+$W8-$AB8)&gt;=$T8+8000,W8,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -2184,23 +2184,23 @@
         <v>6000</v>
       </c>
       <c r="J9" s="17">
-        <f>(1-$D9)*E9</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K9" s="17">
-        <f>(1-$D9)*F9</f>
+        <f t="shared" si="1"/>
         <v>23100</v>
       </c>
       <c r="L9" s="17">
-        <f>G9</f>
+        <f t="shared" si="2"/>
         <v>5000</v>
       </c>
       <c r="M9" s="17">
-        <f>(1-$D9)*H9</f>
+        <f t="shared" si="3"/>
         <v>1400</v>
       </c>
       <c r="N9" s="17">
-        <f>(1-$D9)*I9</f>
+        <f t="shared" si="4"/>
         <v>4200</v>
       </c>
       <c r="O9" s="17">
@@ -2237,26 +2237,26 @@
         <v>0</v>
       </c>
       <c r="Z9" s="17">
-        <f>SUM(J9:Y9)</f>
+        <f t="shared" si="5"/>
         <v>67590</v>
       </c>
       <c r="AA9" s="17">
         <v>0</v>
       </c>
       <c r="AB9" s="14">
-        <f>Z9-AA9</f>
+        <f t="shared" si="6"/>
         <v>67590</v>
       </c>
       <c r="AC9" s="17" t="str">
-        <f>IF(AND($T9=6000, ($T9+$W9-$AB9)&gt;=6000),T9,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD9" s="17" t="str">
-        <f>IF(AND($T9=8000, ($T9+$W9-$AB9)&gt;=8000),T9,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE9" s="17" t="str">
-        <f>IF(($T9+$W9-$AB9)&gt;=$T9+8000,W9,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -2289,23 +2289,23 @@
         <v>6000</v>
       </c>
       <c r="J10" s="17">
-        <f>(1-$D10)*E10</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K10" s="17">
-        <f>(1-$D10)*F10</f>
+        <f t="shared" si="1"/>
         <v>16500</v>
       </c>
       <c r="L10" s="17">
-        <f>G10</f>
+        <f t="shared" si="2"/>
         <v>5000</v>
       </c>
       <c r="M10" s="17">
-        <f>(1-$D10)*H10</f>
+        <f t="shared" si="3"/>
         <v>1000</v>
       </c>
       <c r="N10" s="17">
-        <f>(1-$D10)*I10</f>
+        <f t="shared" si="4"/>
         <v>3000</v>
       </c>
       <c r="O10" s="17">
@@ -2342,26 +2342,26 @@
         <v>0</v>
       </c>
       <c r="Z10" s="17">
-        <f>SUM(J10:Y10)</f>
+        <f t="shared" si="5"/>
         <v>62410</v>
       </c>
       <c r="AA10" s="17">
         <v>0</v>
       </c>
       <c r="AB10" s="14">
-        <f>Z10-AA10</f>
+        <f t="shared" si="6"/>
         <v>62410</v>
       </c>
       <c r="AC10" s="17" t="str">
-        <f>IF(AND($T10=6000, ($T10+$W10-$AB10)&gt;=6000),T10,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD10" s="17" t="str">
-        <f>IF(AND($T10=8000, ($T10+$W10-$AB10)&gt;=8000),T10,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE10" s="17" t="str">
-        <f>IF(($T10+$W10-$AB10)&gt;=$T10+8000,W10,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -2394,23 +2394,23 @@
         <v>6000</v>
       </c>
       <c r="J11" s="17">
-        <f>(1-$D11)*E11</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K11" s="17">
-        <f>(1-$D11)*F11</f>
+        <f t="shared" si="1"/>
         <v>16500</v>
       </c>
       <c r="L11" s="17">
-        <f>G11</f>
+        <f t="shared" si="2"/>
         <v>5000</v>
       </c>
       <c r="M11" s="17">
-        <f>(1-$D11)*H11</f>
+        <f t="shared" si="3"/>
         <v>1000</v>
       </c>
       <c r="N11" s="17">
-        <f>(1-$D11)*I11</f>
+        <f t="shared" si="4"/>
         <v>3000</v>
       </c>
       <c r="O11" s="17">
@@ -2447,26 +2447,26 @@
         <v>0</v>
       </c>
       <c r="Z11" s="17">
-        <f>SUM(J11:Y11)</f>
+        <f t="shared" si="5"/>
         <v>62410</v>
       </c>
       <c r="AA11" s="17">
         <v>0</v>
       </c>
       <c r="AB11" s="14">
-        <f>Z11-AA11</f>
+        <f t="shared" si="6"/>
         <v>62410</v>
       </c>
       <c r="AC11" s="17" t="str">
-        <f>IF(AND($T11=6000, ($T11+$W11-$AB11)&gt;=6000),T11,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD11" s="17" t="str">
-        <f>IF(AND($T11=8000, ($T11+$W11-$AB11)&gt;=8000),T11,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE11" s="17" t="str">
-        <f>IF(($T11+$W11-$AB11)&gt;=$T11+8000,W11,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -2499,23 +2499,23 @@
         <v>6000</v>
       </c>
       <c r="J12" s="17">
-        <f>(1-$D12)*E12</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K12" s="17">
-        <f>(1-$D12)*F12</f>
+        <f t="shared" si="1"/>
         <v>16500</v>
       </c>
       <c r="L12" s="17">
-        <f>G12</f>
+        <f t="shared" si="2"/>
         <v>5000</v>
       </c>
       <c r="M12" s="17">
-        <f>(1-$D12)*H12</f>
+        <f t="shared" si="3"/>
         <v>1000</v>
       </c>
       <c r="N12" s="17">
-        <f>(1-$D12)*I12</f>
+        <f t="shared" si="4"/>
         <v>3000</v>
       </c>
       <c r="O12" s="17">
@@ -2552,26 +2552,26 @@
         <v>-30</v>
       </c>
       <c r="Z12" s="17">
-        <f>SUM(J12:Y12)</f>
+        <f t="shared" si="5"/>
         <v>70380</v>
       </c>
       <c r="AA12" s="17">
         <v>0</v>
       </c>
       <c r="AB12" s="14">
-        <f>Z12-AA12</f>
+        <f t="shared" si="6"/>
         <v>70380</v>
       </c>
       <c r="AC12" s="17" t="str">
-        <f>IF(AND($T12=6000, ($T12+$W12-$AB12)&gt;=6000),T12,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD12" s="17" t="str">
-        <f>IF(AND($T12=8000, ($T12+$W12-$AB12)&gt;=8000),T12,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE12" s="17" t="str">
-        <f>IF(($T12+$W12-$AB12)&gt;=$T12+8000,W12,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -2604,23 +2604,23 @@
         <v>6000</v>
       </c>
       <c r="J13" s="17">
-        <f>(1-$D13)*E13</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K13" s="17">
-        <f>(1-$D13)*F13</f>
+        <f t="shared" si="1"/>
         <v>33000</v>
       </c>
       <c r="L13" s="17">
-        <f>G13</f>
+        <f t="shared" si="2"/>
         <v>5000</v>
       </c>
       <c r="M13" s="17">
-        <f>(1-$D13)*H13</f>
+        <f t="shared" si="3"/>
         <v>2000</v>
       </c>
       <c r="N13" s="17">
-        <f>(1-$D13)*I13</f>
+        <f t="shared" si="4"/>
         <v>6000</v>
       </c>
       <c r="O13" s="17">
@@ -2657,26 +2657,26 @@
         <v>-8970</v>
       </c>
       <c r="Z13" s="17">
-        <f>SUM(J13:Y13)</f>
+        <f t="shared" si="5"/>
         <v>73940</v>
       </c>
       <c r="AA13" s="17">
         <v>0</v>
       </c>
       <c r="AB13" s="14">
-        <f>Z13-AA13</f>
+        <f t="shared" si="6"/>
         <v>73940</v>
       </c>
       <c r="AC13" s="17" t="str">
-        <f>IF(AND($T13=6000, ($T13+$W13-$AB13)&gt;=6000),T13,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD13" s="17" t="str">
-        <f>IF(AND($T13=8000, ($T13+$W13-$AB13)&gt;=8000),T13,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE13" s="17" t="str">
-        <f>IF(($T13+$W13-$AB13)&gt;=$T13+8000,W13,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -2709,23 +2709,23 @@
         <v>6000</v>
       </c>
       <c r="J14" s="17">
-        <f>(1-$D14)*E14</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K14" s="17">
-        <f>(1-$D14)*F14</f>
+        <f t="shared" si="1"/>
         <v>16500</v>
       </c>
       <c r="L14" s="17">
-        <f>G14</f>
+        <f t="shared" si="2"/>
         <v>5000</v>
       </c>
       <c r="M14" s="17">
-        <f>(1-$D14)*H14</f>
+        <f t="shared" si="3"/>
         <v>1000</v>
       </c>
       <c r="N14" s="17">
-        <f>(1-$D14)*I14</f>
+        <f t="shared" si="4"/>
         <v>3000</v>
       </c>
       <c r="O14" s="17">
@@ -2762,26 +2762,26 @@
         <v>480</v>
       </c>
       <c r="Z14" s="17">
-        <f>SUM(J14:Y14)</f>
+        <f t="shared" si="5"/>
         <v>62890</v>
       </c>
       <c r="AA14" s="17">
         <v>0</v>
       </c>
       <c r="AB14" s="14">
-        <f>Z14-AA14</f>
+        <f t="shared" si="6"/>
         <v>62890</v>
       </c>
       <c r="AC14" s="17" t="str">
-        <f>IF(AND($T14=6000, ($T14+$W14-$AB14)&gt;=6000),T14,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD14" s="17" t="str">
-        <f>IF(AND($T14=8000, ($T14+$W14-$AB14)&gt;=8000),T14,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE14" s="17" t="str">
-        <f>IF(($T14+$W14-$AB14)&gt;=$T14+8000,W14,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -2814,23 +2814,23 @@
         <v>6000</v>
       </c>
       <c r="J15" s="17">
-        <f>(1-$D15)*E15</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K15" s="17">
-        <f>(1-$D15)*F15</f>
+        <f t="shared" si="1"/>
         <v>24750</v>
       </c>
       <c r="L15" s="17">
-        <f>G15</f>
+        <f t="shared" si="2"/>
         <v>5000</v>
       </c>
       <c r="M15" s="17">
-        <f>(1-$D15)*H15</f>
+        <f t="shared" si="3"/>
         <v>1500</v>
       </c>
       <c r="N15" s="17">
-        <f>(1-$D15)*I15</f>
+        <f t="shared" si="4"/>
         <v>4500</v>
       </c>
       <c r="O15" s="17">
@@ -2867,26 +2867,26 @@
         <v>0</v>
       </c>
       <c r="Z15" s="17">
-        <f>SUM(J15:Y15)</f>
+        <f t="shared" si="5"/>
         <v>72660</v>
       </c>
       <c r="AA15" s="17">
         <v>0</v>
       </c>
       <c r="AB15" s="14">
-        <f>Z15-AA15</f>
+        <f t="shared" si="6"/>
         <v>72660</v>
       </c>
       <c r="AC15" s="17" t="str">
-        <f>IF(AND($T15=6000, ($T15+$W15-$AB15)&gt;=6000),T15,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD15" s="17" t="str">
-        <f>IF(AND($T15=8000, ($T15+$W15-$AB15)&gt;=8000),T15,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE15" s="17" t="str">
-        <f>IF(($T15+$W15-$AB15)&gt;=$T15+8000,W15,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -2919,23 +2919,23 @@
         <v>6000</v>
       </c>
       <c r="J16" s="17">
-        <f>(1-$D16)*E16</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K16" s="17">
-        <f>(1-$D16)*F16</f>
+        <f t="shared" si="1"/>
         <v>16500</v>
       </c>
       <c r="L16" s="17">
-        <f>G16</f>
+        <f t="shared" si="2"/>
         <v>5000</v>
       </c>
       <c r="M16" s="17">
-        <f>(1-$D16)*H16</f>
+        <f t="shared" si="3"/>
         <v>1000</v>
       </c>
       <c r="N16" s="17">
-        <f>(1-$D16)*I16</f>
+        <f t="shared" si="4"/>
         <v>3000</v>
       </c>
       <c r="O16" s="17">
@@ -2972,26 +2972,26 @@
         <v>500</v>
       </c>
       <c r="Z16" s="17">
-        <f>SUM(J16:Y16)</f>
+        <f t="shared" si="5"/>
         <v>62910</v>
       </c>
       <c r="AA16" s="17">
         <v>0</v>
       </c>
       <c r="AB16" s="14">
-        <f>Z16-AA16</f>
+        <f t="shared" si="6"/>
         <v>62910</v>
       </c>
       <c r="AC16" s="17" t="str">
-        <f>IF(AND($T16=6000, ($T16+$W16-$AB16)&gt;=6000),T16,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD16" s="17" t="str">
-        <f>IF(AND($T16=8000, ($T16+$W16-$AB16)&gt;=8000),T16,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE16" s="17" t="str">
-        <f>IF(($T16+$W16-$AB16)&gt;=$T16+8000,W16,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -3024,23 +3024,23 @@
         <v>6000</v>
       </c>
       <c r="J17" s="17">
-        <f>(1-$D17)*E17</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K17" s="17">
-        <f>(1-$D17)*F17</f>
+        <f t="shared" si="1"/>
         <v>16500</v>
       </c>
       <c r="L17" s="17">
-        <f>G17</f>
+        <f t="shared" si="2"/>
         <v>5000</v>
       </c>
       <c r="M17" s="17">
-        <f>(1-$D17)*H17</f>
+        <f t="shared" si="3"/>
         <v>1000</v>
       </c>
       <c r="N17" s="17">
-        <f>(1-$D17)*I17</f>
+        <f t="shared" si="4"/>
         <v>3000</v>
       </c>
       <c r="O17" s="17">
@@ -3077,26 +3077,26 @@
         <v>0</v>
       </c>
       <c r="Z17" s="17">
-        <f>SUM(J17:Y17)</f>
+        <f t="shared" si="5"/>
         <v>62410</v>
       </c>
       <c r="AA17" s="17">
         <v>0</v>
       </c>
       <c r="AB17" s="14">
-        <f>Z17-AA17</f>
+        <f t="shared" si="6"/>
         <v>62410</v>
       </c>
       <c r="AC17" s="17" t="str">
-        <f>IF(AND($T17=6000, ($T17+$W17-$AB17)&gt;=6000),T17,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD17" s="17" t="str">
-        <f>IF(AND($T17=8000, ($T17+$W17-$AB17)&gt;=8000),T17,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE17" s="17" t="str">
-        <f>IF(($T17+$W17-$AB17)&gt;=$T17+8000,W17,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -3129,23 +3129,23 @@
         <v>6000</v>
       </c>
       <c r="J18" s="17">
-        <f>(1-$D18)*E18</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K18" s="17">
-        <f>(1-$D18)*F18</f>
+        <f t="shared" si="1"/>
         <v>23100</v>
       </c>
       <c r="L18" s="17">
-        <f>G18</f>
+        <f t="shared" si="2"/>
         <v>5000</v>
       </c>
       <c r="M18" s="17">
-        <f>(1-$D18)*H18</f>
+        <f t="shared" si="3"/>
         <v>1400</v>
       </c>
       <c r="N18" s="17">
-        <f>(1-$D18)*I18</f>
+        <f t="shared" si="4"/>
         <v>4200</v>
       </c>
       <c r="O18" s="17">
@@ -3182,26 +3182,26 @@
         <v>0</v>
       </c>
       <c r="Z18" s="17">
-        <f>SUM(J18:Y18)</f>
+        <f t="shared" si="5"/>
         <v>70610</v>
       </c>
       <c r="AA18" s="17">
         <v>0</v>
       </c>
       <c r="AB18" s="14">
-        <f>Z18-AA18</f>
+        <f t="shared" si="6"/>
         <v>70610</v>
       </c>
       <c r="AC18" s="17" t="str">
-        <f>IF(AND($T18=6000, ($T18+$W18-$AB18)&gt;=6000),T18,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD18" s="17" t="str">
-        <f>IF(AND($T18=8000, ($T18+$W18-$AB18)&gt;=8000),T18,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE18" s="17" t="str">
-        <f>IF(($T18+$W18-$AB18)&gt;=$T18+8000,W18,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -3234,23 +3234,23 @@
         <v>6000</v>
       </c>
       <c r="J19" s="17">
-        <f>(1-$D19)*E19</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K19" s="17">
-        <f>(1-$D19)*F19</f>
+        <f t="shared" si="1"/>
         <v>16500</v>
       </c>
       <c r="L19" s="17">
-        <f>G19</f>
+        <f t="shared" si="2"/>
         <v>5000</v>
       </c>
       <c r="M19" s="17">
-        <f>(1-$D19)*H19</f>
+        <f t="shared" si="3"/>
         <v>1000</v>
       </c>
       <c r="N19" s="17">
-        <f>(1-$D19)*I19</f>
+        <f t="shared" si="4"/>
         <v>3000</v>
       </c>
       <c r="O19" s="17">
@@ -3287,26 +3287,26 @@
         <v>-3145</v>
       </c>
       <c r="Z19" s="17">
-        <f>SUM(J19:Y19)</f>
+        <f t="shared" si="5"/>
         <v>67265</v>
       </c>
       <c r="AA19" s="17">
         <v>0</v>
       </c>
       <c r="AB19" s="14">
-        <f>Z19-AA19</f>
+        <f t="shared" si="6"/>
         <v>67265</v>
       </c>
       <c r="AC19" s="17" t="str">
-        <f>IF(AND($T19=6000, ($T19+$W19-$AB19)&gt;=6000),T19,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD19" s="17" t="str">
-        <f>IF(AND($T19=8000, ($T19+$W19-$AB19)&gt;=8000),T19,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE19" s="17" t="str">
-        <f>IF(($T19+$W19-$AB19)&gt;=$T19+8000,W19,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -3339,23 +3339,23 @@
         <v>6000</v>
       </c>
       <c r="J20" s="17">
-        <f>(1-$D20)*E20</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K20" s="17">
-        <f>(1-$D20)*F20</f>
+        <f t="shared" si="1"/>
         <v>23100</v>
       </c>
       <c r="L20" s="17">
-        <f>G20</f>
+        <f t="shared" si="2"/>
         <v>5000</v>
       </c>
       <c r="M20" s="17">
-        <f>(1-$D20)*H20</f>
+        <f t="shared" si="3"/>
         <v>1400</v>
       </c>
       <c r="N20" s="17">
-        <f>(1-$D20)*I20</f>
+        <f t="shared" si="4"/>
         <v>4200</v>
       </c>
       <c r="O20" s="17">
@@ -3392,26 +3392,26 @@
         <v>0</v>
       </c>
       <c r="Z20" s="17">
-        <f>SUM(J20:Y20)</f>
+        <f t="shared" si="5"/>
         <v>78610</v>
       </c>
       <c r="AA20" s="17">
         <v>0</v>
       </c>
       <c r="AB20" s="14">
-        <f>Z20-AA20</f>
+        <f t="shared" si="6"/>
         <v>78610</v>
       </c>
       <c r="AC20" s="17" t="str">
-        <f>IF(AND($T20=6000, ($T20+$W20-$AB20)&gt;=6000),T20,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD20" s="17" t="str">
-        <f>IF(AND($T20=8000, ($T20+$W20-$AB20)&gt;=8000),T20,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE20" s="17" t="str">
-        <f>IF(($T20+$W20-$AB20)&gt;=$T20+8000,W20,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -3444,23 +3444,23 @@
         <v>0</v>
       </c>
       <c r="J21" s="17">
-        <f>(1-$D21)*E21</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K21" s="17">
-        <f>(1-$D21)*F21</f>
+        <f t="shared" si="1"/>
         <v>19500</v>
       </c>
       <c r="L21" s="17">
-        <f>G21</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M21" s="17">
-        <f>(1-$D21)*H21</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N21" s="17">
-        <f>(1-$D21)*I21</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O21" s="17">
@@ -3497,26 +3497,26 @@
         <v>750</v>
       </c>
       <c r="Z21" s="17">
-        <f>SUM(J21:Y21)</f>
+        <f t="shared" si="5"/>
         <v>50880</v>
       </c>
       <c r="AA21" s="17">
         <v>0</v>
       </c>
       <c r="AB21" s="14">
-        <f>Z21-AA21</f>
+        <f t="shared" si="6"/>
         <v>50880</v>
       </c>
       <c r="AC21" s="17" t="str">
-        <f>IF(AND($T21=6000, ($T21+$W21-$AB21)&gt;=6000),T21,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD21" s="17" t="str">
-        <f>IF(AND($T21=8000, ($T21+$W21-$AB21)&gt;=8000),T21,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE21" s="17" t="str">
-        <f>IF(($T21+$W21-$AB21)&gt;=$T21+8000,W21,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -3549,23 +3549,23 @@
         <v>0</v>
       </c>
       <c r="J22" s="17">
-        <f>(1-$D22)*E22</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K22" s="17">
-        <f>(1-$D22)*F22</f>
+        <f t="shared" si="1"/>
         <v>19500</v>
       </c>
       <c r="L22" s="17">
-        <f>G22</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M22" s="17">
-        <f>(1-$D22)*H22</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N22" s="17">
-        <f>(1-$D22)*I22</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O22" s="17">
@@ -3602,26 +3602,26 @@
         <v>0</v>
       </c>
       <c r="Z22" s="17">
-        <f>SUM(J22:Y22)</f>
+        <f t="shared" si="5"/>
         <v>44130</v>
       </c>
       <c r="AA22" s="17">
         <v>0</v>
       </c>
       <c r="AB22" s="14">
-        <f>Z22-AA22</f>
+        <f t="shared" si="6"/>
         <v>44130</v>
       </c>
       <c r="AC22" s="17" t="str">
-        <f>IF(AND($T22=6000, ($T22+$W22-$AB22)&gt;=6000),T22,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD22" s="17" t="str">
-        <f>IF(AND($T22=8000, ($T22+$W22-$AB22)&gt;=8000),T22,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE22" s="17" t="str">
-        <f>IF(($T22+$W22-$AB22)&gt;=$T22+8000,W22,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -3654,23 +3654,23 @@
         <v>0</v>
       </c>
       <c r="J23" s="17">
-        <f>(1-$D23)*E23</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K23" s="17">
-        <f>(1-$D23)*F23</f>
+        <f t="shared" si="1"/>
         <v>19500</v>
       </c>
       <c r="L23" s="17">
-        <f>G23</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M23" s="17">
-        <f>(1-$D23)*H23</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N23" s="17">
-        <f>(1-$D23)*I23</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O23" s="17">
@@ -3707,26 +3707,26 @@
         <v>0</v>
       </c>
       <c r="Z23" s="17">
-        <f>SUM(J23:Y23)</f>
+        <f t="shared" si="5"/>
         <v>50130</v>
       </c>
       <c r="AA23" s="17">
         <v>0</v>
       </c>
       <c r="AB23" s="14">
-        <f>Z23-AA23</f>
+        <f t="shared" si="6"/>
         <v>50130</v>
       </c>
       <c r="AC23" s="17" t="str">
-        <f>IF(AND($T23=6000, ($T23+$W23-$AB23)&gt;=6000),T23,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD23" s="17" t="str">
-        <f>IF(AND($T23=8000, ($T23+$W23-$AB23)&gt;=8000),T23,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE23" s="17" t="str">
-        <f>IF(($T23+$W23-$AB23)&gt;=$T23+8000,W23,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -3759,23 +3759,23 @@
         <v>0</v>
       </c>
       <c r="J24" s="17">
-        <f>(1-$D24)*E24</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K24" s="17">
-        <f>(1-$D24)*F24</f>
+        <f t="shared" si="1"/>
         <v>26000</v>
       </c>
       <c r="L24" s="17">
-        <f>G24</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M24" s="17">
-        <f>(1-$D24)*H24</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N24" s="17">
-        <f>(1-$D24)*I24</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O24" s="17">
@@ -3812,26 +3812,26 @@
         <v>0</v>
       </c>
       <c r="Z24" s="17">
-        <f>SUM(J24:Y24)</f>
+        <f t="shared" si="5"/>
         <v>56630</v>
       </c>
       <c r="AA24" s="17">
         <v>0</v>
       </c>
       <c r="AB24" s="14">
-        <f>Z24-AA24</f>
+        <f t="shared" si="6"/>
         <v>56630</v>
       </c>
       <c r="AC24" s="17" t="str">
-        <f>IF(AND($T24=6000, ($T24+$W24-$AB24)&gt;=6000),T24,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD24" s="17" t="str">
-        <f>IF(AND($T24=8000, ($T24+$W24-$AB24)&gt;=8000),T24,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE24" s="17" t="str">
-        <f>IF(($T24+$W24-$AB24)&gt;=$T24+8000,W24,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -3864,23 +3864,23 @@
         <v>0</v>
       </c>
       <c r="J25" s="17">
-        <f>(1-$D25)*E25</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K25" s="17">
-        <f>(1-$D25)*F25</f>
+        <f t="shared" si="1"/>
         <v>26000</v>
       </c>
       <c r="L25" s="17">
-        <f>G25</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M25" s="17">
-        <f>(1-$D25)*H25</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N25" s="17">
-        <f>(1-$D25)*I25</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O25" s="17">
@@ -3917,26 +3917,26 @@
         <v>0</v>
       </c>
       <c r="Z25" s="17">
-        <f>SUM(J25:Y25)</f>
+        <f t="shared" si="5"/>
         <v>56630</v>
       </c>
       <c r="AA25" s="17">
         <v>0</v>
       </c>
       <c r="AB25" s="14">
-        <f>Z25-AA25</f>
+        <f t="shared" si="6"/>
         <v>56630</v>
       </c>
       <c r="AC25" s="17" t="str">
-        <f>IF(AND($T25=6000, ($T25+$W25-$AB25)&gt;=6000),T25,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD25" s="17" t="str">
-        <f>IF(AND($T25=8000, ($T25+$W25-$AB25)&gt;=8000),T25,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE25" s="17" t="str">
-        <f>IF(($T25+$W25-$AB25)&gt;=$T25+8000,W25,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -3969,23 +3969,23 @@
         <v>0</v>
       </c>
       <c r="J26" s="17">
-        <f>(1-$D26)*E26</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K26" s="17">
-        <f>(1-$D26)*F26</f>
+        <f t="shared" si="1"/>
         <v>26000</v>
       </c>
       <c r="L26" s="17">
-        <f>G26</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M26" s="17">
-        <f>(1-$D26)*H26</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N26" s="17">
-        <f>(1-$D26)*I26</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O26" s="17">
@@ -4022,26 +4022,26 @@
         <v>0</v>
       </c>
       <c r="Z26" s="17">
-        <f>SUM(J26:Y26)</f>
+        <f t="shared" si="5"/>
         <v>50630</v>
       </c>
       <c r="AA26" s="17">
         <v>0</v>
       </c>
       <c r="AB26" s="14">
-        <f>Z26-AA26</f>
+        <f t="shared" si="6"/>
         <v>50630</v>
       </c>
       <c r="AC26" s="17" t="str">
-        <f>IF(AND($T26=6000, ($T26+$W26-$AB26)&gt;=6000),T26,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD26" s="17" t="str">
-        <f>IF(AND($T26=8000, ($T26+$W26-$AB26)&gt;=8000),T26,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE26" s="17" t="str">
-        <f>IF(($T26+$W26-$AB26)&gt;=$T26+8000,W26,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -4074,23 +4074,23 @@
         <v>0</v>
       </c>
       <c r="J27" s="17">
-        <f>(1-$D27)*E27</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K27" s="17">
-        <f>(1-$D27)*F27</f>
+        <f t="shared" si="1"/>
         <v>26000</v>
       </c>
       <c r="L27" s="17">
-        <f>G27</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M27" s="17">
-        <f>(1-$D27)*H27</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N27" s="17">
-        <f>(1-$D27)*I27</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O27" s="17">
@@ -4127,26 +4127,26 @@
         <v>1000</v>
       </c>
       <c r="Z27" s="17">
-        <f>SUM(J27:Y27)</f>
+        <f t="shared" si="5"/>
         <v>57630</v>
       </c>
       <c r="AA27" s="17">
         <v>0</v>
       </c>
       <c r="AB27" s="14">
-        <f>Z27-AA27</f>
+        <f t="shared" si="6"/>
         <v>57630</v>
       </c>
       <c r="AC27" s="17" t="str">
-        <f>IF(AND($T27=6000, ($T27+$W27-$AB27)&gt;=6000),T27,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD27" s="17" t="str">
-        <f>IF(AND($T27=8000, ($T27+$W27-$AB27)&gt;=8000),T27,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE27" s="17" t="str">
-        <f>IF(($T27+$W27-$AB27)&gt;=$T27+8000,W27,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -4179,23 +4179,23 @@
         <v>0</v>
       </c>
       <c r="J28" s="17">
-        <f>(1-$D28)*E28</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K28" s="17">
-        <f>(1-$D28)*F28</f>
+        <f t="shared" si="1"/>
         <v>13000</v>
       </c>
       <c r="L28" s="17">
-        <f>G28</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M28" s="17">
-        <f>(1-$D28)*H28</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N28" s="17">
-        <f>(1-$D28)*I28</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O28" s="17">
@@ -4232,26 +4232,26 @@
         <v>8000</v>
       </c>
       <c r="Z28" s="17">
-        <f>SUM(J28:Y28)</f>
+        <f t="shared" si="5"/>
         <v>45630</v>
       </c>
       <c r="AA28" s="17">
         <v>0</v>
       </c>
       <c r="AB28" s="14">
-        <f>Z28-AA28</f>
+        <f t="shared" si="6"/>
         <v>45630</v>
       </c>
       <c r="AC28" s="17" t="str">
-        <f>IF(AND($T28=6000, ($T28+$W28-$AB28)&gt;=6000),T28,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD28" s="17" t="str">
-        <f>IF(AND($T28=8000, ($T28+$W28-$AB28)&gt;=8000),T28,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE28" s="17" t="str">
-        <f>IF(($T28+$W28-$AB28)&gt;=$T28+8000,W28,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -4284,23 +4284,23 @@
         <v>0</v>
       </c>
       <c r="J29" s="17">
-        <f>(1-$D29)*E29</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K29" s="17">
-        <f>(1-$D29)*F29</f>
+        <f t="shared" si="1"/>
         <v>13000</v>
       </c>
       <c r="L29" s="17">
-        <f>G29</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M29" s="17">
-        <f>(1-$D29)*H29</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N29" s="17">
-        <f>(1-$D29)*I29</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O29" s="17">
@@ -4337,26 +4337,26 @@
         <v>8000</v>
       </c>
       <c r="Z29" s="17">
-        <f>SUM(J29:Y29)</f>
+        <f t="shared" si="5"/>
         <v>45630</v>
       </c>
       <c r="AA29" s="17">
         <v>0</v>
       </c>
       <c r="AB29" s="14">
-        <f>Z29-AA29</f>
+        <f t="shared" si="6"/>
         <v>45630</v>
       </c>
       <c r="AC29" s="17" t="str">
-        <f>IF(AND($T29=6000, ($T29+$W29-$AB29)&gt;=6000),T29,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD29" s="17" t="str">
-        <f>IF(AND($T29=8000, ($T29+$W29-$AB29)&gt;=8000),T29,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE29" s="17" t="str">
-        <f>IF(($T29+$W29-$AB29)&gt;=$T29+8000,W29,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -4389,23 +4389,23 @@
         <v>0</v>
       </c>
       <c r="J30" s="17">
-        <f>(1-$D30)*E30</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K30" s="17">
-        <f>(1-$D30)*F30</f>
+        <f t="shared" si="1"/>
         <v>19500</v>
       </c>
       <c r="L30" s="17">
-        <f>G30</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M30" s="17">
-        <f>(1-$D30)*H30</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N30" s="17">
-        <f>(1-$D30)*I30</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O30" s="17">
@@ -4442,26 +4442,26 @@
         <v>0</v>
       </c>
       <c r="Z30" s="17">
-        <f>SUM(J30:Y30)</f>
+        <f t="shared" si="5"/>
         <v>50130</v>
       </c>
       <c r="AA30" s="17">
         <v>0</v>
       </c>
       <c r="AB30" s="14">
-        <f>Z30-AA30</f>
+        <f t="shared" si="6"/>
         <v>50130</v>
       </c>
       <c r="AC30" s="17" t="str">
-        <f>IF(AND($T30=6000, ($T30+$W30-$AB30)&gt;=6000),T30,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD30" s="17" t="str">
-        <f>IF(AND($T30=8000, ($T30+$W30-$AB30)&gt;=8000),T30,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE30" s="17" t="str">
-        <f>IF(($T30+$W30-$AB30)&gt;=$T30+8000,W30,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -4494,23 +4494,23 @@
         <v>0</v>
       </c>
       <c r="J31" s="17">
-        <f>(1-$D31)*E31</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K31" s="17">
-        <f>(1-$D31)*F31</f>
+        <f t="shared" si="1"/>
         <v>19500</v>
       </c>
       <c r="L31" s="17">
-        <f>G31</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M31" s="17">
-        <f>(1-$D31)*H31</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N31" s="17">
-        <f>(1-$D31)*I31</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O31" s="17">
@@ -4547,26 +4547,26 @@
         <v>0</v>
       </c>
       <c r="Z31" s="17">
-        <f>SUM(J31:Y31)</f>
+        <f t="shared" si="5"/>
         <v>50130</v>
       </c>
       <c r="AA31" s="17">
         <v>0</v>
       </c>
       <c r="AB31" s="14">
-        <f>Z31-AA31</f>
+        <f t="shared" si="6"/>
         <v>50130</v>
       </c>
       <c r="AC31" s="17" t="str">
-        <f>IF(AND($T31=6000, ($T31+$W31-$AB31)&gt;=6000),T31,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD31" s="17" t="str">
-        <f>IF(AND($T31=8000, ($T31+$W31-$AB31)&gt;=8000),T31,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE31" s="17" t="str">
-        <f>IF(($T31+$W31-$AB31)&gt;=$T31+8000,W31,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -4599,23 +4599,23 @@
         <v>0</v>
       </c>
       <c r="J32" s="17">
-        <f>(1-$D32)*E32</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K32" s="17">
-        <f>(1-$D32)*F32</f>
+        <f t="shared" si="1"/>
         <v>26000</v>
       </c>
       <c r="L32" s="17">
-        <f>G32</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M32" s="17">
-        <f>(1-$D32)*H32</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N32" s="17">
-        <f>(1-$D32)*I32</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O32" s="17">
@@ -4652,26 +4652,26 @@
         <v>14000</v>
       </c>
       <c r="Z32" s="17">
-        <f>SUM(J32:Y32)</f>
+        <f t="shared" si="5"/>
         <v>64630</v>
       </c>
       <c r="AA32" s="17">
         <v>0</v>
       </c>
       <c r="AB32" s="14">
-        <f>Z32-AA32</f>
+        <f t="shared" si="6"/>
         <v>64630</v>
       </c>
       <c r="AC32" s="17" t="str">
-        <f>IF(AND($T32=6000, ($T32+$W32-$AB32)&gt;=6000),T32,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD32" s="17" t="str">
-        <f>IF(AND($T32=8000, ($T32+$W32-$AB32)&gt;=8000),T32,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE32" s="17" t="str">
-        <f>IF(($T32+$W32-$AB32)&gt;=$T32+8000,W32,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -4704,23 +4704,23 @@
         <v>0</v>
       </c>
       <c r="J33" s="17">
-        <f>(1-$D33)*E33</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K33" s="17">
-        <f>(1-$D33)*F33</f>
+        <f t="shared" si="1"/>
         <v>26000</v>
       </c>
       <c r="L33" s="17">
-        <f>G33</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M33" s="17">
-        <f>(1-$D33)*H33</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N33" s="17">
-        <f>(1-$D33)*I33</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O33" s="17">
@@ -4757,26 +4757,26 @@
         <v>7000</v>
       </c>
       <c r="Z33" s="17">
-        <f>SUM(J33:Y33)</f>
+        <f t="shared" si="5"/>
         <v>57630</v>
       </c>
       <c r="AA33" s="17">
         <v>0</v>
       </c>
       <c r="AB33" s="14">
-        <f>Z33-AA33</f>
+        <f t="shared" si="6"/>
         <v>57630</v>
       </c>
       <c r="AC33" s="17" t="str">
-        <f>IF(AND($T33=6000, ($T33+$W33-$AB33)&gt;=6000),T33,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD33" s="17" t="str">
-        <f>IF(AND($T33=8000, ($T33+$W33-$AB33)&gt;=8000),T33,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE33" s="17" t="str">
-        <f>IF(($T33+$W33-$AB33)&gt;=$T33+8000,W33,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -4809,23 +4809,23 @@
         <v>0</v>
       </c>
       <c r="J34" s="17">
-        <f>(1-$D34)*E34</f>
+        <f t="shared" ref="J34:J65" si="10">(1-$D34)*E34</f>
         <v>0</v>
       </c>
       <c r="K34" s="17">
-        <f>(1-$D34)*F34</f>
+        <f t="shared" ref="K34:K65" si="11">(1-$D34)*F34</f>
         <v>26000</v>
       </c>
       <c r="L34" s="17">
-        <f>G34</f>
+        <f t="shared" ref="L34:L65" si="12">G34</f>
         <v>4000</v>
       </c>
       <c r="M34" s="17">
-        <f>(1-$D34)*H34</f>
+        <f t="shared" ref="M34:M65" si="13">(1-$D34)*H34</f>
         <v>0</v>
       </c>
       <c r="N34" s="17">
-        <f>(1-$D34)*I34</f>
+        <f t="shared" ref="N34:N65" si="14">(1-$D34)*I34</f>
         <v>0</v>
       </c>
       <c r="O34" s="17">
@@ -4862,26 +4862,26 @@
         <v>-3030</v>
       </c>
       <c r="Z34" s="17">
-        <f>SUM(J34:Y34)</f>
+        <f t="shared" ref="Z34:Z65" si="15">SUM(J34:Y34)</f>
         <v>47600</v>
       </c>
       <c r="AA34" s="17">
         <v>0</v>
       </c>
       <c r="AB34" s="14">
-        <f>Z34-AA34</f>
+        <f t="shared" ref="AB34:AB65" si="16">Z34-AA34</f>
         <v>47600</v>
       </c>
       <c r="AC34" s="17" t="str">
-        <f>IF(AND($T34=6000, ($T34+$W34-$AB34)&gt;=6000),T34,"")</f>
+        <f t="shared" ref="AC34:AC65" si="17">IF(AND($T34=6000, ($T34+$W34-$AB34)&gt;=6000),T34,"")</f>
         <v/>
       </c>
       <c r="AD34" s="17" t="str">
-        <f>IF(AND($T34=8000, ($T34+$W34-$AB34)&gt;=8000),T34,"")</f>
+        <f t="shared" ref="AD34:AD65" si="18">IF(AND($T34=8000, ($T34+$W34-$AB34)&gt;=8000),T34,"")</f>
         <v/>
       </c>
       <c r="AE34" s="17" t="str">
-        <f>IF(($T34+$W34-$AB34)&gt;=$T34+8000,W34,"")</f>
+        <f t="shared" ref="AE34:AE65" si="19">IF(($T34+$W34-$AB34)&gt;=$T34+8000,W34,"")</f>
         <v/>
       </c>
     </row>
@@ -4914,23 +4914,23 @@
         <v>0</v>
       </c>
       <c r="J35" s="17">
-        <f>(1-$D35)*E35</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K35" s="17">
-        <f>(1-$D35)*F35</f>
+        <f t="shared" si="11"/>
         <v>26000</v>
       </c>
       <c r="L35" s="17">
-        <f>G35</f>
+        <f t="shared" si="12"/>
         <v>4000</v>
       </c>
       <c r="M35" s="17">
-        <f>(1-$D35)*H35</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="N35" s="17">
-        <f>(1-$D35)*I35</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O35" s="17">
@@ -4967,26 +4967,26 @@
         <v>0</v>
       </c>
       <c r="Z35" s="17">
-        <f>SUM(J35:Y35)</f>
+        <f t="shared" si="15"/>
         <v>56630</v>
       </c>
       <c r="AA35" s="17">
         <v>0</v>
       </c>
       <c r="AB35" s="14">
-        <f>Z35-AA35</f>
+        <f t="shared" si="16"/>
         <v>56630</v>
       </c>
       <c r="AC35" s="17" t="str">
-        <f>IF(AND($T35=6000, ($T35+$W35-$AB35)&gt;=6000),T35,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AD35" s="17" t="str">
-        <f>IF(AND($T35=8000, ($T35+$W35-$AB35)&gt;=8000),T35,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AE35" s="17" t="str">
-        <f>IF(($T35+$W35-$AB35)&gt;=$T35+8000,W35,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -5019,23 +5019,23 @@
         <v>0</v>
       </c>
       <c r="J36" s="17">
-        <f>(1-$D36)*E36</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K36" s="17">
-        <f>(1-$D36)*F36</f>
+        <f t="shared" si="11"/>
         <v>19500</v>
       </c>
       <c r="L36" s="17">
-        <f>G36</f>
+        <f t="shared" si="12"/>
         <v>4000</v>
       </c>
       <c r="M36" s="17">
-        <f>(1-$D36)*H36</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="N36" s="17">
-        <f>(1-$D36)*I36</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O36" s="17">
@@ -5072,26 +5072,26 @@
         <v>0</v>
       </c>
       <c r="Z36" s="17">
-        <f>SUM(J36:Y36)</f>
+        <f t="shared" si="15"/>
         <v>50130</v>
       </c>
       <c r="AA36" s="17">
         <v>0</v>
       </c>
       <c r="AB36" s="14">
-        <f>Z36-AA36</f>
+        <f t="shared" si="16"/>
         <v>50130</v>
       </c>
       <c r="AC36" s="17" t="str">
-        <f>IF(AND($T36=6000, ($T36+$W36-$AB36)&gt;=6000),T36,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AD36" s="17" t="str">
-        <f>IF(AND($T36=8000, ($T36+$W36-$AB36)&gt;=8000),T36,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AE36" s="17" t="str">
-        <f>IF(($T36+$W36-$AB36)&gt;=$T36+8000,W36,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -5124,23 +5124,23 @@
         <v>0</v>
       </c>
       <c r="J37" s="17">
-        <f>(1-$D37)*E37</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K37" s="17">
-        <f>(1-$D37)*F37</f>
+        <f t="shared" si="11"/>
         <v>13000</v>
       </c>
       <c r="L37" s="17">
-        <f>G37</f>
+        <f t="shared" si="12"/>
         <v>4000</v>
       </c>
       <c r="M37" s="17">
-        <f>(1-$D37)*H37</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="N37" s="17">
-        <f>(1-$D37)*I37</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O37" s="17">
@@ -5177,26 +5177,26 @@
         <v>8000</v>
       </c>
       <c r="Z37" s="17">
-        <f>SUM(J37:Y37)</f>
+        <f t="shared" si="15"/>
         <v>45630</v>
       </c>
       <c r="AA37" s="17">
         <v>0</v>
       </c>
       <c r="AB37" s="14">
-        <f>Z37-AA37</f>
+        <f t="shared" si="16"/>
         <v>45630</v>
       </c>
       <c r="AC37" s="17" t="str">
-        <f>IF(AND($T37=6000, ($T37+$W37-$AB37)&gt;=6000),T37,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AD37" s="17" t="str">
-        <f>IF(AND($T37=8000, ($T37+$W37-$AB37)&gt;=8000),T37,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AE37" s="17" t="str">
-        <f>IF(($T37+$W37-$AB37)&gt;=$T37+8000,W37,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -5229,23 +5229,23 @@
         <v>0</v>
       </c>
       <c r="J38" s="17">
-        <f>(1-$D38)*E38</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K38" s="17">
-        <f>(1-$D38)*F38</f>
+        <f t="shared" si="11"/>
         <v>19500</v>
       </c>
       <c r="L38" s="17">
-        <f>G38</f>
+        <f t="shared" si="12"/>
         <v>4000</v>
       </c>
       <c r="M38" s="17">
-        <f>(1-$D38)*H38</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="N38" s="17">
-        <f>(1-$D38)*I38</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O38" s="17">
@@ -5282,26 +5282,26 @@
         <v>0</v>
       </c>
       <c r="Z38" s="17">
-        <f>SUM(J38:Y38)</f>
+        <f t="shared" si="15"/>
         <v>44130</v>
       </c>
       <c r="AA38" s="17">
         <v>0</v>
       </c>
       <c r="AB38" s="14">
-        <f>Z38-AA38</f>
+        <f t="shared" si="16"/>
         <v>44130</v>
       </c>
       <c r="AC38" s="17" t="str">
-        <f>IF(AND($T38=6000, ($T38+$W38-$AB38)&gt;=6000),T38,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AD38" s="17" t="str">
-        <f>IF(AND($T38=8000, ($T38+$W38-$AB38)&gt;=8000),T38,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AE38" s="17" t="str">
-        <f>IF(($T38+$W38-$AB38)&gt;=$T38+8000,W38,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -5334,23 +5334,23 @@
         <v>0</v>
       </c>
       <c r="J39" s="17">
-        <f>(1-$D39)*E39</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K39" s="17">
-        <f>(1-$D39)*F39</f>
+        <f t="shared" si="11"/>
         <v>19500</v>
       </c>
       <c r="L39" s="17">
-        <f>G39</f>
+        <f t="shared" si="12"/>
         <v>4000</v>
       </c>
       <c r="M39" s="17">
-        <f>(1-$D39)*H39</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="N39" s="17">
-        <f>(1-$D39)*I39</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O39" s="17">
@@ -5387,26 +5387,26 @@
         <v>0</v>
       </c>
       <c r="Z39" s="17">
-        <f>SUM(J39:Y39)</f>
+        <f t="shared" si="15"/>
         <v>44130</v>
       </c>
       <c r="AA39" s="17">
         <v>0</v>
       </c>
       <c r="AB39" s="14">
-        <f>Z39-AA39</f>
+        <f t="shared" si="16"/>
         <v>44130</v>
       </c>
       <c r="AC39" s="17" t="str">
-        <f>IF(AND($T39=6000, ($T39+$W39-$AB39)&gt;=6000),T39,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AD39" s="17" t="str">
-        <f>IF(AND($T39=8000, ($T39+$W39-$AB39)&gt;=8000),T39,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AE39" s="17" t="str">
-        <f>IF(($T39+$W39-$AB39)&gt;=$T39+8000,W39,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -5439,23 +5439,23 @@
         <v>0</v>
       </c>
       <c r="J40" s="17">
-        <f>(1-$D40)*E40</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K40" s="17">
-        <f>(1-$D40)*F40</f>
+        <f t="shared" si="11"/>
         <v>26000</v>
       </c>
       <c r="L40" s="17">
-        <f>G40</f>
+        <f t="shared" si="12"/>
         <v>4000</v>
       </c>
       <c r="M40" s="17">
-        <f>(1-$D40)*H40</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="N40" s="17">
-        <f>(1-$D40)*I40</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O40" s="17">
@@ -5492,26 +5492,26 @@
         <v>0</v>
       </c>
       <c r="Z40" s="17">
-        <f>SUM(J40:Y40)</f>
+        <f t="shared" si="15"/>
         <v>50630</v>
       </c>
       <c r="AA40" s="17">
         <v>0</v>
       </c>
       <c r="AB40" s="14">
-        <f>Z40-AA40</f>
+        <f t="shared" si="16"/>
         <v>50630</v>
       </c>
       <c r="AC40" s="17" t="str">
-        <f>IF(AND($T40=6000, ($T40+$W40-$AB40)&gt;=6000),T40,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AD40" s="17" t="str">
-        <f>IF(AND($T40=8000, ($T40+$W40-$AB40)&gt;=8000),T40,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AE40" s="17" t="str">
-        <f>IF(($T40+$W40-$AB40)&gt;=$T40+8000,W40,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -5544,23 +5544,23 @@
         <v>0</v>
       </c>
       <c r="J41" s="17">
-        <f>(1-$D41)*E41</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K41" s="17">
-        <f>(1-$D41)*F41</f>
+        <f t="shared" si="11"/>
         <v>19500</v>
       </c>
       <c r="L41" s="17">
-        <f>G41</f>
+        <f t="shared" si="12"/>
         <v>4000</v>
       </c>
       <c r="M41" s="17">
-        <f>(1-$D41)*H41</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="N41" s="17">
-        <f>(1-$D41)*I41</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O41" s="17">
@@ -5597,26 +5597,26 @@
         <v>0</v>
       </c>
       <c r="Z41" s="17">
-        <f>SUM(J41:Y41)</f>
+        <f t="shared" si="15"/>
         <v>59100</v>
       </c>
       <c r="AA41" s="17">
         <v>0</v>
       </c>
       <c r="AB41" s="14">
-        <f>Z41-AA41</f>
+        <f t="shared" si="16"/>
         <v>59100</v>
       </c>
       <c r="AC41" s="17" t="str">
-        <f>IF(AND($T41=6000, ($T41+$W41-$AB41)&gt;=6000),T41,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AD41" s="17" t="str">
-        <f>IF(AND($T41=8000, ($T41+$W41-$AB41)&gt;=8000),T41,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AE41" s="17" t="str">
-        <f>IF(($T41+$W41-$AB41)&gt;=$T41+8000,W41,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -5649,23 +5649,23 @@
         <v>0</v>
       </c>
       <c r="J42" s="17">
-        <f>(1-$D42)*E42</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K42" s="17">
-        <f>(1-$D42)*F42</f>
+        <f t="shared" si="11"/>
         <v>13000</v>
       </c>
       <c r="L42" s="17">
-        <f>G42</f>
+        <f t="shared" si="12"/>
         <v>4000</v>
       </c>
       <c r="M42" s="17">
-        <f>(1-$D42)*H42</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="N42" s="17">
-        <f>(1-$D42)*I42</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O42" s="17">
@@ -5702,26 +5702,26 @@
         <v>0</v>
       </c>
       <c r="Z42" s="17">
-        <f>SUM(J42:Y42)</f>
+        <f t="shared" si="15"/>
         <v>52600</v>
       </c>
       <c r="AA42" s="17">
         <v>0</v>
       </c>
       <c r="AB42" s="14">
-        <f>Z42-AA42</f>
+        <f t="shared" si="16"/>
         <v>52600</v>
       </c>
       <c r="AC42" s="17" t="str">
-        <f>IF(AND($T42=6000, ($T42+$W42-$AB42)&gt;=6000),T42,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AD42" s="17" t="str">
-        <f>IF(AND($T42=8000, ($T42+$W42-$AB42)&gt;=8000),T42,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AE42" s="17" t="str">
-        <f>IF(($T42+$W42-$AB42)&gt;=$T42+8000,W42,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -5754,23 +5754,23 @@
         <v>0</v>
       </c>
       <c r="J43" s="17">
-        <f>(1-$D43)*E43</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K43" s="17">
-        <f>(1-$D43)*F43</f>
+        <f t="shared" si="11"/>
         <v>19500</v>
       </c>
       <c r="L43" s="17">
-        <f>G43</f>
+        <f t="shared" si="12"/>
         <v>4000</v>
       </c>
       <c r="M43" s="17">
-        <f>(1-$D43)*H43</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="N43" s="17">
-        <f>(1-$D43)*I43</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O43" s="17">
@@ -5807,26 +5807,26 @@
         <v>0</v>
       </c>
       <c r="Z43" s="17">
-        <f>SUM(J43:Y43)</f>
+        <f t="shared" si="15"/>
         <v>59100</v>
       </c>
       <c r="AA43" s="17">
         <v>0</v>
       </c>
       <c r="AB43" s="14">
-        <f>Z43-AA43</f>
+        <f t="shared" si="16"/>
         <v>59100</v>
       </c>
       <c r="AC43" s="17" t="str">
-        <f>IF(AND($T43=6000, ($T43+$W43-$AB43)&gt;=6000),T43,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AD43" s="17" t="str">
-        <f>IF(AND($T43=8000, ($T43+$W43-$AB43)&gt;=8000),T43,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AE43" s="17" t="str">
-        <f>IF(($T43+$W43-$AB43)&gt;=$T43+8000,W43,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -5859,23 +5859,23 @@
         <v>0</v>
       </c>
       <c r="J44" s="17">
-        <f>(1-$D44)*E44</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K44" s="17">
-        <f>(1-$D44)*F44</f>
+        <f t="shared" si="11"/>
         <v>19500</v>
       </c>
       <c r="L44" s="17">
-        <f>G44</f>
+        <f t="shared" si="12"/>
         <v>4000</v>
       </c>
       <c r="M44" s="17">
-        <f>(1-$D44)*H44</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="N44" s="17">
-        <f>(1-$D44)*I44</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O44" s="17">
@@ -5912,26 +5912,26 @@
         <v>0</v>
       </c>
       <c r="Z44" s="17">
-        <f>SUM(J44:Y44)</f>
+        <f t="shared" si="15"/>
         <v>65100</v>
       </c>
       <c r="AA44" s="17">
         <v>0</v>
       </c>
       <c r="AB44" s="14">
-        <f>Z44-AA44</f>
+        <f t="shared" si="16"/>
         <v>65100</v>
       </c>
       <c r="AC44" s="17" t="str">
-        <f>IF(AND($T44=6000, ($T44+$W44-$AB44)&gt;=6000),T44,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AD44" s="17" t="str">
-        <f>IF(AND($T44=8000, ($T44+$W44-$AB44)&gt;=8000),T44,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AE44" s="17" t="str">
-        <f>IF(($T44+$W44-$AB44)&gt;=$T44+8000,W44,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -5964,23 +5964,23 @@
         <v>0</v>
       </c>
       <c r="J45" s="17">
-        <f>(1-$D45)*E45</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K45" s="17">
-        <f>(1-$D45)*F45</f>
+        <f t="shared" si="11"/>
         <v>19500</v>
       </c>
       <c r="L45" s="17">
-        <f>G45</f>
+        <f t="shared" si="12"/>
         <v>4000</v>
       </c>
       <c r="M45" s="17">
-        <f>(1-$D45)*H45</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="N45" s="17">
-        <f>(1-$D45)*I45</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O45" s="17">
@@ -6017,26 +6017,26 @@
         <v>18500</v>
       </c>
       <c r="Z45" s="17">
-        <f>SUM(J45:Y45)</f>
+        <f t="shared" si="15"/>
         <v>83600</v>
       </c>
       <c r="AA45" s="17">
         <v>48000</v>
       </c>
       <c r="AB45" s="14">
-        <f>Z45-AA45</f>
+        <f t="shared" si="16"/>
         <v>35600</v>
       </c>
       <c r="AC45" s="17" t="str">
-        <f>IF(AND($T45=6000, ($T45+$W45-$AB45)&gt;=6000),T45,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AD45" s="17" t="str">
-        <f>IF(AND($T45=8000, ($T45+$W45-$AB45)&gt;=8000),T45,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AE45" s="17" t="str">
-        <f>IF(($T45+$W45-$AB45)&gt;=$T45+8000,W45,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -6069,23 +6069,23 @@
         <v>0</v>
       </c>
       <c r="J46" s="17">
-        <f>(1-$D46)*E46</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K46" s="17">
-        <f>(1-$D46)*F46</f>
+        <f t="shared" si="11"/>
         <v>19500</v>
       </c>
       <c r="L46" s="17">
-        <f>G46</f>
+        <f t="shared" si="12"/>
         <v>4000</v>
       </c>
       <c r="M46" s="17">
-        <f>(1-$D46)*H46</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="N46" s="17">
-        <f>(1-$D46)*I46</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O46" s="17">
@@ -6122,26 +6122,26 @@
         <v>0</v>
       </c>
       <c r="Z46" s="17">
-        <f>SUM(J46:Y46)</f>
+        <f t="shared" si="15"/>
         <v>65100</v>
       </c>
       <c r="AA46" s="17">
         <v>0</v>
       </c>
       <c r="AB46" s="14">
-        <f>Z46-AA46</f>
+        <f t="shared" si="16"/>
         <v>65100</v>
       </c>
       <c r="AC46" s="17" t="str">
-        <f>IF(AND($T46=6000, ($T46+$W46-$AB46)&gt;=6000),T46,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AD46" s="17" t="str">
-        <f>IF(AND($T46=8000, ($T46+$W46-$AB46)&gt;=8000),T46,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AE46" s="17" t="str">
-        <f>IF(($T46+$W46-$AB46)&gt;=$T46+8000,W46,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -6174,23 +6174,23 @@
         <v>0</v>
       </c>
       <c r="J47" s="17">
-        <f>(1-$D47)*E47</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K47" s="17">
-        <f>(1-$D47)*F47</f>
+        <f t="shared" si="11"/>
         <v>19500</v>
       </c>
       <c r="L47" s="17">
-        <f>G47</f>
+        <f t="shared" si="12"/>
         <v>4000</v>
       </c>
       <c r="M47" s="17">
-        <f>(1-$D47)*H47</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="N47" s="17">
-        <f>(1-$D47)*I47</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O47" s="17">
@@ -6227,26 +6227,26 @@
         <v>0</v>
       </c>
       <c r="Z47" s="17">
-        <f>SUM(J47:Y47)</f>
+        <f t="shared" si="15"/>
         <v>65100</v>
       </c>
       <c r="AA47" s="17">
         <v>0</v>
       </c>
       <c r="AB47" s="14">
-        <f>Z47-AA47</f>
+        <f t="shared" si="16"/>
         <v>65100</v>
       </c>
       <c r="AC47" s="17" t="str">
-        <f>IF(AND($T47=6000, ($T47+$W47-$AB47)&gt;=6000),T47,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AD47" s="17" t="str">
-        <f>IF(AND($T47=8000, ($T47+$W47-$AB47)&gt;=8000),T47,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AE47" s="17" t="str">
-        <f>IF(($T47+$W47-$AB47)&gt;=$T47+8000,W47,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -6279,23 +6279,23 @@
         <v>0</v>
       </c>
       <c r="J48" s="17">
-        <f>(1-$D48)*E48</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K48" s="17">
-        <f>(1-$D48)*F48</f>
+        <f t="shared" si="11"/>
         <v>19500</v>
       </c>
       <c r="L48" s="17">
-        <f>G48</f>
+        <f t="shared" si="12"/>
         <v>4000</v>
       </c>
       <c r="M48" s="17">
-        <f>(1-$D48)*H48</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="N48" s="17">
-        <f>(1-$D48)*I48</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O48" s="17">
@@ -6332,26 +6332,26 @@
         <v>0</v>
       </c>
       <c r="Z48" s="17">
-        <f>SUM(J48:Y48)</f>
+        <f t="shared" si="15"/>
         <v>65100</v>
       </c>
       <c r="AA48" s="17">
         <v>0</v>
       </c>
       <c r="AB48" s="14">
-        <f>Z48-AA48</f>
+        <f t="shared" si="16"/>
         <v>65100</v>
       </c>
       <c r="AC48" s="17" t="str">
-        <f>IF(AND($T48=6000, ($T48+$W48-$AB48)&gt;=6000),T48,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AD48" s="17" t="str">
-        <f>IF(AND($T48=8000, ($T48+$W48-$AB48)&gt;=8000),T48,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AE48" s="17" t="str">
-        <f>IF(($T48+$W48-$AB48)&gt;=$T48+8000,W48,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -6384,23 +6384,23 @@
         <v>0</v>
       </c>
       <c r="J49" s="17">
-        <f>(1-$D49)*E49</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K49" s="17">
-        <f>(1-$D49)*F49</f>
+        <f t="shared" si="11"/>
         <v>26000</v>
       </c>
       <c r="L49" s="17">
-        <f>G49</f>
+        <f t="shared" si="12"/>
         <v>4000</v>
       </c>
       <c r="M49" s="17">
-        <f>(1-$D49)*H49</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="N49" s="17">
-        <f>(1-$D49)*I49</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O49" s="17">
@@ -6437,26 +6437,26 @@
         <v>14240</v>
       </c>
       <c r="Z49" s="17">
-        <f>SUM(J49:Y49)</f>
+        <f t="shared" si="15"/>
         <v>85840</v>
       </c>
       <c r="AA49" s="17">
         <v>0</v>
       </c>
       <c r="AB49" s="14">
-        <f>Z49-AA49</f>
+        <f t="shared" si="16"/>
         <v>85840</v>
       </c>
       <c r="AC49" s="17" t="str">
-        <f>IF(AND($T49=6000, ($T49+$W49-$AB49)&gt;=6000),T49,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AD49" s="17" t="str">
-        <f>IF(AND($T49=8000, ($T49+$W49-$AB49)&gt;=8000),T49,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AE49" s="17" t="str">
-        <f>IF(($T49+$W49-$AB49)&gt;=$T49+8000,W49,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -6489,23 +6489,23 @@
         <v>0</v>
       </c>
       <c r="J50" s="17">
-        <f>(1-$D50)*E50</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K50" s="17">
-        <f>(1-$D50)*F50</f>
+        <f t="shared" si="11"/>
         <v>26000</v>
       </c>
       <c r="L50" s="17">
-        <f>G50</f>
+        <f t="shared" si="12"/>
         <v>4000</v>
       </c>
       <c r="M50" s="17">
-        <f>(1-$D50)*H50</f>
+        <f t="shared" si="13"/>
         <v>1000</v>
       </c>
       <c r="N50" s="17">
-        <f>(1-$D50)*I50</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O50" s="17">
@@ -6542,26 +6542,26 @@
         <v>-1000</v>
       </c>
       <c r="Z50" s="17">
-        <f>SUM(J50:Y50)</f>
+        <f t="shared" si="15"/>
         <v>74340</v>
       </c>
       <c r="AA50" s="17">
         <v>0</v>
       </c>
       <c r="AB50" s="14">
-        <f>Z50-AA50</f>
+        <f t="shared" si="16"/>
         <v>74340</v>
       </c>
       <c r="AC50" s="17" t="str">
-        <f>IF(AND($T50=6000, ($T50+$W50-$AB50)&gt;=6000),T50,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AD50" s="17" t="str">
-        <f>IF(AND($T50=8000, ($T50+$W50-$AB50)&gt;=8000),T50,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AE50" s="17" t="str">
-        <f>IF(($T50+$W50-$AB50)&gt;=$T50+8000,W50,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -6594,23 +6594,23 @@
         <v>0</v>
       </c>
       <c r="J51" s="17">
-        <f>(1-$D51)*E51</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K51" s="17">
-        <f>(1-$D51)*F51</f>
+        <f t="shared" si="11"/>
         <v>26000</v>
       </c>
       <c r="L51" s="17">
-        <f>G51</f>
+        <f t="shared" si="12"/>
         <v>4000</v>
       </c>
       <c r="M51" s="17">
-        <f>(1-$D51)*H51</f>
+        <f t="shared" si="13"/>
         <v>1000</v>
       </c>
       <c r="N51" s="17">
-        <f>(1-$D51)*I51</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O51" s="17">
@@ -6647,26 +6647,26 @@
         <v>0</v>
       </c>
       <c r="Z51" s="17">
-        <f>SUM(J51:Y51)</f>
+        <f t="shared" si="15"/>
         <v>75340</v>
       </c>
       <c r="AA51" s="17">
         <v>0</v>
       </c>
       <c r="AB51" s="14">
-        <f>Z51-AA51</f>
+        <f t="shared" si="16"/>
         <v>75340</v>
       </c>
       <c r="AC51" s="17" t="str">
-        <f>IF(AND($T51=6000, ($T51+$W51-$AB51)&gt;=6000),T51,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AD51" s="17" t="str">
-        <f>IF(AND($T51=8000, ($T51+$W51-$AB51)&gt;=8000),T51,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AE51" s="17" t="str">
-        <f>IF(($T51+$W51-$AB51)&gt;=$T51+8000,W51,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -6699,23 +6699,23 @@
         <v>0</v>
       </c>
       <c r="J52" s="17">
-        <f>(1-$D52)*E52</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K52" s="17">
-        <f>(1-$D52)*F52</f>
+        <f t="shared" si="11"/>
         <v>26000</v>
       </c>
       <c r="L52" s="17">
-        <f>G52</f>
+        <f t="shared" si="12"/>
         <v>4000</v>
       </c>
       <c r="M52" s="17">
-        <f>(1-$D52)*H52</f>
+        <f t="shared" si="13"/>
         <v>1000</v>
       </c>
       <c r="N52" s="17">
-        <f>(1-$D52)*I52</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O52" s="17">
@@ -6752,26 +6752,26 @@
         <v>0</v>
       </c>
       <c r="Z52" s="17">
-        <f>SUM(J52:Y52)</f>
+        <f t="shared" si="15"/>
         <v>75340</v>
       </c>
       <c r="AA52" s="17">
         <v>0</v>
       </c>
       <c r="AB52" s="14">
-        <f>Z52-AA52</f>
+        <f t="shared" si="16"/>
         <v>75340</v>
       </c>
       <c r="AC52" s="17" t="str">
-        <f>IF(AND($T52=6000, ($T52+$W52-$AB52)&gt;=6000),T52,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AD52" s="17" t="str">
-        <f>IF(AND($T52=8000, ($T52+$W52-$AB52)&gt;=8000),T52,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AE52" s="17" t="str">
-        <f>IF(($T52+$W52-$AB52)&gt;=$T52+8000,W52,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -6804,23 +6804,23 @@
         <v>0</v>
       </c>
       <c r="J53" s="17">
-        <f>(1-$D53)*E53</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K53" s="17">
-        <f>(1-$D53)*F53</f>
+        <f t="shared" si="11"/>
         <v>26000</v>
       </c>
       <c r="L53" s="17">
-        <f>G53</f>
+        <f t="shared" si="12"/>
         <v>4000</v>
       </c>
       <c r="M53" s="17">
-        <f>(1-$D53)*H53</f>
+        <f t="shared" si="13"/>
         <v>1000</v>
       </c>
       <c r="N53" s="17">
-        <f>(1-$D53)*I53</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O53" s="17">
@@ -6857,26 +6857,26 @@
         <v>0</v>
       </c>
       <c r="Z53" s="17">
-        <f>SUM(J53:Y53)</f>
+        <f t="shared" si="15"/>
         <v>75340</v>
       </c>
       <c r="AA53" s="17">
         <v>0</v>
       </c>
       <c r="AB53" s="14">
-        <f>Z53-AA53</f>
+        <f t="shared" si="16"/>
         <v>75340</v>
       </c>
       <c r="AC53" s="17" t="str">
-        <f>IF(AND($T53=6000, ($T53+$W53-$AB53)&gt;=6000),T53,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AD53" s="17" t="str">
-        <f>IF(AND($T53=8000, ($T53+$W53-$AB53)&gt;=8000),T53,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AE53" s="17" t="str">
-        <f>IF(($T53+$W53-$AB53)&gt;=$T53+8000,W53,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -6909,23 +6909,23 @@
         <v>0</v>
       </c>
       <c r="J54" s="17">
-        <f>(1-$D54)*E54</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K54" s="17">
-        <f>(1-$D54)*F54</f>
+        <f t="shared" si="11"/>
         <v>26000</v>
       </c>
       <c r="L54" s="17">
-        <f>G54</f>
+        <f t="shared" si="12"/>
         <v>4000</v>
       </c>
       <c r="M54" s="17">
-        <f>(1-$D54)*H54</f>
+        <f t="shared" si="13"/>
         <v>1000</v>
       </c>
       <c r="N54" s="17">
-        <f>(1-$D54)*I54</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O54" s="17">
@@ -6962,26 +6962,26 @@
         <v>0</v>
       </c>
       <c r="Z54" s="17">
-        <f>SUM(J54:Y54)</f>
+        <f t="shared" si="15"/>
         <v>75340</v>
       </c>
       <c r="AA54" s="17">
         <v>0</v>
       </c>
       <c r="AB54" s="14">
-        <f>Z54-AA54</f>
+        <f t="shared" si="16"/>
         <v>75340</v>
       </c>
       <c r="AC54" s="17" t="str">
-        <f>IF(AND($T54=6000, ($T54+$W54-$AB54)&gt;=6000),T54,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AD54" s="17" t="str">
-        <f>IF(AND($T54=8000, ($T54+$W54-$AB54)&gt;=8000),T54,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AE54" s="17" t="str">
-        <f>IF(($T54+$W54-$AB54)&gt;=$T54+8000,W54,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -7014,23 +7014,23 @@
         <v>0</v>
       </c>
       <c r="J55" s="17">
-        <f>(1-$D55)*E55</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K55" s="17">
-        <f>(1-$D55)*F55</f>
+        <f t="shared" si="11"/>
         <v>26000</v>
       </c>
       <c r="L55" s="17">
-        <f>G55</f>
+        <f t="shared" si="12"/>
         <v>4000</v>
       </c>
       <c r="M55" s="17">
-        <f>(1-$D55)*H55</f>
+        <f t="shared" si="13"/>
         <v>1000</v>
       </c>
       <c r="N55" s="17">
-        <f>(1-$D55)*I55</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O55" s="17">
@@ -7067,26 +7067,26 @@
         <v>0</v>
       </c>
       <c r="Z55" s="17">
-        <f>SUM(J55:Y55)</f>
+        <f t="shared" si="15"/>
         <v>75340</v>
       </c>
       <c r="AA55" s="17">
         <v>0</v>
       </c>
       <c r="AB55" s="14">
-        <f>Z55-AA55</f>
+        <f t="shared" si="16"/>
         <v>75340</v>
       </c>
       <c r="AC55" s="17" t="str">
-        <f>IF(AND($T55=6000, ($T55+$W55-$AB55)&gt;=6000),T55,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AD55" s="17" t="str">
-        <f>IF(AND($T55=8000, ($T55+$W55-$AB55)&gt;=8000),T55,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AE55" s="17" t="str">
-        <f>IF(($T55+$W55-$AB55)&gt;=$T55+8000,W55,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -7119,23 +7119,23 @@
         <v>0</v>
       </c>
       <c r="J56" s="17">
-        <f>(1-$D56)*E56</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K56" s="17">
-        <f>(1-$D56)*F56</f>
+        <f t="shared" si="11"/>
         <v>26000</v>
       </c>
       <c r="L56" s="17">
-        <f>G56</f>
+        <f t="shared" si="12"/>
         <v>4000</v>
       </c>
       <c r="M56" s="17">
-        <f>(1-$D56)*H56</f>
+        <f t="shared" si="13"/>
         <v>1000</v>
       </c>
       <c r="N56" s="17">
-        <f>(1-$D56)*I56</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O56" s="17">
@@ -7172,26 +7172,26 @@
         <v>2000</v>
       </c>
       <c r="Z56" s="17">
-        <f>SUM(J56:Y56)</f>
+        <f t="shared" si="15"/>
         <v>77340</v>
       </c>
       <c r="AA56" s="17">
         <v>0</v>
       </c>
       <c r="AB56" s="14">
-        <f>Z56-AA56</f>
+        <f t="shared" si="16"/>
         <v>77340</v>
       </c>
       <c r="AC56" s="17" t="str">
-        <f>IF(AND($T56=6000, ($T56+$W56-$AB56)&gt;=6000),T56,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AD56" s="17" t="str">
-        <f>IF(AND($T56=8000, ($T56+$W56-$AB56)&gt;=8000),T56,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AE56" s="17" t="str">
-        <f>IF(($T56+$W56-$AB56)&gt;=$T56+8000,W56,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -7224,23 +7224,23 @@
         <v>0</v>
       </c>
       <c r="J57" s="17">
-        <f>(1-$D57)*E57</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K57" s="17">
-        <f>(1-$D57)*F57</f>
+        <f t="shared" si="11"/>
         <v>13000</v>
       </c>
       <c r="L57" s="17">
-        <f>G57</f>
+        <f t="shared" si="12"/>
         <v>4000</v>
       </c>
       <c r="M57" s="17">
-        <f>(1-$D57)*H57</f>
+        <f t="shared" si="13"/>
         <v>500</v>
       </c>
       <c r="N57" s="17">
-        <f>(1-$D57)*I57</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O57" s="17">
@@ -7250,13 +7250,13 @@
         <v>5300</v>
       </c>
       <c r="Q57" s="17">
-        <v>16000</v>
+        <v>0</v>
       </c>
       <c r="R57" s="17">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="S57" s="17">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="T57" s="17">
         <v>0</v>
@@ -7277,26 +7277,26 @@
         <v>0</v>
       </c>
       <c r="Z57" s="17">
-        <f>SUM(J57:Y57)</f>
-        <v>61840</v>
+        <f t="shared" si="15"/>
+        <v>30840</v>
       </c>
       <c r="AA57" s="17">
         <v>0</v>
       </c>
       <c r="AB57" s="14">
-        <f>Z57-AA57</f>
-        <v>61840</v>
+        <f t="shared" si="16"/>
+        <v>30840</v>
       </c>
       <c r="AC57" s="17" t="str">
-        <f>IF(AND($T57=6000, ($T57+$W57-$AB57)&gt;=6000),T57,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AD57" s="17" t="str">
-        <f>IF(AND($T57=8000, ($T57+$W57-$AB57)&gt;=8000),T57,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AE57" s="17" t="str">
-        <f>IF(($T57+$W57-$AB57)&gt;=$T57+8000,W57,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -7329,23 +7329,23 @@
         <v>0</v>
       </c>
       <c r="J58" s="17">
-        <f>(1-$D58)*E58</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K58" s="17">
-        <f>(1-$D58)*F58</f>
+        <f t="shared" si="11"/>
         <v>26000</v>
       </c>
       <c r="L58" s="17">
-        <f>G58</f>
+        <f t="shared" si="12"/>
         <v>4000</v>
       </c>
       <c r="M58" s="17">
-        <f>(1-$D58)*H58</f>
+        <f t="shared" si="13"/>
         <v>1000</v>
       </c>
       <c r="N58" s="17">
-        <f>(1-$D58)*I58</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O58" s="17">
@@ -7382,26 +7382,26 @@
         <v>0</v>
       </c>
       <c r="Z58" s="17">
-        <f>SUM(J58:Y58)</f>
+        <f t="shared" si="15"/>
         <v>75340</v>
       </c>
       <c r="AA58" s="17">
         <v>0</v>
       </c>
       <c r="AB58" s="14">
-        <f>Z58-AA58</f>
+        <f t="shared" si="16"/>
         <v>75340</v>
       </c>
       <c r="AC58" s="17" t="str">
-        <f>IF(AND($T58=6000, ($T58+$W58-$AB58)&gt;=6000),T58,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AD58" s="17" t="str">
-        <f>IF(AND($T58=8000, ($T58+$W58-$AB58)&gt;=8000),T58,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AE58" s="17" t="str">
-        <f>IF(($T58+$W58-$AB58)&gt;=$T58+8000,W58,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -7434,23 +7434,23 @@
         <v>0</v>
       </c>
       <c r="J59" s="17">
-        <f>(1-$D59)*E59</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K59" s="17">
-        <f>(1-$D59)*F59</f>
+        <f t="shared" si="11"/>
         <v>19500</v>
       </c>
       <c r="L59" s="17">
-        <f>G59</f>
+        <f t="shared" si="12"/>
         <v>4000</v>
       </c>
       <c r="M59" s="17">
-        <f>(1-$D59)*H59</f>
+        <f t="shared" si="13"/>
         <v>750</v>
       </c>
       <c r="N59" s="17">
-        <f>(1-$D59)*I59</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O59" s="17">
@@ -7487,26 +7487,26 @@
         <v>-500</v>
       </c>
       <c r="Z59" s="17">
-        <f>SUM(J59:Y59)</f>
+        <f t="shared" si="15"/>
         <v>68090</v>
       </c>
       <c r="AA59" s="17">
         <v>0</v>
       </c>
       <c r="AB59" s="14">
-        <f>Z59-AA59</f>
+        <f t="shared" si="16"/>
         <v>68090</v>
       </c>
       <c r="AC59" s="17" t="str">
-        <f>IF(AND($T59=6000, ($T59+$W59-$AB59)&gt;=6000),T59,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AD59" s="17" t="str">
-        <f>IF(AND($T59=8000, ($T59+$W59-$AB59)&gt;=8000),T59,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AE59" s="17" t="str">
-        <f>IF(($T59+$W59-$AB59)&gt;=$T59+8000,W59,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -7539,23 +7539,23 @@
         <v>0</v>
       </c>
       <c r="J60" s="17">
-        <f>(1-$D60)*E60</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K60" s="17">
-        <f>(1-$D60)*F60</f>
+        <f t="shared" si="11"/>
         <v>19500</v>
       </c>
       <c r="L60" s="17">
-        <f>G60</f>
+        <f t="shared" si="12"/>
         <v>4000</v>
       </c>
       <c r="M60" s="17">
-        <f>(1-$D60)*H60</f>
+        <f t="shared" si="13"/>
         <v>750</v>
       </c>
       <c r="N60" s="17">
-        <f>(1-$D60)*I60</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O60" s="17">
@@ -7592,26 +7592,26 @@
         <v>0</v>
       </c>
       <c r="Z60" s="17">
-        <f>SUM(J60:Y60)</f>
+        <f t="shared" si="15"/>
         <v>68590</v>
       </c>
       <c r="AA60" s="17">
         <v>0</v>
       </c>
       <c r="AB60" s="14">
-        <f>Z60-AA60</f>
+        <f t="shared" si="16"/>
         <v>68590</v>
       </c>
       <c r="AC60" s="17" t="str">
-        <f>IF(AND($T60=6000, ($T60+$W60-$AB60)&gt;=6000),T60,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AD60" s="17" t="str">
-        <f>IF(AND($T60=8000, ($T60+$W60-$AB60)&gt;=8000),T60,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AE60" s="17" t="str">
-        <f>IF(($T60+$W60-$AB60)&gt;=$T60+8000,W60,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -7644,23 +7644,23 @@
         <v>0</v>
       </c>
       <c r="J61" s="17">
-        <f>(1-$D61)*E61</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K61" s="17">
-        <f>(1-$D61)*F61</f>
+        <f t="shared" si="11"/>
         <v>19500</v>
       </c>
       <c r="L61" s="17">
-        <f>G61</f>
+        <f t="shared" si="12"/>
         <v>4000</v>
       </c>
       <c r="M61" s="17">
-        <f>(1-$D61)*H61</f>
+        <f t="shared" si="13"/>
         <v>750</v>
       </c>
       <c r="N61" s="17">
-        <f>(1-$D61)*I61</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O61" s="17">
@@ -7697,26 +7697,26 @@
         <v>19200</v>
       </c>
       <c r="Z61" s="17">
-        <f>SUM(J61:Y61)</f>
+        <f t="shared" si="15"/>
         <v>87790</v>
       </c>
       <c r="AA61" s="17">
         <v>0</v>
       </c>
       <c r="AB61" s="14">
-        <f>Z61-AA61</f>
+        <f t="shared" si="16"/>
         <v>87790</v>
       </c>
       <c r="AC61" s="17" t="str">
-        <f>IF(AND($T61=6000, ($T61+$W61-$AB61)&gt;=6000),T61,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AD61" s="17" t="str">
-        <f>IF(AND($T61=8000, ($T61+$W61-$AB61)&gt;=8000),T61,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AE61" s="17" t="str">
-        <f>IF(($T61+$W61-$AB61)&gt;=$T61+8000,W61,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -7749,23 +7749,23 @@
         <v>0</v>
       </c>
       <c r="J62" s="17">
-        <f>(1-$D62)*E62</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K62" s="17">
-        <f>(1-$D62)*F62</f>
+        <f t="shared" si="11"/>
         <v>19500</v>
       </c>
       <c r="L62" s="17">
-        <f>G62</f>
+        <f t="shared" si="12"/>
         <v>4000</v>
       </c>
       <c r="M62" s="17">
-        <f>(1-$D62)*H62</f>
+        <f t="shared" si="13"/>
         <v>750</v>
       </c>
       <c r="N62" s="17">
-        <f>(1-$D62)*I62</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O62" s="17">
@@ -7802,26 +7802,26 @@
         <v>19200</v>
       </c>
       <c r="Z62" s="17">
-        <f>SUM(J62:Y62)</f>
+        <f t="shared" si="15"/>
         <v>87790</v>
       </c>
       <c r="AA62" s="17">
         <v>0</v>
       </c>
       <c r="AB62" s="14">
-        <f>Z62-AA62</f>
+        <f t="shared" si="16"/>
         <v>87790</v>
       </c>
       <c r="AC62" s="17" t="str">
-        <f>IF(AND($T62=6000, ($T62+$W62-$AB62)&gt;=6000),T62,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AD62" s="17" t="str">
-        <f>IF(AND($T62=8000, ($T62+$W62-$AB62)&gt;=8000),T62,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AE62" s="17" t="str">
-        <f>IF(($T62+$W62-$AB62)&gt;=$T62+8000,W62,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -7854,23 +7854,23 @@
         <v>0</v>
       </c>
       <c r="J63" s="17">
-        <f>(1-$D63)*E63</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K63" s="17">
-        <f>(1-$D63)*F63</f>
+        <f t="shared" si="11"/>
         <v>19500</v>
       </c>
       <c r="L63" s="17">
-        <f>G63</f>
+        <f t="shared" si="12"/>
         <v>4000</v>
       </c>
       <c r="M63" s="17">
-        <f>(1-$D63)*H63</f>
+        <f t="shared" si="13"/>
         <v>750</v>
       </c>
       <c r="N63" s="17">
-        <f>(1-$D63)*I63</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O63" s="17">
@@ -7907,26 +7907,26 @@
         <v>0</v>
       </c>
       <c r="Z63" s="17">
-        <f>SUM(J63:Y63)</f>
+        <f t="shared" si="15"/>
         <v>68590</v>
       </c>
       <c r="AA63" s="17">
         <v>0</v>
       </c>
       <c r="AB63" s="14">
-        <f>Z63-AA63</f>
+        <f t="shared" si="16"/>
         <v>68590</v>
       </c>
       <c r="AC63" s="17" t="str">
-        <f>IF(AND($T63=6000, ($T63+$W63-$AB63)&gt;=6000),T63,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AD63" s="17" t="str">
-        <f>IF(AND($T63=8000, ($T63+$W63-$AB63)&gt;=8000),T63,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AE63" s="17" t="str">
-        <f>IF(($T63+$W63-$AB63)&gt;=$T63+8000,W63,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -7959,23 +7959,23 @@
         <v>0</v>
       </c>
       <c r="J64" s="17">
-        <f>(1-$D64)*E64</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K64" s="17">
-        <f>(1-$D64)*F64</f>
+        <f t="shared" si="11"/>
         <v>19500</v>
       </c>
       <c r="L64" s="17">
-        <f>G64</f>
+        <f t="shared" si="12"/>
         <v>4000</v>
       </c>
       <c r="M64" s="17">
-        <f>(1-$D64)*H64</f>
+        <f t="shared" si="13"/>
         <v>750</v>
       </c>
       <c r="N64" s="17">
-        <f>(1-$D64)*I64</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O64" s="17">
@@ -8012,26 +8012,26 @@
         <v>3500</v>
       </c>
       <c r="Z64" s="17">
-        <f>SUM(J64:Y64)</f>
+        <f t="shared" si="15"/>
         <v>72090</v>
       </c>
       <c r="AA64" s="17">
         <v>0</v>
       </c>
       <c r="AB64" s="14">
-        <f>Z64-AA64</f>
+        <f t="shared" si="16"/>
         <v>72090</v>
       </c>
       <c r="AC64" s="17" t="str">
-        <f>IF(AND($T64=6000, ($T64+$W64-$AB64)&gt;=6000),T64,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AD64" s="17" t="str">
-        <f>IF(AND($T64=8000, ($T64+$W64-$AB64)&gt;=8000),T64,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AE64" s="17" t="str">
-        <f>IF(($T64+$W64-$AB64)&gt;=$T64+8000,W64,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -8064,23 +8064,23 @@
         <v>0</v>
       </c>
       <c r="J65" s="17">
-        <f>(1-$D65)*E65</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K65" s="17">
-        <f>(1-$D65)*F65</f>
+        <f t="shared" si="11"/>
         <v>26000</v>
       </c>
       <c r="L65" s="17">
-        <f>G65</f>
+        <f t="shared" si="12"/>
         <v>4000</v>
       </c>
       <c r="M65" s="17">
-        <f>(1-$D65)*H65</f>
+        <f t="shared" si="13"/>
         <v>1000</v>
       </c>
       <c r="N65" s="17">
-        <f>(1-$D65)*I65</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O65" s="17">
@@ -8117,26 +8117,26 @@
         <v>-10000</v>
       </c>
       <c r="Z65" s="17">
-        <f>SUM(J65:Y65)</f>
+        <f t="shared" si="15"/>
         <v>65340</v>
       </c>
       <c r="AA65" s="17">
         <v>0</v>
       </c>
       <c r="AB65" s="14">
-        <f>Z65-AA65</f>
+        <f t="shared" si="16"/>
         <v>65340</v>
       </c>
       <c r="AC65" s="17" t="str">
-        <f>IF(AND($T65=6000, ($T65+$W65-$AB65)&gt;=6000),T65,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AD65" s="17" t="str">
-        <f>IF(AND($T65=8000, ($T65+$W65-$AB65)&gt;=8000),T65,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AE65" s="17" t="str">
-        <f>IF(($T65+$W65-$AB65)&gt;=$T65+8000,W65,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -8169,23 +8169,23 @@
         <v>0</v>
       </c>
       <c r="J66" s="17">
-        <f>(1-$D66)*E66</f>
+        <f t="shared" ref="J66:J97" si="20">(1-$D66)*E66</f>
         <v>0</v>
       </c>
       <c r="K66" s="17">
-        <f>(1-$D66)*F66</f>
+        <f t="shared" ref="K66:K97" si="21">(1-$D66)*F66</f>
         <v>26000</v>
       </c>
       <c r="L66" s="17">
-        <f>G66</f>
+        <f t="shared" ref="L66:L97" si="22">G66</f>
         <v>4000</v>
       </c>
       <c r="M66" s="17">
-        <f>(1-$D66)*H66</f>
+        <f t="shared" ref="M66:M97" si="23">(1-$D66)*H66</f>
         <v>1000</v>
       </c>
       <c r="N66" s="17">
-        <f>(1-$D66)*I66</f>
+        <f t="shared" ref="N66:N97" si="24">(1-$D66)*I66</f>
         <v>0</v>
       </c>
       <c r="O66" s="17">
@@ -8222,26 +8222,26 @@
         <v>1000</v>
       </c>
       <c r="Z66" s="17">
-        <f>SUM(J66:Y66)</f>
+        <f t="shared" ref="Z66:Z97" si="25">SUM(J66:Y66)</f>
         <v>76340</v>
       </c>
       <c r="AA66" s="17">
         <v>0</v>
       </c>
       <c r="AB66" s="14">
-        <f>Z66-AA66</f>
+        <f t="shared" ref="AB66:AB97" si="26">Z66-AA66</f>
         <v>76340</v>
       </c>
       <c r="AC66" s="17" t="str">
-        <f>IF(AND($T66=6000, ($T66+$W66-$AB66)&gt;=6000),T66,"")</f>
+        <f t="shared" ref="AC66:AC97" si="27">IF(AND($T66=6000, ($T66+$W66-$AB66)&gt;=6000),T66,"")</f>
         <v/>
       </c>
       <c r="AD66" s="17" t="str">
-        <f>IF(AND($T66=8000, ($T66+$W66-$AB66)&gt;=8000),T66,"")</f>
+        <f t="shared" ref="AD66:AD97" si="28">IF(AND($T66=8000, ($T66+$W66-$AB66)&gt;=8000),T66,"")</f>
         <v/>
       </c>
       <c r="AE66" s="17" t="str">
-        <f>IF(($T66+$W66-$AB66)&gt;=$T66+8000,W66,"")</f>
+        <f t="shared" ref="AE66:AE97" si="29">IF(($T66+$W66-$AB66)&gt;=$T66+8000,W66,"")</f>
         <v/>
       </c>
     </row>
@@ -8274,23 +8274,23 @@
         <v>0</v>
       </c>
       <c r="J67" s="17">
-        <f>(1-$D67)*E67</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="K67" s="17">
-        <f>(1-$D67)*F67</f>
+        <f t="shared" si="21"/>
         <v>19500</v>
       </c>
       <c r="L67" s="17">
-        <f>G67</f>
+        <f t="shared" si="22"/>
         <v>4000</v>
       </c>
       <c r="M67" s="17">
-        <f>(1-$D67)*H67</f>
+        <f t="shared" si="23"/>
         <v>750</v>
       </c>
       <c r="N67" s="17">
-        <f>(1-$D67)*I67</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="O67" s="17">
@@ -8327,26 +8327,26 @@
         <v>0</v>
       </c>
       <c r="Z67" s="17">
-        <f>SUM(J67:Y67)</f>
+        <f t="shared" si="25"/>
         <v>68590</v>
       </c>
       <c r="AA67" s="17">
         <v>0</v>
       </c>
       <c r="AB67" s="14">
-        <f>Z67-AA67</f>
+        <f t="shared" si="26"/>
         <v>68590</v>
       </c>
       <c r="AC67" s="17" t="str">
-        <f>IF(AND($T67=6000, ($T67+$W67-$AB67)&gt;=6000),T67,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AD67" s="17" t="str">
-        <f>IF(AND($T67=8000, ($T67+$W67-$AB67)&gt;=8000),T67,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AE67" s="17" t="str">
-        <f>IF(($T67+$W67-$AB67)&gt;=$T67+8000,W67,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -8379,23 +8379,23 @@
         <v>0</v>
       </c>
       <c r="J68" s="17">
-        <f>(1-$D68)*E68</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="K68" s="17">
-        <f>(1-$D68)*F68</f>
+        <f t="shared" si="21"/>
         <v>19500</v>
       </c>
       <c r="L68" s="17">
-        <f>G68</f>
+        <f t="shared" si="22"/>
         <v>4000</v>
       </c>
       <c r="M68" s="17">
-        <f>(1-$D68)*H68</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="N68" s="17">
-        <f>(1-$D68)*I68</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="O68" s="17">
@@ -8432,26 +8432,26 @@
         <v>0</v>
       </c>
       <c r="Z68" s="17">
-        <f>SUM(J68:Y68)</f>
+        <f t="shared" si="25"/>
         <v>43290</v>
       </c>
       <c r="AA68" s="17">
         <v>0</v>
       </c>
       <c r="AB68" s="14">
-        <f>Z68-AA68</f>
+        <f t="shared" si="26"/>
         <v>43290</v>
       </c>
       <c r="AC68" s="17" t="str">
-        <f>IF(AND($T68=6000, ($T68+$W68-$AB68)&gt;=6000),T68,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AD68" s="17" t="str">
-        <f>IF(AND($T68=8000, ($T68+$W68-$AB68)&gt;=8000),T68,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AE68" s="17" t="str">
-        <f>IF(($T68+$W68-$AB68)&gt;=$T68+8000,W68,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -8484,23 +8484,23 @@
         <v>0</v>
       </c>
       <c r="J69" s="17">
-        <f>(1-$D69)*E69</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="K69" s="17">
-        <f>(1-$D69)*F69</f>
+        <f t="shared" si="21"/>
         <v>19500</v>
       </c>
       <c r="L69" s="17">
-        <f>G69</f>
+        <f t="shared" si="22"/>
         <v>4000</v>
       </c>
       <c r="M69" s="17">
-        <f>(1-$D69)*H69</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="N69" s="17">
-        <f>(1-$D69)*I69</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="O69" s="17">
@@ -8537,26 +8537,26 @@
         <v>-90</v>
       </c>
       <c r="Z69" s="17">
-        <f>SUM(J69:Y69)</f>
+        <f t="shared" si="25"/>
         <v>49200</v>
       </c>
       <c r="AA69" s="17">
         <v>0</v>
       </c>
       <c r="AB69" s="14">
-        <f>Z69-AA69</f>
+        <f t="shared" si="26"/>
         <v>49200</v>
       </c>
       <c r="AC69" s="17" t="str">
-        <f>IF(AND($T69=6000, ($T69+$W69-$AB69)&gt;=6000),T69,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AD69" s="17" t="str">
-        <f>IF(AND($T69=8000, ($T69+$W69-$AB69)&gt;=8000),T69,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AE69" s="17" t="str">
-        <f>IF(($T69+$W69-$AB69)&gt;=$T69+8000,W69,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -8589,23 +8589,23 @@
         <v>0</v>
       </c>
       <c r="J70" s="17">
-        <f>(1-$D70)*E70</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="K70" s="17">
-        <f>(1-$D70)*F70</f>
+        <f t="shared" si="21"/>
         <v>19500</v>
       </c>
       <c r="L70" s="17">
-        <f>G70</f>
+        <f t="shared" si="22"/>
         <v>4000</v>
       </c>
       <c r="M70" s="17">
-        <f>(1-$D70)*H70</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="N70" s="17">
-        <f>(1-$D70)*I70</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="O70" s="17">
@@ -8642,26 +8642,26 @@
         <v>0</v>
       </c>
       <c r="Z70" s="17">
-        <f>SUM(J70:Y70)</f>
+        <f t="shared" si="25"/>
         <v>43290</v>
       </c>
       <c r="AA70" s="17">
         <v>0</v>
       </c>
       <c r="AB70" s="14">
-        <f>Z70-AA70</f>
+        <f t="shared" si="26"/>
         <v>43290</v>
       </c>
       <c r="AC70" s="17" t="str">
-        <f>IF(AND($T70=6000, ($T70+$W70-$AB70)&gt;=6000),T70,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AD70" s="17" t="str">
-        <f>IF(AND($T70=8000, ($T70+$W70-$AB70)&gt;=8000),T70,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AE70" s="17" t="str">
-        <f>IF(($T70+$W70-$AB70)&gt;=$T70+8000,W70,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -8694,23 +8694,23 @@
         <v>0</v>
       </c>
       <c r="J71" s="17">
-        <f>(1-$D71)*E71</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="K71" s="17">
-        <f>(1-$D71)*F71</f>
+        <f t="shared" si="21"/>
         <v>19500</v>
       </c>
       <c r="L71" s="17">
-        <f>G71</f>
+        <f t="shared" si="22"/>
         <v>4000</v>
       </c>
       <c r="M71" s="17">
-        <f>(1-$D71)*H71</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="N71" s="17">
-        <f>(1-$D71)*I71</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="O71" s="17">
@@ -8747,26 +8747,26 @@
         <v>0</v>
       </c>
       <c r="Z71" s="17">
-        <f>SUM(J71:Y71)</f>
+        <f t="shared" si="25"/>
         <v>43290</v>
       </c>
       <c r="AA71" s="17">
         <v>0</v>
       </c>
       <c r="AB71" s="14">
-        <f>Z71-AA71</f>
+        <f t="shared" si="26"/>
         <v>43290</v>
       </c>
       <c r="AC71" s="17" t="str">
-        <f>IF(AND($T71=6000, ($T71+$W71-$AB71)&gt;=6000),T71,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AD71" s="17" t="str">
-        <f>IF(AND($T71=8000, ($T71+$W71-$AB71)&gt;=8000),T71,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AE71" s="17" t="str">
-        <f>IF(($T71+$W71-$AB71)&gt;=$T71+8000,W71,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -8799,23 +8799,23 @@
         <v>0</v>
       </c>
       <c r="J72" s="17">
-        <f>(1-$D72)*E72</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="K72" s="17">
-        <f>(1-$D72)*F72</f>
+        <f t="shared" si="21"/>
         <v>26000</v>
       </c>
       <c r="L72" s="17">
-        <f>G72</f>
+        <f t="shared" si="22"/>
         <v>4000</v>
       </c>
       <c r="M72" s="17">
-        <f>(1-$D72)*H72</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="N72" s="17">
-        <f>(1-$D72)*I72</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="O72" s="17">
@@ -8852,26 +8852,26 @@
         <v>-400</v>
       </c>
       <c r="Z72" s="17">
-        <f>SUM(J72:Y72)</f>
+        <f t="shared" si="25"/>
         <v>55390</v>
       </c>
       <c r="AA72" s="17">
         <v>0</v>
       </c>
       <c r="AB72" s="14">
-        <f>Z72-AA72</f>
+        <f t="shared" si="26"/>
         <v>55390</v>
       </c>
       <c r="AC72" s="17" t="str">
-        <f>IF(AND($T72=6000, ($T72+$W72-$AB72)&gt;=6000),T72,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AD72" s="17" t="str">
-        <f>IF(AND($T72=8000, ($T72+$W72-$AB72)&gt;=8000),T72,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AE72" s="17" t="str">
-        <f>IF(($T72+$W72-$AB72)&gt;=$T72+8000,W72,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -8904,23 +8904,23 @@
         <v>0</v>
       </c>
       <c r="J73" s="17">
-        <f>(1-$D73)*E73</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="K73" s="17">
-        <f>(1-$D73)*F73</f>
+        <f t="shared" si="21"/>
         <v>26000</v>
       </c>
       <c r="L73" s="17">
-        <f>G73</f>
+        <f t="shared" si="22"/>
         <v>4000</v>
       </c>
       <c r="M73" s="17">
-        <f>(1-$D73)*H73</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="N73" s="17">
-        <f>(1-$D73)*I73</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="O73" s="17">
@@ -8957,26 +8957,26 @@
         <v>11000</v>
       </c>
       <c r="Z73" s="17">
-        <f>SUM(J73:Y73)</f>
+        <f t="shared" si="25"/>
         <v>60790</v>
       </c>
       <c r="AA73" s="17">
         <v>0</v>
       </c>
       <c r="AB73" s="14">
-        <f>Z73-AA73</f>
+        <f t="shared" si="26"/>
         <v>60790</v>
       </c>
       <c r="AC73" s="17" t="str">
-        <f>IF(AND($T73=6000, ($T73+$W73-$AB73)&gt;=6000),T73,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AD73" s="17" t="str">
-        <f>IF(AND($T73=8000, ($T73+$W73-$AB73)&gt;=8000),T73,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AE73" s="17" t="str">
-        <f>IF(($T73+$W73-$AB73)&gt;=$T73+8000,W73,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -9009,23 +9009,23 @@
         <v>0</v>
       </c>
       <c r="J74" s="17">
-        <f>(1-$D74)*E74</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="K74" s="17">
-        <f>(1-$D74)*F74</f>
+        <f t="shared" si="21"/>
         <v>26000</v>
       </c>
       <c r="L74" s="17">
-        <f>G74</f>
+        <f t="shared" si="22"/>
         <v>4000</v>
       </c>
       <c r="M74" s="17">
-        <f>(1-$D74)*H74</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="N74" s="17">
-        <f>(1-$D74)*I74</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="O74" s="17">
@@ -9062,26 +9062,26 @@
         <v>0</v>
       </c>
       <c r="Z74" s="17">
-        <f>SUM(J74:Y74)</f>
+        <f t="shared" si="25"/>
         <v>49790</v>
       </c>
       <c r="AA74" s="17">
         <v>0</v>
       </c>
       <c r="AB74" s="14">
-        <f>Z74-AA74</f>
+        <f t="shared" si="26"/>
         <v>49790</v>
       </c>
       <c r="AC74" s="17" t="str">
-        <f>IF(AND($T74=6000, ($T74+$W74-$AB74)&gt;=6000),T74,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AD74" s="17" t="str">
-        <f>IF(AND($T74=8000, ($T74+$W74-$AB74)&gt;=8000),T74,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AE74" s="17" t="str">
-        <f>IF(($T74+$W74-$AB74)&gt;=$T74+8000,W74,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -9114,23 +9114,23 @@
         <v>0</v>
       </c>
       <c r="J75" s="17">
-        <f>(1-$D75)*E75</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="K75" s="17">
-        <f>(1-$D75)*F75</f>
+        <f t="shared" si="21"/>
         <v>19500</v>
       </c>
       <c r="L75" s="17">
-        <f>G75</f>
+        <f t="shared" si="22"/>
         <v>4000</v>
       </c>
       <c r="M75" s="17">
-        <f>(1-$D75)*H75</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="N75" s="17">
-        <f>(1-$D75)*I75</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="O75" s="17">
@@ -9167,26 +9167,26 @@
         <v>65</v>
       </c>
       <c r="Z75" s="17">
-        <f>SUM(J75:Y75)</f>
+        <f t="shared" si="25"/>
         <v>49355</v>
       </c>
       <c r="AA75" s="17">
         <v>0</v>
       </c>
       <c r="AB75" s="14">
-        <f>Z75-AA75</f>
+        <f t="shared" si="26"/>
         <v>49355</v>
       </c>
       <c r="AC75" s="17" t="str">
-        <f>IF(AND($T75=6000, ($T75+$W75-$AB75)&gt;=6000),T75,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AD75" s="17" t="str">
-        <f>IF(AND($T75=8000, ($T75+$W75-$AB75)&gt;=8000),T75,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AE75" s="17" t="str">
-        <f>IF(($T75+$W75-$AB75)&gt;=$T75+8000,W75,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -9219,23 +9219,23 @@
         <v>0</v>
       </c>
       <c r="J76" s="17">
-        <f>(1-$D76)*E76</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="K76" s="17">
-        <f>(1-$D76)*F76</f>
+        <f t="shared" si="21"/>
         <v>19500</v>
       </c>
       <c r="L76" s="17">
-        <f>G76</f>
+        <f t="shared" si="22"/>
         <v>4000</v>
       </c>
       <c r="M76" s="17">
-        <f>(1-$D76)*H76</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="N76" s="17">
-        <f>(1-$D76)*I76</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="O76" s="17">
@@ -9272,26 +9272,26 @@
         <v>1250</v>
       </c>
       <c r="Z76" s="17">
-        <f>SUM(J76:Y76)</f>
+        <f t="shared" si="25"/>
         <v>50540</v>
       </c>
       <c r="AA76" s="17">
         <v>0</v>
       </c>
       <c r="AB76" s="14">
-        <f>Z76-AA76</f>
+        <f t="shared" si="26"/>
         <v>50540</v>
       </c>
       <c r="AC76" s="17" t="str">
-        <f>IF(AND($T76=6000, ($T76+$W76-$AB76)&gt;=6000),T76,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AD76" s="17" t="str">
-        <f>IF(AND($T76=8000, ($T76+$W76-$AB76)&gt;=8000),T76,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AE76" s="17" t="str">
-        <f>IF(($T76+$W76-$AB76)&gt;=$T76+8000,W76,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -9324,23 +9324,23 @@
         <v>0</v>
       </c>
       <c r="J77" s="17">
-        <f>(1-$D77)*E77</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="K77" s="17">
-        <f>(1-$D77)*F77</f>
+        <f t="shared" si="21"/>
         <v>19500</v>
       </c>
       <c r="L77" s="17">
-        <f>G77</f>
+        <f t="shared" si="22"/>
         <v>4000</v>
       </c>
       <c r="M77" s="17">
-        <f>(1-$D77)*H77</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="N77" s="17">
-        <f>(1-$D77)*I77</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="O77" s="17">
@@ -9377,26 +9377,26 @@
         <v>0</v>
       </c>
       <c r="Z77" s="17">
-        <f>SUM(J77:Y77)</f>
+        <f t="shared" si="25"/>
         <v>43290</v>
       </c>
       <c r="AA77" s="17">
         <v>0</v>
       </c>
       <c r="AB77" s="14">
-        <f>Z77-AA77</f>
+        <f t="shared" si="26"/>
         <v>43290</v>
       </c>
       <c r="AC77" s="17" t="str">
-        <f>IF(AND($T77=6000, ($T77+$W77-$AB77)&gt;=6000),T77,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AD77" s="17" t="str">
-        <f>IF(AND($T77=8000, ($T77+$W77-$AB77)&gt;=8000),T77,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AE77" s="17" t="str">
-        <f>IF(($T77+$W77-$AB77)&gt;=$T77+8000,W77,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -9423,29 +9423,29 @@
         <v>4000</v>
       </c>
       <c r="H78" s="17">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="I78" s="17">
         <v>5000</v>
       </c>
       <c r="J78" s="17">
-        <f>(1-$D78)*E78</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="K78" s="17">
-        <f>(1-$D78)*F78</f>
+        <f t="shared" si="21"/>
         <v>21000</v>
       </c>
       <c r="L78" s="17">
-        <f>G78</f>
+        <f t="shared" si="22"/>
         <v>4000</v>
       </c>
       <c r="M78" s="17">
-        <f>(1-$D78)*H78</f>
-        <v>0</v>
+        <f t="shared" si="23"/>
+        <v>1875</v>
       </c>
       <c r="N78" s="17">
-        <f>(1-$D78)*I78</f>
+        <f t="shared" si="24"/>
         <v>3750</v>
       </c>
       <c r="O78" s="17">
@@ -9482,26 +9482,26 @@
         <v>0</v>
       </c>
       <c r="Z78" s="17">
-        <f>SUM(J78:Y78)</f>
-        <v>71970</v>
+        <f t="shared" si="25"/>
+        <v>73845</v>
       </c>
       <c r="AA78" s="17">
         <v>0</v>
       </c>
       <c r="AB78" s="14">
-        <f>Z78-AA78</f>
-        <v>71970</v>
+        <f t="shared" si="26"/>
+        <v>73845</v>
       </c>
       <c r="AC78" s="17" t="str">
-        <f>IF(AND($T78=6000, ($T78+$W78-$AB78)&gt;=6000),T78,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AD78" s="17" t="str">
-        <f>IF(AND($T78=8000, ($T78+$W78-$AB78)&gt;=8000),T78,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AE78" s="17" t="str">
-        <f>IF(($T78+$W78-$AB78)&gt;=$T78+8000,W78,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -9528,29 +9528,29 @@
         <v>4000</v>
       </c>
       <c r="H79" s="17">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="I79" s="17">
         <v>5000</v>
       </c>
       <c r="J79" s="17">
-        <f>(1-$D79)*E79</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="K79" s="17">
-        <f>(1-$D79)*F79</f>
+        <f t="shared" si="21"/>
         <v>28000</v>
       </c>
       <c r="L79" s="17">
-        <f>G79</f>
+        <f t="shared" si="22"/>
         <v>4000</v>
       </c>
       <c r="M79" s="17">
-        <f>(1-$D79)*H79</f>
-        <v>0</v>
+        <f t="shared" si="23"/>
+        <v>2500</v>
       </c>
       <c r="N79" s="17">
-        <f>(1-$D79)*I79</f>
+        <f t="shared" si="24"/>
         <v>5000</v>
       </c>
       <c r="O79" s="17">
@@ -9587,26 +9587,26 @@
         <v>0</v>
       </c>
       <c r="Z79" s="17">
-        <f>SUM(J79:Y79)</f>
-        <v>80220</v>
+        <f t="shared" si="25"/>
+        <v>82720</v>
       </c>
       <c r="AA79" s="17">
         <v>0</v>
       </c>
       <c r="AB79" s="14">
-        <f>Z79-AA79</f>
-        <v>80220</v>
+        <f t="shared" si="26"/>
+        <v>82720</v>
       </c>
       <c r="AC79" s="17" t="str">
-        <f>IF(AND($T79=6000, ($T79+$W79-$AB79)&gt;=6000),T79,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AD79" s="17" t="str">
-        <f>IF(AND($T79=8000, ($T79+$W79-$AB79)&gt;=8000),T79,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AE79" s="17" t="str">
-        <f>IF(($T79+$W79-$AB79)&gt;=$T79+8000,W79,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -9633,29 +9633,29 @@
         <v>4000</v>
       </c>
       <c r="H80" s="17">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="I80" s="17">
         <v>5000</v>
       </c>
       <c r="J80" s="17">
-        <f>(1-$D80)*E80</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="K80" s="17">
-        <f>(1-$D80)*F80</f>
+        <f t="shared" si="21"/>
         <v>28000</v>
       </c>
       <c r="L80" s="17">
-        <f>G80</f>
+        <f t="shared" si="22"/>
         <v>4000</v>
       </c>
       <c r="M80" s="17">
-        <f>(1-$D80)*H80</f>
-        <v>0</v>
+        <f t="shared" si="23"/>
+        <v>2500</v>
       </c>
       <c r="N80" s="17">
-        <f>(1-$D80)*I80</f>
+        <f t="shared" si="24"/>
         <v>5000</v>
       </c>
       <c r="O80" s="17">
@@ -9692,26 +9692,26 @@
         <v>0</v>
       </c>
       <c r="Z80" s="17">
-        <f>SUM(J80:Y80)</f>
-        <v>74220</v>
+        <f t="shared" si="25"/>
+        <v>76720</v>
       </c>
       <c r="AA80" s="17">
         <v>0</v>
       </c>
       <c r="AB80" s="14">
-        <f>Z80-AA80</f>
-        <v>74220</v>
+        <f t="shared" si="26"/>
+        <v>76720</v>
       </c>
       <c r="AC80" s="17" t="str">
-        <f>IF(AND($T80=6000, ($T80+$W80-$AB80)&gt;=6000),T80,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AD80" s="17" t="str">
-        <f>IF(AND($T80=8000, ($T80+$W80-$AB80)&gt;=8000),T80,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AE80" s="17" t="str">
-        <f>IF(($T80+$W80-$AB80)&gt;=$T80+8000,W80,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -9738,29 +9738,29 @@
         <v>4000</v>
       </c>
       <c r="H81" s="17">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="I81" s="17">
         <v>5000</v>
       </c>
       <c r="J81" s="17">
-        <f>(1-$D81)*E81</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="K81" s="17">
-        <f>(1-$D81)*F81</f>
+        <f t="shared" si="21"/>
         <v>28000</v>
       </c>
       <c r="L81" s="17">
-        <f>G81</f>
+        <f t="shared" si="22"/>
         <v>4000</v>
       </c>
       <c r="M81" s="17">
-        <f>(1-$D81)*H81</f>
-        <v>0</v>
+        <f t="shared" si="23"/>
+        <v>2500</v>
       </c>
       <c r="N81" s="17">
-        <f>(1-$D81)*I81</f>
+        <f t="shared" si="24"/>
         <v>5000</v>
       </c>
       <c r="O81" s="17">
@@ -9797,26 +9797,26 @@
         <v>550</v>
       </c>
       <c r="Z81" s="17">
-        <f>SUM(J81:Y81)</f>
-        <v>74770</v>
+        <f t="shared" si="25"/>
+        <v>77270</v>
       </c>
       <c r="AA81" s="17">
         <v>0</v>
       </c>
       <c r="AB81" s="14">
-        <f>Z81-AA81</f>
-        <v>74770</v>
+        <f t="shared" si="26"/>
+        <v>77270</v>
       </c>
       <c r="AC81" s="17" t="str">
-        <f>IF(AND($T81=6000, ($T81+$W81-$AB81)&gt;=6000),T81,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AD81" s="17" t="str">
-        <f>IF(AND($T81=8000, ($T81+$W81-$AB81)&gt;=8000),T81,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AE81" s="17" t="str">
-        <f>IF(($T81+$W81-$AB81)&gt;=$T81+8000,W81,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -9843,29 +9843,29 @@
         <v>4000</v>
       </c>
       <c r="H82" s="17">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="I82" s="17">
         <v>5000</v>
       </c>
       <c r="J82" s="17">
-        <f>(1-$D82)*E82</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="K82" s="17">
-        <f>(1-$D82)*F82</f>
+        <f t="shared" si="21"/>
         <v>21000</v>
       </c>
       <c r="L82" s="17">
-        <f>G82</f>
+        <f t="shared" si="22"/>
         <v>4000</v>
       </c>
       <c r="M82" s="17">
-        <f>(1-$D82)*H82</f>
-        <v>0</v>
+        <f t="shared" si="23"/>
+        <v>1875</v>
       </c>
       <c r="N82" s="17">
-        <f>(1-$D82)*I82</f>
+        <f t="shared" si="24"/>
         <v>3750</v>
       </c>
       <c r="O82" s="17">
@@ -9902,26 +9902,26 @@
         <v>0</v>
       </c>
       <c r="Z82" s="17">
-        <f>SUM(J82:Y82)</f>
-        <v>65970</v>
+        <f t="shared" si="25"/>
+        <v>67845</v>
       </c>
       <c r="AA82" s="17">
         <v>0</v>
       </c>
       <c r="AB82" s="14">
-        <f>Z82-AA82</f>
-        <v>65970</v>
+        <f t="shared" si="26"/>
+        <v>67845</v>
       </c>
       <c r="AC82" s="17" t="str">
-        <f>IF(AND($T82=6000, ($T82+$W82-$AB82)&gt;=6000),T82,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AD82" s="17" t="str">
-        <f>IF(AND($T82=8000, ($T82+$W82-$AB82)&gt;=8000),T82,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AE82" s="17" t="str">
-        <f>IF(($T82+$W82-$AB82)&gt;=$T82+8000,W82,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -9948,29 +9948,29 @@
         <v>4000</v>
       </c>
       <c r="H83" s="17">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="I83" s="17">
         <v>5000</v>
       </c>
       <c r="J83" s="17">
-        <f>(1-$D83)*E83</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="K83" s="17">
-        <f>(1-$D83)*F83</f>
+        <f t="shared" si="21"/>
         <v>21000</v>
       </c>
       <c r="L83" s="17">
-        <f>G83</f>
+        <f t="shared" si="22"/>
         <v>4000</v>
       </c>
       <c r="M83" s="17">
-        <f>(1-$D83)*H83</f>
-        <v>0</v>
+        <f t="shared" si="23"/>
+        <v>1875</v>
       </c>
       <c r="N83" s="17">
-        <f>(1-$D83)*I83</f>
+        <f t="shared" si="24"/>
         <v>3750</v>
       </c>
       <c r="O83" s="17">
@@ -10007,26 +10007,26 @@
         <v>0</v>
       </c>
       <c r="Z83" s="17">
-        <f>SUM(J83:Y83)</f>
-        <v>71970</v>
+        <f t="shared" si="25"/>
+        <v>73845</v>
       </c>
       <c r="AA83" s="17">
         <v>0</v>
       </c>
       <c r="AB83" s="14">
-        <f>Z83-AA83</f>
-        <v>71970</v>
+        <f t="shared" si="26"/>
+        <v>73845</v>
       </c>
       <c r="AC83" s="17" t="str">
-        <f>IF(AND($T83=6000, ($T83+$W83-$AB83)&gt;=6000),T83,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AD83" s="17" t="str">
-        <f>IF(AND($T83=8000, ($T83+$W83-$AB83)&gt;=8000),T83,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AE83" s="17" t="str">
-        <f>IF(($T83+$W83-$AB83)&gt;=$T83+8000,W83,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -10053,29 +10053,29 @@
         <v>4000</v>
       </c>
       <c r="H84" s="17">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="I84" s="17">
         <v>5000</v>
       </c>
       <c r="J84" s="17">
-        <f>(1-$D84)*E84</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="K84" s="17">
-        <f>(1-$D84)*F84</f>
+        <f t="shared" si="21"/>
         <v>28000</v>
       </c>
       <c r="L84" s="17">
-        <f>G84</f>
+        <f t="shared" si="22"/>
         <v>4000</v>
       </c>
       <c r="M84" s="17">
-        <f>(1-$D84)*H84</f>
-        <v>0</v>
+        <f t="shared" si="23"/>
+        <v>2500</v>
       </c>
       <c r="N84" s="17">
-        <f>(1-$D84)*I84</f>
+        <f t="shared" si="24"/>
         <v>5000</v>
       </c>
       <c r="O84" s="17">
@@ -10112,26 +10112,26 @@
         <v>0</v>
       </c>
       <c r="Z84" s="17">
-        <f>SUM(J84:Y84)</f>
-        <v>74220</v>
+        <f t="shared" si="25"/>
+        <v>76720</v>
       </c>
       <c r="AA84" s="17">
         <v>0</v>
       </c>
       <c r="AB84" s="14">
-        <f>Z84-AA84</f>
-        <v>74220</v>
+        <f t="shared" si="26"/>
+        <v>76720</v>
       </c>
       <c r="AC84" s="17" t="str">
-        <f>IF(AND($T84=6000, ($T84+$W84-$AB84)&gt;=6000),T84,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AD84" s="17" t="str">
-        <f>IF(AND($T84=8000, ($T84+$W84-$AB84)&gt;=8000),T84,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AE84" s="17" t="str">
-        <f>IF(($T84+$W84-$AB84)&gt;=$T84+8000,W84,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -10158,29 +10158,29 @@
         <v>4000</v>
       </c>
       <c r="H85" s="17">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="I85" s="17">
         <v>5000</v>
       </c>
       <c r="J85" s="17">
-        <f>(1-$D85)*E85</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="K85" s="17">
-        <f>(1-$D85)*F85</f>
+        <f t="shared" si="21"/>
         <v>21000</v>
       </c>
       <c r="L85" s="17">
-        <f>G85</f>
+        <f t="shared" si="22"/>
         <v>4000</v>
       </c>
       <c r="M85" s="17">
-        <f>(1-$D85)*H85</f>
-        <v>0</v>
+        <f t="shared" si="23"/>
+        <v>1875</v>
       </c>
       <c r="N85" s="17">
-        <f>(1-$D85)*I85</f>
+        <f t="shared" si="24"/>
         <v>3750</v>
       </c>
       <c r="O85" s="17">
@@ -10217,26 +10217,26 @@
         <v>0</v>
       </c>
       <c r="Z85" s="17">
-        <f>SUM(J85:Y85)</f>
-        <v>71970</v>
+        <f t="shared" si="25"/>
+        <v>73845</v>
       </c>
       <c r="AA85" s="17">
         <v>0</v>
       </c>
       <c r="AB85" s="14">
-        <f>Z85-AA85</f>
-        <v>71970</v>
+        <f t="shared" si="26"/>
+        <v>73845</v>
       </c>
       <c r="AC85" s="17" t="str">
-        <f>IF(AND($T85=6000, ($T85+$W85-$AB85)&gt;=6000),T85,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AD85" s="17" t="str">
-        <f>IF(AND($T85=8000, ($T85+$W85-$AB85)&gt;=8000),T85,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AE85" s="17" t="str">
-        <f>IF(($T85+$W85-$AB85)&gt;=$T85+8000,W85,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -10263,29 +10263,29 @@
         <v>4000</v>
       </c>
       <c r="H86" s="17">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="I86" s="17">
         <v>5000</v>
       </c>
       <c r="J86" s="17">
-        <f>(1-$D86)*E86</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="K86" s="17">
-        <f>(1-$D86)*F86</f>
+        <f t="shared" si="21"/>
         <v>21000</v>
       </c>
       <c r="L86" s="17">
-        <f>G86</f>
+        <f t="shared" si="22"/>
         <v>4000</v>
       </c>
       <c r="M86" s="17">
-        <f>(1-$D86)*H86</f>
-        <v>0</v>
+        <f t="shared" si="23"/>
+        <v>1875</v>
       </c>
       <c r="N86" s="17">
-        <f>(1-$D86)*I86</f>
+        <f t="shared" si="24"/>
         <v>3750</v>
       </c>
       <c r="O86" s="17">
@@ -10322,26 +10322,26 @@
         <v>9500</v>
       </c>
       <c r="Z86" s="17">
-        <f>SUM(J86:Y86)</f>
-        <v>81470</v>
+        <f t="shared" si="25"/>
+        <v>83345</v>
       </c>
       <c r="AA86" s="17">
         <v>0</v>
       </c>
       <c r="AB86" s="14">
-        <f>Z86-AA86</f>
-        <v>81470</v>
+        <f t="shared" si="26"/>
+        <v>83345</v>
       </c>
       <c r="AC86" s="17" t="str">
-        <f>IF(AND($T86=6000, ($T86+$W86-$AB86)&gt;=6000),T86,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AD86" s="17" t="str">
-        <f>IF(AND($T86=8000, ($T86+$W86-$AB86)&gt;=8000),T86,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AE86" s="17" t="str">
-        <f>IF(($T86+$W86-$AB86)&gt;=$T86+8000,W86,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -10374,23 +10374,23 @@
         <v>5000</v>
       </c>
       <c r="J87" s="17">
-        <f>(1-$D87)*E87</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="K87" s="17">
-        <f>(1-$D87)*F87</f>
+        <f t="shared" si="21"/>
         <v>21000</v>
       </c>
       <c r="L87" s="17">
-        <f>G87</f>
+        <f t="shared" si="22"/>
         <v>4000</v>
       </c>
       <c r="M87" s="17">
-        <f>(1-$D87)*H87</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="N87" s="17">
-        <f>(1-$D87)*I87</f>
+        <f t="shared" si="24"/>
         <v>3750</v>
       </c>
       <c r="O87" s="17">
@@ -10427,26 +10427,26 @@
         <v>125</v>
       </c>
       <c r="Z87" s="17">
-        <f>SUM(J87:Y87)</f>
+        <f t="shared" si="25"/>
         <v>72095</v>
       </c>
       <c r="AA87" s="17">
         <v>0</v>
       </c>
       <c r="AB87" s="14">
-        <f>Z87-AA87</f>
+        <f t="shared" si="26"/>
         <v>72095</v>
       </c>
       <c r="AC87" s="17" t="str">
-        <f>IF(AND($T87=6000, ($T87+$W87-$AB87)&gt;=6000),T87,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AD87" s="17" t="str">
-        <f>IF(AND($T87=8000, ($T87+$W87-$AB87)&gt;=8000),T87,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AE87" s="17" t="str">
-        <f>IF(($T87+$W87-$AB87)&gt;=$T87+8000,W87,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -10479,23 +10479,23 @@
         <v>5000</v>
       </c>
       <c r="J88" s="17">
-        <f>(1-$D88)*E88</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="K88" s="17">
-        <f>(1-$D88)*F88</f>
+        <f t="shared" si="21"/>
         <v>21000</v>
       </c>
       <c r="L88" s="17">
-        <f>G88</f>
+        <f t="shared" si="22"/>
         <v>4000</v>
       </c>
       <c r="M88" s="17">
-        <f>(1-$D88)*H88</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="N88" s="17">
-        <f>(1-$D88)*I88</f>
+        <f t="shared" si="24"/>
         <v>3750</v>
       </c>
       <c r="O88" s="17">
@@ -10532,26 +10532,26 @@
         <v>0</v>
       </c>
       <c r="Z88" s="17">
-        <f>SUM(J88:Y88)</f>
+        <f t="shared" si="25"/>
         <v>65970</v>
       </c>
       <c r="AA88" s="17">
         <v>0</v>
       </c>
       <c r="AB88" s="14">
-        <f>Z88-AA88</f>
+        <f t="shared" si="26"/>
         <v>65970</v>
       </c>
       <c r="AC88" s="17" t="str">
-        <f>IF(AND($T88=6000, ($T88+$W88-$AB88)&gt;=6000),T88,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AD88" s="17" t="str">
-        <f>IF(AND($T88=8000, ($T88+$W88-$AB88)&gt;=8000),T88,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AE88" s="17" t="str">
-        <f>IF(($T88+$W88-$AB88)&gt;=$T88+8000,W88,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -10584,23 +10584,23 @@
         <v>5000</v>
       </c>
       <c r="J89" s="17">
-        <f>(1-$D89)*E89</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="K89" s="17">
-        <f>(1-$D89)*F89</f>
+        <f t="shared" si="21"/>
         <v>21000</v>
       </c>
       <c r="L89" s="17">
-        <f>G89</f>
+        <f t="shared" si="22"/>
         <v>4000</v>
       </c>
       <c r="M89" s="17">
-        <f>(1-$D89)*H89</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="N89" s="17">
-        <f>(1-$D89)*I89</f>
+        <f t="shared" si="24"/>
         <v>3750</v>
       </c>
       <c r="O89" s="17">
@@ -10637,26 +10637,26 @@
         <v>0</v>
       </c>
       <c r="Z89" s="17">
-        <f>SUM(J89:Y89)</f>
+        <f t="shared" si="25"/>
         <v>65970</v>
       </c>
       <c r="AA89" s="17">
         <v>0</v>
       </c>
       <c r="AB89" s="14">
-        <f>Z89-AA89</f>
+        <f t="shared" si="26"/>
         <v>65970</v>
       </c>
       <c r="AC89" s="17" t="str">
-        <f>IF(AND($T89=6000, ($T89+$W89-$AB89)&gt;=6000),T89,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AD89" s="17" t="str">
-        <f>IF(AND($T89=8000, ($T89+$W89-$AB89)&gt;=8000),T89,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AE89" s="17" t="str">
-        <f>IF(($T89+$W89-$AB89)&gt;=$T89+8000,W89,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -10689,23 +10689,23 @@
         <v>5000</v>
       </c>
       <c r="J90" s="17">
-        <f>(1-$D90)*E90</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="K90" s="17">
-        <f>(1-$D90)*F90</f>
+        <f t="shared" si="21"/>
         <v>21000</v>
       </c>
       <c r="L90" s="17">
-        <f>G90</f>
+        <f t="shared" si="22"/>
         <v>4000</v>
       </c>
       <c r="M90" s="17">
-        <f>(1-$D90)*H90</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="N90" s="17">
-        <f>(1-$D90)*I90</f>
+        <f t="shared" si="24"/>
         <v>3750</v>
       </c>
       <c r="O90" s="17">
@@ -10742,26 +10742,26 @@
         <v>250</v>
       </c>
       <c r="Z90" s="17">
-        <f>SUM(J90:Y90)</f>
+        <f t="shared" si="25"/>
         <v>72220</v>
       </c>
       <c r="AA90" s="17">
         <v>0</v>
       </c>
       <c r="AB90" s="14">
-        <f>Z90-AA90</f>
+        <f t="shared" si="26"/>
         <v>72220</v>
       </c>
       <c r="AC90" s="17" t="str">
-        <f>IF(AND($T90=6000, ($T90+$W90-$AB90)&gt;=6000),T90,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AD90" s="17" t="str">
-        <f>IF(AND($T90=8000, ($T90+$W90-$AB90)&gt;=8000),T90,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AE90" s="17" t="str">
-        <f>IF(($T90+$W90-$AB90)&gt;=$T90+8000,W90,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -10794,23 +10794,23 @@
         <v>5000</v>
       </c>
       <c r="J91" s="17">
-        <f>(1-$D91)*E91</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="K91" s="17">
-        <f>(1-$D91)*F91</f>
+        <f t="shared" si="21"/>
         <v>21000</v>
       </c>
       <c r="L91" s="17">
-        <f>G91</f>
+        <f t="shared" si="22"/>
         <v>4000</v>
       </c>
       <c r="M91" s="17">
-        <f>(1-$D91)*H91</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="N91" s="17">
-        <f>(1-$D91)*I91</f>
+        <f t="shared" si="24"/>
         <v>3750</v>
       </c>
       <c r="O91" s="17">
@@ -10847,26 +10847,26 @@
         <v>22105</v>
       </c>
       <c r="Z91" s="17">
-        <f>SUM(J91:Y91)</f>
+        <f t="shared" si="25"/>
         <v>94075</v>
       </c>
       <c r="AA91" s="17">
         <v>0</v>
       </c>
       <c r="AB91" s="14">
-        <f>Z91-AA91</f>
+        <f t="shared" si="26"/>
         <v>94075</v>
       </c>
       <c r="AC91" s="17" t="str">
-        <f>IF(AND($T91=6000, ($T91+$W91-$AB91)&gt;=6000),T91,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AD91" s="17" t="str">
-        <f>IF(AND($T91=8000, ($T91+$W91-$AB91)&gt;=8000),T91,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AE91" s="17" t="str">
-        <f>IF(($T91+$W91-$AB91)&gt;=$T91+8000,W91,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -10899,23 +10899,23 @@
         <v>5000</v>
       </c>
       <c r="J92" s="17">
-        <f>(1-$D92)*E92</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="K92" s="17">
-        <f>(1-$D92)*F92</f>
+        <f t="shared" si="21"/>
         <v>14000</v>
       </c>
       <c r="L92" s="17">
-        <f>G92</f>
+        <f t="shared" si="22"/>
         <v>4000</v>
       </c>
       <c r="M92" s="17">
-        <f>(1-$D92)*H92</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="N92" s="17">
-        <f>(1-$D92)*I92</f>
+        <f t="shared" si="24"/>
         <v>2500</v>
       </c>
       <c r="O92" s="17">
@@ -10952,26 +10952,26 @@
         <v>0</v>
       </c>
       <c r="Z92" s="17">
-        <f>SUM(J92:Y92)</f>
+        <f t="shared" si="25"/>
         <v>57720</v>
       </c>
       <c r="AA92" s="17">
         <v>0</v>
       </c>
       <c r="AB92" s="14">
-        <f>Z92-AA92</f>
+        <f t="shared" si="26"/>
         <v>57720</v>
       </c>
       <c r="AC92" s="17" t="str">
-        <f>IF(AND($T92=6000, ($T92+$W92-$AB92)&gt;=6000),T92,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AD92" s="17" t="str">
-        <f>IF(AND($T92=8000, ($T92+$W92-$AB92)&gt;=8000),T92,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AE92" s="17" t="str">
-        <f>IF(($T92+$W92-$AB92)&gt;=$T92+8000,W92,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -11004,23 +11004,23 @@
         <v>5000</v>
       </c>
       <c r="J93" s="17">
-        <f>(1-$D93)*E93</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="K93" s="17">
-        <f>(1-$D93)*F93</f>
+        <f t="shared" si="21"/>
         <v>21000</v>
       </c>
       <c r="L93" s="17">
-        <f>G93</f>
+        <f t="shared" si="22"/>
         <v>4000</v>
       </c>
       <c r="M93" s="17">
-        <f>(1-$D93)*H93</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="N93" s="17">
-        <f>(1-$D93)*I93</f>
+        <f t="shared" si="24"/>
         <v>3750</v>
       </c>
       <c r="O93" s="17">
@@ -11057,26 +11057,26 @@
         <v>0</v>
       </c>
       <c r="Z93" s="17">
-        <f>SUM(J93:Y93)</f>
+        <f t="shared" si="25"/>
         <v>65970</v>
       </c>
       <c r="AA93" s="17">
         <v>0</v>
       </c>
       <c r="AB93" s="14">
-        <f>Z93-AA93</f>
+        <f t="shared" si="26"/>
         <v>65970</v>
       </c>
       <c r="AC93" s="17" t="str">
-        <f>IF(AND($T93=6000, ($T93+$W93-$AB93)&gt;=6000),T93,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AD93" s="17" t="str">
-        <f>IF(AND($T93=8000, ($T93+$W93-$AB93)&gt;=8000),T93,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AE93" s="17" t="str">
-        <f>IF(($T93+$W93-$AB93)&gt;=$T93+8000,W93,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -11109,23 +11109,23 @@
         <v>5000</v>
       </c>
       <c r="J94" s="17">
-        <f>(1-$D94)*E94</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="K94" s="17">
-        <f>(1-$D94)*F94</f>
+        <f t="shared" si="21"/>
         <v>28000</v>
       </c>
       <c r="L94" s="17">
-        <f>G94</f>
+        <f t="shared" si="22"/>
         <v>4000</v>
       </c>
       <c r="M94" s="17">
-        <f>(1-$D94)*H94</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="N94" s="17">
-        <f>(1-$D94)*I94</f>
+        <f t="shared" si="24"/>
         <v>5000</v>
       </c>
       <c r="O94" s="17">
@@ -11162,26 +11162,26 @@
         <v>4020</v>
       </c>
       <c r="Z94" s="17">
-        <f>SUM(J94:Y94)</f>
+        <f t="shared" si="25"/>
         <v>78240</v>
       </c>
       <c r="AA94" s="17">
         <v>0</v>
       </c>
       <c r="AB94" s="14">
-        <f>Z94-AA94</f>
+        <f t="shared" si="26"/>
         <v>78240</v>
       </c>
       <c r="AC94" s="17" t="str">
-        <f>IF(AND($T94=6000, ($T94+$W94-$AB94)&gt;=6000),T94,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AD94" s="17" t="str">
-        <f>IF(AND($T94=8000, ($T94+$W94-$AB94)&gt;=8000),T94,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AE94" s="17" t="str">
-        <f>IF(($T94+$W94-$AB94)&gt;=$T94+8000,W94,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -11214,23 +11214,23 @@
         <v>5000</v>
       </c>
       <c r="J95" s="17">
-        <f>(1-$D95)*E95</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="K95" s="17">
-        <f>(1-$D95)*F95</f>
+        <f t="shared" si="21"/>
         <v>21000</v>
       </c>
       <c r="L95" s="17">
-        <f>G95</f>
+        <f t="shared" si="22"/>
         <v>4000</v>
       </c>
       <c r="M95" s="17">
-        <f>(1-$D95)*H95</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="N95" s="17">
-        <f>(1-$D95)*I95</f>
+        <f t="shared" si="24"/>
         <v>3750</v>
       </c>
       <c r="O95" s="17">
@@ -11267,26 +11267,26 @@
         <v>0</v>
       </c>
       <c r="Z95" s="17">
-        <f>SUM(J95:Y95)</f>
+        <f t="shared" si="25"/>
         <v>69010</v>
       </c>
       <c r="AA95" s="17">
         <v>0</v>
       </c>
       <c r="AB95" s="14">
-        <f>Z95-AA95</f>
+        <f t="shared" si="26"/>
         <v>69010</v>
       </c>
       <c r="AC95" s="17" t="str">
-        <f>IF(AND($T95=6000, ($T95+$W95-$AB95)&gt;=6000),T95,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AD95" s="17" t="str">
-        <f>IF(AND($T95=8000, ($T95+$W95-$AB95)&gt;=8000),T95,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AE95" s="17" t="str">
-        <f>IF(($T95+$W95-$AB95)&gt;=$T95+8000,W95,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -11319,23 +11319,23 @@
         <v>5000</v>
       </c>
       <c r="J96" s="17">
-        <f>(1-$D96)*E96</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="K96" s="17">
-        <f>(1-$D96)*F96</f>
+        <f t="shared" si="21"/>
         <v>14000</v>
       </c>
       <c r="L96" s="17">
-        <f>G96</f>
+        <f t="shared" si="22"/>
         <v>4000</v>
       </c>
       <c r="M96" s="17">
-        <f>(1-$D96)*H96</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="N96" s="17">
-        <f>(1-$D96)*I96</f>
+        <f t="shared" si="24"/>
         <v>2500</v>
       </c>
       <c r="O96" s="17">
@@ -11372,26 +11372,26 @@
         <v>-530</v>
       </c>
       <c r="Z96" s="17">
-        <f>SUM(J96:Y96)</f>
+        <f t="shared" si="25"/>
         <v>60230</v>
       </c>
       <c r="AA96" s="17">
         <v>0</v>
       </c>
       <c r="AB96" s="14">
-        <f>Z96-AA96</f>
+        <f t="shared" si="26"/>
         <v>60230</v>
       </c>
       <c r="AC96" s="17" t="str">
-        <f>IF(AND($T96=6000, ($T96+$W96-$AB96)&gt;=6000),T96,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AD96" s="17" t="str">
-        <f>IF(AND($T96=8000, ($T96+$W96-$AB96)&gt;=8000),T96,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AE96" s="17" t="str">
-        <f>IF(($T96+$W96-$AB96)&gt;=$T96+8000,W96,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -11424,23 +11424,23 @@
         <v>5000</v>
       </c>
       <c r="J97" s="17">
-        <f>(1-$D97)*E97</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="K97" s="17">
-        <f>(1-$D97)*F97</f>
+        <f t="shared" si="21"/>
         <v>21000</v>
       </c>
       <c r="L97" s="17">
-        <f>G97</f>
+        <f t="shared" si="22"/>
         <v>4000</v>
       </c>
       <c r="M97" s="17">
-        <f>(1-$D97)*H97</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="N97" s="17">
-        <f>(1-$D97)*I97</f>
+        <f t="shared" si="24"/>
         <v>3750</v>
       </c>
       <c r="O97" s="17">
@@ -11477,26 +11477,26 @@
         <v>0</v>
       </c>
       <c r="Z97" s="17">
-        <f>SUM(J97:Y97)</f>
+        <f t="shared" si="25"/>
         <v>69010</v>
       </c>
       <c r="AA97" s="17">
         <v>0</v>
       </c>
       <c r="AB97" s="14">
-        <f>Z97-AA97</f>
+        <f t="shared" si="26"/>
         <v>69010</v>
       </c>
       <c r="AC97" s="17" t="str">
-        <f>IF(AND($T97=6000, ($T97+$W97-$AB97)&gt;=6000),T97,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AD97" s="17" t="str">
-        <f>IF(AND($T97=8000, ($T97+$W97-$AB97)&gt;=8000),T97,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AE97" s="17" t="str">
-        <f>IF(($T97+$W97-$AB97)&gt;=$T97+8000,W97,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -11529,23 +11529,23 @@
         <v>5000</v>
       </c>
       <c r="J98" s="17">
-        <f>(1-$D98)*E98</f>
+        <f t="shared" ref="J98:J120" si="30">(1-$D98)*E98</f>
         <v>0</v>
       </c>
       <c r="K98" s="17">
-        <f>(1-$D98)*F98</f>
+        <f t="shared" ref="K98:K120" si="31">(1-$D98)*F98</f>
         <v>28000</v>
       </c>
       <c r="L98" s="17">
-        <f>G98</f>
+        <f t="shared" ref="L98:L120" si="32">G98</f>
         <v>4000</v>
       </c>
       <c r="M98" s="17">
-        <f>(1-$D98)*H98</f>
+        <f t="shared" ref="M98:M120" si="33">(1-$D98)*H98</f>
         <v>0</v>
       </c>
       <c r="N98" s="17">
-        <f>(1-$D98)*I98</f>
+        <f t="shared" ref="N98:N120" si="34">(1-$D98)*I98</f>
         <v>5000</v>
       </c>
       <c r="O98" s="17">
@@ -11582,26 +11582,26 @@
         <v>0</v>
       </c>
       <c r="Z98" s="17">
-        <f>SUM(J98:Y98)</f>
+        <f t="shared" ref="Z98:Z129" si="35">SUM(J98:Y98)</f>
         <v>77260</v>
       </c>
       <c r="AA98" s="17">
         <v>0</v>
       </c>
       <c r="AB98" s="14">
-        <f>Z98-AA98</f>
+        <f t="shared" ref="AB98:AB129" si="36">Z98-AA98</f>
         <v>77260</v>
       </c>
       <c r="AC98" s="17" t="str">
-        <f>IF(AND($T98=6000, ($T98+$W98-$AB98)&gt;=6000),T98,"")</f>
+        <f t="shared" ref="AC98:AC120" si="37">IF(AND($T98=6000, ($T98+$W98-$AB98)&gt;=6000),T98,"")</f>
         <v/>
       </c>
       <c r="AD98" s="17" t="str">
-        <f>IF(AND($T98=8000, ($T98+$W98-$AB98)&gt;=8000),T98,"")</f>
+        <f t="shared" ref="AD98:AD120" si="38">IF(AND($T98=8000, ($T98+$W98-$AB98)&gt;=8000),T98,"")</f>
         <v/>
       </c>
       <c r="AE98" s="17" t="str">
-        <f>IF(($T98+$W98-$AB98)&gt;=$T98+8000,W98,"")</f>
+        <f t="shared" ref="AE98:AE120" si="39">IF(($T98+$W98-$AB98)&gt;=$T98+8000,W98,"")</f>
         <v/>
       </c>
     </row>
@@ -11634,23 +11634,23 @@
         <v>5000</v>
       </c>
       <c r="J99" s="17">
-        <f>(1-$D99)*E99</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="K99" s="17">
-        <f>(1-$D99)*F99</f>
+        <f t="shared" si="31"/>
         <v>21000</v>
       </c>
       <c r="L99" s="17">
-        <f>G99</f>
+        <f t="shared" si="32"/>
         <v>4000</v>
       </c>
       <c r="M99" s="17">
-        <f>(1-$D99)*H99</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="N99" s="17">
-        <f>(1-$D99)*I99</f>
+        <f t="shared" si="34"/>
         <v>3750</v>
       </c>
       <c r="O99" s="17">
@@ -11687,26 +11687,26 @@
         <v>-695</v>
       </c>
       <c r="Z99" s="17">
-        <f>SUM(J99:Y99)</f>
+        <f t="shared" si="35"/>
         <v>74315</v>
       </c>
       <c r="AA99" s="17">
         <v>0</v>
       </c>
       <c r="AB99" s="14">
-        <f>Z99-AA99</f>
+        <f t="shared" si="36"/>
         <v>74315</v>
       </c>
       <c r="AC99" s="17" t="str">
-        <f>IF(AND($T99=6000, ($T99+$W99-$AB99)&gt;=6000),T99,"")</f>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AD99" s="17" t="str">
-        <f>IF(AND($T99=8000, ($T99+$W99-$AB99)&gt;=8000),T99,"")</f>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AE99" s="17" t="str">
-        <f>IF(($T99+$W99-$AB99)&gt;=$T99+8000,W99,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -11739,23 +11739,23 @@
         <v>5000</v>
       </c>
       <c r="J100" s="17">
-        <f>(1-$D100)*E100</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="K100" s="17">
-        <f>(1-$D100)*F100</f>
+        <f t="shared" si="31"/>
         <v>21000</v>
       </c>
       <c r="L100" s="17">
-        <f>G100</f>
+        <f t="shared" si="32"/>
         <v>4000</v>
       </c>
       <c r="M100" s="17">
-        <f>(1-$D100)*H100</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="N100" s="17">
-        <f>(1-$D100)*I100</f>
+        <f t="shared" si="34"/>
         <v>3750</v>
       </c>
       <c r="O100" s="17">
@@ -11792,26 +11792,26 @@
         <v>450</v>
       </c>
       <c r="Z100" s="17">
-        <f>SUM(J100:Y100)</f>
+        <f t="shared" si="35"/>
         <v>69460</v>
       </c>
       <c r="AA100" s="17">
         <v>0</v>
       </c>
       <c r="AB100" s="14">
-        <f>Z100-AA100</f>
+        <f t="shared" si="36"/>
         <v>69460</v>
       </c>
       <c r="AC100" s="17" t="str">
-        <f>IF(AND($T100=6000, ($T100+$W100-$AB100)&gt;=6000),T100,"")</f>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AD100" s="17" t="str">
-        <f>IF(AND($T100=8000, ($T100+$W100-$AB100)&gt;=8000),T100,"")</f>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AE100" s="17" t="str">
-        <f>IF(($T100+$W100-$AB100)&gt;=$T100+8000,W100,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -11844,23 +11844,23 @@
         <v>5000</v>
       </c>
       <c r="J101" s="17">
-        <f>(1-$D101)*E101</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="K101" s="17">
-        <f>(1-$D101)*F101</f>
+        <f t="shared" si="31"/>
         <v>21000</v>
       </c>
       <c r="L101" s="17">
-        <f>G101</f>
+        <f t="shared" si="32"/>
         <v>4000</v>
       </c>
       <c r="M101" s="17">
-        <f>(1-$D101)*H101</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="N101" s="17">
-        <f>(1-$D101)*I101</f>
+        <f t="shared" si="34"/>
         <v>3750</v>
       </c>
       <c r="O101" s="17">
@@ -11897,26 +11897,26 @@
         <v>0</v>
       </c>
       <c r="Z101" s="17">
-        <f>SUM(J101:Y101)</f>
+        <f t="shared" si="35"/>
         <v>75010</v>
       </c>
       <c r="AA101" s="17">
         <v>0</v>
       </c>
       <c r="AB101" s="14">
-        <f>Z101-AA101</f>
+        <f t="shared" si="36"/>
         <v>75010</v>
       </c>
       <c r="AC101" s="17" t="str">
-        <f>IF(AND($T101=6000, ($T101+$W101-$AB101)&gt;=6000),T101,"")</f>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AD101" s="17" t="str">
-        <f>IF(AND($T101=8000, ($T101+$W101-$AB101)&gt;=8000),T101,"")</f>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AE101" s="17" t="str">
-        <f>IF(($T101+$W101-$AB101)&gt;=$T101+8000,W101,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -11949,23 +11949,23 @@
         <v>5000</v>
       </c>
       <c r="J102" s="17">
-        <f>(1-$D102)*E102</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="K102" s="17">
-        <f>(1-$D102)*F102</f>
+        <f t="shared" si="31"/>
         <v>21000</v>
       </c>
       <c r="L102" s="17">
-        <f>G102</f>
+        <f t="shared" si="32"/>
         <v>4000</v>
       </c>
       <c r="M102" s="17">
-        <f>(1-$D102)*H102</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="N102" s="17">
-        <f>(1-$D102)*I102</f>
+        <f t="shared" si="34"/>
         <v>3750</v>
       </c>
       <c r="O102" s="17">
@@ -12002,26 +12002,26 @@
         <v>0</v>
       </c>
       <c r="Z102" s="17">
-        <f>SUM(J102:Y102)</f>
+        <f t="shared" si="35"/>
         <v>69010</v>
       </c>
       <c r="AA102" s="17">
         <v>0</v>
       </c>
       <c r="AB102" s="14">
-        <f>Z102-AA102</f>
+        <f t="shared" si="36"/>
         <v>69010</v>
       </c>
       <c r="AC102" s="17" t="str">
-        <f>IF(AND($T102=6000, ($T102+$W102-$AB102)&gt;=6000),T102,"")</f>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AD102" s="17" t="str">
-        <f>IF(AND($T102=8000, ($T102+$W102-$AB102)&gt;=8000),T102,"")</f>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AE102" s="17" t="str">
-        <f>IF(($T102+$W102-$AB102)&gt;=$T102+8000,W102,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -12054,23 +12054,23 @@
         <v>5000</v>
       </c>
       <c r="J103" s="17">
-        <f>(1-$D103)*E103</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="K103" s="17">
-        <f>(1-$D103)*F103</f>
+        <f t="shared" si="31"/>
         <v>21000</v>
       </c>
       <c r="L103" s="17">
-        <f>G103</f>
+        <f t="shared" si="32"/>
         <v>4000</v>
       </c>
       <c r="M103" s="17">
-        <f>(1-$D103)*H103</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="N103" s="17">
-        <f>(1-$D103)*I103</f>
+        <f t="shared" si="34"/>
         <v>3750</v>
       </c>
       <c r="O103" s="17">
@@ -12107,26 +12107,26 @@
         <v>0</v>
       </c>
       <c r="Z103" s="17">
-        <f>SUM(J103:Y103)</f>
+        <f t="shared" si="35"/>
         <v>75010</v>
       </c>
       <c r="AA103" s="17">
         <v>0</v>
       </c>
       <c r="AB103" s="14">
-        <f>Z103-AA103</f>
+        <f t="shared" si="36"/>
         <v>75010</v>
       </c>
       <c r="AC103" s="17" t="str">
-        <f>IF(AND($T103=6000, ($T103+$W103-$AB103)&gt;=6000),T103,"")</f>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AD103" s="17" t="str">
-        <f>IF(AND($T103=8000, ($T103+$W103-$AB103)&gt;=8000),T103,"")</f>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AE103" s="17" t="str">
-        <f>IF(($T103+$W103-$AB103)&gt;=$T103+8000,W103,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -12159,23 +12159,23 @@
         <v>5000</v>
       </c>
       <c r="J104" s="17">
-        <f>(1-$D104)*E104</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="K104" s="17">
-        <f>(1-$D104)*F104</f>
+        <f t="shared" si="31"/>
         <v>21000</v>
       </c>
       <c r="L104" s="17">
-        <f>G104</f>
+        <f t="shared" si="32"/>
         <v>4000</v>
       </c>
       <c r="M104" s="17">
-        <f>(1-$D104)*H104</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="N104" s="17">
-        <f>(1-$D104)*I104</f>
+        <f t="shared" si="34"/>
         <v>3750</v>
       </c>
       <c r="O104" s="17">
@@ -12212,26 +12212,26 @@
         <v>0</v>
       </c>
       <c r="Z104" s="17">
-        <f>SUM(J104:Y104)</f>
+        <f t="shared" si="35"/>
         <v>69010</v>
       </c>
       <c r="AA104" s="17">
         <v>0</v>
       </c>
       <c r="AB104" s="14">
-        <f>Z104-AA104</f>
+        <f t="shared" si="36"/>
         <v>69010</v>
       </c>
       <c r="AC104" s="17" t="str">
-        <f>IF(AND($T104=6000, ($T104+$W104-$AB104)&gt;=6000),T104,"")</f>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AD104" s="17" t="str">
-        <f>IF(AND($T104=8000, ($T104+$W104-$AB104)&gt;=8000),T104,"")</f>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AE104" s="17" t="str">
-        <f>IF(($T104+$W104-$AB104)&gt;=$T104+8000,W104,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -12264,23 +12264,23 @@
         <v>5000</v>
       </c>
       <c r="J105" s="17">
-        <f>(1-$D105)*E105</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="K105" s="17">
-        <f>(1-$D105)*F105</f>
+        <f t="shared" si="31"/>
         <v>14000</v>
       </c>
       <c r="L105" s="17">
-        <f>G105</f>
+        <f t="shared" si="32"/>
         <v>4000</v>
       </c>
       <c r="M105" s="17">
-        <f>(1-$D105)*H105</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="N105" s="17">
-        <f>(1-$D105)*I105</f>
+        <f t="shared" si="34"/>
         <v>2500</v>
       </c>
       <c r="O105" s="17">
@@ -12317,26 +12317,26 @@
         <v>8080</v>
       </c>
       <c r="Z105" s="17">
-        <f>SUM(J105:Y105)</f>
+        <f t="shared" si="35"/>
         <v>68840</v>
       </c>
       <c r="AA105" s="17">
         <v>0</v>
       </c>
       <c r="AB105" s="14">
-        <f>Z105-AA105</f>
+        <f t="shared" si="36"/>
         <v>68840</v>
       </c>
       <c r="AC105" s="17" t="str">
-        <f>IF(AND($T105=6000, ($T105+$W105-$AB105)&gt;=6000),T105,"")</f>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AD105" s="17" t="str">
-        <f>IF(AND($T105=8000, ($T105+$W105-$AB105)&gt;=8000),T105,"")</f>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AE105" s="17" t="str">
-        <f>IF(($T105+$W105-$AB105)&gt;=$T105+8000,W105,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -12369,23 +12369,23 @@
         <v>5000</v>
       </c>
       <c r="J106" s="17">
-        <f>(1-$D106)*E106</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="K106" s="17">
-        <f>(1-$D106)*F106</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="L106" s="17">
-        <f>G106</f>
+        <f t="shared" si="32"/>
         <v>4000</v>
       </c>
       <c r="M106" s="17">
-        <f>(1-$D106)*H106</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="N106" s="17">
-        <f>(1-$D106)*I106</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="O106" s="17">
@@ -12422,26 +12422,26 @@
         <v>0</v>
       </c>
       <c r="Z106" s="17">
-        <f>SUM(J106:Y106)</f>
+        <f t="shared" si="35"/>
         <v>50260</v>
       </c>
       <c r="AA106" s="17">
         <v>0</v>
       </c>
       <c r="AB106" s="14">
-        <f>Z106-AA106</f>
+        <f t="shared" si="36"/>
         <v>50260</v>
       </c>
       <c r="AC106" s="17" t="str">
-        <f>IF(AND($T106=6000, ($T106+$W106-$AB106)&gt;=6000),T106,"")</f>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AD106" s="17" t="str">
-        <f>IF(AND($T106=8000, ($T106+$W106-$AB106)&gt;=8000),T106,"")</f>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AE106" s="17" t="str">
-        <f>IF(($T106+$W106-$AB106)&gt;=$T106+8000,W106,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -12474,23 +12474,23 @@
         <v>5000</v>
       </c>
       <c r="J107" s="17">
-        <f>(1-$D107)*E107</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="K107" s="17">
-        <f>(1-$D107)*F107</f>
+        <f t="shared" si="31"/>
         <v>21000</v>
       </c>
       <c r="L107" s="17">
-        <f>G107</f>
+        <f t="shared" si="32"/>
         <v>4000</v>
       </c>
       <c r="M107" s="17">
-        <f>(1-$D107)*H107</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="N107" s="17">
-        <f>(1-$D107)*I107</f>
+        <f t="shared" si="34"/>
         <v>3750</v>
       </c>
       <c r="O107" s="17">
@@ -12527,26 +12527,26 @@
         <v>0</v>
       </c>
       <c r="Z107" s="17">
-        <f>SUM(J107:Y107)</f>
+        <f t="shared" si="35"/>
         <v>75010</v>
       </c>
       <c r="AA107" s="17">
         <v>0</v>
       </c>
       <c r="AB107" s="14">
-        <f>Z107-AA107</f>
+        <f t="shared" si="36"/>
         <v>75010</v>
       </c>
       <c r="AC107" s="17" t="str">
-        <f>IF(AND($T107=6000, ($T107+$W107-$AB107)&gt;=6000),T107,"")</f>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AD107" s="17" t="str">
-        <f>IF(AND($T107=8000, ($T107+$W107-$AB107)&gt;=8000),T107,"")</f>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AE107" s="17" t="str">
-        <f>IF(($T107+$W107-$AB107)&gt;=$T107+8000,W107,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -12579,23 +12579,23 @@
         <v>5000</v>
       </c>
       <c r="J108" s="17">
-        <f>(1-$D108)*E108</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="K108" s="17">
-        <f>(1-$D108)*F108</f>
+        <f t="shared" si="31"/>
         <v>21000</v>
       </c>
       <c r="L108" s="17">
-        <f>G108</f>
+        <f t="shared" si="32"/>
         <v>4000</v>
       </c>
       <c r="M108" s="17">
-        <f>(1-$D108)*H108</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="N108" s="17">
-        <f>(1-$D108)*I108</f>
+        <f t="shared" si="34"/>
         <v>3750</v>
       </c>
       <c r="O108" s="17">
@@ -12632,26 +12632,26 @@
         <v>0</v>
       </c>
       <c r="Z108" s="17">
-        <f>SUM(J108:Y108)</f>
+        <f t="shared" si="35"/>
         <v>76870</v>
       </c>
       <c r="AA108" s="17">
         <v>0</v>
       </c>
       <c r="AB108" s="14">
-        <f>Z108-AA108</f>
+        <f t="shared" si="36"/>
         <v>76870</v>
       </c>
       <c r="AC108" s="17" t="str">
-        <f>IF(AND($T108=6000, ($T108+$W108-$AB108)&gt;=6000),T108,"")</f>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AD108" s="17" t="str">
-        <f>IF(AND($T108=8000, ($T108+$W108-$AB108)&gt;=8000),T108,"")</f>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AE108" s="17" t="str">
-        <f>IF(($T108+$W108-$AB108)&gt;=$T108+8000,W108,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -12684,23 +12684,23 @@
         <v>5000</v>
       </c>
       <c r="J109" s="17">
-        <f>(1-$D109)*E109</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="K109" s="17">
-        <f>(1-$D109)*F109</f>
+        <f t="shared" si="31"/>
         <v>28000</v>
       </c>
       <c r="L109" s="17">
-        <f>G109</f>
+        <f t="shared" si="32"/>
         <v>4000</v>
       </c>
       <c r="M109" s="17">
-        <f>(1-$D109)*H109</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="N109" s="17">
-        <f>(1-$D109)*I109</f>
+        <f t="shared" si="34"/>
         <v>5000</v>
       </c>
       <c r="O109" s="17">
@@ -12737,26 +12737,26 @@
         <v>0</v>
       </c>
       <c r="Z109" s="17">
-        <f>SUM(J109:Y109)</f>
+        <f t="shared" si="35"/>
         <v>79120</v>
       </c>
       <c r="AA109" s="17">
         <v>0</v>
       </c>
       <c r="AB109" s="14">
-        <f>Z109-AA109</f>
+        <f t="shared" si="36"/>
         <v>79120</v>
       </c>
       <c r="AC109" s="17" t="str">
-        <f>IF(AND($T109=6000, ($T109+$W109-$AB109)&gt;=6000),T109,"")</f>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AD109" s="17" t="str">
-        <f>IF(AND($T109=8000, ($T109+$W109-$AB109)&gt;=8000),T109,"")</f>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AE109" s="17" t="str">
-        <f>IF(($T109+$W109-$AB109)&gt;=$T109+8000,W109,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -12789,23 +12789,23 @@
         <v>5000</v>
       </c>
       <c r="J110" s="17">
-        <f>(1-$D110)*E110</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="K110" s="17">
-        <f>(1-$D110)*F110</f>
+        <f t="shared" si="31"/>
         <v>21000</v>
       </c>
       <c r="L110" s="17">
-        <f>G110</f>
+        <f t="shared" si="32"/>
         <v>4000</v>
       </c>
       <c r="M110" s="17">
-        <f>(1-$D110)*H110</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="N110" s="17">
-        <f>(1-$D110)*I110</f>
+        <f t="shared" si="34"/>
         <v>3750</v>
       </c>
       <c r="O110" s="17">
@@ -12842,26 +12842,26 @@
         <v>24395</v>
       </c>
       <c r="Z110" s="17">
-        <f>SUM(J110:Y110)</f>
+        <f t="shared" si="35"/>
         <v>101265</v>
       </c>
       <c r="AA110" s="17">
         <v>0</v>
       </c>
       <c r="AB110" s="14">
-        <f>Z110-AA110</f>
+        <f t="shared" si="36"/>
         <v>101265</v>
       </c>
       <c r="AC110" s="17" t="str">
-        <f>IF(AND($T110=6000, ($T110+$W110-$AB110)&gt;=6000),T110,"")</f>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AD110" s="17" t="str">
-        <f>IF(AND($T110=8000, ($T110+$W110-$AB110)&gt;=8000),T110,"")</f>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AE110" s="17" t="str">
-        <f>IF(($T110+$W110-$AB110)&gt;=$T110+8000,W110,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -12894,23 +12894,23 @@
         <v>5000</v>
       </c>
       <c r="J111" s="17">
-        <f>(1-$D111)*E111</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="K111" s="17">
-        <f>(1-$D111)*F111</f>
+        <f t="shared" si="31"/>
         <v>21000</v>
       </c>
       <c r="L111" s="17">
-        <f>G111</f>
+        <f t="shared" si="32"/>
         <v>4000</v>
       </c>
       <c r="M111" s="17">
-        <f>(1-$D111)*H111</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="N111" s="17">
-        <f>(1-$D111)*I111</f>
+        <f t="shared" si="34"/>
         <v>3750</v>
       </c>
       <c r="O111" s="17">
@@ -12947,26 +12947,26 @@
         <v>0</v>
       </c>
       <c r="Z111" s="17">
-        <f>SUM(J111:Y111)</f>
+        <f t="shared" si="35"/>
         <v>76870</v>
       </c>
       <c r="AA111" s="17">
         <v>0</v>
       </c>
       <c r="AB111" s="14">
-        <f>Z111-AA111</f>
+        <f t="shared" si="36"/>
         <v>76870</v>
       </c>
       <c r="AC111" s="17" t="str">
-        <f>IF(AND($T111=6000, ($T111+$W111-$AB111)&gt;=6000),T111,"")</f>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AD111" s="17" t="str">
-        <f>IF(AND($T111=8000, ($T111+$W111-$AB111)&gt;=8000),T111,"")</f>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AE111" s="17" t="str">
-        <f>IF(($T111+$W111-$AB111)&gt;=$T111+8000,W111,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -12999,23 +12999,23 @@
         <v>8000</v>
       </c>
       <c r="J112" s="17">
-        <f>(1-$D112)*E112</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="K112" s="17">
-        <f>(1-$D112)*F112</f>
+        <f t="shared" si="31"/>
         <v>30000</v>
       </c>
       <c r="L112" s="17">
-        <f>G112</f>
+        <f t="shared" si="32"/>
         <v>5000</v>
       </c>
       <c r="M112" s="17">
-        <f>(1-$D112)*H112</f>
+        <f t="shared" si="33"/>
         <v>1500</v>
       </c>
       <c r="N112" s="17">
-        <f>(1-$D112)*I112</f>
+        <f t="shared" si="34"/>
         <v>6000</v>
       </c>
       <c r="O112" s="17">
@@ -13052,26 +13052,26 @@
         <v>540</v>
       </c>
       <c r="Z112" s="17">
-        <f>SUM(J112:Y112)</f>
+        <f t="shared" si="35"/>
         <v>99650</v>
       </c>
       <c r="AA112" s="17">
         <v>0</v>
       </c>
       <c r="AB112" s="14">
-        <f>Z112-AA112</f>
+        <f t="shared" si="36"/>
         <v>99650</v>
       </c>
       <c r="AC112" s="17" t="str">
-        <f>IF(AND($T112=6000, ($T112+$W112-$AB112)&gt;=6000),T112,"")</f>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AD112" s="17" t="str">
-        <f>IF(AND($T112=8000, ($T112+$W112-$AB112)&gt;=8000),T112,"")</f>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AE112" s="17" t="str">
-        <f>IF(($T112+$W112-$AB112)&gt;=$T112+8000,W112,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -13104,23 +13104,23 @@
         <v>8000</v>
       </c>
       <c r="J113" s="17">
-        <f>(1-$D113)*E113</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="K113" s="17">
-        <f>(1-$D113)*F113</f>
+        <f t="shared" si="31"/>
         <v>40000</v>
       </c>
       <c r="L113" s="17">
-        <f>G113</f>
+        <f t="shared" si="32"/>
         <v>5000</v>
       </c>
       <c r="M113" s="17">
-        <f>(1-$D113)*H113</f>
+        <f t="shared" si="33"/>
         <v>2000</v>
       </c>
       <c r="N113" s="17">
-        <f>(1-$D113)*I113</f>
+        <f t="shared" si="34"/>
         <v>8000</v>
       </c>
       <c r="O113" s="17">
@@ -13157,26 +13157,26 @@
         <v>0</v>
       </c>
       <c r="Z113" s="17">
-        <f>SUM(J113:Y113)</f>
+        <f t="shared" si="35"/>
         <v>83610</v>
       </c>
       <c r="AA113" s="17">
         <v>0</v>
       </c>
       <c r="AB113" s="14">
-        <f>Z113-AA113</f>
+        <f t="shared" si="36"/>
         <v>83610</v>
       </c>
       <c r="AC113" s="17" t="str">
-        <f>IF(AND($T113=6000, ($T113+$W113-$AB113)&gt;=6000),T113,"")</f>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AD113" s="17" t="str">
-        <f>IF(AND($T113=8000, ($T113+$W113-$AB113)&gt;=8000),T113,"")</f>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AE113" s="17" t="str">
-        <f>IF(($T113+$W113-$AB113)&gt;=$T113+8000,W113,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -13209,23 +13209,23 @@
         <v>8000</v>
       </c>
       <c r="J114" s="17">
-        <f>(1-$D114)*E114</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="K114" s="17">
-        <f>(1-$D114)*F114</f>
+        <f t="shared" si="31"/>
         <v>40000</v>
       </c>
       <c r="L114" s="17">
-        <f>G114</f>
+        <f t="shared" si="32"/>
         <v>5000</v>
       </c>
       <c r="M114" s="17">
-        <f>(1-$D114)*H114</f>
+        <f t="shared" si="33"/>
         <v>2000</v>
       </c>
       <c r="N114" s="17">
-        <f>(1-$D114)*I114</f>
+        <f t="shared" si="34"/>
         <v>8000</v>
       </c>
       <c r="O114" s="17">
@@ -13262,26 +13262,26 @@
         <v>0</v>
       </c>
       <c r="Z114" s="17">
-        <f>SUM(J114:Y114)</f>
+        <f t="shared" si="35"/>
         <v>83610</v>
       </c>
       <c r="AA114" s="17">
         <v>0</v>
       </c>
       <c r="AB114" s="14">
-        <f>Z114-AA114</f>
+        <f t="shared" si="36"/>
         <v>83610</v>
       </c>
       <c r="AC114" s="17" t="str">
-        <f>IF(AND($T114=6000, ($T114+$W114-$AB114)&gt;=6000),T114,"")</f>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AD114" s="17" t="str">
-        <f>IF(AND($T114=8000, ($T114+$W114-$AB114)&gt;=8000),T114,"")</f>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AE114" s="17" t="str">
-        <f>IF(($T114+$W114-$AB114)&gt;=$T114+8000,W114,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -13314,23 +13314,23 @@
         <v>8000</v>
       </c>
       <c r="J115" s="17">
-        <f>(1-$D115)*E115</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="K115" s="17">
-        <f>(1-$D115)*F115</f>
+        <f t="shared" si="31"/>
         <v>40000</v>
       </c>
       <c r="L115" s="17">
-        <f>G115</f>
+        <f t="shared" si="32"/>
         <v>5000</v>
       </c>
       <c r="M115" s="17">
-        <f>(1-$D115)*H115</f>
+        <f t="shared" si="33"/>
         <v>2000</v>
       </c>
       <c r="N115" s="17">
-        <f>(1-$D115)*I115</f>
+        <f t="shared" si="34"/>
         <v>8000</v>
       </c>
       <c r="O115" s="17">
@@ -13367,26 +13367,26 @@
         <v>120</v>
       </c>
       <c r="Z115" s="17">
-        <f>SUM(J115:Y115)</f>
+        <f t="shared" si="35"/>
         <v>83730</v>
       </c>
       <c r="AA115" s="17">
         <v>0</v>
       </c>
       <c r="AB115" s="14">
-        <f>Z115-AA115</f>
+        <f t="shared" si="36"/>
         <v>83730</v>
       </c>
       <c r="AC115" s="17" t="str">
-        <f>IF(AND($T115=6000, ($T115+$W115-$AB115)&gt;=6000),T115,"")</f>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AD115" s="17" t="str">
-        <f>IF(AND($T115=8000, ($T115+$W115-$AB115)&gt;=8000),T115,"")</f>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AE115" s="17" t="str">
-        <f>IF(($T115+$W115-$AB115)&gt;=$T115+8000,W115,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -13419,23 +13419,23 @@
         <v>8000</v>
       </c>
       <c r="J116" s="17">
-        <f>(1-$D116)*E116</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="K116" s="17">
-        <f>(1-$D116)*F116</f>
+        <f t="shared" si="31"/>
         <v>30000</v>
       </c>
       <c r="L116" s="17">
-        <f>G116</f>
+        <f t="shared" si="32"/>
         <v>5000</v>
       </c>
       <c r="M116" s="17">
-        <f>(1-$D116)*H116</f>
+        <f t="shared" si="33"/>
         <v>1500</v>
       </c>
       <c r="N116" s="17">
-        <f>(1-$D116)*I116</f>
+        <f t="shared" si="34"/>
         <v>6000</v>
       </c>
       <c r="O116" s="17">
@@ -13472,26 +13472,26 @@
         <v>0</v>
       </c>
       <c r="Z116" s="17">
-        <f>SUM(J116:Y116)</f>
+        <f t="shared" si="35"/>
         <v>71110</v>
       </c>
       <c r="AA116" s="17">
         <v>0</v>
       </c>
       <c r="AB116" s="14">
-        <f>Z116-AA116</f>
+        <f t="shared" si="36"/>
         <v>71110</v>
       </c>
       <c r="AC116" s="17" t="str">
-        <f>IF(AND($T116=6000, ($T116+$W116-$AB116)&gt;=6000),T116,"")</f>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AD116" s="17" t="str">
-        <f>IF(AND($T116=8000, ($T116+$W116-$AB116)&gt;=8000),T116,"")</f>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AE116" s="17" t="str">
-        <f>IF(($T116+$W116-$AB116)&gt;=$T116+8000,W116,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -13524,23 +13524,23 @@
         <v>8000</v>
       </c>
       <c r="J117" s="17">
-        <f>(1-$D117)*E117</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="K117" s="17">
-        <f>(1-$D117)*F117</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="L117" s="17">
-        <f>G117</f>
+        <f t="shared" si="32"/>
         <v>5000</v>
       </c>
       <c r="M117" s="17">
-        <f>(1-$D117)*H117</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="N117" s="17">
-        <f>(1-$D117)*I117</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="O117" s="17">
@@ -13577,26 +13577,26 @@
         <v>0</v>
       </c>
       <c r="Z117" s="17">
-        <f>SUM(J117:Y117)</f>
+        <f t="shared" si="35"/>
         <v>33610</v>
       </c>
       <c r="AA117" s="17">
         <v>0</v>
       </c>
       <c r="AB117" s="14">
-        <f>Z117-AA117</f>
+        <f t="shared" si="36"/>
         <v>33610</v>
       </c>
       <c r="AC117" s="17" t="str">
-        <f>IF(AND($T117=6000, ($T117+$W117-$AB117)&gt;=6000),T117,"")</f>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AD117" s="17" t="str">
-        <f>IF(AND($T117=8000, ($T117+$W117-$AB117)&gt;=8000),T117,"")</f>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AE117" s="17" t="str">
-        <f>IF(($T117+$W117-$AB117)&gt;=$T117+8000,W117,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -13629,23 +13629,23 @@
         <v>8000</v>
       </c>
       <c r="J118" s="17">
-        <f>(1-$D118)*E118</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="K118" s="17">
-        <f>(1-$D118)*F118</f>
+        <f t="shared" si="31"/>
         <v>30000</v>
       </c>
       <c r="L118" s="17">
-        <f>G118</f>
+        <f t="shared" si="32"/>
         <v>5000</v>
       </c>
       <c r="M118" s="17">
-        <f>(1-$D118)*H118</f>
+        <f t="shared" si="33"/>
         <v>1500</v>
       </c>
       <c r="N118" s="17">
-        <f>(1-$D118)*I118</f>
+        <f t="shared" si="34"/>
         <v>6000</v>
       </c>
       <c r="O118" s="17">
@@ -13682,26 +13682,26 @@
         <v>2660</v>
       </c>
       <c r="Z118" s="17">
-        <f>SUM(J118:Y118)</f>
+        <f t="shared" si="35"/>
         <v>81770</v>
       </c>
       <c r="AA118" s="17">
         <v>0</v>
       </c>
       <c r="AB118" s="14">
-        <f>Z118-AA118</f>
+        <f t="shared" si="36"/>
         <v>81770</v>
       </c>
       <c r="AC118" s="17" t="str">
-        <f>IF(AND($T118=6000, ($T118+$W118-$AB118)&gt;=6000),T118,"")</f>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AD118" s="17" t="str">
-        <f>IF(AND($T118=8000, ($T118+$W118-$AB118)&gt;=8000),T118,"")</f>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AE118" s="17" t="str">
-        <f>IF(($T118+$W118-$AB118)&gt;=$T118+8000,W118,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -13734,23 +13734,23 @@
         <v>8000</v>
       </c>
       <c r="J119" s="17">
-        <f>(1-$D119)*E119</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="K119" s="17">
-        <f>(1-$D119)*F119</f>
+        <f t="shared" si="31"/>
         <v>30000</v>
       </c>
       <c r="L119" s="17">
-        <f>G119</f>
+        <f t="shared" si="32"/>
         <v>5000</v>
       </c>
       <c r="M119" s="17">
-        <f>(1-$D119)*H119</f>
+        <f t="shared" si="33"/>
         <v>1500</v>
       </c>
       <c r="N119" s="17">
-        <f>(1-$D119)*I119</f>
+        <f t="shared" si="34"/>
         <v>6000</v>
       </c>
       <c r="O119" s="17">
@@ -13787,26 +13787,26 @@
         <v>0</v>
       </c>
       <c r="Z119" s="17">
-        <f>SUM(J119:Y119)</f>
+        <f t="shared" si="35"/>
         <v>71110</v>
       </c>
       <c r="AA119" s="17">
         <v>0</v>
       </c>
       <c r="AB119" s="14">
-        <f>Z119-AA119</f>
+        <f t="shared" si="36"/>
         <v>71110</v>
       </c>
       <c r="AC119" s="17" t="str">
-        <f>IF(AND($T119=6000, ($T119+$W119-$AB119)&gt;=6000),T119,"")</f>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AD119" s="17" t="str">
-        <f>IF(AND($T119=8000, ($T119+$W119-$AB119)&gt;=8000),T119,"")</f>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AE119" s="17" t="str">
-        <f>IF(($T119+$W119-$AB119)&gt;=$T119+8000,W119,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -13839,23 +13839,23 @@
         <v>8000</v>
       </c>
       <c r="J120" s="17">
-        <f>(1-$D120)*E120</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="K120" s="17">
-        <f>(1-$D120)*F120</f>
+        <f t="shared" si="31"/>
         <v>40000</v>
       </c>
       <c r="L120" s="17">
-        <f>G120</f>
+        <f t="shared" si="32"/>
         <v>5000</v>
       </c>
       <c r="M120" s="17">
-        <f>(1-$D120)*H120</f>
+        <f t="shared" si="33"/>
         <v>2000</v>
       </c>
       <c r="N120" s="17">
-        <f>(1-$D120)*I120</f>
+        <f t="shared" si="34"/>
         <v>8000</v>
       </c>
       <c r="O120" s="17">
@@ -13892,26 +13892,26 @@
         <v>5830</v>
       </c>
       <c r="Z120" s="17">
-        <f>SUM(J120:Y120)</f>
+        <f t="shared" si="35"/>
         <v>89440</v>
       </c>
       <c r="AA120" s="17">
         <v>0</v>
       </c>
       <c r="AB120" s="14">
-        <f>Z120-AA120</f>
+        <f t="shared" si="36"/>
         <v>89440</v>
       </c>
       <c r="AC120" s="17" t="str">
-        <f>IF(AND($T120=6000, ($T120+$W120-$AB120)&gt;=6000),T120,"")</f>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AD120" s="17" t="str">
-        <f>IF(AND($T120=8000, ($T120+$W120-$AB120)&gt;=8000),T120,"")</f>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AE120" s="17" t="str">
-        <f>IF(($T120+$W120-$AB120)&gt;=$T120+8000,W120,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -13941,31 +13941,31 @@
       <c r="W121" s="29"/>
       <c r="X121" s="29"/>
       <c r="Y121" s="29">
-        <f>SUM(Y2:Y120)</f>
+        <f t="shared" ref="Y121:AE121" si="40">SUM(Y2:Y120)</f>
         <v>188670</v>
       </c>
       <c r="Z121" s="29">
-        <f>SUM(Z2:Z120)</f>
-        <v>7807440</v>
+        <f t="shared" si="40"/>
+        <v>7795815</v>
       </c>
       <c r="AA121" s="29">
-        <f>SUM(AA2:AA120)</f>
+        <f t="shared" si="40"/>
         <v>48000</v>
       </c>
       <c r="AB121" s="29">
-        <f>SUM(AB2:AB120)</f>
-        <v>7759440</v>
+        <f t="shared" si="40"/>
+        <v>7747815</v>
       </c>
       <c r="AC121" s="29">
-        <f>SUM(AC2:AC120)</f>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AD121" s="29">
-        <f>SUM(AD2:AD120)</f>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AE121" s="29">
-        <f>SUM(AE2:AE120)</f>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
     </row>
@@ -22157,7 +22157,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="Y89:Y90 J47:M55 J38:N46 N112:N120 H112:I120 D112:D120 Y112:Y120 K112:K120 Y93:Y105 Z67:Z120 Y67:Y86 I38:I111 J56:J120 L56:M120 N47:N105 K56:K105 Y2:Z66 I2:N37 AA2:AB120 E2:G120 H2:H111 D2:D96 O2:X120" xr:uid="{8FCCCF8D-A982-4ECC-8B53-E3BEBA112740}">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="Y89:Y90 J47:M55 J38:N46 N112:N120 H112:I120 D112:D120 Y112:Y120 K112:K120 Y93:Y105 Z67:Z120 Y67:Y86 I38:I111 J56:J120 L56:M120 N47:N105 K56:K105 Y2:Z66 I2:N37 AA2:AB120 E2:G120 O2:X120 D2:D96 H2:H111" xr:uid="{8FCCCF8D-A982-4ECC-8B53-E3BEBA112740}">
       <formula1>AND(ISNUMBER(D2),(NOT(OR(NOT(ISERROR(DATEVALUE(D2))), AND(ISNUMBER(D2), LEFT(CELL("format", D2))="D")))))</formula1>
     </dataValidation>
   </dataValidations>

--- a/source/2026 - 2027 FEE.xlsx
+++ b/source/2026 - 2027 FEE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\KBI\ACCOUNTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A16758B-C668-4C10-8774-B70E2515AE17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{056D1BA0-9702-4A36-843B-44663388CA0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="781" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="256">
   <si>
     <t>LAST NAME</t>
   </si>
@@ -800,6 +800,12 @@
   <si>
     <t>CRECHE</t>
   </si>
+  <si>
+    <t>NIP:PAUL SUNDAY ADEDOJA</t>
+  </si>
+  <si>
+    <t>ADEDOJA FAMILY</t>
+  </si>
 </sst>
 </file>
 
@@ -8750,11 +8756,11 @@
         <v>44280</v>
       </c>
       <c r="AA71" s="24">
-        <v>0</v>
+        <v>43000</v>
       </c>
       <c r="AB71" s="20">
         <f>Z71-AA71</f>
-        <v>44280</v>
+        <v>1280</v>
       </c>
       <c r="AC71" s="24" t="str">
         <f>IF(AND($T71=6000, ($T71+$W71-$AB71)&gt;=6000),T71,"")</f>
@@ -13949,11 +13955,11 @@
       </c>
       <c r="AA121" s="27">
         <f>SUM(AA2:AA120)</f>
-        <v>48000</v>
+        <v>91000</v>
       </c>
       <c r="AB121" s="27">
         <f>SUM(AB2:AB120)</f>
-        <v>7203495</v>
+        <v>7160495</v>
       </c>
       <c r="AC121" s="27">
         <f>SUM(AC2:AC120)</f>
@@ -22239,7 +22245,23 @@
         <v>252</v>
       </c>
     </row>
-    <row r="3" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="8">
+        <v>46255</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="D3" s="9">
+        <v>43000</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>255</v>
+      </c>
+    </row>
     <row r="4" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/source/2026 - 2027 FEE.xlsx
+++ b/source/2026 - 2027 FEE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\KBI\ACCOUNTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{056D1BA0-9702-4A36-843B-44663388CA0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EB1001F-A16E-49DD-B2A1-F42FB38F518D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="781" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -744,9 +744,6 @@
     <t>GANIYU</t>
   </si>
   <si>
-    <t>OLUWAJUEDALO FARHAN</t>
-  </si>
-  <si>
     <t>ABDULAZEEZ</t>
   </si>
   <si>
@@ -805,6 +802,9 @@
   </si>
   <si>
     <t>ADEDOJA FAMILY</t>
+  </si>
+  <si>
+    <t>FARHAN OLUWAJEDALO</t>
   </si>
 </sst>
 </file>
@@ -1430,10 +1430,10 @@
         <v>143</v>
       </c>
       <c r="B2" s="22" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C2" s="22" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D2" s="23">
         <v>0.25</v>
@@ -1454,23 +1454,23 @@
         <v>0</v>
       </c>
       <c r="J2" s="24">
-        <f>(1-$D2)*E2</f>
+        <f t="shared" ref="J2:J33" si="0">(1-$D2)*E2</f>
         <v>0</v>
       </c>
       <c r="K2" s="24">
-        <f>(1-$D2)*F2</f>
+        <f t="shared" ref="K2:K33" si="1">(1-$D2)*F2</f>
         <v>19500</v>
       </c>
       <c r="L2" s="24">
-        <f>G2</f>
+        <f t="shared" ref="L2:L33" si="2">G2</f>
         <v>2000</v>
       </c>
       <c r="M2" s="24">
-        <f>(1-$D2)*H2</f>
+        <f t="shared" ref="M2:M33" si="3">(1-$D2)*H2</f>
         <v>0</v>
       </c>
       <c r="N2" s="24">
-        <f>(1-$D2)*I2</f>
+        <f t="shared" ref="N2:N33" si="4">(1-$D2)*I2</f>
         <v>0</v>
       </c>
       <c r="O2" s="24">
@@ -1507,38 +1507,38 @@
         <v>0</v>
       </c>
       <c r="Z2" s="24">
-        <f>SUM(J2:Y2)</f>
+        <f t="shared" ref="Z2:Z33" si="5">SUM(J2:Y2)</f>
         <v>24550</v>
       </c>
       <c r="AA2" s="24">
         <v>0</v>
       </c>
       <c r="AB2" s="20">
-        <f>Z2-AA2</f>
+        <f t="shared" ref="AB2:AB33" si="6">Z2-AA2</f>
         <v>24550</v>
       </c>
       <c r="AC2" s="24" t="str">
-        <f>IF(AND($T2=6000, ($T2+$W2-$AB2)&gt;=6000),T2,"")</f>
+        <f t="shared" ref="AC2:AC33" si="7">IF(AND($T2=6000, ($T2+$W2-$AB2)&gt;=6000),T2,"")</f>
         <v/>
       </c>
       <c r="AD2" s="24" t="str">
-        <f>IF(AND($T2=8000, ($T2+$W2-$AB2)&gt;=8000),T2,"")</f>
+        <f t="shared" ref="AD2:AD33" si="8">IF(AND($T2=8000, ($T2+$W2-$AB2)&gt;=8000),T2,"")</f>
         <v/>
       </c>
       <c r="AE2" s="24" t="str">
-        <f>IF(($T2+$W2-$AB2)&gt;=$T2+8000,W2,"")</f>
+        <f t="shared" ref="AE2:AE33" si="9">IF(($T2+$W2-$AB2)&gt;=$T2+8000,W2,"")</f>
         <v/>
       </c>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B3" s="22" t="s">
         <v>50</v>
       </c>
       <c r="C3" s="22" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D3" s="23">
         <v>0</v>
@@ -1559,23 +1559,23 @@
         <v>0</v>
       </c>
       <c r="J3" s="24">
-        <f>(1-$D3)*E3</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K3" s="24">
-        <f>(1-$D3)*F3</f>
+        <f t="shared" si="1"/>
         <v>26000</v>
       </c>
       <c r="L3" s="24">
-        <f>G3</f>
+        <f t="shared" si="2"/>
         <v>2000</v>
       </c>
       <c r="M3" s="24">
-        <f>(1-$D3)*H3</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N3" s="24">
-        <f>(1-$D3)*I3</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O3" s="24">
@@ -1612,26 +1612,26 @@
         <v>0</v>
       </c>
       <c r="Z3" s="24">
-        <f>SUM(J3:Y3)</f>
+        <f t="shared" si="5"/>
         <v>31050</v>
       </c>
       <c r="AA3" s="24">
         <v>0</v>
       </c>
       <c r="AB3" s="20">
-        <f>Z3-AA3</f>
+        <f t="shared" si="6"/>
         <v>31050</v>
       </c>
       <c r="AC3" s="24" t="str">
-        <f>IF(AND($T3=6000, ($T3+$W3-$AB3)&gt;=6000),T3,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD3" s="24" t="str">
-        <f>IF(AND($T3=8000, ($T3+$W3-$AB3)&gt;=8000),T3,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE3" s="24" t="str">
-        <f>IF(($T3+$W3-$AB3)&gt;=$T3+8000,W3,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -1640,10 +1640,10 @@
         <v>121</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C4" s="22" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D4" s="23">
         <v>0.25</v>
@@ -1664,23 +1664,23 @@
         <v>0</v>
       </c>
       <c r="J4" s="24">
-        <f>(1-$D4)*E4</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K4" s="24">
-        <f>(1-$D4)*F4</f>
+        <f t="shared" si="1"/>
         <v>19500</v>
       </c>
       <c r="L4" s="24">
-        <f>G4</f>
+        <f t="shared" si="2"/>
         <v>2000</v>
       </c>
       <c r="M4" s="24">
-        <f>(1-$D4)*H4</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N4" s="24">
-        <f>(1-$D4)*I4</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O4" s="24">
@@ -1717,26 +1717,26 @@
         <v>0</v>
       </c>
       <c r="Z4" s="24">
-        <f>SUM(J4:Y4)</f>
+        <f t="shared" si="5"/>
         <v>24550</v>
       </c>
       <c r="AA4" s="24">
         <v>0</v>
       </c>
       <c r="AB4" s="20">
-        <f>Z4-AA4</f>
+        <f t="shared" si="6"/>
         <v>24550</v>
       </c>
       <c r="AC4" s="24" t="str">
-        <f>IF(AND($T4=6000, ($T4+$W4-$AB4)&gt;=6000),T4,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD4" s="24" t="str">
-        <f>IF(AND($T4=8000, ($T4+$W4-$AB4)&gt;=8000),T4,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE4" s="24" t="str">
-        <f>IF(($T4+$W4-$AB4)&gt;=$T4+8000,W4,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -1769,23 +1769,23 @@
         <v>6000</v>
       </c>
       <c r="J5" s="24">
-        <f>(1-$D5)*E5</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K5" s="24">
-        <f>(1-$D5)*F5</f>
+        <f t="shared" si="1"/>
         <v>24750</v>
       </c>
       <c r="L5" s="24">
-        <f>G5</f>
+        <f t="shared" si="2"/>
         <v>5000</v>
       </c>
       <c r="M5" s="24">
-        <f>(1-$D5)*H5</f>
+        <f t="shared" si="3"/>
         <v>1500</v>
       </c>
       <c r="N5" s="24">
-        <f>(1-$D5)*I5</f>
+        <f t="shared" si="4"/>
         <v>4500</v>
       </c>
       <c r="O5" s="24">
@@ -1822,26 +1822,26 @@
         <v>750</v>
       </c>
       <c r="Z5" s="24">
-        <f>SUM(J5:Y5)</f>
+        <f t="shared" si="5"/>
         <v>78390</v>
       </c>
       <c r="AA5" s="24">
         <v>0</v>
       </c>
       <c r="AB5" s="20">
-        <f>Z5-AA5</f>
+        <f t="shared" si="6"/>
         <v>78390</v>
       </c>
       <c r="AC5" s="24" t="str">
-        <f>IF(AND($T5=6000, ($T5+$W5-$AB5)&gt;=6000),T5,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD5" s="24" t="str">
-        <f>IF(AND($T5=8000, ($T5+$W5-$AB5)&gt;=8000),T5,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE5" s="24" t="str">
-        <f>IF(($T5+$W5-$AB5)&gt;=$T5+8000,W5,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -1874,23 +1874,23 @@
         <v>6000</v>
       </c>
       <c r="J6" s="24">
-        <f>(1-$D6)*E6</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K6" s="24">
-        <f>(1-$D6)*F6</f>
+        <f t="shared" si="1"/>
         <v>23100</v>
       </c>
       <c r="L6" s="24">
-        <f>G6</f>
+        <f t="shared" si="2"/>
         <v>5000</v>
       </c>
       <c r="M6" s="24">
-        <f>(1-$D6)*H6</f>
+        <f t="shared" si="3"/>
         <v>1400</v>
       </c>
       <c r="N6" s="24">
-        <f>(1-$D6)*I6</f>
+        <f t="shared" si="4"/>
         <v>4200</v>
       </c>
       <c r="O6" s="24">
@@ -1927,26 +1927,26 @@
         <v>0</v>
       </c>
       <c r="Z6" s="24">
-        <f>SUM(J6:Y6)</f>
+        <f t="shared" si="5"/>
         <v>67590</v>
       </c>
       <c r="AA6" s="24">
         <v>0</v>
       </c>
       <c r="AB6" s="20">
-        <f>Z6-AA6</f>
+        <f t="shared" si="6"/>
         <v>67590</v>
       </c>
       <c r="AC6" s="24" t="str">
-        <f>IF(AND($T6=6000, ($T6+$W6-$AB6)&gt;=6000),T6,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD6" s="24" t="str">
-        <f>IF(AND($T6=8000, ($T6+$W6-$AB6)&gt;=8000),T6,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE6" s="24" t="str">
-        <f>IF(($T6+$W6-$AB6)&gt;=$T6+8000,W6,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -1979,23 +1979,23 @@
         <v>6000</v>
       </c>
       <c r="J7" s="24">
-        <f>(1-$D7)*E7</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K7" s="24">
-        <f>(1-$D7)*F7</f>
+        <f t="shared" si="1"/>
         <v>33000</v>
       </c>
       <c r="L7" s="24">
-        <f>G7</f>
+        <f t="shared" si="2"/>
         <v>5000</v>
       </c>
       <c r="M7" s="24">
-        <f>(1-$D7)*H7</f>
+        <f t="shared" si="3"/>
         <v>2000</v>
       </c>
       <c r="N7" s="24">
-        <f>(1-$D7)*I7</f>
+        <f t="shared" si="4"/>
         <v>6000</v>
       </c>
       <c r="O7" s="24">
@@ -2032,26 +2032,26 @@
         <v>0</v>
       </c>
       <c r="Z7" s="24">
-        <f>SUM(J7:Y7)</f>
+        <f t="shared" si="5"/>
         <v>79890</v>
       </c>
       <c r="AA7" s="24">
         <v>0</v>
       </c>
       <c r="AB7" s="20">
-        <f>Z7-AA7</f>
+        <f t="shared" si="6"/>
         <v>79890</v>
       </c>
       <c r="AC7" s="24" t="str">
-        <f>IF(AND($T7=6000, ($T7+$W7-$AB7)&gt;=6000),T7,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD7" s="24" t="str">
-        <f>IF(AND($T7=8000, ($T7+$W7-$AB7)&gt;=8000),T7,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE7" s="24" t="str">
-        <f>IF(($T7+$W7-$AB7)&gt;=$T7+8000,W7,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -2084,23 +2084,23 @@
         <v>6000</v>
       </c>
       <c r="J8" s="24">
-        <f>(1-$D8)*E8</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K8" s="24">
-        <f>(1-$D8)*F8</f>
+        <f t="shared" si="1"/>
         <v>33000</v>
       </c>
       <c r="L8" s="24">
-        <f>G8</f>
+        <f t="shared" si="2"/>
         <v>5000</v>
       </c>
       <c r="M8" s="24">
-        <f>(1-$D8)*H8</f>
+        <f t="shared" si="3"/>
         <v>2000</v>
       </c>
       <c r="N8" s="24">
-        <f>(1-$D8)*I8</f>
+        <f t="shared" si="4"/>
         <v>6000</v>
       </c>
       <c r="O8" s="24">
@@ -2137,26 +2137,26 @@
         <v>0</v>
       </c>
       <c r="Z8" s="24">
-        <f>SUM(J8:Y8)</f>
+        <f t="shared" si="5"/>
         <v>79890</v>
       </c>
       <c r="AA8" s="24">
         <v>0</v>
       </c>
       <c r="AB8" s="20">
-        <f>Z8-AA8</f>
+        <f t="shared" si="6"/>
         <v>79890</v>
       </c>
       <c r="AC8" s="24" t="str">
-        <f>IF(AND($T8=6000, ($T8+$W8-$AB8)&gt;=6000),T8,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD8" s="24" t="str">
-        <f>IF(AND($T8=8000, ($T8+$W8-$AB8)&gt;=8000),T8,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE8" s="24" t="str">
-        <f>IF(($T8+$W8-$AB8)&gt;=$T8+8000,W8,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -2189,23 +2189,23 @@
         <v>6000</v>
       </c>
       <c r="J9" s="24">
-        <f>(1-$D9)*E9</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K9" s="24">
-        <f>(1-$D9)*F9</f>
+        <f t="shared" si="1"/>
         <v>23100</v>
       </c>
       <c r="L9" s="24">
-        <f>G9</f>
+        <f t="shared" si="2"/>
         <v>5000</v>
       </c>
       <c r="M9" s="24">
-        <f>(1-$D9)*H9</f>
+        <f t="shared" si="3"/>
         <v>1400</v>
       </c>
       <c r="N9" s="24">
-        <f>(1-$D9)*I9</f>
+        <f t="shared" si="4"/>
         <v>4200</v>
       </c>
       <c r="O9" s="24">
@@ -2242,26 +2242,26 @@
         <v>0</v>
       </c>
       <c r="Z9" s="24">
-        <f>SUM(J9:Y9)</f>
+        <f t="shared" si="5"/>
         <v>67590</v>
       </c>
       <c r="AA9" s="24">
         <v>0</v>
       </c>
       <c r="AB9" s="20">
-        <f>Z9-AA9</f>
+        <f t="shared" si="6"/>
         <v>67590</v>
       </c>
       <c r="AC9" s="24" t="str">
-        <f>IF(AND($T9=6000, ($T9+$W9-$AB9)&gt;=6000),T9,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD9" s="24" t="str">
-        <f>IF(AND($T9=8000, ($T9+$W9-$AB9)&gt;=8000),T9,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE9" s="24" t="str">
-        <f>IF(($T9+$W9-$AB9)&gt;=$T9+8000,W9,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -2294,23 +2294,23 @@
         <v>6000</v>
       </c>
       <c r="J10" s="24">
-        <f>(1-$D10)*E10</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K10" s="24">
-        <f>(1-$D10)*F10</f>
+        <f t="shared" si="1"/>
         <v>16500</v>
       </c>
       <c r="L10" s="24">
-        <f>G10</f>
+        <f t="shared" si="2"/>
         <v>5000</v>
       </c>
       <c r="M10" s="24">
-        <f>(1-$D10)*H10</f>
+        <f t="shared" si="3"/>
         <v>1000</v>
       </c>
       <c r="N10" s="24">
-        <f>(1-$D10)*I10</f>
+        <f t="shared" si="4"/>
         <v>3000</v>
       </c>
       <c r="O10" s="24">
@@ -2347,26 +2347,26 @@
         <v>0</v>
       </c>
       <c r="Z10" s="24">
-        <f>SUM(J10:Y10)</f>
+        <f t="shared" si="5"/>
         <v>62410</v>
       </c>
       <c r="AA10" s="24">
         <v>0</v>
       </c>
       <c r="AB10" s="20">
-        <f>Z10-AA10</f>
+        <f t="shared" si="6"/>
         <v>62410</v>
       </c>
       <c r="AC10" s="24" t="str">
-        <f>IF(AND($T10=6000, ($T10+$W10-$AB10)&gt;=6000),T10,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD10" s="24" t="str">
-        <f>IF(AND($T10=8000, ($T10+$W10-$AB10)&gt;=8000),T10,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE10" s="24" t="str">
-        <f>IF(($T10+$W10-$AB10)&gt;=$T10+8000,W10,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -2399,23 +2399,23 @@
         <v>6000</v>
       </c>
       <c r="J11" s="24">
-        <f>(1-$D11)*E11</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K11" s="24">
-        <f>(1-$D11)*F11</f>
+        <f t="shared" si="1"/>
         <v>16500</v>
       </c>
       <c r="L11" s="24">
-        <f>G11</f>
+        <f t="shared" si="2"/>
         <v>5000</v>
       </c>
       <c r="M11" s="24">
-        <f>(1-$D11)*H11</f>
+        <f t="shared" si="3"/>
         <v>1000</v>
       </c>
       <c r="N11" s="24">
-        <f>(1-$D11)*I11</f>
+        <f t="shared" si="4"/>
         <v>3000</v>
       </c>
       <c r="O11" s="24">
@@ -2452,26 +2452,26 @@
         <v>0</v>
       </c>
       <c r="Z11" s="24">
-        <f>SUM(J11:Y11)</f>
+        <f t="shared" si="5"/>
         <v>62410</v>
       </c>
       <c r="AA11" s="24">
         <v>0</v>
       </c>
       <c r="AB11" s="20">
-        <f>Z11-AA11</f>
+        <f t="shared" si="6"/>
         <v>62410</v>
       </c>
       <c r="AC11" s="24" t="str">
-        <f>IF(AND($T11=6000, ($T11+$W11-$AB11)&gt;=6000),T11,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD11" s="24" t="str">
-        <f>IF(AND($T11=8000, ($T11+$W11-$AB11)&gt;=8000),T11,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE11" s="24" t="str">
-        <f>IF(($T11+$W11-$AB11)&gt;=$T11+8000,W11,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -2504,23 +2504,23 @@
         <v>6000</v>
       </c>
       <c r="J12" s="24">
-        <f>(1-$D12)*E12</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K12" s="24">
-        <f>(1-$D12)*F12</f>
+        <f t="shared" si="1"/>
         <v>16500</v>
       </c>
       <c r="L12" s="24">
-        <f>G12</f>
+        <f t="shared" si="2"/>
         <v>5000</v>
       </c>
       <c r="M12" s="24">
-        <f>(1-$D12)*H12</f>
+        <f t="shared" si="3"/>
         <v>1000</v>
       </c>
       <c r="N12" s="24">
-        <f>(1-$D12)*I12</f>
+        <f t="shared" si="4"/>
         <v>3000</v>
       </c>
       <c r="O12" s="24">
@@ -2557,26 +2557,26 @@
         <v>-30</v>
       </c>
       <c r="Z12" s="24">
-        <f>SUM(J12:Y12)</f>
+        <f t="shared" si="5"/>
         <v>70380</v>
       </c>
       <c r="AA12" s="24">
         <v>0</v>
       </c>
       <c r="AB12" s="20">
-        <f>Z12-AA12</f>
+        <f t="shared" si="6"/>
         <v>70380</v>
       </c>
       <c r="AC12" s="24" t="str">
-        <f>IF(AND($T12=6000, ($T12+$W12-$AB12)&gt;=6000),T12,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD12" s="24" t="str">
-        <f>IF(AND($T12=8000, ($T12+$W12-$AB12)&gt;=8000),T12,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE12" s="24" t="str">
-        <f>IF(($T12+$W12-$AB12)&gt;=$T12+8000,W12,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -2609,23 +2609,23 @@
         <v>6000</v>
       </c>
       <c r="J13" s="24">
-        <f>(1-$D13)*E13</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K13" s="24">
-        <f>(1-$D13)*F13</f>
+        <f t="shared" si="1"/>
         <v>33000</v>
       </c>
       <c r="L13" s="24">
-        <f>G13</f>
+        <f t="shared" si="2"/>
         <v>5000</v>
       </c>
       <c r="M13" s="24">
-        <f>(1-$D13)*H13</f>
+        <f t="shared" si="3"/>
         <v>2000</v>
       </c>
       <c r="N13" s="24">
-        <f>(1-$D13)*I13</f>
+        <f t="shared" si="4"/>
         <v>6000</v>
       </c>
       <c r="O13" s="24">
@@ -2662,26 +2662,26 @@
         <v>-8970</v>
       </c>
       <c r="Z13" s="24">
-        <f>SUM(J13:Y13)</f>
+        <f t="shared" si="5"/>
         <v>73940</v>
       </c>
       <c r="AA13" s="24">
         <v>0</v>
       </c>
       <c r="AB13" s="20">
-        <f>Z13-AA13</f>
+        <f t="shared" si="6"/>
         <v>73940</v>
       </c>
       <c r="AC13" s="24" t="str">
-        <f>IF(AND($T13=6000, ($T13+$W13-$AB13)&gt;=6000),T13,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD13" s="24" t="str">
-        <f>IF(AND($T13=8000, ($T13+$W13-$AB13)&gt;=8000),T13,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE13" s="24" t="str">
-        <f>IF(($T13+$W13-$AB13)&gt;=$T13+8000,W13,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -2714,23 +2714,23 @@
         <v>6000</v>
       </c>
       <c r="J14" s="24">
-        <f>(1-$D14)*E14</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K14" s="24">
-        <f>(1-$D14)*F14</f>
+        <f t="shared" si="1"/>
         <v>16500</v>
       </c>
       <c r="L14" s="24">
-        <f>G14</f>
+        <f t="shared" si="2"/>
         <v>5000</v>
       </c>
       <c r="M14" s="24">
-        <f>(1-$D14)*H14</f>
+        <f t="shared" si="3"/>
         <v>1000</v>
       </c>
       <c r="N14" s="24">
-        <f>(1-$D14)*I14</f>
+        <f t="shared" si="4"/>
         <v>3000</v>
       </c>
       <c r="O14" s="24">
@@ -2767,26 +2767,26 @@
         <v>480</v>
       </c>
       <c r="Z14" s="24">
-        <f>SUM(J14:Y14)</f>
+        <f t="shared" si="5"/>
         <v>62890</v>
       </c>
       <c r="AA14" s="24">
         <v>0</v>
       </c>
       <c r="AB14" s="20">
-        <f>Z14-AA14</f>
+        <f t="shared" si="6"/>
         <v>62890</v>
       </c>
       <c r="AC14" s="24" t="str">
-        <f>IF(AND($T14=6000, ($T14+$W14-$AB14)&gt;=6000),T14,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD14" s="24" t="str">
-        <f>IF(AND($T14=8000, ($T14+$W14-$AB14)&gt;=8000),T14,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE14" s="24" t="str">
-        <f>IF(($T14+$W14-$AB14)&gt;=$T14+8000,W14,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -2819,23 +2819,23 @@
         <v>6000</v>
       </c>
       <c r="J15" s="24">
-        <f>(1-$D15)*E15</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K15" s="24">
-        <f>(1-$D15)*F15</f>
+        <f t="shared" si="1"/>
         <v>24750</v>
       </c>
       <c r="L15" s="24">
-        <f>G15</f>
+        <f t="shared" si="2"/>
         <v>5000</v>
       </c>
       <c r="M15" s="24">
-        <f>(1-$D15)*H15</f>
+        <f t="shared" si="3"/>
         <v>1500</v>
       </c>
       <c r="N15" s="24">
-        <f>(1-$D15)*I15</f>
+        <f t="shared" si="4"/>
         <v>4500</v>
       </c>
       <c r="O15" s="24">
@@ -2872,26 +2872,26 @@
         <v>0</v>
       </c>
       <c r="Z15" s="24">
-        <f>SUM(J15:Y15)</f>
+        <f t="shared" si="5"/>
         <v>72660</v>
       </c>
       <c r="AA15" s="24">
         <v>0</v>
       </c>
       <c r="AB15" s="20">
-        <f>Z15-AA15</f>
+        <f t="shared" si="6"/>
         <v>72660</v>
       </c>
       <c r="AC15" s="24" t="str">
-        <f>IF(AND($T15=6000, ($T15+$W15-$AB15)&gt;=6000),T15,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD15" s="24" t="str">
-        <f>IF(AND($T15=8000, ($T15+$W15-$AB15)&gt;=8000),T15,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE15" s="24" t="str">
-        <f>IF(($T15+$W15-$AB15)&gt;=$T15+8000,W15,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -2924,23 +2924,23 @@
         <v>6000</v>
       </c>
       <c r="J16" s="24">
-        <f>(1-$D16)*E16</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K16" s="24">
-        <f>(1-$D16)*F16</f>
+        <f t="shared" si="1"/>
         <v>16500</v>
       </c>
       <c r="L16" s="24">
-        <f>G16</f>
+        <f t="shared" si="2"/>
         <v>5000</v>
       </c>
       <c r="M16" s="24">
-        <f>(1-$D16)*H16</f>
+        <f t="shared" si="3"/>
         <v>1000</v>
       </c>
       <c r="N16" s="24">
-        <f>(1-$D16)*I16</f>
+        <f t="shared" si="4"/>
         <v>3000</v>
       </c>
       <c r="O16" s="24">
@@ -2977,26 +2977,26 @@
         <v>500</v>
       </c>
       <c r="Z16" s="24">
-        <f>SUM(J16:Y16)</f>
+        <f t="shared" si="5"/>
         <v>62910</v>
       </c>
       <c r="AA16" s="24">
         <v>0</v>
       </c>
       <c r="AB16" s="20">
-        <f>Z16-AA16</f>
+        <f t="shared" si="6"/>
         <v>62910</v>
       </c>
       <c r="AC16" s="24" t="str">
-        <f>IF(AND($T16=6000, ($T16+$W16-$AB16)&gt;=6000),T16,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD16" s="24" t="str">
-        <f>IF(AND($T16=8000, ($T16+$W16-$AB16)&gt;=8000),T16,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE16" s="24" t="str">
-        <f>IF(($T16+$W16-$AB16)&gt;=$T16+8000,W16,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -3029,23 +3029,23 @@
         <v>6000</v>
       </c>
       <c r="J17" s="24">
-        <f>(1-$D17)*E17</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K17" s="24">
-        <f>(1-$D17)*F17</f>
+        <f t="shared" si="1"/>
         <v>16500</v>
       </c>
       <c r="L17" s="24">
-        <f>G17</f>
+        <f t="shared" si="2"/>
         <v>5000</v>
       </c>
       <c r="M17" s="24">
-        <f>(1-$D17)*H17</f>
+        <f t="shared" si="3"/>
         <v>1000</v>
       </c>
       <c r="N17" s="24">
-        <f>(1-$D17)*I17</f>
+        <f t="shared" si="4"/>
         <v>3000</v>
       </c>
       <c r="O17" s="24">
@@ -3082,26 +3082,26 @@
         <v>0</v>
       </c>
       <c r="Z17" s="24">
-        <f>SUM(J17:Y17)</f>
+        <f t="shared" si="5"/>
         <v>62410</v>
       </c>
       <c r="AA17" s="24">
         <v>0</v>
       </c>
       <c r="AB17" s="20">
-        <f>Z17-AA17</f>
+        <f t="shared" si="6"/>
         <v>62410</v>
       </c>
       <c r="AC17" s="24" t="str">
-        <f>IF(AND($T17=6000, ($T17+$W17-$AB17)&gt;=6000),T17,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD17" s="24" t="str">
-        <f>IF(AND($T17=8000, ($T17+$W17-$AB17)&gt;=8000),T17,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE17" s="24" t="str">
-        <f>IF(($T17+$W17-$AB17)&gt;=$T17+8000,W17,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -3134,23 +3134,23 @@
         <v>6000</v>
       </c>
       <c r="J18" s="24">
-        <f>(1-$D18)*E18</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K18" s="24">
-        <f>(1-$D18)*F18</f>
+        <f t="shared" si="1"/>
         <v>23100</v>
       </c>
       <c r="L18" s="24">
-        <f>G18</f>
+        <f t="shared" si="2"/>
         <v>5000</v>
       </c>
       <c r="M18" s="24">
-        <f>(1-$D18)*H18</f>
+        <f t="shared" si="3"/>
         <v>1400</v>
       </c>
       <c r="N18" s="24">
-        <f>(1-$D18)*I18</f>
+        <f t="shared" si="4"/>
         <v>4200</v>
       </c>
       <c r="O18" s="24">
@@ -3187,26 +3187,26 @@
         <v>0</v>
       </c>
       <c r="Z18" s="24">
-        <f>SUM(J18:Y18)</f>
+        <f t="shared" si="5"/>
         <v>70610</v>
       </c>
       <c r="AA18" s="24">
         <v>0</v>
       </c>
       <c r="AB18" s="20">
-        <f>Z18-AA18</f>
+        <f t="shared" si="6"/>
         <v>70610</v>
       </c>
       <c r="AC18" s="24" t="str">
-        <f>IF(AND($T18=6000, ($T18+$W18-$AB18)&gt;=6000),T18,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD18" s="24" t="str">
-        <f>IF(AND($T18=8000, ($T18+$W18-$AB18)&gt;=8000),T18,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE18" s="24" t="str">
-        <f>IF(($T18+$W18-$AB18)&gt;=$T18+8000,W18,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -3239,23 +3239,23 @@
         <v>6000</v>
       </c>
       <c r="J19" s="24">
-        <f>(1-$D19)*E19</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K19" s="24">
-        <f>(1-$D19)*F19</f>
+        <f t="shared" si="1"/>
         <v>16500</v>
       </c>
       <c r="L19" s="24">
-        <f>G19</f>
+        <f t="shared" si="2"/>
         <v>5000</v>
       </c>
       <c r="M19" s="24">
-        <f>(1-$D19)*H19</f>
+        <f t="shared" si="3"/>
         <v>1000</v>
       </c>
       <c r="N19" s="24">
-        <f>(1-$D19)*I19</f>
+        <f t="shared" si="4"/>
         <v>3000</v>
       </c>
       <c r="O19" s="24">
@@ -3292,26 +3292,26 @@
         <v>-3145</v>
       </c>
       <c r="Z19" s="24">
-        <f>SUM(J19:Y19)</f>
+        <f t="shared" si="5"/>
         <v>67265</v>
       </c>
       <c r="AA19" s="24">
         <v>0</v>
       </c>
       <c r="AB19" s="20">
-        <f>Z19-AA19</f>
+        <f t="shared" si="6"/>
         <v>67265</v>
       </c>
       <c r="AC19" s="24" t="str">
-        <f>IF(AND($T19=6000, ($T19+$W19-$AB19)&gt;=6000),T19,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD19" s="24" t="str">
-        <f>IF(AND($T19=8000, ($T19+$W19-$AB19)&gt;=8000),T19,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE19" s="24" t="str">
-        <f>IF(($T19+$W19-$AB19)&gt;=$T19+8000,W19,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -3344,23 +3344,23 @@
         <v>6000</v>
       </c>
       <c r="J20" s="24">
-        <f>(1-$D20)*E20</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K20" s="24">
-        <f>(1-$D20)*F20</f>
+        <f t="shared" si="1"/>
         <v>23100</v>
       </c>
       <c r="L20" s="24">
-        <f>G20</f>
+        <f t="shared" si="2"/>
         <v>5000</v>
       </c>
       <c r="M20" s="24">
-        <f>(1-$D20)*H20</f>
+        <f t="shared" si="3"/>
         <v>1400</v>
       </c>
       <c r="N20" s="24">
-        <f>(1-$D20)*I20</f>
+        <f t="shared" si="4"/>
         <v>4200</v>
       </c>
       <c r="O20" s="24">
@@ -3397,35 +3397,35 @@
         <v>0</v>
       </c>
       <c r="Z20" s="24">
-        <f>SUM(J20:Y20)</f>
+        <f t="shared" si="5"/>
         <v>78610</v>
       </c>
       <c r="AA20" s="24">
         <v>0</v>
       </c>
       <c r="AB20" s="20">
-        <f>Z20-AA20</f>
+        <f t="shared" si="6"/>
         <v>78610</v>
       </c>
       <c r="AC20" s="24" t="str">
-        <f>IF(AND($T20=6000, ($T20+$W20-$AB20)&gt;=6000),T20,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD20" s="24" t="str">
-        <f>IF(AND($T20=8000, ($T20+$W20-$AB20)&gt;=8000),T20,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE20" s="24" t="str">
-        <f>IF(($T20+$W20-$AB20)&gt;=$T20+8000,W20,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="21" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A21" s="22" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B21" s="22" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C21" s="22" t="s">
         <v>44</v>
@@ -3449,23 +3449,23 @@
         <v>0</v>
       </c>
       <c r="J21" s="24">
-        <f>(1-$D21)*E21</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K21" s="24">
-        <f>(1-$D21)*F21</f>
+        <f t="shared" si="1"/>
         <v>19500</v>
       </c>
       <c r="L21" s="24">
-        <f>G21</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M21" s="24">
-        <f>(1-$D21)*H21</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N21" s="24">
-        <f>(1-$D21)*I21</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O21" s="24">
@@ -3502,26 +3502,26 @@
         <v>750</v>
       </c>
       <c r="Z21" s="24">
-        <f>SUM(J21:Y21)</f>
+        <f t="shared" si="5"/>
         <v>51180</v>
       </c>
       <c r="AA21" s="24">
         <v>0</v>
       </c>
       <c r="AB21" s="20">
-        <f>Z21-AA21</f>
+        <f t="shared" si="6"/>
         <v>51180</v>
       </c>
       <c r="AC21" s="24" t="str">
-        <f>IF(AND($T21=6000, ($T21+$W21-$AB21)&gt;=6000),T21,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD21" s="24" t="str">
-        <f>IF(AND($T21=8000, ($T21+$W21-$AB21)&gt;=8000),T21,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE21" s="24" t="str">
-        <f>IF(($T21+$W21-$AB21)&gt;=$T21+8000,W21,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -3554,23 +3554,23 @@
         <v>0</v>
       </c>
       <c r="J22" s="24">
-        <f>(1-$D22)*E22</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K22" s="24">
-        <f>(1-$D22)*F22</f>
+        <f t="shared" si="1"/>
         <v>19500</v>
       </c>
       <c r="L22" s="24">
-        <f>G22</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M22" s="24">
-        <f>(1-$D22)*H22</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N22" s="24">
-        <f>(1-$D22)*I22</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O22" s="24">
@@ -3607,26 +3607,26 @@
         <v>0</v>
       </c>
       <c r="Z22" s="24">
-        <f>SUM(J22:Y22)</f>
+        <f t="shared" si="5"/>
         <v>44430</v>
       </c>
       <c r="AA22" s="24">
         <v>0</v>
       </c>
       <c r="AB22" s="20">
-        <f>Z22-AA22</f>
+        <f t="shared" si="6"/>
         <v>44430</v>
       </c>
       <c r="AC22" s="24" t="str">
-        <f>IF(AND($T22=6000, ($T22+$W22-$AB22)&gt;=6000),T22,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD22" s="24" t="str">
-        <f>IF(AND($T22=8000, ($T22+$W22-$AB22)&gt;=8000),T22,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE22" s="24" t="str">
-        <f>IF(($T22+$W22-$AB22)&gt;=$T22+8000,W22,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -3659,23 +3659,23 @@
         <v>0</v>
       </c>
       <c r="J23" s="24">
-        <f>(1-$D23)*E23</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K23" s="24">
-        <f>(1-$D23)*F23</f>
+        <f t="shared" si="1"/>
         <v>19500</v>
       </c>
       <c r="L23" s="24">
-        <f>G23</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M23" s="24">
-        <f>(1-$D23)*H23</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N23" s="24">
-        <f>(1-$D23)*I23</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O23" s="24">
@@ -3712,26 +3712,26 @@
         <v>0</v>
       </c>
       <c r="Z23" s="24">
-        <f>SUM(J23:Y23)</f>
+        <f t="shared" si="5"/>
         <v>50430</v>
       </c>
       <c r="AA23" s="24">
         <v>0</v>
       </c>
       <c r="AB23" s="20">
-        <f>Z23-AA23</f>
+        <f t="shared" si="6"/>
         <v>50430</v>
       </c>
       <c r="AC23" s="24" t="str">
-        <f>IF(AND($T23=6000, ($T23+$W23-$AB23)&gt;=6000),T23,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD23" s="24" t="str">
-        <f>IF(AND($T23=8000, ($T23+$W23-$AB23)&gt;=8000),T23,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE23" s="24" t="str">
-        <f>IF(($T23+$W23-$AB23)&gt;=$T23+8000,W23,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -3764,23 +3764,23 @@
         <v>0</v>
       </c>
       <c r="J24" s="24">
-        <f>(1-$D24)*E24</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K24" s="24">
-        <f>(1-$D24)*F24</f>
+        <f t="shared" si="1"/>
         <v>26000</v>
       </c>
       <c r="L24" s="24">
-        <f>G24</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M24" s="24">
-        <f>(1-$D24)*H24</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N24" s="24">
-        <f>(1-$D24)*I24</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O24" s="24">
@@ -3817,26 +3817,26 @@
         <v>0</v>
       </c>
       <c r="Z24" s="24">
-        <f>SUM(J24:Y24)</f>
+        <f t="shared" si="5"/>
         <v>56930</v>
       </c>
       <c r="AA24" s="24">
         <v>0</v>
       </c>
       <c r="AB24" s="20">
-        <f>Z24-AA24</f>
+        <f t="shared" si="6"/>
         <v>56930</v>
       </c>
       <c r="AC24" s="24" t="str">
-        <f>IF(AND($T24=6000, ($T24+$W24-$AB24)&gt;=6000),T24,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD24" s="24" t="str">
-        <f>IF(AND($T24=8000, ($T24+$W24-$AB24)&gt;=8000),T24,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE24" s="24" t="str">
-        <f>IF(($T24+$W24-$AB24)&gt;=$T24+8000,W24,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -3869,23 +3869,23 @@
         <v>0</v>
       </c>
       <c r="J25" s="24">
-        <f>(1-$D25)*E25</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K25" s="24">
-        <f>(1-$D25)*F25</f>
+        <f t="shared" si="1"/>
         <v>26000</v>
       </c>
       <c r="L25" s="24">
-        <f>G25</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M25" s="24">
-        <f>(1-$D25)*H25</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N25" s="24">
-        <f>(1-$D25)*I25</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O25" s="24">
@@ -3922,26 +3922,26 @@
         <v>0</v>
       </c>
       <c r="Z25" s="24">
-        <f>SUM(J25:Y25)</f>
+        <f t="shared" si="5"/>
         <v>56930</v>
       </c>
       <c r="AA25" s="24">
         <v>0</v>
       </c>
       <c r="AB25" s="20">
-        <f>Z25-AA25</f>
+        <f t="shared" si="6"/>
         <v>56930</v>
       </c>
       <c r="AC25" s="24" t="str">
-        <f>IF(AND($T25=6000, ($T25+$W25-$AB25)&gt;=6000),T25,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD25" s="24" t="str">
-        <f>IF(AND($T25=8000, ($T25+$W25-$AB25)&gt;=8000),T25,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE25" s="24" t="str">
-        <f>IF(($T25+$W25-$AB25)&gt;=$T25+8000,W25,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -3974,23 +3974,23 @@
         <v>0</v>
       </c>
       <c r="J26" s="24">
-        <f>(1-$D26)*E26</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K26" s="24">
-        <f>(1-$D26)*F26</f>
+        <f t="shared" si="1"/>
         <v>19500</v>
       </c>
       <c r="L26" s="24">
-        <f>G26</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M26" s="24">
-        <f>(1-$D26)*H26</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N26" s="24">
-        <f>(1-$D26)*I26</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O26" s="24">
@@ -4027,26 +4027,26 @@
         <v>0</v>
       </c>
       <c r="Z26" s="24">
-        <f>SUM(J26:Y26)</f>
+        <f t="shared" si="5"/>
         <v>44430</v>
       </c>
       <c r="AA26" s="24">
         <v>0</v>
       </c>
       <c r="AB26" s="20">
-        <f>Z26-AA26</f>
+        <f t="shared" si="6"/>
         <v>44430</v>
       </c>
       <c r="AC26" s="24" t="str">
-        <f>IF(AND($T26=6000, ($T26+$W26-$AB26)&gt;=6000),T26,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD26" s="24" t="str">
-        <f>IF(AND($T26=8000, ($T26+$W26-$AB26)&gt;=8000),T26,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE26" s="24" t="str">
-        <f>IF(($T26+$W26-$AB26)&gt;=$T26+8000,W26,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
         <v>234</v>
       </c>
       <c r="B27" s="22" t="s">
-        <v>235</v>
+        <v>255</v>
       </c>
       <c r="C27" s="22" t="s">
         <v>44</v>
@@ -4079,23 +4079,23 @@
         <v>0</v>
       </c>
       <c r="J27" s="24">
-        <f>(1-$D27)*E27</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K27" s="24">
-        <f>(1-$D27)*F27</f>
+        <f t="shared" si="1"/>
         <v>26000</v>
       </c>
       <c r="L27" s="24">
-        <f>G27</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M27" s="24">
-        <f>(1-$D27)*H27</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N27" s="24">
-        <f>(1-$D27)*I27</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O27" s="24">
@@ -4132,26 +4132,26 @@
         <v>1000</v>
       </c>
       <c r="Z27" s="24">
-        <f>SUM(J27:Y27)</f>
+        <f t="shared" si="5"/>
         <v>57930</v>
       </c>
       <c r="AA27" s="24">
         <v>0</v>
       </c>
       <c r="AB27" s="20">
-        <f>Z27-AA27</f>
+        <f t="shared" si="6"/>
         <v>57930</v>
       </c>
       <c r="AC27" s="24" t="str">
-        <f>IF(AND($T27=6000, ($T27+$W27-$AB27)&gt;=6000),T27,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD27" s="24" t="str">
-        <f>IF(AND($T27=8000, ($T27+$W27-$AB27)&gt;=8000),T27,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE27" s="24" t="str">
-        <f>IF(($T27+$W27-$AB27)&gt;=$T27+8000,W27,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -4184,23 +4184,23 @@
         <v>0</v>
       </c>
       <c r="J28" s="24">
-        <f>(1-$D28)*E28</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K28" s="24">
-        <f>(1-$D28)*F28</f>
+        <f t="shared" si="1"/>
         <v>13000</v>
       </c>
       <c r="L28" s="24">
-        <f>G28</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M28" s="24">
-        <f>(1-$D28)*H28</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N28" s="24">
-        <f>(1-$D28)*I28</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O28" s="24">
@@ -4237,26 +4237,26 @@
         <v>8000</v>
       </c>
       <c r="Z28" s="24">
-        <f>SUM(J28:Y28)</f>
+        <f t="shared" si="5"/>
         <v>45930</v>
       </c>
       <c r="AA28" s="24">
         <v>0</v>
       </c>
       <c r="AB28" s="20">
-        <f>Z28-AA28</f>
+        <f t="shared" si="6"/>
         <v>45930</v>
       </c>
       <c r="AC28" s="24" t="str">
-        <f>IF(AND($T28=6000, ($T28+$W28-$AB28)&gt;=6000),T28,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD28" s="24" t="str">
-        <f>IF(AND($T28=8000, ($T28+$W28-$AB28)&gt;=8000),T28,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE28" s="24" t="str">
-        <f>IF(($T28+$W28-$AB28)&gt;=$T28+8000,W28,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -4289,23 +4289,23 @@
         <v>0</v>
       </c>
       <c r="J29" s="24">
-        <f>(1-$D29)*E29</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K29" s="24">
-        <f>(1-$D29)*F29</f>
+        <f t="shared" si="1"/>
         <v>13000</v>
       </c>
       <c r="L29" s="24">
-        <f>G29</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M29" s="24">
-        <f>(1-$D29)*H29</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N29" s="24">
-        <f>(1-$D29)*I29</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O29" s="24">
@@ -4342,26 +4342,26 @@
         <v>8000</v>
       </c>
       <c r="Z29" s="24">
-        <f>SUM(J29:Y29)</f>
+        <f t="shared" si="5"/>
         <v>45930</v>
       </c>
       <c r="AA29" s="24">
         <v>0</v>
       </c>
       <c r="AB29" s="20">
-        <f>Z29-AA29</f>
+        <f t="shared" si="6"/>
         <v>45930</v>
       </c>
       <c r="AC29" s="24" t="str">
-        <f>IF(AND($T29=6000, ($T29+$W29-$AB29)&gt;=6000),T29,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD29" s="24" t="str">
-        <f>IF(AND($T29=8000, ($T29+$W29-$AB29)&gt;=8000),T29,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE29" s="24" t="str">
-        <f>IF(($T29+$W29-$AB29)&gt;=$T29+8000,W29,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -4394,23 +4394,23 @@
         <v>0</v>
       </c>
       <c r="J30" s="24">
-        <f>(1-$D30)*E30</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K30" s="24">
-        <f>(1-$D30)*F30</f>
+        <f t="shared" si="1"/>
         <v>19500</v>
       </c>
       <c r="L30" s="24">
-        <f>G30</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M30" s="24">
-        <f>(1-$D30)*H30</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N30" s="24">
-        <f>(1-$D30)*I30</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O30" s="24">
@@ -4447,26 +4447,26 @@
         <v>0</v>
       </c>
       <c r="Z30" s="24">
-        <f>SUM(J30:Y30)</f>
+        <f t="shared" si="5"/>
         <v>50430</v>
       </c>
       <c r="AA30" s="24">
         <v>0</v>
       </c>
       <c r="AB30" s="20">
-        <f>Z30-AA30</f>
+        <f t="shared" si="6"/>
         <v>50430</v>
       </c>
       <c r="AC30" s="24" t="str">
-        <f>IF(AND($T30=6000, ($T30+$W30-$AB30)&gt;=6000),T30,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD30" s="24" t="str">
-        <f>IF(AND($T30=8000, ($T30+$W30-$AB30)&gt;=8000),T30,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE30" s="24" t="str">
-        <f>IF(($T30+$W30-$AB30)&gt;=$T30+8000,W30,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -4499,23 +4499,23 @@
         <v>0</v>
       </c>
       <c r="J31" s="24">
-        <f>(1-$D31)*E31</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K31" s="24">
-        <f>(1-$D31)*F31</f>
+        <f t="shared" si="1"/>
         <v>19500</v>
       </c>
       <c r="L31" s="24">
-        <f>G31</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M31" s="24">
-        <f>(1-$D31)*H31</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N31" s="24">
-        <f>(1-$D31)*I31</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O31" s="24">
@@ -4552,35 +4552,35 @@
         <v>0</v>
       </c>
       <c r="Z31" s="24">
-        <f>SUM(J31:Y31)</f>
+        <f t="shared" si="5"/>
         <v>50430</v>
       </c>
       <c r="AA31" s="24">
         <v>0</v>
       </c>
       <c r="AB31" s="20">
-        <f>Z31-AA31</f>
+        <f t="shared" si="6"/>
         <v>50430</v>
       </c>
       <c r="AC31" s="24" t="str">
-        <f>IF(AND($T31=6000, ($T31+$W31-$AB31)&gt;=6000),T31,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD31" s="24" t="str">
-        <f>IF(AND($T31=8000, ($T31+$W31-$AB31)&gt;=8000),T31,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE31" s="24" t="str">
-        <f>IF(($T31+$W31-$AB31)&gt;=$T31+8000,W31,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="32" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A32" s="22" t="s">
+        <v>237</v>
+      </c>
+      <c r="B32" s="22" t="s">
         <v>238</v>
-      </c>
-      <c r="B32" s="22" t="s">
-        <v>239</v>
       </c>
       <c r="C32" s="22" t="s">
         <v>44</v>
@@ -4604,23 +4604,23 @@
         <v>0</v>
       </c>
       <c r="J32" s="24">
-        <f>(1-$D32)*E32</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K32" s="24">
-        <f>(1-$D32)*F32</f>
+        <f t="shared" si="1"/>
         <v>26000</v>
       </c>
       <c r="L32" s="24">
-        <f>G32</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M32" s="24">
-        <f>(1-$D32)*H32</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N32" s="24">
-        <f>(1-$D32)*I32</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O32" s="24">
@@ -4657,26 +4657,26 @@
         <v>14000</v>
       </c>
       <c r="Z32" s="24">
-        <f>SUM(J32:Y32)</f>
+        <f t="shared" si="5"/>
         <v>64930</v>
       </c>
       <c r="AA32" s="24">
         <v>0</v>
       </c>
       <c r="AB32" s="20">
-        <f>Z32-AA32</f>
+        <f t="shared" si="6"/>
         <v>64930</v>
       </c>
       <c r="AC32" s="24" t="str">
-        <f>IF(AND($T32=6000, ($T32+$W32-$AB32)&gt;=6000),T32,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD32" s="24" t="str">
-        <f>IF(AND($T32=8000, ($T32+$W32-$AB32)&gt;=8000),T32,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE32" s="24" t="str">
-        <f>IF(($T32+$W32-$AB32)&gt;=$T32+8000,W32,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -4709,23 +4709,23 @@
         <v>0</v>
       </c>
       <c r="J33" s="24">
-        <f>(1-$D33)*E33</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K33" s="24">
-        <f>(1-$D33)*F33</f>
+        <f t="shared" si="1"/>
         <v>26000</v>
       </c>
       <c r="L33" s="24">
-        <f>G33</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M33" s="24">
-        <f>(1-$D33)*H33</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N33" s="24">
-        <f>(1-$D33)*I33</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O33" s="24">
@@ -4762,26 +4762,26 @@
         <v>7000</v>
       </c>
       <c r="Z33" s="24">
-        <f>SUM(J33:Y33)</f>
+        <f t="shared" si="5"/>
         <v>57930</v>
       </c>
       <c r="AA33" s="24">
         <v>0</v>
       </c>
       <c r="AB33" s="20">
-        <f>Z33-AA33</f>
+        <f t="shared" si="6"/>
         <v>57930</v>
       </c>
       <c r="AC33" s="24" t="str">
-        <f>IF(AND($T33=6000, ($T33+$W33-$AB33)&gt;=6000),T33,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD33" s="24" t="str">
-        <f>IF(AND($T33=8000, ($T33+$W33-$AB33)&gt;=8000),T33,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE33" s="24" t="str">
-        <f>IF(($T33+$W33-$AB33)&gt;=$T33+8000,W33,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -4814,23 +4814,23 @@
         <v>0</v>
       </c>
       <c r="J34" s="24">
-        <f>(1-$D34)*E34</f>
+        <f t="shared" ref="J34:J65" si="10">(1-$D34)*E34</f>
         <v>0</v>
       </c>
       <c r="K34" s="24">
-        <f>(1-$D34)*F34</f>
+        <f t="shared" ref="K34:K65" si="11">(1-$D34)*F34</f>
         <v>26000</v>
       </c>
       <c r="L34" s="24">
-        <f>G34</f>
+        <f t="shared" ref="L34:L65" si="12">G34</f>
         <v>4000</v>
       </c>
       <c r="M34" s="24">
-        <f>(1-$D34)*H34</f>
+        <f t="shared" ref="M34:M65" si="13">(1-$D34)*H34</f>
         <v>0</v>
       </c>
       <c r="N34" s="24">
-        <f>(1-$D34)*I34</f>
+        <f t="shared" ref="N34:N65" si="14">(1-$D34)*I34</f>
         <v>0</v>
       </c>
       <c r="O34" s="24">
@@ -4867,26 +4867,26 @@
         <v>-3030</v>
       </c>
       <c r="Z34" s="24">
-        <f>SUM(J34:Y34)</f>
+        <f t="shared" ref="Z34:Z65" si="15">SUM(J34:Y34)</f>
         <v>47900</v>
       </c>
       <c r="AA34" s="24">
         <v>0</v>
       </c>
       <c r="AB34" s="20">
-        <f>Z34-AA34</f>
+        <f t="shared" ref="AB34:AB65" si="16">Z34-AA34</f>
         <v>47900</v>
       </c>
       <c r="AC34" s="24" t="str">
-        <f>IF(AND($T34=6000, ($T34+$W34-$AB34)&gt;=6000),T34,"")</f>
+        <f t="shared" ref="AC34:AC65" si="17">IF(AND($T34=6000, ($T34+$W34-$AB34)&gt;=6000),T34,"")</f>
         <v/>
       </c>
       <c r="AD34" s="24" t="str">
-        <f>IF(AND($T34=8000, ($T34+$W34-$AB34)&gt;=8000),T34,"")</f>
+        <f t="shared" ref="AD34:AD65" si="18">IF(AND($T34=8000, ($T34+$W34-$AB34)&gt;=8000),T34,"")</f>
         <v/>
       </c>
       <c r="AE34" s="24" t="str">
-        <f>IF(($T34+$W34-$AB34)&gt;=$T34+8000,W34,"")</f>
+        <f t="shared" ref="AE34:AE65" si="19">IF(($T34+$W34-$AB34)&gt;=$T34+8000,W34,"")</f>
         <v/>
       </c>
     </row>
@@ -4919,23 +4919,23 @@
         <v>0</v>
       </c>
       <c r="J35" s="24">
-        <f>(1-$D35)*E35</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K35" s="24">
-        <f>(1-$D35)*F35</f>
+        <f t="shared" si="11"/>
         <v>26000</v>
       </c>
       <c r="L35" s="24">
-        <f>G35</f>
+        <f t="shared" si="12"/>
         <v>4000</v>
       </c>
       <c r="M35" s="24">
-        <f>(1-$D35)*H35</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="N35" s="24">
-        <f>(1-$D35)*I35</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O35" s="24">
@@ -4972,26 +4972,26 @@
         <v>0</v>
       </c>
       <c r="Z35" s="24">
-        <f>SUM(J35:Y35)</f>
+        <f t="shared" si="15"/>
         <v>56930</v>
       </c>
       <c r="AA35" s="24">
         <v>0</v>
       </c>
       <c r="AB35" s="20">
-        <f>Z35-AA35</f>
+        <f t="shared" si="16"/>
         <v>56930</v>
       </c>
       <c r="AC35" s="24" t="str">
-        <f>IF(AND($T35=6000, ($T35+$W35-$AB35)&gt;=6000),T35,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AD35" s="24" t="str">
-        <f>IF(AND($T35=8000, ($T35+$W35-$AB35)&gt;=8000),T35,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AE35" s="24" t="str">
-        <f>IF(($T35+$W35-$AB35)&gt;=$T35+8000,W35,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -5024,23 +5024,23 @@
         <v>0</v>
       </c>
       <c r="J36" s="24">
-        <f>(1-$D36)*E36</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K36" s="24">
-        <f>(1-$D36)*F36</f>
+        <f t="shared" si="11"/>
         <v>19500</v>
       </c>
       <c r="L36" s="24">
-        <f>G36</f>
+        <f t="shared" si="12"/>
         <v>4000</v>
       </c>
       <c r="M36" s="24">
-        <f>(1-$D36)*H36</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="N36" s="24">
-        <f>(1-$D36)*I36</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O36" s="24">
@@ -5077,26 +5077,26 @@
         <v>0</v>
       </c>
       <c r="Z36" s="24">
-        <f>SUM(J36:Y36)</f>
+        <f t="shared" si="15"/>
         <v>50430</v>
       </c>
       <c r="AA36" s="24">
         <v>0</v>
       </c>
       <c r="AB36" s="20">
-        <f>Z36-AA36</f>
+        <f t="shared" si="16"/>
         <v>50430</v>
       </c>
       <c r="AC36" s="24" t="str">
-        <f>IF(AND($T36=6000, ($T36+$W36-$AB36)&gt;=6000),T36,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AD36" s="24" t="str">
-        <f>IF(AND($T36=8000, ($T36+$W36-$AB36)&gt;=8000),T36,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AE36" s="24" t="str">
-        <f>IF(($T36+$W36-$AB36)&gt;=$T36+8000,W36,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -5129,23 +5129,23 @@
         <v>0</v>
       </c>
       <c r="J37" s="24">
-        <f>(1-$D37)*E37</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K37" s="24">
-        <f>(1-$D37)*F37</f>
+        <f t="shared" si="11"/>
         <v>13000</v>
       </c>
       <c r="L37" s="24">
-        <f>G37</f>
+        <f t="shared" si="12"/>
         <v>4000</v>
       </c>
       <c r="M37" s="24">
-        <f>(1-$D37)*H37</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="N37" s="24">
-        <f>(1-$D37)*I37</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O37" s="24">
@@ -5182,26 +5182,26 @@
         <v>8000</v>
       </c>
       <c r="Z37" s="24">
-        <f>SUM(J37:Y37)</f>
+        <f t="shared" si="15"/>
         <v>45930</v>
       </c>
       <c r="AA37" s="24">
         <v>0</v>
       </c>
       <c r="AB37" s="20">
-        <f>Z37-AA37</f>
+        <f t="shared" si="16"/>
         <v>45930</v>
       </c>
       <c r="AC37" s="24" t="str">
-        <f>IF(AND($T37=6000, ($T37+$W37-$AB37)&gt;=6000),T37,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AD37" s="24" t="str">
-        <f>IF(AND($T37=8000, ($T37+$W37-$AB37)&gt;=8000),T37,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AE37" s="24" t="str">
-        <f>IF(($T37+$W37-$AB37)&gt;=$T37+8000,W37,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -5234,23 +5234,23 @@
         <v>0</v>
       </c>
       <c r="J38" s="24">
-        <f>(1-$D38)*E38</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K38" s="24">
-        <f>(1-$D38)*F38</f>
+        <f t="shared" si="11"/>
         <v>19500</v>
       </c>
       <c r="L38" s="24">
-        <f>G38</f>
+        <f t="shared" si="12"/>
         <v>4000</v>
       </c>
       <c r="M38" s="24">
-        <f>(1-$D38)*H38</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="N38" s="24">
-        <f>(1-$D38)*I38</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O38" s="24">
@@ -5287,26 +5287,26 @@
         <v>0</v>
       </c>
       <c r="Z38" s="24">
-        <f>SUM(J38:Y38)</f>
+        <f t="shared" si="15"/>
         <v>44430</v>
       </c>
       <c r="AA38" s="24">
         <v>0</v>
       </c>
       <c r="AB38" s="20">
-        <f>Z38-AA38</f>
+        <f t="shared" si="16"/>
         <v>44430</v>
       </c>
       <c r="AC38" s="24" t="str">
-        <f>IF(AND($T38=6000, ($T38+$W38-$AB38)&gt;=6000),T38,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AD38" s="24" t="str">
-        <f>IF(AND($T38=8000, ($T38+$W38-$AB38)&gt;=8000),T38,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AE38" s="24" t="str">
-        <f>IF(($T38+$W38-$AB38)&gt;=$T38+8000,W38,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -5339,23 +5339,23 @@
         <v>0</v>
       </c>
       <c r="J39" s="24">
-        <f>(1-$D39)*E39</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K39" s="24">
-        <f>(1-$D39)*F39</f>
+        <f t="shared" si="11"/>
         <v>19500</v>
       </c>
       <c r="L39" s="24">
-        <f>G39</f>
+        <f t="shared" si="12"/>
         <v>4000</v>
       </c>
       <c r="M39" s="24">
-        <f>(1-$D39)*H39</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="N39" s="24">
-        <f>(1-$D39)*I39</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O39" s="24">
@@ -5392,26 +5392,26 @@
         <v>0</v>
       </c>
       <c r="Z39" s="24">
-        <f>SUM(J39:Y39)</f>
+        <f t="shared" si="15"/>
         <v>44430</v>
       </c>
       <c r="AA39" s="24">
         <v>0</v>
       </c>
       <c r="AB39" s="20">
-        <f>Z39-AA39</f>
+        <f t="shared" si="16"/>
         <v>44430</v>
       </c>
       <c r="AC39" s="24" t="str">
-        <f>IF(AND($T39=6000, ($T39+$W39-$AB39)&gt;=6000),T39,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AD39" s="24" t="str">
-        <f>IF(AND($T39=8000, ($T39+$W39-$AB39)&gt;=8000),T39,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AE39" s="24" t="str">
-        <f>IF(($T39+$W39-$AB39)&gt;=$T39+8000,W39,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -5444,23 +5444,23 @@
         <v>0</v>
       </c>
       <c r="J40" s="24">
-        <f>(1-$D40)*E40</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K40" s="24">
-        <f>(1-$D40)*F40</f>
+        <f t="shared" si="11"/>
         <v>26000</v>
       </c>
       <c r="L40" s="24">
-        <f>G40</f>
+        <f t="shared" si="12"/>
         <v>4000</v>
       </c>
       <c r="M40" s="24">
-        <f>(1-$D40)*H40</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="N40" s="24">
-        <f>(1-$D40)*I40</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O40" s="24">
@@ -5497,26 +5497,26 @@
         <v>0</v>
       </c>
       <c r="Z40" s="24">
-        <f>SUM(J40:Y40)</f>
+        <f t="shared" si="15"/>
         <v>50930</v>
       </c>
       <c r="AA40" s="24">
         <v>0</v>
       </c>
       <c r="AB40" s="20">
-        <f>Z40-AA40</f>
+        <f t="shared" si="16"/>
         <v>50930</v>
       </c>
       <c r="AC40" s="24" t="str">
-        <f>IF(AND($T40=6000, ($T40+$W40-$AB40)&gt;=6000),T40,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AD40" s="24" t="str">
-        <f>IF(AND($T40=8000, ($T40+$W40-$AB40)&gt;=8000),T40,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AE40" s="24" t="str">
-        <f>IF(($T40+$W40-$AB40)&gt;=$T40+8000,W40,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -5549,23 +5549,23 @@
         <v>0</v>
       </c>
       <c r="J41" s="24">
-        <f>(1-$D41)*E41</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K41" s="24">
-        <f>(1-$D41)*F41</f>
+        <f t="shared" si="11"/>
         <v>19500</v>
       </c>
       <c r="L41" s="24">
-        <f>G41</f>
+        <f t="shared" si="12"/>
         <v>4000</v>
       </c>
       <c r="M41" s="24">
-        <f>(1-$D41)*H41</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="N41" s="24">
-        <f>(1-$D41)*I41</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O41" s="24">
@@ -5602,26 +5602,26 @@
         <v>0</v>
       </c>
       <c r="Z41" s="24">
-        <f>SUM(J41:Y41)</f>
+        <f t="shared" si="15"/>
         <v>58680</v>
       </c>
       <c r="AA41" s="24">
         <v>0</v>
       </c>
       <c r="AB41" s="20">
-        <f>Z41-AA41</f>
+        <f t="shared" si="16"/>
         <v>58680</v>
       </c>
       <c r="AC41" s="24" t="str">
-        <f>IF(AND($T41=6000, ($T41+$W41-$AB41)&gt;=6000),T41,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AD41" s="24" t="str">
-        <f>IF(AND($T41=8000, ($T41+$W41-$AB41)&gt;=8000),T41,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AE41" s="24" t="str">
-        <f>IF(($T41+$W41-$AB41)&gt;=$T41+8000,W41,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -5654,23 +5654,23 @@
         <v>0</v>
       </c>
       <c r="J42" s="24">
-        <f>(1-$D42)*E42</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K42" s="24">
-        <f>(1-$D42)*F42</f>
+        <f t="shared" si="11"/>
         <v>13000</v>
       </c>
       <c r="L42" s="24">
-        <f>G42</f>
+        <f t="shared" si="12"/>
         <v>4000</v>
       </c>
       <c r="M42" s="24">
-        <f>(1-$D42)*H42</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="N42" s="24">
-        <f>(1-$D42)*I42</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O42" s="24">
@@ -5707,26 +5707,26 @@
         <v>0</v>
       </c>
       <c r="Z42" s="24">
-        <f>SUM(J42:Y42)</f>
+        <f t="shared" si="15"/>
         <v>52180</v>
       </c>
       <c r="AA42" s="24">
         <v>0</v>
       </c>
       <c r="AB42" s="20">
-        <f>Z42-AA42</f>
+        <f t="shared" si="16"/>
         <v>52180</v>
       </c>
       <c r="AC42" s="24" t="str">
-        <f>IF(AND($T42=6000, ($T42+$W42-$AB42)&gt;=6000),T42,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AD42" s="24" t="str">
-        <f>IF(AND($T42=8000, ($T42+$W42-$AB42)&gt;=8000),T42,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AE42" s="24" t="str">
-        <f>IF(($T42+$W42-$AB42)&gt;=$T42+8000,W42,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -5759,23 +5759,23 @@
         <v>0</v>
       </c>
       <c r="J43" s="24">
-        <f>(1-$D43)*E43</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K43" s="24">
-        <f>(1-$D43)*F43</f>
+        <f t="shared" si="11"/>
         <v>19500</v>
       </c>
       <c r="L43" s="24">
-        <f>G43</f>
+        <f t="shared" si="12"/>
         <v>4000</v>
       </c>
       <c r="M43" s="24">
-        <f>(1-$D43)*H43</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="N43" s="24">
-        <f>(1-$D43)*I43</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O43" s="24">
@@ -5812,26 +5812,26 @@
         <v>0</v>
       </c>
       <c r="Z43" s="24">
-        <f>SUM(J43:Y43)</f>
+        <f t="shared" si="15"/>
         <v>58680</v>
       </c>
       <c r="AA43" s="24">
         <v>0</v>
       </c>
       <c r="AB43" s="20">
-        <f>Z43-AA43</f>
+        <f t="shared" si="16"/>
         <v>58680</v>
       </c>
       <c r="AC43" s="24" t="str">
-        <f>IF(AND($T43=6000, ($T43+$W43-$AB43)&gt;=6000),T43,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AD43" s="24" t="str">
-        <f>IF(AND($T43=8000, ($T43+$W43-$AB43)&gt;=8000),T43,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AE43" s="24" t="str">
-        <f>IF(($T43+$W43-$AB43)&gt;=$T43+8000,W43,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -5864,23 +5864,23 @@
         <v>0</v>
       </c>
       <c r="J44" s="24">
-        <f>(1-$D44)*E44</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K44" s="24">
-        <f>(1-$D44)*F44</f>
+        <f t="shared" si="11"/>
         <v>19500</v>
       </c>
       <c r="L44" s="24">
-        <f>G44</f>
+        <f t="shared" si="12"/>
         <v>4000</v>
       </c>
       <c r="M44" s="24">
-        <f>(1-$D44)*H44</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="N44" s="24">
-        <f>(1-$D44)*I44</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O44" s="24">
@@ -5917,26 +5917,26 @@
         <v>0</v>
       </c>
       <c r="Z44" s="24">
-        <f>SUM(J44:Y44)</f>
+        <f t="shared" si="15"/>
         <v>64680</v>
       </c>
       <c r="AA44" s="24">
         <v>0</v>
       </c>
       <c r="AB44" s="20">
-        <f>Z44-AA44</f>
+        <f t="shared" si="16"/>
         <v>64680</v>
       </c>
       <c r="AC44" s="24" t="str">
-        <f>IF(AND($T44=6000, ($T44+$W44-$AB44)&gt;=6000),T44,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AD44" s="24" t="str">
-        <f>IF(AND($T44=8000, ($T44+$W44-$AB44)&gt;=8000),T44,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AE44" s="24" t="str">
-        <f>IF(($T44+$W44-$AB44)&gt;=$T44+8000,W44,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -5969,23 +5969,23 @@
         <v>0</v>
       </c>
       <c r="J45" s="24">
-        <f>(1-$D45)*E45</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K45" s="24">
-        <f>(1-$D45)*F45</f>
+        <f t="shared" si="11"/>
         <v>19500</v>
       </c>
       <c r="L45" s="24">
-        <f>G45</f>
+        <f t="shared" si="12"/>
         <v>4000</v>
       </c>
       <c r="M45" s="24">
-        <f>(1-$D45)*H45</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="N45" s="24">
-        <f>(1-$D45)*I45</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O45" s="24">
@@ -6022,26 +6022,26 @@
         <v>18500</v>
       </c>
       <c r="Z45" s="24">
-        <f>SUM(J45:Y45)</f>
+        <f t="shared" si="15"/>
         <v>83180</v>
       </c>
       <c r="AA45" s="24">
         <v>48000</v>
       </c>
       <c r="AB45" s="20">
-        <f>Z45-AA45</f>
+        <f t="shared" si="16"/>
         <v>35180</v>
       </c>
       <c r="AC45" s="24" t="str">
-        <f>IF(AND($T45=6000, ($T45+$W45-$AB45)&gt;=6000),T45,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AD45" s="24" t="str">
-        <f>IF(AND($T45=8000, ($T45+$W45-$AB45)&gt;=8000),T45,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AE45" s="24" t="str">
-        <f>IF(($T45+$W45-$AB45)&gt;=$T45+8000,W45,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -6074,23 +6074,23 @@
         <v>0</v>
       </c>
       <c r="J46" s="24">
-        <f>(1-$D46)*E46</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K46" s="24">
-        <f>(1-$D46)*F46</f>
+        <f t="shared" si="11"/>
         <v>19500</v>
       </c>
       <c r="L46" s="24">
-        <f>G46</f>
+        <f t="shared" si="12"/>
         <v>4000</v>
       </c>
       <c r="M46" s="24">
-        <f>(1-$D46)*H46</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="N46" s="24">
-        <f>(1-$D46)*I46</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O46" s="24">
@@ -6127,26 +6127,26 @@
         <v>0</v>
       </c>
       <c r="Z46" s="24">
-        <f>SUM(J46:Y46)</f>
+        <f t="shared" si="15"/>
         <v>64680</v>
       </c>
       <c r="AA46" s="24">
         <v>0</v>
       </c>
       <c r="AB46" s="20">
-        <f>Z46-AA46</f>
+        <f t="shared" si="16"/>
         <v>64680</v>
       </c>
       <c r="AC46" s="24" t="str">
-        <f>IF(AND($T46=6000, ($T46+$W46-$AB46)&gt;=6000),T46,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AD46" s="24" t="str">
-        <f>IF(AND($T46=8000, ($T46+$W46-$AB46)&gt;=8000),T46,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AE46" s="24" t="str">
-        <f>IF(($T46+$W46-$AB46)&gt;=$T46+8000,W46,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -6179,23 +6179,23 @@
         <v>0</v>
       </c>
       <c r="J47" s="24">
-        <f>(1-$D47)*E47</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K47" s="24">
-        <f>(1-$D47)*F47</f>
+        <f t="shared" si="11"/>
         <v>19500</v>
       </c>
       <c r="L47" s="24">
-        <f>G47</f>
+        <f t="shared" si="12"/>
         <v>4000</v>
       </c>
       <c r="M47" s="24">
-        <f>(1-$D47)*H47</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="N47" s="24">
-        <f>(1-$D47)*I47</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O47" s="24">
@@ -6232,26 +6232,26 @@
         <v>0</v>
       </c>
       <c r="Z47" s="24">
-        <f>SUM(J47:Y47)</f>
+        <f t="shared" si="15"/>
         <v>64680</v>
       </c>
       <c r="AA47" s="24">
         <v>0</v>
       </c>
       <c r="AB47" s="20">
-        <f>Z47-AA47</f>
+        <f t="shared" si="16"/>
         <v>64680</v>
       </c>
       <c r="AC47" s="24" t="str">
-        <f>IF(AND($T47=6000, ($T47+$W47-$AB47)&gt;=6000),T47,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AD47" s="24" t="str">
-        <f>IF(AND($T47=8000, ($T47+$W47-$AB47)&gt;=8000),T47,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AE47" s="24" t="str">
-        <f>IF(($T47+$W47-$AB47)&gt;=$T47+8000,W47,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -6284,23 +6284,23 @@
         <v>0</v>
       </c>
       <c r="J48" s="24">
-        <f>(1-$D48)*E48</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K48" s="24">
-        <f>(1-$D48)*F48</f>
+        <f t="shared" si="11"/>
         <v>19500</v>
       </c>
       <c r="L48" s="24">
-        <f>G48</f>
+        <f t="shared" si="12"/>
         <v>4000</v>
       </c>
       <c r="M48" s="24">
-        <f>(1-$D48)*H48</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="N48" s="24">
-        <f>(1-$D48)*I48</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O48" s="24">
@@ -6337,26 +6337,26 @@
         <v>0</v>
       </c>
       <c r="Z48" s="24">
-        <f>SUM(J48:Y48)</f>
+        <f t="shared" si="15"/>
         <v>64680</v>
       </c>
       <c r="AA48" s="24">
         <v>0</v>
       </c>
       <c r="AB48" s="20">
-        <f>Z48-AA48</f>
+        <f t="shared" si="16"/>
         <v>64680</v>
       </c>
       <c r="AC48" s="24" t="str">
-        <f>IF(AND($T48=6000, ($T48+$W48-$AB48)&gt;=6000),T48,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AD48" s="24" t="str">
-        <f>IF(AND($T48=8000, ($T48+$W48-$AB48)&gt;=8000),T48,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AE48" s="24" t="str">
-        <f>IF(($T48+$W48-$AB48)&gt;=$T48+8000,W48,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -6389,23 +6389,23 @@
         <v>0</v>
       </c>
       <c r="J49" s="24">
-        <f>(1-$D49)*E49</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K49" s="24">
-        <f>(1-$D49)*F49</f>
+        <f t="shared" si="11"/>
         <v>26000</v>
       </c>
       <c r="L49" s="24">
-        <f>G49</f>
+        <f t="shared" si="12"/>
         <v>4000</v>
       </c>
       <c r="M49" s="24">
-        <f>(1-$D49)*H49</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="N49" s="24">
-        <f>(1-$D49)*I49</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O49" s="24">
@@ -6442,26 +6442,26 @@
         <v>14240</v>
       </c>
       <c r="Z49" s="24">
-        <f>SUM(J49:Y49)</f>
+        <f t="shared" si="15"/>
         <v>85420</v>
       </c>
       <c r="AA49" s="24">
         <v>0</v>
       </c>
       <c r="AB49" s="20">
-        <f>Z49-AA49</f>
+        <f t="shared" si="16"/>
         <v>85420</v>
       </c>
       <c r="AC49" s="24" t="str">
-        <f>IF(AND($T49=6000, ($T49+$W49-$AB49)&gt;=6000),T49,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AD49" s="24" t="str">
-        <f>IF(AND($T49=8000, ($T49+$W49-$AB49)&gt;=8000),T49,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AE49" s="24" t="str">
-        <f>IF(($T49+$W49-$AB49)&gt;=$T49+8000,W49,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -6494,23 +6494,23 @@
         <v>0</v>
       </c>
       <c r="J50" s="24">
-        <f>(1-$D50)*E50</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K50" s="24">
-        <f>(1-$D50)*F50</f>
+        <f t="shared" si="11"/>
         <v>26000</v>
       </c>
       <c r="L50" s="24">
-        <f>G50</f>
+        <f t="shared" si="12"/>
         <v>4000</v>
       </c>
       <c r="M50" s="24">
-        <f>(1-$D50)*H50</f>
+        <f t="shared" si="13"/>
         <v>1000</v>
       </c>
       <c r="N50" s="24">
-        <f>(1-$D50)*I50</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O50" s="24">
@@ -6547,26 +6547,26 @@
         <v>-1000</v>
       </c>
       <c r="Z50" s="24">
-        <f>SUM(J50:Y50)</f>
+        <f t="shared" si="15"/>
         <v>42140</v>
       </c>
       <c r="AA50" s="24">
         <v>0</v>
       </c>
       <c r="AB50" s="20">
-        <f>Z50-AA50</f>
+        <f t="shared" si="16"/>
         <v>42140</v>
       </c>
       <c r="AC50" s="24" t="str">
-        <f>IF(AND($T50=6000, ($T50+$W50-$AB50)&gt;=6000),T50,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AD50" s="24" t="str">
-        <f>IF(AND($T50=8000, ($T50+$W50-$AB50)&gt;=8000),T50,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AE50" s="24" t="str">
-        <f>IF(($T50+$W50-$AB50)&gt;=$T50+8000,W50,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -6599,23 +6599,23 @@
         <v>0</v>
       </c>
       <c r="J51" s="24">
-        <f>(1-$D51)*E51</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K51" s="24">
-        <f>(1-$D51)*F51</f>
+        <f t="shared" si="11"/>
         <v>26000</v>
       </c>
       <c r="L51" s="24">
-        <f>G51</f>
+        <f t="shared" si="12"/>
         <v>4000</v>
       </c>
       <c r="M51" s="24">
-        <f>(1-$D51)*H51</f>
+        <f t="shared" si="13"/>
         <v>1000</v>
       </c>
       <c r="N51" s="24">
-        <f>(1-$D51)*I51</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O51" s="24">
@@ -6652,26 +6652,26 @@
         <v>0</v>
       </c>
       <c r="Z51" s="24">
-        <f>SUM(J51:Y51)</f>
+        <f t="shared" si="15"/>
         <v>43140</v>
       </c>
       <c r="AA51" s="24">
         <v>0</v>
       </c>
       <c r="AB51" s="20">
-        <f>Z51-AA51</f>
+        <f t="shared" si="16"/>
         <v>43140</v>
       </c>
       <c r="AC51" s="24" t="str">
-        <f>IF(AND($T51=6000, ($T51+$W51-$AB51)&gt;=6000),T51,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AD51" s="24" t="str">
-        <f>IF(AND($T51=8000, ($T51+$W51-$AB51)&gt;=8000),T51,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AE51" s="24" t="str">
-        <f>IF(($T51+$W51-$AB51)&gt;=$T51+8000,W51,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -6704,23 +6704,23 @@
         <v>0</v>
       </c>
       <c r="J52" s="24">
-        <f>(1-$D52)*E52</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K52" s="24">
-        <f>(1-$D52)*F52</f>
+        <f t="shared" si="11"/>
         <v>26000</v>
       </c>
       <c r="L52" s="24">
-        <f>G52</f>
+        <f t="shared" si="12"/>
         <v>4000</v>
       </c>
       <c r="M52" s="24">
-        <f>(1-$D52)*H52</f>
+        <f t="shared" si="13"/>
         <v>1000</v>
       </c>
       <c r="N52" s="24">
-        <f>(1-$D52)*I52</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O52" s="24">
@@ -6757,26 +6757,26 @@
         <v>0</v>
       </c>
       <c r="Z52" s="24">
-        <f>SUM(J52:Y52)</f>
+        <f t="shared" si="15"/>
         <v>43140</v>
       </c>
       <c r="AA52" s="24">
         <v>0</v>
       </c>
       <c r="AB52" s="20">
-        <f>Z52-AA52</f>
+        <f t="shared" si="16"/>
         <v>43140</v>
       </c>
       <c r="AC52" s="24" t="str">
-        <f>IF(AND($T52=6000, ($T52+$W52-$AB52)&gt;=6000),T52,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AD52" s="24" t="str">
-        <f>IF(AND($T52=8000, ($T52+$W52-$AB52)&gt;=8000),T52,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AE52" s="24" t="str">
-        <f>IF(($T52+$W52-$AB52)&gt;=$T52+8000,W52,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -6809,23 +6809,23 @@
         <v>0</v>
       </c>
       <c r="J53" s="24">
-        <f>(1-$D53)*E53</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K53" s="24">
-        <f>(1-$D53)*F53</f>
+        <f t="shared" si="11"/>
         <v>26000</v>
       </c>
       <c r="L53" s="24">
-        <f>G53</f>
+        <f t="shared" si="12"/>
         <v>4000</v>
       </c>
       <c r="M53" s="24">
-        <f>(1-$D53)*H53</f>
+        <f t="shared" si="13"/>
         <v>1000</v>
       </c>
       <c r="N53" s="24">
-        <f>(1-$D53)*I53</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O53" s="24">
@@ -6862,26 +6862,26 @@
         <v>0</v>
       </c>
       <c r="Z53" s="24">
-        <f>SUM(J53:Y53)</f>
+        <f t="shared" si="15"/>
         <v>43140</v>
       </c>
       <c r="AA53" s="24">
         <v>0</v>
       </c>
       <c r="AB53" s="20">
-        <f>Z53-AA53</f>
+        <f t="shared" si="16"/>
         <v>43140</v>
       </c>
       <c r="AC53" s="24" t="str">
-        <f>IF(AND($T53=6000, ($T53+$W53-$AB53)&gt;=6000),T53,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AD53" s="24" t="str">
-        <f>IF(AND($T53=8000, ($T53+$W53-$AB53)&gt;=8000),T53,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AE53" s="24" t="str">
-        <f>IF(($T53+$W53-$AB53)&gt;=$T53+8000,W53,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -6914,23 +6914,23 @@
         <v>0</v>
       </c>
       <c r="J54" s="24">
-        <f>(1-$D54)*E54</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K54" s="24">
-        <f>(1-$D54)*F54</f>
+        <f t="shared" si="11"/>
         <v>26000</v>
       </c>
       <c r="L54" s="24">
-        <f>G54</f>
+        <f t="shared" si="12"/>
         <v>4000</v>
       </c>
       <c r="M54" s="24">
-        <f>(1-$D54)*H54</f>
+        <f t="shared" si="13"/>
         <v>1000</v>
       </c>
       <c r="N54" s="24">
-        <f>(1-$D54)*I54</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O54" s="24">
@@ -6967,35 +6967,35 @@
         <v>0</v>
       </c>
       <c r="Z54" s="24">
-        <f>SUM(J54:Y54)</f>
+        <f t="shared" si="15"/>
         <v>43140</v>
       </c>
       <c r="AA54" s="24">
         <v>0</v>
       </c>
       <c r="AB54" s="20">
-        <f>Z54-AA54</f>
+        <f t="shared" si="16"/>
         <v>43140</v>
       </c>
       <c r="AC54" s="24" t="str">
-        <f>IF(AND($T54=6000, ($T54+$W54-$AB54)&gt;=6000),T54,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AD54" s="24" t="str">
-        <f>IF(AND($T54=8000, ($T54+$W54-$AB54)&gt;=8000),T54,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AE54" s="24" t="str">
-        <f>IF(($T54+$W54-$AB54)&gt;=$T54+8000,W54,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="55" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A55" s="22" t="s">
+        <v>243</v>
+      </c>
+      <c r="B55" s="22" t="s">
         <v>244</v>
-      </c>
-      <c r="B55" s="22" t="s">
-        <v>245</v>
       </c>
       <c r="C55" s="22" t="s">
         <v>49</v>
@@ -7019,23 +7019,23 @@
         <v>0</v>
       </c>
       <c r="J55" s="24">
-        <f>(1-$D55)*E55</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K55" s="24">
-        <f>(1-$D55)*F55</f>
+        <f t="shared" si="11"/>
         <v>26000</v>
       </c>
       <c r="L55" s="24">
-        <f>G55</f>
+        <f t="shared" si="12"/>
         <v>4000</v>
       </c>
       <c r="M55" s="24">
-        <f>(1-$D55)*H55</f>
+        <f t="shared" si="13"/>
         <v>1000</v>
       </c>
       <c r="N55" s="24">
-        <f>(1-$D55)*I55</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O55" s="24">
@@ -7072,26 +7072,26 @@
         <v>0</v>
       </c>
       <c r="Z55" s="24">
-        <f>SUM(J55:Y55)</f>
+        <f t="shared" si="15"/>
         <v>43140</v>
       </c>
       <c r="AA55" s="24">
         <v>0</v>
       </c>
       <c r="AB55" s="20">
-        <f>Z55-AA55</f>
+        <f t="shared" si="16"/>
         <v>43140</v>
       </c>
       <c r="AC55" s="24" t="str">
-        <f>IF(AND($T55=6000, ($T55+$W55-$AB55)&gt;=6000),T55,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AD55" s="24" t="str">
-        <f>IF(AND($T55=8000, ($T55+$W55-$AB55)&gt;=8000),T55,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AE55" s="24" t="str">
-        <f>IF(($T55+$W55-$AB55)&gt;=$T55+8000,W55,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -7124,23 +7124,23 @@
         <v>0</v>
       </c>
       <c r="J56" s="24">
-        <f>(1-$D56)*E56</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K56" s="24">
-        <f>(1-$D56)*F56</f>
+        <f t="shared" si="11"/>
         <v>26000</v>
       </c>
       <c r="L56" s="24">
-        <f>G56</f>
+        <f t="shared" si="12"/>
         <v>4000</v>
       </c>
       <c r="M56" s="24">
-        <f>(1-$D56)*H56</f>
+        <f t="shared" si="13"/>
         <v>1000</v>
       </c>
       <c r="N56" s="24">
-        <f>(1-$D56)*I56</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O56" s="24">
@@ -7177,26 +7177,26 @@
         <v>2000</v>
       </c>
       <c r="Z56" s="24">
-        <f>SUM(J56:Y56)</f>
+        <f t="shared" si="15"/>
         <v>45140</v>
       </c>
       <c r="AA56" s="24">
         <v>0</v>
       </c>
       <c r="AB56" s="20">
-        <f>Z56-AA56</f>
+        <f t="shared" si="16"/>
         <v>45140</v>
       </c>
       <c r="AC56" s="24" t="str">
-        <f>IF(AND($T56=6000, ($T56+$W56-$AB56)&gt;=6000),T56,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AD56" s="24" t="str">
-        <f>IF(AND($T56=8000, ($T56+$W56-$AB56)&gt;=8000),T56,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AE56" s="24" t="str">
-        <f>IF(($T56+$W56-$AB56)&gt;=$T56+8000,W56,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -7229,23 +7229,23 @@
         <v>0</v>
       </c>
       <c r="J57" s="24">
-        <f>(1-$D57)*E57</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K57" s="24">
-        <f>(1-$D57)*F57</f>
+        <f t="shared" si="11"/>
         <v>13000</v>
       </c>
       <c r="L57" s="24">
-        <f>G57</f>
+        <f t="shared" si="12"/>
         <v>4000</v>
       </c>
       <c r="M57" s="24">
-        <f>(1-$D57)*H57</f>
+        <f t="shared" si="13"/>
         <v>500</v>
       </c>
       <c r="N57" s="24">
-        <f>(1-$D57)*I57</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O57" s="24">
@@ -7282,26 +7282,26 @@
         <v>0</v>
       </c>
       <c r="Z57" s="24">
-        <f>SUM(J57:Y57)</f>
+        <f t="shared" si="15"/>
         <v>29640</v>
       </c>
       <c r="AA57" s="24">
         <v>0</v>
       </c>
       <c r="AB57" s="20">
-        <f>Z57-AA57</f>
+        <f t="shared" si="16"/>
         <v>29640</v>
       </c>
       <c r="AC57" s="24" t="str">
-        <f>IF(AND($T57=6000, ($T57+$W57-$AB57)&gt;=6000),T57,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AD57" s="24" t="str">
-        <f>IF(AND($T57=8000, ($T57+$W57-$AB57)&gt;=8000),T57,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AE57" s="24" t="str">
-        <f>IF(($T57+$W57-$AB57)&gt;=$T57+8000,W57,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -7334,23 +7334,23 @@
         <v>0</v>
       </c>
       <c r="J58" s="24">
-        <f>(1-$D58)*E58</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K58" s="24">
-        <f>(1-$D58)*F58</f>
+        <f t="shared" si="11"/>
         <v>26000</v>
       </c>
       <c r="L58" s="24">
-        <f>G58</f>
+        <f t="shared" si="12"/>
         <v>4000</v>
       </c>
       <c r="M58" s="24">
-        <f>(1-$D58)*H58</f>
+        <f t="shared" si="13"/>
         <v>1000</v>
       </c>
       <c r="N58" s="24">
-        <f>(1-$D58)*I58</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O58" s="24">
@@ -7387,26 +7387,26 @@
         <v>0</v>
       </c>
       <c r="Z58" s="24">
-        <f>SUM(J58:Y58)</f>
+        <f t="shared" si="15"/>
         <v>43140</v>
       </c>
       <c r="AA58" s="24">
         <v>0</v>
       </c>
       <c r="AB58" s="20">
-        <f>Z58-AA58</f>
+        <f t="shared" si="16"/>
         <v>43140</v>
       </c>
       <c r="AC58" s="24" t="str">
-        <f>IF(AND($T58=6000, ($T58+$W58-$AB58)&gt;=6000),T58,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AD58" s="24" t="str">
-        <f>IF(AND($T58=8000, ($T58+$W58-$AB58)&gt;=8000),T58,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AE58" s="24" t="str">
-        <f>IF(($T58+$W58-$AB58)&gt;=$T58+8000,W58,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -7439,23 +7439,23 @@
         <v>0</v>
       </c>
       <c r="J59" s="24">
-        <f>(1-$D59)*E59</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K59" s="24">
-        <f>(1-$D59)*F59</f>
+        <f t="shared" si="11"/>
         <v>19500</v>
       </c>
       <c r="L59" s="24">
-        <f>G59</f>
+        <f t="shared" si="12"/>
         <v>4000</v>
       </c>
       <c r="M59" s="24">
-        <f>(1-$D59)*H59</f>
+        <f t="shared" si="13"/>
         <v>750</v>
       </c>
       <c r="N59" s="24">
-        <f>(1-$D59)*I59</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O59" s="24">
@@ -7492,26 +7492,26 @@
         <v>-500</v>
       </c>
       <c r="Z59" s="24">
-        <f>SUM(J59:Y59)</f>
+        <f t="shared" si="15"/>
         <v>35890</v>
       </c>
       <c r="AA59" s="24">
         <v>0</v>
       </c>
       <c r="AB59" s="20">
-        <f>Z59-AA59</f>
+        <f t="shared" si="16"/>
         <v>35890</v>
       </c>
       <c r="AC59" s="24" t="str">
-        <f>IF(AND($T59=6000, ($T59+$W59-$AB59)&gt;=6000),T59,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AD59" s="24" t="str">
-        <f>IF(AND($T59=8000, ($T59+$W59-$AB59)&gt;=8000),T59,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AE59" s="24" t="str">
-        <f>IF(($T59+$W59-$AB59)&gt;=$T59+8000,W59,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -7544,23 +7544,23 @@
         <v>0</v>
       </c>
       <c r="J60" s="24">
-        <f>(1-$D60)*E60</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K60" s="24">
-        <f>(1-$D60)*F60</f>
+        <f t="shared" si="11"/>
         <v>19500</v>
       </c>
       <c r="L60" s="24">
-        <f>G60</f>
+        <f t="shared" si="12"/>
         <v>4000</v>
       </c>
       <c r="M60" s="24">
-        <f>(1-$D60)*H60</f>
+        <f t="shared" si="13"/>
         <v>750</v>
       </c>
       <c r="N60" s="24">
-        <f>(1-$D60)*I60</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O60" s="24">
@@ -7597,26 +7597,26 @@
         <v>0</v>
       </c>
       <c r="Z60" s="24">
-        <f>SUM(J60:Y60)</f>
+        <f t="shared" si="15"/>
         <v>36390</v>
       </c>
       <c r="AA60" s="24">
         <v>0</v>
       </c>
       <c r="AB60" s="20">
-        <f>Z60-AA60</f>
+        <f t="shared" si="16"/>
         <v>36390</v>
       </c>
       <c r="AC60" s="24" t="str">
-        <f>IF(AND($T60=6000, ($T60+$W60-$AB60)&gt;=6000),T60,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AD60" s="24" t="str">
-        <f>IF(AND($T60=8000, ($T60+$W60-$AB60)&gt;=8000),T60,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AE60" s="24" t="str">
-        <f>IF(($T60+$W60-$AB60)&gt;=$T60+8000,W60,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -7649,23 +7649,23 @@
         <v>0</v>
       </c>
       <c r="J61" s="24">
-        <f>(1-$D61)*E61</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K61" s="24">
-        <f>(1-$D61)*F61</f>
+        <f t="shared" si="11"/>
         <v>19500</v>
       </c>
       <c r="L61" s="24">
-        <f>G61</f>
+        <f t="shared" si="12"/>
         <v>4000</v>
       </c>
       <c r="M61" s="24">
-        <f>(1-$D61)*H61</f>
+        <f t="shared" si="13"/>
         <v>750</v>
       </c>
       <c r="N61" s="24">
-        <f>(1-$D61)*I61</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O61" s="24">
@@ -7702,26 +7702,26 @@
         <v>19200</v>
       </c>
       <c r="Z61" s="24">
-        <f>SUM(J61:Y61)</f>
+        <f t="shared" si="15"/>
         <v>55590</v>
       </c>
       <c r="AA61" s="24">
         <v>0</v>
       </c>
       <c r="AB61" s="20">
-        <f>Z61-AA61</f>
+        <f t="shared" si="16"/>
         <v>55590</v>
       </c>
       <c r="AC61" s="24" t="str">
-        <f>IF(AND($T61=6000, ($T61+$W61-$AB61)&gt;=6000),T61,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AD61" s="24" t="str">
-        <f>IF(AND($T61=8000, ($T61+$W61-$AB61)&gt;=8000),T61,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AE61" s="24" t="str">
-        <f>IF(($T61+$W61-$AB61)&gt;=$T61+8000,W61,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -7754,23 +7754,23 @@
         <v>0</v>
       </c>
       <c r="J62" s="24">
-        <f>(1-$D62)*E62</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K62" s="24">
-        <f>(1-$D62)*F62</f>
+        <f t="shared" si="11"/>
         <v>19500</v>
       </c>
       <c r="L62" s="24">
-        <f>G62</f>
+        <f t="shared" si="12"/>
         <v>4000</v>
       </c>
       <c r="M62" s="24">
-        <f>(1-$D62)*H62</f>
+        <f t="shared" si="13"/>
         <v>750</v>
       </c>
       <c r="N62" s="24">
-        <f>(1-$D62)*I62</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O62" s="24">
@@ -7807,26 +7807,26 @@
         <v>19200</v>
       </c>
       <c r="Z62" s="24">
-        <f>SUM(J62:Y62)</f>
+        <f t="shared" si="15"/>
         <v>55590</v>
       </c>
       <c r="AA62" s="24">
         <v>0</v>
       </c>
       <c r="AB62" s="20">
-        <f>Z62-AA62</f>
+        <f t="shared" si="16"/>
         <v>55590</v>
       </c>
       <c r="AC62" s="24" t="str">
-        <f>IF(AND($T62=6000, ($T62+$W62-$AB62)&gt;=6000),T62,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AD62" s="24" t="str">
-        <f>IF(AND($T62=8000, ($T62+$W62-$AB62)&gt;=8000),T62,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AE62" s="24" t="str">
-        <f>IF(($T62+$W62-$AB62)&gt;=$T62+8000,W62,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -7859,23 +7859,23 @@
         <v>0</v>
       </c>
       <c r="J63" s="24">
-        <f>(1-$D63)*E63</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K63" s="24">
-        <f>(1-$D63)*F63</f>
+        <f t="shared" si="11"/>
         <v>19500</v>
       </c>
       <c r="L63" s="24">
-        <f>G63</f>
+        <f t="shared" si="12"/>
         <v>4000</v>
       </c>
       <c r="M63" s="24">
-        <f>(1-$D63)*H63</f>
+        <f t="shared" si="13"/>
         <v>750</v>
       </c>
       <c r="N63" s="24">
-        <f>(1-$D63)*I63</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O63" s="24">
@@ -7912,26 +7912,26 @@
         <v>0</v>
       </c>
       <c r="Z63" s="24">
-        <f>SUM(J63:Y63)</f>
+        <f t="shared" si="15"/>
         <v>60390</v>
       </c>
       <c r="AA63" s="24">
         <v>0</v>
       </c>
       <c r="AB63" s="20">
-        <f>Z63-AA63</f>
+        <f t="shared" si="16"/>
         <v>60390</v>
       </c>
       <c r="AC63" s="24" t="str">
-        <f>IF(AND($T63=6000, ($T63+$W63-$AB63)&gt;=6000),T63,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AD63" s="24" t="str">
-        <f>IF(AND($T63=8000, ($T63+$W63-$AB63)&gt;=8000),T63,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AE63" s="24" t="str">
-        <f>IF(($T63+$W63-$AB63)&gt;=$T63+8000,W63,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -7964,23 +7964,23 @@
         <v>0</v>
       </c>
       <c r="J64" s="24">
-        <f>(1-$D64)*E64</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K64" s="24">
-        <f>(1-$D64)*F64</f>
+        <f t="shared" si="11"/>
         <v>19500</v>
       </c>
       <c r="L64" s="24">
-        <f>G64</f>
+        <f t="shared" si="12"/>
         <v>4000</v>
       </c>
       <c r="M64" s="24">
-        <f>(1-$D64)*H64</f>
+        <f t="shared" si="13"/>
         <v>750</v>
       </c>
       <c r="N64" s="24">
-        <f>(1-$D64)*I64</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O64" s="24">
@@ -8017,26 +8017,26 @@
         <v>3500</v>
       </c>
       <c r="Z64" s="24">
-        <f>SUM(J64:Y64)</f>
+        <f t="shared" si="15"/>
         <v>39890</v>
       </c>
       <c r="AA64" s="24">
         <v>0</v>
       </c>
       <c r="AB64" s="20">
-        <f>Z64-AA64</f>
+        <f t="shared" si="16"/>
         <v>39890</v>
       </c>
       <c r="AC64" s="24" t="str">
-        <f>IF(AND($T64=6000, ($T64+$W64-$AB64)&gt;=6000),T64,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AD64" s="24" t="str">
-        <f>IF(AND($T64=8000, ($T64+$W64-$AB64)&gt;=8000),T64,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AE64" s="24" t="str">
-        <f>IF(($T64+$W64-$AB64)&gt;=$T64+8000,W64,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -8069,23 +8069,23 @@
         <v>0</v>
       </c>
       <c r="J65" s="24">
-        <f>(1-$D65)*E65</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K65" s="24">
-        <f>(1-$D65)*F65</f>
+        <f t="shared" si="11"/>
         <v>26000</v>
       </c>
       <c r="L65" s="24">
-        <f>G65</f>
+        <f t="shared" si="12"/>
         <v>4000</v>
       </c>
       <c r="M65" s="24">
-        <f>(1-$D65)*H65</f>
+        <f t="shared" si="13"/>
         <v>1000</v>
       </c>
       <c r="N65" s="24">
-        <f>(1-$D65)*I65</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O65" s="24">
@@ -8122,26 +8122,26 @@
         <v>-10000</v>
       </c>
       <c r="Z65" s="24">
-        <f>SUM(J65:Y65)</f>
+        <f t="shared" si="15"/>
         <v>33140</v>
       </c>
       <c r="AA65" s="24">
         <v>0</v>
       </c>
       <c r="AB65" s="20">
-        <f>Z65-AA65</f>
+        <f t="shared" si="16"/>
         <v>33140</v>
       </c>
       <c r="AC65" s="24" t="str">
-        <f>IF(AND($T65=6000, ($T65+$W65-$AB65)&gt;=6000),T65,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AD65" s="24" t="str">
-        <f>IF(AND($T65=8000, ($T65+$W65-$AB65)&gt;=8000),T65,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AE65" s="24" t="str">
-        <f>IF(($T65+$W65-$AB65)&gt;=$T65+8000,W65,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -8174,23 +8174,23 @@
         <v>0</v>
       </c>
       <c r="J66" s="24">
-        <f>(1-$D66)*E66</f>
+        <f t="shared" ref="J66:J97" si="20">(1-$D66)*E66</f>
         <v>0</v>
       </c>
       <c r="K66" s="24">
-        <f>(1-$D66)*F66</f>
+        <f t="shared" ref="K66:K97" si="21">(1-$D66)*F66</f>
         <v>26000</v>
       </c>
       <c r="L66" s="24">
-        <f>G66</f>
+        <f t="shared" ref="L66:L97" si="22">G66</f>
         <v>4000</v>
       </c>
       <c r="M66" s="24">
-        <f>(1-$D66)*H66</f>
+        <f t="shared" ref="M66:M97" si="23">(1-$D66)*H66</f>
         <v>1000</v>
       </c>
       <c r="N66" s="24">
-        <f>(1-$D66)*I66</f>
+        <f t="shared" ref="N66:N97" si="24">(1-$D66)*I66</f>
         <v>0</v>
       </c>
       <c r="O66" s="24">
@@ -8227,26 +8227,26 @@
         <v>1000</v>
       </c>
       <c r="Z66" s="24">
-        <f>SUM(J66:Y66)</f>
+        <f t="shared" ref="Z66:Z97" si="25">SUM(J66:Y66)</f>
         <v>44140</v>
       </c>
       <c r="AA66" s="24">
         <v>0</v>
       </c>
       <c r="AB66" s="20">
-        <f>Z66-AA66</f>
+        <f t="shared" ref="AB66:AB97" si="26">Z66-AA66</f>
         <v>44140</v>
       </c>
       <c r="AC66" s="24" t="str">
-        <f>IF(AND($T66=6000, ($T66+$W66-$AB66)&gt;=6000),T66,"")</f>
+        <f t="shared" ref="AC66:AC97" si="27">IF(AND($T66=6000, ($T66+$W66-$AB66)&gt;=6000),T66,"")</f>
         <v/>
       </c>
       <c r="AD66" s="24" t="str">
-        <f>IF(AND($T66=8000, ($T66+$W66-$AB66)&gt;=8000),T66,"")</f>
+        <f t="shared" ref="AD66:AD97" si="28">IF(AND($T66=8000, ($T66+$W66-$AB66)&gt;=8000),T66,"")</f>
         <v/>
       </c>
       <c r="AE66" s="24" t="str">
-        <f>IF(($T66+$W66-$AB66)&gt;=$T66+8000,W66,"")</f>
+        <f t="shared" ref="AE66:AE97" si="29">IF(($T66+$W66-$AB66)&gt;=$T66+8000,W66,"")</f>
         <v/>
       </c>
     </row>
@@ -8279,23 +8279,23 @@
         <v>0</v>
       </c>
       <c r="J67" s="24">
-        <f>(1-$D67)*E67</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="K67" s="24">
-        <f>(1-$D67)*F67</f>
+        <f t="shared" si="21"/>
         <v>19500</v>
       </c>
       <c r="L67" s="24">
-        <f>G67</f>
+        <f t="shared" si="22"/>
         <v>4000</v>
       </c>
       <c r="M67" s="24">
-        <f>(1-$D67)*H67</f>
+        <f t="shared" si="23"/>
         <v>750</v>
       </c>
       <c r="N67" s="24">
-        <f>(1-$D67)*I67</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="O67" s="24">
@@ -8332,26 +8332,26 @@
         <v>0</v>
       </c>
       <c r="Z67" s="24">
-        <f>SUM(J67:Y67)</f>
+        <f t="shared" si="25"/>
         <v>36390</v>
       </c>
       <c r="AA67" s="24">
         <v>0</v>
       </c>
       <c r="AB67" s="20">
-        <f>Z67-AA67</f>
+        <f t="shared" si="26"/>
         <v>36390</v>
       </c>
       <c r="AC67" s="24" t="str">
-        <f>IF(AND($T67=6000, ($T67+$W67-$AB67)&gt;=6000),T67,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AD67" s="24" t="str">
-        <f>IF(AND($T67=8000, ($T67+$W67-$AB67)&gt;=8000),T67,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AE67" s="24" t="str">
-        <f>IF(($T67+$W67-$AB67)&gt;=$T67+8000,W67,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -8384,23 +8384,23 @@
         <v>0</v>
       </c>
       <c r="J68" s="24">
-        <f>(1-$D68)*E68</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="K68" s="24">
-        <f>(1-$D68)*F68</f>
+        <f t="shared" si="21"/>
         <v>19500</v>
       </c>
       <c r="L68" s="24">
-        <f>G68</f>
+        <f t="shared" si="22"/>
         <v>4000</v>
       </c>
       <c r="M68" s="24">
-        <f>(1-$D68)*H68</f>
+        <f t="shared" si="23"/>
         <v>750</v>
       </c>
       <c r="N68" s="24">
-        <f>(1-$D68)*I68</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="O68" s="24">
@@ -8437,26 +8437,26 @@
         <v>0</v>
       </c>
       <c r="Z68" s="24">
-        <f>SUM(J68:Y68)</f>
+        <f t="shared" si="25"/>
         <v>44280</v>
       </c>
       <c r="AA68" s="24">
         <v>0</v>
       </c>
       <c r="AB68" s="20">
-        <f>Z68-AA68</f>
+        <f t="shared" si="26"/>
         <v>44280</v>
       </c>
       <c r="AC68" s="24" t="str">
-        <f>IF(AND($T68=6000, ($T68+$W68-$AB68)&gt;=6000),T68,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AD68" s="24" t="str">
-        <f>IF(AND($T68=8000, ($T68+$W68-$AB68)&gt;=8000),T68,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AE68" s="24" t="str">
-        <f>IF(($T68+$W68-$AB68)&gt;=$T68+8000,W68,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -8489,23 +8489,23 @@
         <v>0</v>
       </c>
       <c r="J69" s="24">
-        <f>(1-$D69)*E69</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="K69" s="24">
-        <f>(1-$D69)*F69</f>
+        <f t="shared" si="21"/>
         <v>19500</v>
       </c>
       <c r="L69" s="24">
-        <f>G69</f>
+        <f t="shared" si="22"/>
         <v>4000</v>
       </c>
       <c r="M69" s="24">
-        <f>(1-$D69)*H69</f>
+        <f t="shared" si="23"/>
         <v>750</v>
       </c>
       <c r="N69" s="24">
-        <f>(1-$D69)*I69</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="O69" s="24">
@@ -8542,26 +8542,26 @@
         <v>-90</v>
       </c>
       <c r="Z69" s="24">
-        <f>SUM(J69:Y69)</f>
+        <f t="shared" si="25"/>
         <v>50190</v>
       </c>
       <c r="AA69" s="24">
         <v>0</v>
       </c>
       <c r="AB69" s="20">
-        <f>Z69-AA69</f>
+        <f t="shared" si="26"/>
         <v>50190</v>
       </c>
       <c r="AC69" s="24" t="str">
-        <f>IF(AND($T69=6000, ($T69+$W69-$AB69)&gt;=6000),T69,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AD69" s="24" t="str">
-        <f>IF(AND($T69=8000, ($T69+$W69-$AB69)&gt;=8000),T69,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AE69" s="24" t="str">
-        <f>IF(($T69+$W69-$AB69)&gt;=$T69+8000,W69,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -8594,23 +8594,23 @@
         <v>0</v>
       </c>
       <c r="J70" s="24">
-        <f>(1-$D70)*E70</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="K70" s="24">
-        <f>(1-$D70)*F70</f>
+        <f t="shared" si="21"/>
         <v>19500</v>
       </c>
       <c r="L70" s="24">
-        <f>G70</f>
+        <f t="shared" si="22"/>
         <v>4000</v>
       </c>
       <c r="M70" s="24">
-        <f>(1-$D70)*H70</f>
+        <f t="shared" si="23"/>
         <v>750</v>
       </c>
       <c r="N70" s="24">
-        <f>(1-$D70)*I70</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="O70" s="24">
@@ -8647,26 +8647,26 @@
         <v>0</v>
       </c>
       <c r="Z70" s="24">
-        <f>SUM(J70:Y70)</f>
+        <f t="shared" si="25"/>
         <v>44280</v>
       </c>
       <c r="AA70" s="24">
         <v>0</v>
       </c>
       <c r="AB70" s="20">
-        <f>Z70-AA70</f>
+        <f t="shared" si="26"/>
         <v>44280</v>
       </c>
       <c r="AC70" s="24" t="str">
-        <f>IF(AND($T70=6000, ($T70+$W70-$AB70)&gt;=6000),T70,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AD70" s="24" t="str">
-        <f>IF(AND($T70=8000, ($T70+$W70-$AB70)&gt;=8000),T70,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AE70" s="24" t="str">
-        <f>IF(($T70+$W70-$AB70)&gt;=$T70+8000,W70,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -8699,23 +8699,23 @@
         <v>0</v>
       </c>
       <c r="J71" s="24">
-        <f>(1-$D71)*E71</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="K71" s="24">
-        <f>(1-$D71)*F71</f>
+        <f t="shared" si="21"/>
         <v>19500</v>
       </c>
       <c r="L71" s="24">
-        <f>G71</f>
+        <f t="shared" si="22"/>
         <v>4000</v>
       </c>
       <c r="M71" s="24">
-        <f>(1-$D71)*H71</f>
+        <f t="shared" si="23"/>
         <v>750</v>
       </c>
       <c r="N71" s="24">
-        <f>(1-$D71)*I71</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="O71" s="24">
@@ -8752,26 +8752,26 @@
         <v>0</v>
       </c>
       <c r="Z71" s="24">
-        <f>SUM(J71:Y71)</f>
+        <f t="shared" si="25"/>
         <v>44280</v>
       </c>
       <c r="AA71" s="24">
         <v>43000</v>
       </c>
       <c r="AB71" s="20">
-        <f>Z71-AA71</f>
+        <f t="shared" si="26"/>
         <v>1280</v>
       </c>
       <c r="AC71" s="24" t="str">
-        <f>IF(AND($T71=6000, ($T71+$W71-$AB71)&gt;=6000),T71,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AD71" s="24" t="str">
-        <f>IF(AND($T71=8000, ($T71+$W71-$AB71)&gt;=8000),T71,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AE71" s="24" t="str">
-        <f>IF(($T71+$W71-$AB71)&gt;=$T71+8000,W71,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -8804,23 +8804,23 @@
         <v>0</v>
       </c>
       <c r="J72" s="24">
-        <f>(1-$D72)*E72</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="K72" s="24">
-        <f>(1-$D72)*F72</f>
+        <f t="shared" si="21"/>
         <v>26000</v>
       </c>
       <c r="L72" s="24">
-        <f>G72</f>
+        <f t="shared" si="22"/>
         <v>4000</v>
       </c>
       <c r="M72" s="24">
-        <f>(1-$D72)*H72</f>
+        <f t="shared" si="23"/>
         <v>1000</v>
       </c>
       <c r="N72" s="24">
-        <f>(1-$D72)*I72</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="O72" s="24">
@@ -8857,26 +8857,26 @@
         <v>-400</v>
       </c>
       <c r="Z72" s="24">
-        <f>SUM(J72:Y72)</f>
+        <f t="shared" si="25"/>
         <v>56630</v>
       </c>
       <c r="AA72" s="24">
         <v>0</v>
       </c>
       <c r="AB72" s="20">
-        <f>Z72-AA72</f>
+        <f t="shared" si="26"/>
         <v>56630</v>
       </c>
       <c r="AC72" s="24" t="str">
-        <f>IF(AND($T72=6000, ($T72+$W72-$AB72)&gt;=6000),T72,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AD72" s="24" t="str">
-        <f>IF(AND($T72=8000, ($T72+$W72-$AB72)&gt;=8000),T72,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AE72" s="24" t="str">
-        <f>IF(($T72+$W72-$AB72)&gt;=$T72+8000,W72,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -8909,23 +8909,23 @@
         <v>0</v>
       </c>
       <c r="J73" s="24">
-        <f>(1-$D73)*E73</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="K73" s="24">
-        <f>(1-$D73)*F73</f>
+        <f t="shared" si="21"/>
         <v>26000</v>
       </c>
       <c r="L73" s="24">
-        <f>G73</f>
+        <f t="shared" si="22"/>
         <v>4000</v>
       </c>
       <c r="M73" s="24">
-        <f>(1-$D73)*H73</f>
+        <f t="shared" si="23"/>
         <v>1000</v>
       </c>
       <c r="N73" s="24">
-        <f>(1-$D73)*I73</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="O73" s="24">
@@ -8962,26 +8962,26 @@
         <v>11000</v>
       </c>
       <c r="Z73" s="24">
-        <f>SUM(J73:Y73)</f>
+        <f t="shared" si="25"/>
         <v>62030</v>
       </c>
       <c r="AA73" s="24">
         <v>0</v>
       </c>
       <c r="AB73" s="20">
-        <f>Z73-AA73</f>
+        <f t="shared" si="26"/>
         <v>62030</v>
       </c>
       <c r="AC73" s="24" t="str">
-        <f>IF(AND($T73=6000, ($T73+$W73-$AB73)&gt;=6000),T73,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AD73" s="24" t="str">
-        <f>IF(AND($T73=8000, ($T73+$W73-$AB73)&gt;=8000),T73,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AE73" s="24" t="str">
-        <f>IF(($T73+$W73-$AB73)&gt;=$T73+8000,W73,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -9014,23 +9014,23 @@
         <v>0</v>
       </c>
       <c r="J74" s="24">
-        <f>(1-$D74)*E74</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="K74" s="24">
-        <f>(1-$D74)*F74</f>
+        <f t="shared" si="21"/>
         <v>26000</v>
       </c>
       <c r="L74" s="24">
-        <f>G74</f>
+        <f t="shared" si="22"/>
         <v>4000</v>
       </c>
       <c r="M74" s="24">
-        <f>(1-$D74)*H74</f>
+        <f t="shared" si="23"/>
         <v>1000</v>
       </c>
       <c r="N74" s="24">
-        <f>(1-$D74)*I74</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="O74" s="24">
@@ -9067,26 +9067,26 @@
         <v>0</v>
       </c>
       <c r="Z74" s="24">
-        <f>SUM(J74:Y74)</f>
+        <f t="shared" si="25"/>
         <v>51030</v>
       </c>
       <c r="AA74" s="24">
         <v>0</v>
       </c>
       <c r="AB74" s="20">
-        <f>Z74-AA74</f>
+        <f t="shared" si="26"/>
         <v>51030</v>
       </c>
       <c r="AC74" s="24" t="str">
-        <f>IF(AND($T74=6000, ($T74+$W74-$AB74)&gt;=6000),T74,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AD74" s="24" t="str">
-        <f>IF(AND($T74=8000, ($T74+$W74-$AB74)&gt;=8000),T74,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AE74" s="24" t="str">
-        <f>IF(($T74+$W74-$AB74)&gt;=$T74+8000,W74,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -9119,23 +9119,23 @@
         <v>0</v>
       </c>
       <c r="J75" s="24">
-        <f>(1-$D75)*E75</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="K75" s="24">
-        <f>(1-$D75)*F75</f>
+        <f t="shared" si="21"/>
         <v>19500</v>
       </c>
       <c r="L75" s="24">
-        <f>G75</f>
+        <f t="shared" si="22"/>
         <v>4000</v>
       </c>
       <c r="M75" s="24">
-        <f>(1-$D75)*H75</f>
+        <f t="shared" si="23"/>
         <v>750</v>
       </c>
       <c r="N75" s="24">
-        <f>(1-$D75)*I75</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="O75" s="24">
@@ -9172,26 +9172,26 @@
         <v>65</v>
       </c>
       <c r="Z75" s="24">
-        <f>SUM(J75:Y75)</f>
+        <f t="shared" si="25"/>
         <v>50345</v>
       </c>
       <c r="AA75" s="24">
         <v>0</v>
       </c>
       <c r="AB75" s="20">
-        <f>Z75-AA75</f>
+        <f t="shared" si="26"/>
         <v>50345</v>
       </c>
       <c r="AC75" s="24" t="str">
-        <f>IF(AND($T75=6000, ($T75+$W75-$AB75)&gt;=6000),T75,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AD75" s="24" t="str">
-        <f>IF(AND($T75=8000, ($T75+$W75-$AB75)&gt;=8000),T75,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AE75" s="24" t="str">
-        <f>IF(($T75+$W75-$AB75)&gt;=$T75+8000,W75,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -9224,23 +9224,23 @@
         <v>0</v>
       </c>
       <c r="J76" s="24">
-        <f>(1-$D76)*E76</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="K76" s="24">
-        <f>(1-$D76)*F76</f>
+        <f t="shared" si="21"/>
         <v>19500</v>
       </c>
       <c r="L76" s="24">
-        <f>G76</f>
+        <f t="shared" si="22"/>
         <v>4000</v>
       </c>
       <c r="M76" s="24">
-        <f>(1-$D76)*H76</f>
+        <f t="shared" si="23"/>
         <v>750</v>
       </c>
       <c r="N76" s="24">
-        <f>(1-$D76)*I76</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="O76" s="24">
@@ -9277,26 +9277,26 @@
         <v>1250</v>
       </c>
       <c r="Z76" s="24">
-        <f>SUM(J76:Y76)</f>
+        <f t="shared" si="25"/>
         <v>51530</v>
       </c>
       <c r="AA76" s="24">
         <v>0</v>
       </c>
       <c r="AB76" s="20">
-        <f>Z76-AA76</f>
+        <f t="shared" si="26"/>
         <v>51530</v>
       </c>
       <c r="AC76" s="24" t="str">
-        <f>IF(AND($T76=6000, ($T76+$W76-$AB76)&gt;=6000),T76,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AD76" s="24" t="str">
-        <f>IF(AND($T76=8000, ($T76+$W76-$AB76)&gt;=8000),T76,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AE76" s="24" t="str">
-        <f>IF(($T76+$W76-$AB76)&gt;=$T76+8000,W76,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -9329,23 +9329,23 @@
         <v>0</v>
       </c>
       <c r="J77" s="24">
-        <f>(1-$D77)*E77</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="K77" s="24">
-        <f>(1-$D77)*F77</f>
+        <f t="shared" si="21"/>
         <v>19500</v>
       </c>
       <c r="L77" s="24">
-        <f>G77</f>
+        <f t="shared" si="22"/>
         <v>4000</v>
       </c>
       <c r="M77" s="24">
-        <f>(1-$D77)*H77</f>
+        <f t="shared" si="23"/>
         <v>750</v>
       </c>
       <c r="N77" s="24">
-        <f>(1-$D77)*I77</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="O77" s="24">
@@ -9382,26 +9382,26 @@
         <v>0</v>
       </c>
       <c r="Z77" s="24">
-        <f>SUM(J77:Y77)</f>
+        <f t="shared" si="25"/>
         <v>44280</v>
       </c>
       <c r="AA77" s="24">
         <v>0</v>
       </c>
       <c r="AB77" s="20">
-        <f>Z77-AA77</f>
+        <f t="shared" si="26"/>
         <v>44280</v>
       </c>
       <c r="AC77" s="24" t="str">
-        <f>IF(AND($T77=6000, ($T77+$W77-$AB77)&gt;=6000),T77,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AD77" s="24" t="str">
-        <f>IF(AND($T77=8000, ($T77+$W77-$AB77)&gt;=8000),T77,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AE77" s="24" t="str">
-        <f>IF(($T77+$W77-$AB77)&gt;=$T77+8000,W77,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -9434,23 +9434,23 @@
         <v>5000</v>
       </c>
       <c r="J78" s="24">
-        <f>(1-$D78)*E78</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="K78" s="24">
-        <f>(1-$D78)*F78</f>
+        <f t="shared" si="21"/>
         <v>21000</v>
       </c>
       <c r="L78" s="24">
-        <f>G78</f>
+        <f t="shared" si="22"/>
         <v>4000</v>
       </c>
       <c r="M78" s="24">
-        <f>(1-$D78)*H78</f>
+        <f t="shared" si="23"/>
         <v>1875</v>
       </c>
       <c r="N78" s="24">
-        <f>(1-$D78)*I78</f>
+        <f t="shared" si="24"/>
         <v>3750</v>
       </c>
       <c r="O78" s="24">
@@ -9487,26 +9487,26 @@
         <v>0</v>
       </c>
       <c r="Z78" s="24">
-        <f>SUM(J78:Y78)</f>
+        <f t="shared" si="25"/>
         <v>73505</v>
       </c>
       <c r="AA78" s="24">
         <v>0</v>
       </c>
       <c r="AB78" s="20">
-        <f>Z78-AA78</f>
+        <f t="shared" si="26"/>
         <v>73505</v>
       </c>
       <c r="AC78" s="24" t="str">
-        <f>IF(AND($T78=6000, ($T78+$W78-$AB78)&gt;=6000),T78,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AD78" s="24" t="str">
-        <f>IF(AND($T78=8000, ($T78+$W78-$AB78)&gt;=8000),T78,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AE78" s="24" t="str">
-        <f>IF(($T78+$W78-$AB78)&gt;=$T78+8000,W78,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -9539,23 +9539,23 @@
         <v>5000</v>
       </c>
       <c r="J79" s="24">
-        <f>(1-$D79)*E79</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="K79" s="24">
-        <f>(1-$D79)*F79</f>
+        <f t="shared" si="21"/>
         <v>28000</v>
       </c>
       <c r="L79" s="24">
-        <f>G79</f>
+        <f t="shared" si="22"/>
         <v>4000</v>
       </c>
       <c r="M79" s="24">
-        <f>(1-$D79)*H79</f>
+        <f t="shared" si="23"/>
         <v>2500</v>
       </c>
       <c r="N79" s="24">
-        <f>(1-$D79)*I79</f>
+        <f t="shared" si="24"/>
         <v>5000</v>
       </c>
       <c r="O79" s="24">
@@ -9592,26 +9592,26 @@
         <v>0</v>
       </c>
       <c r="Z79" s="24">
-        <f>SUM(J79:Y79)</f>
+        <f t="shared" si="25"/>
         <v>82380</v>
       </c>
       <c r="AA79" s="24">
         <v>0</v>
       </c>
       <c r="AB79" s="20">
-        <f>Z79-AA79</f>
+        <f t="shared" si="26"/>
         <v>82380</v>
       </c>
       <c r="AC79" s="24" t="str">
-        <f>IF(AND($T79=6000, ($T79+$W79-$AB79)&gt;=6000),T79,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AD79" s="24" t="str">
-        <f>IF(AND($T79=8000, ($T79+$W79-$AB79)&gt;=8000),T79,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AE79" s="24" t="str">
-        <f>IF(($T79+$W79-$AB79)&gt;=$T79+8000,W79,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -9644,23 +9644,23 @@
         <v>5000</v>
       </c>
       <c r="J80" s="24">
-        <f>(1-$D80)*E80</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="K80" s="24">
-        <f>(1-$D80)*F80</f>
+        <f t="shared" si="21"/>
         <v>28000</v>
       </c>
       <c r="L80" s="24">
-        <f>G80</f>
+        <f t="shared" si="22"/>
         <v>4000</v>
       </c>
       <c r="M80" s="24">
-        <f>(1-$D80)*H80</f>
+        <f t="shared" si="23"/>
         <v>2500</v>
       </c>
       <c r="N80" s="24">
-        <f>(1-$D80)*I80</f>
+        <f t="shared" si="24"/>
         <v>5000</v>
       </c>
       <c r="O80" s="24">
@@ -9697,26 +9697,26 @@
         <v>0</v>
       </c>
       <c r="Z80" s="24">
-        <f>SUM(J80:Y80)</f>
+        <f t="shared" si="25"/>
         <v>76380</v>
       </c>
       <c r="AA80" s="24">
         <v>0</v>
       </c>
       <c r="AB80" s="20">
-        <f>Z80-AA80</f>
+        <f t="shared" si="26"/>
         <v>76380</v>
       </c>
       <c r="AC80" s="24" t="str">
-        <f>IF(AND($T80=6000, ($T80+$W80-$AB80)&gt;=6000),T80,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AD80" s="24" t="str">
-        <f>IF(AND($T80=8000, ($T80+$W80-$AB80)&gt;=8000),T80,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AE80" s="24" t="str">
-        <f>IF(($T80+$W80-$AB80)&gt;=$T80+8000,W80,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -9749,23 +9749,23 @@
         <v>5000</v>
       </c>
       <c r="J81" s="24">
-        <f>(1-$D81)*E81</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="K81" s="24">
-        <f>(1-$D81)*F81</f>
+        <f t="shared" si="21"/>
         <v>28000</v>
       </c>
       <c r="L81" s="24">
-        <f>G81</f>
+        <f t="shared" si="22"/>
         <v>4000</v>
       </c>
       <c r="M81" s="24">
-        <f>(1-$D81)*H81</f>
+        <f t="shared" si="23"/>
         <v>2500</v>
       </c>
       <c r="N81" s="24">
-        <f>(1-$D81)*I81</f>
+        <f t="shared" si="24"/>
         <v>5000</v>
       </c>
       <c r="O81" s="24">
@@ -9802,26 +9802,26 @@
         <v>550</v>
       </c>
       <c r="Z81" s="24">
-        <f>SUM(J81:Y81)</f>
+        <f t="shared" si="25"/>
         <v>76930</v>
       </c>
       <c r="AA81" s="24">
         <v>0</v>
       </c>
       <c r="AB81" s="20">
-        <f>Z81-AA81</f>
+        <f t="shared" si="26"/>
         <v>76930</v>
       </c>
       <c r="AC81" s="24" t="str">
-        <f>IF(AND($T81=6000, ($T81+$W81-$AB81)&gt;=6000),T81,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AD81" s="24" t="str">
-        <f>IF(AND($T81=8000, ($T81+$W81-$AB81)&gt;=8000),T81,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AE81" s="24" t="str">
-        <f>IF(($T81+$W81-$AB81)&gt;=$T81+8000,W81,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -9854,23 +9854,23 @@
         <v>5000</v>
       </c>
       <c r="J82" s="24">
-        <f>(1-$D82)*E82</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="K82" s="24">
-        <f>(1-$D82)*F82</f>
+        <f t="shared" si="21"/>
         <v>21000</v>
       </c>
       <c r="L82" s="24">
-        <f>G82</f>
+        <f t="shared" si="22"/>
         <v>4000</v>
       </c>
       <c r="M82" s="24">
-        <f>(1-$D82)*H82</f>
+        <f t="shared" si="23"/>
         <v>1875</v>
       </c>
       <c r="N82" s="24">
-        <f>(1-$D82)*I82</f>
+        <f t="shared" si="24"/>
         <v>3750</v>
       </c>
       <c r="O82" s="24">
@@ -9907,26 +9907,26 @@
         <v>0</v>
       </c>
       <c r="Z82" s="24">
-        <f>SUM(J82:Y82)</f>
+        <f t="shared" si="25"/>
         <v>67505</v>
       </c>
       <c r="AA82" s="24">
         <v>0</v>
       </c>
       <c r="AB82" s="20">
-        <f>Z82-AA82</f>
+        <f t="shared" si="26"/>
         <v>67505</v>
       </c>
       <c r="AC82" s="24" t="str">
-        <f>IF(AND($T82=6000, ($T82+$W82-$AB82)&gt;=6000),T82,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AD82" s="24" t="str">
-        <f>IF(AND($T82=8000, ($T82+$W82-$AB82)&gt;=8000),T82,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AE82" s="24" t="str">
-        <f>IF(($T82+$W82-$AB82)&gt;=$T82+8000,W82,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -9959,23 +9959,23 @@
         <v>5000</v>
       </c>
       <c r="J83" s="24">
-        <f>(1-$D83)*E83</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="K83" s="24">
-        <f>(1-$D83)*F83</f>
+        <f t="shared" si="21"/>
         <v>21000</v>
       </c>
       <c r="L83" s="24">
-        <f>G83</f>
+        <f t="shared" si="22"/>
         <v>4000</v>
       </c>
       <c r="M83" s="24">
-        <f>(1-$D83)*H83</f>
+        <f t="shared" si="23"/>
         <v>1875</v>
       </c>
       <c r="N83" s="24">
-        <f>(1-$D83)*I83</f>
+        <f t="shared" si="24"/>
         <v>3750</v>
       </c>
       <c r="O83" s="24">
@@ -10012,26 +10012,26 @@
         <v>0</v>
       </c>
       <c r="Z83" s="24">
-        <f>SUM(J83:Y83)</f>
+        <f t="shared" si="25"/>
         <v>73505</v>
       </c>
       <c r="AA83" s="24">
         <v>0</v>
       </c>
       <c r="AB83" s="20">
-        <f>Z83-AA83</f>
+        <f t="shared" si="26"/>
         <v>73505</v>
       </c>
       <c r="AC83" s="24" t="str">
-        <f>IF(AND($T83=6000, ($T83+$W83-$AB83)&gt;=6000),T83,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AD83" s="24" t="str">
-        <f>IF(AND($T83=8000, ($T83+$W83-$AB83)&gt;=8000),T83,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AE83" s="24" t="str">
-        <f>IF(($T83+$W83-$AB83)&gt;=$T83+8000,W83,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -10064,23 +10064,23 @@
         <v>5000</v>
       </c>
       <c r="J84" s="24">
-        <f>(1-$D84)*E84</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="K84" s="24">
-        <f>(1-$D84)*F84</f>
+        <f t="shared" si="21"/>
         <v>28000</v>
       </c>
       <c r="L84" s="24">
-        <f>G84</f>
+        <f t="shared" si="22"/>
         <v>4000</v>
       </c>
       <c r="M84" s="24">
-        <f>(1-$D84)*H84</f>
+        <f t="shared" si="23"/>
         <v>2500</v>
       </c>
       <c r="N84" s="24">
-        <f>(1-$D84)*I84</f>
+        <f t="shared" si="24"/>
         <v>5000</v>
       </c>
       <c r="O84" s="24">
@@ -10117,26 +10117,26 @@
         <v>0</v>
       </c>
       <c r="Z84" s="24">
-        <f>SUM(J84:Y84)</f>
+        <f t="shared" si="25"/>
         <v>76380</v>
       </c>
       <c r="AA84" s="24">
         <v>0</v>
       </c>
       <c r="AB84" s="20">
-        <f>Z84-AA84</f>
+        <f t="shared" si="26"/>
         <v>76380</v>
       </c>
       <c r="AC84" s="24" t="str">
-        <f>IF(AND($T84=6000, ($T84+$W84-$AB84)&gt;=6000),T84,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AD84" s="24" t="str">
-        <f>IF(AND($T84=8000, ($T84+$W84-$AB84)&gt;=8000),T84,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AE84" s="24" t="str">
-        <f>IF(($T84+$W84-$AB84)&gt;=$T84+8000,W84,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -10169,23 +10169,23 @@
         <v>5000</v>
       </c>
       <c r="J85" s="24">
-        <f>(1-$D85)*E85</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="K85" s="24">
-        <f>(1-$D85)*F85</f>
+        <f t="shared" si="21"/>
         <v>21000</v>
       </c>
       <c r="L85" s="24">
-        <f>G85</f>
+        <f t="shared" si="22"/>
         <v>4000</v>
       </c>
       <c r="M85" s="24">
-        <f>(1-$D85)*H85</f>
+        <f t="shared" si="23"/>
         <v>1875</v>
       </c>
       <c r="N85" s="24">
-        <f>(1-$D85)*I85</f>
+        <f t="shared" si="24"/>
         <v>3750</v>
       </c>
       <c r="O85" s="24">
@@ -10222,26 +10222,26 @@
         <v>0</v>
       </c>
       <c r="Z85" s="24">
-        <f>SUM(J85:Y85)</f>
+        <f t="shared" si="25"/>
         <v>73505</v>
       </c>
       <c r="AA85" s="24">
         <v>0</v>
       </c>
       <c r="AB85" s="20">
-        <f>Z85-AA85</f>
+        <f t="shared" si="26"/>
         <v>73505</v>
       </c>
       <c r="AC85" s="24" t="str">
-        <f>IF(AND($T85=6000, ($T85+$W85-$AB85)&gt;=6000),T85,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AD85" s="24" t="str">
-        <f>IF(AND($T85=8000, ($T85+$W85-$AB85)&gt;=8000),T85,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AE85" s="24" t="str">
-        <f>IF(($T85+$W85-$AB85)&gt;=$T85+8000,W85,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -10274,23 +10274,23 @@
         <v>5000</v>
       </c>
       <c r="J86" s="24">
-        <f>(1-$D86)*E86</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="K86" s="24">
-        <f>(1-$D86)*F86</f>
+        <f t="shared" si="21"/>
         <v>21000</v>
       </c>
       <c r="L86" s="24">
-        <f>G86</f>
+        <f t="shared" si="22"/>
         <v>4000</v>
       </c>
       <c r="M86" s="24">
-        <f>(1-$D86)*H86</f>
+        <f t="shared" si="23"/>
         <v>1875</v>
       </c>
       <c r="N86" s="24">
-        <f>(1-$D86)*I86</f>
+        <f t="shared" si="24"/>
         <v>3750</v>
       </c>
       <c r="O86" s="24">
@@ -10327,35 +10327,35 @@
         <v>9500</v>
       </c>
       <c r="Z86" s="24">
-        <f>SUM(J86:Y86)</f>
+        <f t="shared" si="25"/>
         <v>83005</v>
       </c>
       <c r="AA86" s="24">
         <v>0</v>
       </c>
       <c r="AB86" s="20">
-        <f>Z86-AA86</f>
+        <f t="shared" si="26"/>
         <v>83005</v>
       </c>
       <c r="AC86" s="24" t="str">
-        <f>IF(AND($T86=6000, ($T86+$W86-$AB86)&gt;=6000),T86,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AD86" s="24" t="str">
-        <f>IF(AND($T86=8000, ($T86+$W86-$AB86)&gt;=8000),T86,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AE86" s="24" t="str">
-        <f>IF(($T86+$W86-$AB86)&gt;=$T86+8000,W86,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
     <row r="87" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A87" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="B87" s="22" t="s">
         <v>236</v>
-      </c>
-      <c r="B87" s="22" t="s">
-        <v>237</v>
       </c>
       <c r="C87" s="22" t="s">
         <v>48</v>
@@ -10379,23 +10379,23 @@
         <v>5000</v>
       </c>
       <c r="J87" s="24">
-        <f>(1-$D87)*E87</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="K87" s="24">
-        <f>(1-$D87)*F87</f>
+        <f t="shared" si="21"/>
         <v>21000</v>
       </c>
       <c r="L87" s="24">
-        <f>G87</f>
+        <f t="shared" si="22"/>
         <v>4000</v>
       </c>
       <c r="M87" s="24">
-        <f>(1-$D87)*H87</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="N87" s="24">
-        <f>(1-$D87)*I87</f>
+        <f t="shared" si="24"/>
         <v>3750</v>
       </c>
       <c r="O87" s="24">
@@ -10432,26 +10432,26 @@
         <v>125</v>
       </c>
       <c r="Z87" s="24">
-        <f>SUM(J87:Y87)</f>
+        <f t="shared" si="25"/>
         <v>71935</v>
       </c>
       <c r="AA87" s="24">
         <v>0</v>
       </c>
       <c r="AB87" s="20">
-        <f>Z87-AA87</f>
+        <f t="shared" si="26"/>
         <v>71935</v>
       </c>
       <c r="AC87" s="24" t="str">
-        <f>IF(AND($T87=6000, ($T87+$W87-$AB87)&gt;=6000),T87,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AD87" s="24" t="str">
-        <f>IF(AND($T87=8000, ($T87+$W87-$AB87)&gt;=8000),T87,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AE87" s="24" t="str">
-        <f>IF(($T87+$W87-$AB87)&gt;=$T87+8000,W87,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -10484,23 +10484,23 @@
         <v>5000</v>
       </c>
       <c r="J88" s="24">
-        <f>(1-$D88)*E88</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="K88" s="24">
-        <f>(1-$D88)*F88</f>
+        <f t="shared" si="21"/>
         <v>21000</v>
       </c>
       <c r="L88" s="24">
-        <f>G88</f>
+        <f t="shared" si="22"/>
         <v>4000</v>
       </c>
       <c r="M88" s="24">
-        <f>(1-$D88)*H88</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="N88" s="24">
-        <f>(1-$D88)*I88</f>
+        <f t="shared" si="24"/>
         <v>3750</v>
       </c>
       <c r="O88" s="24">
@@ -10537,26 +10537,26 @@
         <v>0</v>
       </c>
       <c r="Z88" s="24">
-        <f>SUM(J88:Y88)</f>
+        <f t="shared" si="25"/>
         <v>65810</v>
       </c>
       <c r="AA88" s="24">
         <v>0</v>
       </c>
       <c r="AB88" s="20">
-        <f>Z88-AA88</f>
+        <f t="shared" si="26"/>
         <v>65810</v>
       </c>
       <c r="AC88" s="24" t="str">
-        <f>IF(AND($T88=6000, ($T88+$W88-$AB88)&gt;=6000),T88,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AD88" s="24" t="str">
-        <f>IF(AND($T88=8000, ($T88+$W88-$AB88)&gt;=8000),T88,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AE88" s="24" t="str">
-        <f>IF(($T88+$W88-$AB88)&gt;=$T88+8000,W88,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -10589,23 +10589,23 @@
         <v>5000</v>
       </c>
       <c r="J89" s="24">
-        <f>(1-$D89)*E89</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="K89" s="24">
-        <f>(1-$D89)*F89</f>
+        <f t="shared" si="21"/>
         <v>21000</v>
       </c>
       <c r="L89" s="24">
-        <f>G89</f>
+        <f t="shared" si="22"/>
         <v>4000</v>
       </c>
       <c r="M89" s="24">
-        <f>(1-$D89)*H89</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="N89" s="24">
-        <f>(1-$D89)*I89</f>
+        <f t="shared" si="24"/>
         <v>3750</v>
       </c>
       <c r="O89" s="24">
@@ -10642,26 +10642,26 @@
         <v>0</v>
       </c>
       <c r="Z89" s="24">
-        <f>SUM(J89:Y89)</f>
+        <f t="shared" si="25"/>
         <v>65810</v>
       </c>
       <c r="AA89" s="24">
         <v>0</v>
       </c>
       <c r="AB89" s="20">
-        <f>Z89-AA89</f>
+        <f t="shared" si="26"/>
         <v>65810</v>
       </c>
       <c r="AC89" s="24" t="str">
-        <f>IF(AND($T89=6000, ($T89+$W89-$AB89)&gt;=6000),T89,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AD89" s="24" t="str">
-        <f>IF(AND($T89=8000, ($T89+$W89-$AB89)&gt;=8000),T89,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AE89" s="24" t="str">
-        <f>IF(($T89+$W89-$AB89)&gt;=$T89+8000,W89,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -10694,23 +10694,23 @@
         <v>5000</v>
       </c>
       <c r="J90" s="24">
-        <f>(1-$D90)*E90</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="K90" s="24">
-        <f>(1-$D90)*F90</f>
+        <f t="shared" si="21"/>
         <v>21000</v>
       </c>
       <c r="L90" s="24">
-        <f>G90</f>
+        <f t="shared" si="22"/>
         <v>4000</v>
       </c>
       <c r="M90" s="24">
-        <f>(1-$D90)*H90</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="N90" s="24">
-        <f>(1-$D90)*I90</f>
+        <f t="shared" si="24"/>
         <v>3750</v>
       </c>
       <c r="O90" s="24">
@@ -10747,26 +10747,26 @@
         <v>250</v>
       </c>
       <c r="Z90" s="24">
-        <f>SUM(J90:Y90)</f>
+        <f t="shared" si="25"/>
         <v>72060</v>
       </c>
       <c r="AA90" s="24">
         <v>0</v>
       </c>
       <c r="AB90" s="20">
-        <f>Z90-AA90</f>
+        <f t="shared" si="26"/>
         <v>72060</v>
       </c>
       <c r="AC90" s="24" t="str">
-        <f>IF(AND($T90=6000, ($T90+$W90-$AB90)&gt;=6000),T90,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AD90" s="24" t="str">
-        <f>IF(AND($T90=8000, ($T90+$W90-$AB90)&gt;=8000),T90,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AE90" s="24" t="str">
-        <f>IF(($T90+$W90-$AB90)&gt;=$T90+8000,W90,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -10799,23 +10799,23 @@
         <v>5000</v>
       </c>
       <c r="J91" s="24">
-        <f>(1-$D91)*E91</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="K91" s="24">
-        <f>(1-$D91)*F91</f>
+        <f t="shared" si="21"/>
         <v>21000</v>
       </c>
       <c r="L91" s="24">
-        <f>G91</f>
+        <f t="shared" si="22"/>
         <v>4000</v>
       </c>
       <c r="M91" s="24">
-        <f>(1-$D91)*H91</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="N91" s="24">
-        <f>(1-$D91)*I91</f>
+        <f t="shared" si="24"/>
         <v>3750</v>
       </c>
       <c r="O91" s="24">
@@ -10852,26 +10852,26 @@
         <v>22105</v>
       </c>
       <c r="Z91" s="24">
-        <f>SUM(J91:Y91)</f>
+        <f t="shared" si="25"/>
         <v>93915</v>
       </c>
       <c r="AA91" s="24">
         <v>0</v>
       </c>
       <c r="AB91" s="20">
-        <f>Z91-AA91</f>
+        <f t="shared" si="26"/>
         <v>93915</v>
       </c>
       <c r="AC91" s="24" t="str">
-        <f>IF(AND($T91=6000, ($T91+$W91-$AB91)&gt;=6000),T91,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AD91" s="24" t="str">
-        <f>IF(AND($T91=8000, ($T91+$W91-$AB91)&gt;=8000),T91,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AE91" s="24" t="str">
-        <f>IF(($T91+$W91-$AB91)&gt;=$T91+8000,W91,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -10904,23 +10904,23 @@
         <v>5000</v>
       </c>
       <c r="J92" s="24">
-        <f>(1-$D92)*E92</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="K92" s="24">
-        <f>(1-$D92)*F92</f>
+        <f t="shared" si="21"/>
         <v>14000</v>
       </c>
       <c r="L92" s="24">
-        <f>G92</f>
+        <f t="shared" si="22"/>
         <v>4000</v>
       </c>
       <c r="M92" s="24">
-        <f>(1-$D92)*H92</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="N92" s="24">
-        <f>(1-$D92)*I92</f>
+        <f t="shared" si="24"/>
         <v>2500</v>
       </c>
       <c r="O92" s="24">
@@ -10957,26 +10957,26 @@
         <v>0</v>
       </c>
       <c r="Z92" s="24">
-        <f>SUM(J92:Y92)</f>
+        <f t="shared" si="25"/>
         <v>57560</v>
       </c>
       <c r="AA92" s="24">
         <v>0</v>
       </c>
       <c r="AB92" s="20">
-        <f>Z92-AA92</f>
+        <f t="shared" si="26"/>
         <v>57560</v>
       </c>
       <c r="AC92" s="24" t="str">
-        <f>IF(AND($T92=6000, ($T92+$W92-$AB92)&gt;=6000),T92,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AD92" s="24" t="str">
-        <f>IF(AND($T92=8000, ($T92+$W92-$AB92)&gt;=8000),T92,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AE92" s="24" t="str">
-        <f>IF(($T92+$W92-$AB92)&gt;=$T92+8000,W92,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -11009,23 +11009,23 @@
         <v>5000</v>
       </c>
       <c r="J93" s="24">
-        <f>(1-$D93)*E93</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="K93" s="24">
-        <f>(1-$D93)*F93</f>
+        <f t="shared" si="21"/>
         <v>21000</v>
       </c>
       <c r="L93" s="24">
-        <f>G93</f>
+        <f t="shared" si="22"/>
         <v>4000</v>
       </c>
       <c r="M93" s="24">
-        <f>(1-$D93)*H93</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="N93" s="24">
-        <f>(1-$D93)*I93</f>
+        <f t="shared" si="24"/>
         <v>3750</v>
       </c>
       <c r="O93" s="24">
@@ -11062,26 +11062,26 @@
         <v>0</v>
       </c>
       <c r="Z93" s="24">
-        <f>SUM(J93:Y93)</f>
+        <f t="shared" si="25"/>
         <v>65810</v>
       </c>
       <c r="AA93" s="24">
         <v>0</v>
       </c>
       <c r="AB93" s="20">
-        <f>Z93-AA93</f>
+        <f t="shared" si="26"/>
         <v>65810</v>
       </c>
       <c r="AC93" s="24" t="str">
-        <f>IF(AND($T93=6000, ($T93+$W93-$AB93)&gt;=6000),T93,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AD93" s="24" t="str">
-        <f>IF(AND($T93=8000, ($T93+$W93-$AB93)&gt;=8000),T93,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AE93" s="24" t="str">
-        <f>IF(($T93+$W93-$AB93)&gt;=$T93+8000,W93,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -11114,23 +11114,23 @@
         <v>5000</v>
       </c>
       <c r="J94" s="24">
-        <f>(1-$D94)*E94</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="K94" s="24">
-        <f>(1-$D94)*F94</f>
+        <f t="shared" si="21"/>
         <v>28000</v>
       </c>
       <c r="L94" s="24">
-        <f>G94</f>
+        <f t="shared" si="22"/>
         <v>4000</v>
       </c>
       <c r="M94" s="24">
-        <f>(1-$D94)*H94</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="N94" s="24">
-        <f>(1-$D94)*I94</f>
+        <f t="shared" si="24"/>
         <v>5000</v>
       </c>
       <c r="O94" s="24">
@@ -11167,26 +11167,26 @@
         <v>4020</v>
       </c>
       <c r="Z94" s="24">
-        <f>SUM(J94:Y94)</f>
+        <f t="shared" si="25"/>
         <v>78080</v>
       </c>
       <c r="AA94" s="24">
         <v>0</v>
       </c>
       <c r="AB94" s="20">
-        <f>Z94-AA94</f>
+        <f t="shared" si="26"/>
         <v>78080</v>
       </c>
       <c r="AC94" s="24" t="str">
-        <f>IF(AND($T94=6000, ($T94+$W94-$AB94)&gt;=6000),T94,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AD94" s="24" t="str">
-        <f>IF(AND($T94=8000, ($T94+$W94-$AB94)&gt;=8000),T94,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AE94" s="24" t="str">
-        <f>IF(($T94+$W94-$AB94)&gt;=$T94+8000,W94,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -11219,23 +11219,23 @@
         <v>5000</v>
       </c>
       <c r="J95" s="24">
-        <f>(1-$D95)*E95</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="K95" s="24">
-        <f>(1-$D95)*F95</f>
+        <f t="shared" si="21"/>
         <v>21000</v>
       </c>
       <c r="L95" s="24">
-        <f>G95</f>
+        <f t="shared" si="22"/>
         <v>4000</v>
       </c>
       <c r="M95" s="24">
-        <f>(1-$D95)*H95</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="N95" s="24">
-        <f>(1-$D95)*I95</f>
+        <f t="shared" si="24"/>
         <v>3750</v>
       </c>
       <c r="O95" s="24">
@@ -11272,26 +11272,26 @@
         <v>0</v>
       </c>
       <c r="Z95" s="24">
-        <f>SUM(J95:Y95)</f>
+        <f t="shared" si="25"/>
         <v>68870</v>
       </c>
       <c r="AA95" s="24">
         <v>0</v>
       </c>
       <c r="AB95" s="20">
-        <f>Z95-AA95</f>
+        <f t="shared" si="26"/>
         <v>68870</v>
       </c>
       <c r="AC95" s="24" t="str">
-        <f>IF(AND($T95=6000, ($T95+$W95-$AB95)&gt;=6000),T95,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AD95" s="24" t="str">
-        <f>IF(AND($T95=8000, ($T95+$W95-$AB95)&gt;=8000),T95,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AE95" s="24" t="str">
-        <f>IF(($T95+$W95-$AB95)&gt;=$T95+8000,W95,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -11324,23 +11324,23 @@
         <v>5000</v>
       </c>
       <c r="J96" s="24">
-        <f>(1-$D96)*E96</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="K96" s="24">
-        <f>(1-$D96)*F96</f>
+        <f t="shared" si="21"/>
         <v>14000</v>
       </c>
       <c r="L96" s="24">
-        <f>G96</f>
+        <f t="shared" si="22"/>
         <v>4000</v>
       </c>
       <c r="M96" s="24">
-        <f>(1-$D96)*H96</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="N96" s="24">
-        <f>(1-$D96)*I96</f>
+        <f t="shared" si="24"/>
         <v>2500</v>
       </c>
       <c r="O96" s="24">
@@ -11377,26 +11377,26 @@
         <v>-530</v>
       </c>
       <c r="Z96" s="24">
-        <f>SUM(J96:Y96)</f>
+        <f t="shared" si="25"/>
         <v>60090</v>
       </c>
       <c r="AA96" s="24">
         <v>0</v>
       </c>
       <c r="AB96" s="20">
-        <f>Z96-AA96</f>
+        <f t="shared" si="26"/>
         <v>60090</v>
       </c>
       <c r="AC96" s="24" t="str">
-        <f>IF(AND($T96=6000, ($T96+$W96-$AB96)&gt;=6000),T96,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AD96" s="24" t="str">
-        <f>IF(AND($T96=8000, ($T96+$W96-$AB96)&gt;=8000),T96,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AE96" s="24" t="str">
-        <f>IF(($T96+$W96-$AB96)&gt;=$T96+8000,W96,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -11429,23 +11429,23 @@
         <v>5000</v>
       </c>
       <c r="J97" s="24">
-        <f>(1-$D97)*E97</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="K97" s="24">
-        <f>(1-$D97)*F97</f>
+        <f t="shared" si="21"/>
         <v>21000</v>
       </c>
       <c r="L97" s="24">
-        <f>G97</f>
+        <f t="shared" si="22"/>
         <v>4000</v>
       </c>
       <c r="M97" s="24">
-        <f>(1-$D97)*H97</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="N97" s="24">
-        <f>(1-$D97)*I97</f>
+        <f t="shared" si="24"/>
         <v>3750</v>
       </c>
       <c r="O97" s="24">
@@ -11482,26 +11482,26 @@
         <v>0</v>
       </c>
       <c r="Z97" s="24">
-        <f>SUM(J97:Y97)</f>
+        <f t="shared" si="25"/>
         <v>68870</v>
       </c>
       <c r="AA97" s="24">
         <v>0</v>
       </c>
       <c r="AB97" s="20">
-        <f>Z97-AA97</f>
+        <f t="shared" si="26"/>
         <v>68870</v>
       </c>
       <c r="AC97" s="24" t="str">
-        <f>IF(AND($T97=6000, ($T97+$W97-$AB97)&gt;=6000),T97,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AD97" s="24" t="str">
-        <f>IF(AND($T97=8000, ($T97+$W97-$AB97)&gt;=8000),T97,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AE97" s="24" t="str">
-        <f>IF(($T97+$W97-$AB97)&gt;=$T97+8000,W97,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -11534,23 +11534,23 @@
         <v>5000</v>
       </c>
       <c r="J98" s="24">
-        <f>(1-$D98)*E98</f>
+        <f t="shared" ref="J98:J120" si="30">(1-$D98)*E98</f>
         <v>0</v>
       </c>
       <c r="K98" s="24">
-        <f>(1-$D98)*F98</f>
+        <f t="shared" ref="K98:K120" si="31">(1-$D98)*F98</f>
         <v>28000</v>
       </c>
       <c r="L98" s="24">
-        <f>G98</f>
+        <f t="shared" ref="L98:L120" si="32">G98</f>
         <v>4000</v>
       </c>
       <c r="M98" s="24">
-        <f>(1-$D98)*H98</f>
+        <f t="shared" ref="M98:M120" si="33">(1-$D98)*H98</f>
         <v>0</v>
       </c>
       <c r="N98" s="24">
-        <f>(1-$D98)*I98</f>
+        <f t="shared" ref="N98:N120" si="34">(1-$D98)*I98</f>
         <v>5000</v>
       </c>
       <c r="O98" s="24">
@@ -11587,26 +11587,26 @@
         <v>0</v>
       </c>
       <c r="Z98" s="24">
-        <f>SUM(J98:Y98)</f>
+        <f t="shared" ref="Z98:Z129" si="35">SUM(J98:Y98)</f>
         <v>77120</v>
       </c>
       <c r="AA98" s="24">
         <v>0</v>
       </c>
       <c r="AB98" s="20">
-        <f>Z98-AA98</f>
+        <f t="shared" ref="AB98:AB129" si="36">Z98-AA98</f>
         <v>77120</v>
       </c>
       <c r="AC98" s="24" t="str">
-        <f>IF(AND($T98=6000, ($T98+$W98-$AB98)&gt;=6000),T98,"")</f>
+        <f t="shared" ref="AC98:AC120" si="37">IF(AND($T98=6000, ($T98+$W98-$AB98)&gt;=6000),T98,"")</f>
         <v/>
       </c>
       <c r="AD98" s="24" t="str">
-        <f>IF(AND($T98=8000, ($T98+$W98-$AB98)&gt;=8000),T98,"")</f>
+        <f t="shared" ref="AD98:AD120" si="38">IF(AND($T98=8000, ($T98+$W98-$AB98)&gt;=8000),T98,"")</f>
         <v/>
       </c>
       <c r="AE98" s="24" t="str">
-        <f>IF(($T98+$W98-$AB98)&gt;=$T98+8000,W98,"")</f>
+        <f t="shared" ref="AE98:AE120" si="39">IF(($T98+$W98-$AB98)&gt;=$T98+8000,W98,"")</f>
         <v/>
       </c>
     </row>
@@ -11639,23 +11639,23 @@
         <v>5000</v>
       </c>
       <c r="J99" s="24">
-        <f>(1-$D99)*E99</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="K99" s="24">
-        <f>(1-$D99)*F99</f>
+        <f t="shared" si="31"/>
         <v>21000</v>
       </c>
       <c r="L99" s="24">
-        <f>G99</f>
+        <f t="shared" si="32"/>
         <v>4000</v>
       </c>
       <c r="M99" s="24">
-        <f>(1-$D99)*H99</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="N99" s="24">
-        <f>(1-$D99)*I99</f>
+        <f t="shared" si="34"/>
         <v>3750</v>
       </c>
       <c r="O99" s="24">
@@ -11692,26 +11692,26 @@
         <v>-695</v>
       </c>
       <c r="Z99" s="24">
-        <f>SUM(J99:Y99)</f>
+        <f t="shared" si="35"/>
         <v>74175</v>
       </c>
       <c r="AA99" s="24">
         <v>0</v>
       </c>
       <c r="AB99" s="20">
-        <f>Z99-AA99</f>
+        <f t="shared" si="36"/>
         <v>74175</v>
       </c>
       <c r="AC99" s="24" t="str">
-        <f>IF(AND($T99=6000, ($T99+$W99-$AB99)&gt;=6000),T99,"")</f>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AD99" s="24" t="str">
-        <f>IF(AND($T99=8000, ($T99+$W99-$AB99)&gt;=8000),T99,"")</f>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AE99" s="24" t="str">
-        <f>IF(($T99+$W99-$AB99)&gt;=$T99+8000,W99,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -11744,23 +11744,23 @@
         <v>5000</v>
       </c>
       <c r="J100" s="24">
-        <f>(1-$D100)*E100</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="K100" s="24">
-        <f>(1-$D100)*F100</f>
+        <f t="shared" si="31"/>
         <v>21000</v>
       </c>
       <c r="L100" s="24">
-        <f>G100</f>
+        <f t="shared" si="32"/>
         <v>4000</v>
       </c>
       <c r="M100" s="24">
-        <f>(1-$D100)*H100</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="N100" s="24">
-        <f>(1-$D100)*I100</f>
+        <f t="shared" si="34"/>
         <v>3750</v>
       </c>
       <c r="O100" s="24">
@@ -11797,26 +11797,26 @@
         <v>450</v>
       </c>
       <c r="Z100" s="24">
-        <f>SUM(J100:Y100)</f>
+        <f t="shared" si="35"/>
         <v>69320</v>
       </c>
       <c r="AA100" s="24">
         <v>0</v>
       </c>
       <c r="AB100" s="20">
-        <f>Z100-AA100</f>
+        <f t="shared" si="36"/>
         <v>69320</v>
       </c>
       <c r="AC100" s="24" t="str">
-        <f>IF(AND($T100=6000, ($T100+$W100-$AB100)&gt;=6000),T100,"")</f>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AD100" s="24" t="str">
-        <f>IF(AND($T100=8000, ($T100+$W100-$AB100)&gt;=8000),T100,"")</f>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AE100" s="24" t="str">
-        <f>IF(($T100+$W100-$AB100)&gt;=$T100+8000,W100,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -11849,23 +11849,23 @@
         <v>5000</v>
       </c>
       <c r="J101" s="24">
-        <f>(1-$D101)*E101</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="K101" s="24">
-        <f>(1-$D101)*F101</f>
+        <f t="shared" si="31"/>
         <v>21000</v>
       </c>
       <c r="L101" s="24">
-        <f>G101</f>
+        <f t="shared" si="32"/>
         <v>4000</v>
       </c>
       <c r="M101" s="24">
-        <f>(1-$D101)*H101</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="N101" s="24">
-        <f>(1-$D101)*I101</f>
+        <f t="shared" si="34"/>
         <v>3750</v>
       </c>
       <c r="O101" s="24">
@@ -11902,26 +11902,26 @@
         <v>0</v>
       </c>
       <c r="Z101" s="24">
-        <f>SUM(J101:Y101)</f>
+        <f t="shared" si="35"/>
         <v>74870</v>
       </c>
       <c r="AA101" s="24">
         <v>0</v>
       </c>
       <c r="AB101" s="20">
-        <f>Z101-AA101</f>
+        <f t="shared" si="36"/>
         <v>74870</v>
       </c>
       <c r="AC101" s="24" t="str">
-        <f>IF(AND($T101=6000, ($T101+$W101-$AB101)&gt;=6000),T101,"")</f>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AD101" s="24" t="str">
-        <f>IF(AND($T101=8000, ($T101+$W101-$AB101)&gt;=8000),T101,"")</f>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AE101" s="24" t="str">
-        <f>IF(($T101+$W101-$AB101)&gt;=$T101+8000,W101,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -11954,23 +11954,23 @@
         <v>5000</v>
       </c>
       <c r="J102" s="24">
-        <f>(1-$D102)*E102</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="K102" s="24">
-        <f>(1-$D102)*F102</f>
+        <f t="shared" si="31"/>
         <v>21000</v>
       </c>
       <c r="L102" s="24">
-        <f>G102</f>
+        <f t="shared" si="32"/>
         <v>4000</v>
       </c>
       <c r="M102" s="24">
-        <f>(1-$D102)*H102</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="N102" s="24">
-        <f>(1-$D102)*I102</f>
+        <f t="shared" si="34"/>
         <v>3750</v>
       </c>
       <c r="O102" s="24">
@@ -12007,26 +12007,26 @@
         <v>0</v>
       </c>
       <c r="Z102" s="24">
-        <f>SUM(J102:Y102)</f>
+        <f t="shared" si="35"/>
         <v>68870</v>
       </c>
       <c r="AA102" s="24">
         <v>0</v>
       </c>
       <c r="AB102" s="20">
-        <f>Z102-AA102</f>
+        <f t="shared" si="36"/>
         <v>68870</v>
       </c>
       <c r="AC102" s="24" t="str">
-        <f>IF(AND($T102=6000, ($T102+$W102-$AB102)&gt;=6000),T102,"")</f>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AD102" s="24" t="str">
-        <f>IF(AND($T102=8000, ($T102+$W102-$AB102)&gt;=8000),T102,"")</f>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AE102" s="24" t="str">
-        <f>IF(($T102+$W102-$AB102)&gt;=$T102+8000,W102,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -12059,23 +12059,23 @@
         <v>5000</v>
       </c>
       <c r="J103" s="24">
-        <f>(1-$D103)*E103</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="K103" s="24">
-        <f>(1-$D103)*F103</f>
+        <f t="shared" si="31"/>
         <v>21000</v>
       </c>
       <c r="L103" s="24">
-        <f>G103</f>
+        <f t="shared" si="32"/>
         <v>4000</v>
       </c>
       <c r="M103" s="24">
-        <f>(1-$D103)*H103</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="N103" s="24">
-        <f>(1-$D103)*I103</f>
+        <f t="shared" si="34"/>
         <v>3750</v>
       </c>
       <c r="O103" s="24">
@@ -12112,26 +12112,26 @@
         <v>0</v>
       </c>
       <c r="Z103" s="24">
-        <f>SUM(J103:Y103)</f>
+        <f t="shared" si="35"/>
         <v>74870</v>
       </c>
       <c r="AA103" s="24">
         <v>0</v>
       </c>
       <c r="AB103" s="20">
-        <f>Z103-AA103</f>
+        <f t="shared" si="36"/>
         <v>74870</v>
       </c>
       <c r="AC103" s="24" t="str">
-        <f>IF(AND($T103=6000, ($T103+$W103-$AB103)&gt;=6000),T103,"")</f>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AD103" s="24" t="str">
-        <f>IF(AND($T103=8000, ($T103+$W103-$AB103)&gt;=8000),T103,"")</f>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AE103" s="24" t="str">
-        <f>IF(($T103+$W103-$AB103)&gt;=$T103+8000,W103,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -12164,23 +12164,23 @@
         <v>5000</v>
       </c>
       <c r="J104" s="24">
-        <f>(1-$D104)*E104</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="K104" s="24">
-        <f>(1-$D104)*F104</f>
+        <f t="shared" si="31"/>
         <v>21000</v>
       </c>
       <c r="L104" s="24">
-        <f>G104</f>
+        <f t="shared" si="32"/>
         <v>4000</v>
       </c>
       <c r="M104" s="24">
-        <f>(1-$D104)*H104</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="N104" s="24">
-        <f>(1-$D104)*I104</f>
+        <f t="shared" si="34"/>
         <v>3750</v>
       </c>
       <c r="O104" s="24">
@@ -12217,26 +12217,26 @@
         <v>0</v>
       </c>
       <c r="Z104" s="24">
-        <f>SUM(J104:Y104)</f>
+        <f t="shared" si="35"/>
         <v>68890</v>
       </c>
       <c r="AA104" s="24">
         <v>0</v>
       </c>
       <c r="AB104" s="20">
-        <f>Z104-AA104</f>
+        <f t="shared" si="36"/>
         <v>68890</v>
       </c>
       <c r="AC104" s="24" t="str">
-        <f>IF(AND($T104=6000, ($T104+$W104-$AB104)&gt;=6000),T104,"")</f>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AD104" s="24" t="str">
-        <f>IF(AND($T104=8000, ($T104+$W104-$AB104)&gt;=8000),T104,"")</f>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AE104" s="24" t="str">
-        <f>IF(($T104+$W104-$AB104)&gt;=$T104+8000,W104,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -12269,23 +12269,23 @@
         <v>5000</v>
       </c>
       <c r="J105" s="24">
-        <f>(1-$D105)*E105</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="K105" s="24">
-        <f>(1-$D105)*F105</f>
+        <f t="shared" si="31"/>
         <v>14000</v>
       </c>
       <c r="L105" s="24">
-        <f>G105</f>
+        <f t="shared" si="32"/>
         <v>4000</v>
       </c>
       <c r="M105" s="24">
-        <f>(1-$D105)*H105</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="N105" s="24">
-        <f>(1-$D105)*I105</f>
+        <f t="shared" si="34"/>
         <v>2500</v>
       </c>
       <c r="O105" s="24">
@@ -12322,26 +12322,26 @@
         <v>8080</v>
       </c>
       <c r="Z105" s="24">
-        <f>SUM(J105:Y105)</f>
+        <f t="shared" si="35"/>
         <v>68720</v>
       </c>
       <c r="AA105" s="24">
         <v>0</v>
       </c>
       <c r="AB105" s="20">
-        <f>Z105-AA105</f>
+        <f t="shared" si="36"/>
         <v>68720</v>
       </c>
       <c r="AC105" s="24" t="str">
-        <f>IF(AND($T105=6000, ($T105+$W105-$AB105)&gt;=6000),T105,"")</f>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AD105" s="24" t="str">
-        <f>IF(AND($T105=8000, ($T105+$W105-$AB105)&gt;=8000),T105,"")</f>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AE105" s="24" t="str">
-        <f>IF(($T105+$W105-$AB105)&gt;=$T105+8000,W105,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -12374,23 +12374,23 @@
         <v>5000</v>
       </c>
       <c r="J106" s="24">
-        <f>(1-$D106)*E106</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="K106" s="24">
-        <f>(1-$D106)*F106</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="L106" s="24">
-        <f>G106</f>
+        <f t="shared" si="32"/>
         <v>4000</v>
       </c>
       <c r="M106" s="24">
-        <f>(1-$D106)*H106</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="N106" s="24">
-        <f>(1-$D106)*I106</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="O106" s="24">
@@ -12427,26 +12427,26 @@
         <v>0</v>
       </c>
       <c r="Z106" s="24">
-        <f>SUM(J106:Y106)</f>
+        <f t="shared" si="35"/>
         <v>50140</v>
       </c>
       <c r="AA106" s="24">
         <v>0</v>
       </c>
       <c r="AB106" s="20">
-        <f>Z106-AA106</f>
+        <f t="shared" si="36"/>
         <v>50140</v>
       </c>
       <c r="AC106" s="24" t="str">
-        <f>IF(AND($T106=6000, ($T106+$W106-$AB106)&gt;=6000),T106,"")</f>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AD106" s="24" t="str">
-        <f>IF(AND($T106=8000, ($T106+$W106-$AB106)&gt;=8000),T106,"")</f>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AE106" s="24" t="str">
-        <f>IF(($T106+$W106-$AB106)&gt;=$T106+8000,W106,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -12479,23 +12479,23 @@
         <v>5000</v>
       </c>
       <c r="J107" s="24">
-        <f>(1-$D107)*E107</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="K107" s="24">
-        <f>(1-$D107)*F107</f>
+        <f t="shared" si="31"/>
         <v>21000</v>
       </c>
       <c r="L107" s="24">
-        <f>G107</f>
+        <f t="shared" si="32"/>
         <v>4000</v>
       </c>
       <c r="M107" s="24">
-        <f>(1-$D107)*H107</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="N107" s="24">
-        <f>(1-$D107)*I107</f>
+        <f t="shared" si="34"/>
         <v>3750</v>
       </c>
       <c r="O107" s="24">
@@ -12532,26 +12532,26 @@
         <v>0</v>
       </c>
       <c r="Z107" s="24">
-        <f>SUM(J107:Y107)</f>
+        <f t="shared" si="35"/>
         <v>74890</v>
       </c>
       <c r="AA107" s="24">
         <v>0</v>
       </c>
       <c r="AB107" s="20">
-        <f>Z107-AA107</f>
+        <f t="shared" si="36"/>
         <v>74890</v>
       </c>
       <c r="AC107" s="24" t="str">
-        <f>IF(AND($T107=6000, ($T107+$W107-$AB107)&gt;=6000),T107,"")</f>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AD107" s="24" t="str">
-        <f>IF(AND($T107=8000, ($T107+$W107-$AB107)&gt;=8000),T107,"")</f>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AE107" s="24" t="str">
-        <f>IF(($T107+$W107-$AB107)&gt;=$T107+8000,W107,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -12563,7 +12563,7 @@
         <v>45</v>
       </c>
       <c r="C108" s="22" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D108" s="23">
         <v>0.25</v>
@@ -12584,23 +12584,23 @@
         <v>5000</v>
       </c>
       <c r="J108" s="24">
-        <f>(1-$D108)*E108</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="K108" s="24">
-        <f>(1-$D108)*F108</f>
+        <f t="shared" si="31"/>
         <v>21000</v>
       </c>
       <c r="L108" s="24">
-        <f>G108</f>
+        <f t="shared" si="32"/>
         <v>4000</v>
       </c>
       <c r="M108" s="24">
-        <f>(1-$D108)*H108</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="N108" s="24">
-        <f>(1-$D108)*I108</f>
+        <f t="shared" si="34"/>
         <v>3750</v>
       </c>
       <c r="O108" s="24">
@@ -12637,26 +12637,26 @@
         <v>0</v>
       </c>
       <c r="Z108" s="24">
-        <f>SUM(J108:Y108)</f>
+        <f t="shared" si="35"/>
         <v>76830</v>
       </c>
       <c r="AA108" s="24">
         <v>0</v>
       </c>
       <c r="AB108" s="20">
-        <f>Z108-AA108</f>
+        <f t="shared" si="36"/>
         <v>76830</v>
       </c>
       <c r="AC108" s="24" t="str">
-        <f>IF(AND($T108=6000, ($T108+$W108-$AB108)&gt;=6000),T108,"")</f>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AD108" s="24" t="str">
-        <f>IF(AND($T108=8000, ($T108+$W108-$AB108)&gt;=8000),T108,"")</f>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AE108" s="24" t="str">
-        <f>IF(($T108+$W108-$AB108)&gt;=$T108+8000,W108,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -12668,7 +12668,7 @@
         <v>77</v>
       </c>
       <c r="C109" s="22" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D109" s="23">
         <v>0</v>
@@ -12689,23 +12689,23 @@
         <v>5000</v>
       </c>
       <c r="J109" s="24">
-        <f>(1-$D109)*E109</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="K109" s="24">
-        <f>(1-$D109)*F109</f>
+        <f t="shared" si="31"/>
         <v>28000</v>
       </c>
       <c r="L109" s="24">
-        <f>G109</f>
+        <f t="shared" si="32"/>
         <v>4000</v>
       </c>
       <c r="M109" s="24">
-        <f>(1-$D109)*H109</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="N109" s="24">
-        <f>(1-$D109)*I109</f>
+        <f t="shared" si="34"/>
         <v>5000</v>
       </c>
       <c r="O109" s="24">
@@ -12742,26 +12742,26 @@
         <v>0</v>
       </c>
       <c r="Z109" s="24">
-        <f>SUM(J109:Y109)</f>
+        <f t="shared" si="35"/>
         <v>79080</v>
       </c>
       <c r="AA109" s="24">
         <v>0</v>
       </c>
       <c r="AB109" s="20">
-        <f>Z109-AA109</f>
+        <f t="shared" si="36"/>
         <v>79080</v>
       </c>
       <c r="AC109" s="24" t="str">
-        <f>IF(AND($T109=6000, ($T109+$W109-$AB109)&gt;=6000),T109,"")</f>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AD109" s="24" t="str">
-        <f>IF(AND($T109=8000, ($T109+$W109-$AB109)&gt;=8000),T109,"")</f>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AE109" s="24" t="str">
-        <f>IF(($T109+$W109-$AB109)&gt;=$T109+8000,W109,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -12773,7 +12773,7 @@
         <v>225</v>
       </c>
       <c r="C110" s="22" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D110" s="23">
         <v>0.25</v>
@@ -12794,23 +12794,23 @@
         <v>5000</v>
       </c>
       <c r="J110" s="24">
-        <f>(1-$D110)*E110</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="K110" s="24">
-        <f>(1-$D110)*F110</f>
+        <f t="shared" si="31"/>
         <v>21000</v>
       </c>
       <c r="L110" s="24">
-        <f>G110</f>
+        <f t="shared" si="32"/>
         <v>4000</v>
       </c>
       <c r="M110" s="24">
-        <f>(1-$D110)*H110</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="N110" s="24">
-        <f>(1-$D110)*I110</f>
+        <f t="shared" si="34"/>
         <v>3750</v>
       </c>
       <c r="O110" s="24">
@@ -12847,26 +12847,26 @@
         <v>24395</v>
       </c>
       <c r="Z110" s="24">
-        <f>SUM(J110:Y110)</f>
+        <f t="shared" si="35"/>
         <v>101225</v>
       </c>
       <c r="AA110" s="24">
         <v>0</v>
       </c>
       <c r="AB110" s="20">
-        <f>Z110-AA110</f>
+        <f t="shared" si="36"/>
         <v>101225</v>
       </c>
       <c r="AC110" s="24" t="str">
-        <f>IF(AND($T110=6000, ($T110+$W110-$AB110)&gt;=6000),T110,"")</f>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AD110" s="24" t="str">
-        <f>IF(AND($T110=8000, ($T110+$W110-$AB110)&gt;=8000),T110,"")</f>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AE110" s="24" t="str">
-        <f>IF(($T110+$W110-$AB110)&gt;=$T110+8000,W110,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -12878,7 +12878,7 @@
         <v>129</v>
       </c>
       <c r="C111" s="22" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D111" s="23">
         <v>0.25</v>
@@ -12899,23 +12899,23 @@
         <v>5000</v>
       </c>
       <c r="J111" s="24">
-        <f>(1-$D111)*E111</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="K111" s="24">
-        <f>(1-$D111)*F111</f>
+        <f t="shared" si="31"/>
         <v>21000</v>
       </c>
       <c r="L111" s="24">
-        <f>G111</f>
+        <f t="shared" si="32"/>
         <v>4000</v>
       </c>
       <c r="M111" s="24">
-        <f>(1-$D111)*H111</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="N111" s="24">
-        <f>(1-$D111)*I111</f>
+        <f t="shared" si="34"/>
         <v>3750</v>
       </c>
       <c r="O111" s="24">
@@ -12952,26 +12952,26 @@
         <v>0</v>
       </c>
       <c r="Z111" s="24">
-        <f>SUM(J111:Y111)</f>
+        <f t="shared" si="35"/>
         <v>76830</v>
       </c>
       <c r="AA111" s="24">
         <v>0</v>
       </c>
       <c r="AB111" s="20">
-        <f>Z111-AA111</f>
+        <f t="shared" si="36"/>
         <v>76830</v>
       </c>
       <c r="AC111" s="24" t="str">
-        <f>IF(AND($T111=6000, ($T111+$W111-$AB111)&gt;=6000),T111,"")</f>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AD111" s="24" t="str">
-        <f>IF(AND($T111=8000, ($T111+$W111-$AB111)&gt;=8000),T111,"")</f>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AE111" s="24" t="str">
-        <f>IF(($T111+$W111-$AB111)&gt;=$T111+8000,W111,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -13004,23 +13004,23 @@
         <v>8000</v>
       </c>
       <c r="J112" s="24">
-        <f>(1-$D112)*E112</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="K112" s="24">
-        <f>(1-$D112)*F112</f>
+        <f t="shared" si="31"/>
         <v>30000</v>
       </c>
       <c r="L112" s="24">
-        <f>G112</f>
+        <f t="shared" si="32"/>
         <v>5000</v>
       </c>
       <c r="M112" s="24">
-        <f>(1-$D112)*H112</f>
+        <f t="shared" si="33"/>
         <v>1500</v>
       </c>
       <c r="N112" s="24">
-        <f>(1-$D112)*I112</f>
+        <f t="shared" si="34"/>
         <v>6000</v>
       </c>
       <c r="O112" s="24">
@@ -13057,26 +13057,26 @@
         <v>540</v>
       </c>
       <c r="Z112" s="24">
-        <f>SUM(J112:Y112)</f>
+        <f t="shared" si="35"/>
         <v>97250</v>
       </c>
       <c r="AA112" s="24">
         <v>0</v>
       </c>
       <c r="AB112" s="20">
-        <f>Z112-AA112</f>
+        <f t="shared" si="36"/>
         <v>97250</v>
       </c>
       <c r="AC112" s="24" t="str">
-        <f>IF(AND($T112=6000, ($T112+$W112-$AB112)&gt;=6000),T112,"")</f>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AD112" s="24" t="str">
-        <f>IF(AND($T112=8000, ($T112+$W112-$AB112)&gt;=8000),T112,"")</f>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AE112" s="24" t="str">
-        <f>IF(($T112+$W112-$AB112)&gt;=$T112+8000,W112,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -13109,23 +13109,23 @@
         <v>8000</v>
       </c>
       <c r="J113" s="24">
-        <f>(1-$D113)*E113</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="K113" s="24">
-        <f>(1-$D113)*F113</f>
+        <f t="shared" si="31"/>
         <v>40000</v>
       </c>
       <c r="L113" s="24">
-        <f>G113</f>
+        <f t="shared" si="32"/>
         <v>5000</v>
       </c>
       <c r="M113" s="24">
-        <f>(1-$D113)*H113</f>
+        <f t="shared" si="33"/>
         <v>2000</v>
       </c>
       <c r="N113" s="24">
-        <f>(1-$D113)*I113</f>
+        <f t="shared" si="34"/>
         <v>8000</v>
       </c>
       <c r="O113" s="24">
@@ -13162,26 +13162,26 @@
         <v>0</v>
       </c>
       <c r="Z113" s="24">
-        <f>SUM(J113:Y113)</f>
+        <f t="shared" si="35"/>
         <v>81210</v>
       </c>
       <c r="AA113" s="24">
         <v>0</v>
       </c>
       <c r="AB113" s="20">
-        <f>Z113-AA113</f>
+        <f t="shared" si="36"/>
         <v>81210</v>
       </c>
       <c r="AC113" s="24" t="str">
-        <f>IF(AND($T113=6000, ($T113+$W113-$AB113)&gt;=6000),T113,"")</f>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AD113" s="24" t="str">
-        <f>IF(AND($T113=8000, ($T113+$W113-$AB113)&gt;=8000),T113,"")</f>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AE113" s="24" t="str">
-        <f>IF(($T113+$W113-$AB113)&gt;=$T113+8000,W113,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -13214,23 +13214,23 @@
         <v>8000</v>
       </c>
       <c r="J114" s="24">
-        <f>(1-$D114)*E114</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="K114" s="24">
-        <f>(1-$D114)*F114</f>
+        <f t="shared" si="31"/>
         <v>40000</v>
       </c>
       <c r="L114" s="24">
-        <f>G114</f>
+        <f t="shared" si="32"/>
         <v>5000</v>
       </c>
       <c r="M114" s="24">
-        <f>(1-$D114)*H114</f>
+        <f t="shared" si="33"/>
         <v>2000</v>
       </c>
       <c r="N114" s="24">
-        <f>(1-$D114)*I114</f>
+        <f t="shared" si="34"/>
         <v>8000</v>
       </c>
       <c r="O114" s="24">
@@ -13267,26 +13267,26 @@
         <v>0</v>
       </c>
       <c r="Z114" s="24">
-        <f>SUM(J114:Y114)</f>
+        <f t="shared" si="35"/>
         <v>81210</v>
       </c>
       <c r="AA114" s="24">
         <v>0</v>
       </c>
       <c r="AB114" s="20">
-        <f>Z114-AA114</f>
+        <f t="shared" si="36"/>
         <v>81210</v>
       </c>
       <c r="AC114" s="24" t="str">
-        <f>IF(AND($T114=6000, ($T114+$W114-$AB114)&gt;=6000),T114,"")</f>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AD114" s="24" t="str">
-        <f>IF(AND($T114=8000, ($T114+$W114-$AB114)&gt;=8000),T114,"")</f>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AE114" s="24" t="str">
-        <f>IF(($T114+$W114-$AB114)&gt;=$T114+8000,W114,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -13319,23 +13319,23 @@
         <v>8000</v>
       </c>
       <c r="J115" s="24">
-        <f>(1-$D115)*E115</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="K115" s="24">
-        <f>(1-$D115)*F115</f>
+        <f t="shared" si="31"/>
         <v>40000</v>
       </c>
       <c r="L115" s="24">
-        <f>G115</f>
+        <f t="shared" si="32"/>
         <v>5000</v>
       </c>
       <c r="M115" s="24">
-        <f>(1-$D115)*H115</f>
+        <f t="shared" si="33"/>
         <v>2000</v>
       </c>
       <c r="N115" s="24">
-        <f>(1-$D115)*I115</f>
+        <f t="shared" si="34"/>
         <v>8000</v>
       </c>
       <c r="O115" s="24">
@@ -13372,26 +13372,26 @@
         <v>120</v>
       </c>
       <c r="Z115" s="24">
-        <f>SUM(J115:Y115)</f>
+        <f t="shared" si="35"/>
         <v>81330</v>
       </c>
       <c r="AA115" s="24">
         <v>0</v>
       </c>
       <c r="AB115" s="20">
-        <f>Z115-AA115</f>
+        <f t="shared" si="36"/>
         <v>81330</v>
       </c>
       <c r="AC115" s="24" t="str">
-        <f>IF(AND($T115=6000, ($T115+$W115-$AB115)&gt;=6000),T115,"")</f>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AD115" s="24" t="str">
-        <f>IF(AND($T115=8000, ($T115+$W115-$AB115)&gt;=8000),T115,"")</f>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AE115" s="24" t="str">
-        <f>IF(($T115+$W115-$AB115)&gt;=$T115+8000,W115,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -13424,23 +13424,23 @@
         <v>8000</v>
       </c>
       <c r="J116" s="24">
-        <f>(1-$D116)*E116</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="K116" s="24">
-        <f>(1-$D116)*F116</f>
+        <f t="shared" si="31"/>
         <v>30000</v>
       </c>
       <c r="L116" s="24">
-        <f>G116</f>
+        <f t="shared" si="32"/>
         <v>5000</v>
       </c>
       <c r="M116" s="24">
-        <f>(1-$D116)*H116</f>
+        <f t="shared" si="33"/>
         <v>1500</v>
       </c>
       <c r="N116" s="24">
-        <f>(1-$D116)*I116</f>
+        <f t="shared" si="34"/>
         <v>6000</v>
       </c>
       <c r="O116" s="24">
@@ -13477,26 +13477,26 @@
         <v>0</v>
       </c>
       <c r="Z116" s="24">
-        <f>SUM(J116:Y116)</f>
+        <f t="shared" si="35"/>
         <v>68710</v>
       </c>
       <c r="AA116" s="24">
         <v>0</v>
       </c>
       <c r="AB116" s="20">
-        <f>Z116-AA116</f>
+        <f t="shared" si="36"/>
         <v>68710</v>
       </c>
       <c r="AC116" s="24" t="str">
-        <f>IF(AND($T116=6000, ($T116+$W116-$AB116)&gt;=6000),T116,"")</f>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AD116" s="24" t="str">
-        <f>IF(AND($T116=8000, ($T116+$W116-$AB116)&gt;=8000),T116,"")</f>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AE116" s="24" t="str">
-        <f>IF(($T116+$W116-$AB116)&gt;=$T116+8000,W116,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -13529,23 +13529,23 @@
         <v>8000</v>
       </c>
       <c r="J117" s="24">
-        <f>(1-$D117)*E117</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="K117" s="24">
-        <f>(1-$D117)*F117</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="L117" s="24">
-        <f>G117</f>
+        <f t="shared" si="32"/>
         <v>5000</v>
       </c>
       <c r="M117" s="24">
-        <f>(1-$D117)*H117</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="N117" s="24">
-        <f>(1-$D117)*I117</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="O117" s="24">
@@ -13582,26 +13582,26 @@
         <v>0</v>
       </c>
       <c r="Z117" s="24">
-        <f>SUM(J117:Y117)</f>
+        <f t="shared" si="35"/>
         <v>31210</v>
       </c>
       <c r="AA117" s="24">
         <v>0</v>
       </c>
       <c r="AB117" s="20">
-        <f>Z117-AA117</f>
+        <f t="shared" si="36"/>
         <v>31210</v>
       </c>
       <c r="AC117" s="24" t="str">
-        <f>IF(AND($T117=6000, ($T117+$W117-$AB117)&gt;=6000),T117,"")</f>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AD117" s="24" t="str">
-        <f>IF(AND($T117=8000, ($T117+$W117-$AB117)&gt;=8000),T117,"")</f>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AE117" s="24" t="str">
-        <f>IF(($T117+$W117-$AB117)&gt;=$T117+8000,W117,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -13634,23 +13634,23 @@
         <v>8000</v>
       </c>
       <c r="J118" s="24">
-        <f>(1-$D118)*E118</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="K118" s="24">
-        <f>(1-$D118)*F118</f>
+        <f t="shared" si="31"/>
         <v>30000</v>
       </c>
       <c r="L118" s="24">
-        <f>G118</f>
+        <f t="shared" si="32"/>
         <v>5000</v>
       </c>
       <c r="M118" s="24">
-        <f>(1-$D118)*H118</f>
+        <f t="shared" si="33"/>
         <v>1500</v>
       </c>
       <c r="N118" s="24">
-        <f>(1-$D118)*I118</f>
+        <f t="shared" si="34"/>
         <v>6000</v>
       </c>
       <c r="O118" s="24">
@@ -13687,26 +13687,26 @@
         <v>2660</v>
       </c>
       <c r="Z118" s="24">
-        <f>SUM(J118:Y118)</f>
+        <f t="shared" si="35"/>
         <v>79370</v>
       </c>
       <c r="AA118" s="24">
         <v>0</v>
       </c>
       <c r="AB118" s="20">
-        <f>Z118-AA118</f>
+        <f t="shared" si="36"/>
         <v>79370</v>
       </c>
       <c r="AC118" s="24" t="str">
-        <f>IF(AND($T118=6000, ($T118+$W118-$AB118)&gt;=6000),T118,"")</f>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AD118" s="24" t="str">
-        <f>IF(AND($T118=8000, ($T118+$W118-$AB118)&gt;=8000),T118,"")</f>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AE118" s="24" t="str">
-        <f>IF(($T118+$W118-$AB118)&gt;=$T118+8000,W118,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -13739,23 +13739,23 @@
         <v>8000</v>
       </c>
       <c r="J119" s="24">
-        <f>(1-$D119)*E119</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="K119" s="24">
-        <f>(1-$D119)*F119</f>
+        <f t="shared" si="31"/>
         <v>30000</v>
       </c>
       <c r="L119" s="24">
-        <f>G119</f>
+        <f t="shared" si="32"/>
         <v>5000</v>
       </c>
       <c r="M119" s="24">
-        <f>(1-$D119)*H119</f>
+        <f t="shared" si="33"/>
         <v>1500</v>
       </c>
       <c r="N119" s="24">
-        <f>(1-$D119)*I119</f>
+        <f t="shared" si="34"/>
         <v>6000</v>
       </c>
       <c r="O119" s="24">
@@ -13792,26 +13792,26 @@
         <v>0</v>
       </c>
       <c r="Z119" s="24">
-        <f>SUM(J119:Y119)</f>
+        <f t="shared" si="35"/>
         <v>68710</v>
       </c>
       <c r="AA119" s="24">
         <v>0</v>
       </c>
       <c r="AB119" s="20">
-        <f>Z119-AA119</f>
+        <f t="shared" si="36"/>
         <v>68710</v>
       </c>
       <c r="AC119" s="24" t="str">
-        <f>IF(AND($T119=6000, ($T119+$W119-$AB119)&gt;=6000),T119,"")</f>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AD119" s="24" t="str">
-        <f>IF(AND($T119=8000, ($T119+$W119-$AB119)&gt;=8000),T119,"")</f>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AE119" s="24" t="str">
-        <f>IF(($T119+$W119-$AB119)&gt;=$T119+8000,W119,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -13844,23 +13844,23 @@
         <v>8000</v>
       </c>
       <c r="J120" s="24">
-        <f>(1-$D120)*E120</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="K120" s="24">
-        <f>(1-$D120)*F120</f>
+        <f t="shared" si="31"/>
         <v>40000</v>
       </c>
       <c r="L120" s="24">
-        <f>G120</f>
+        <f t="shared" si="32"/>
         <v>5000</v>
       </c>
       <c r="M120" s="24">
-        <f>(1-$D120)*H120</f>
+        <f t="shared" si="33"/>
         <v>2000</v>
       </c>
       <c r="N120" s="24">
-        <f>(1-$D120)*I120</f>
+        <f t="shared" si="34"/>
         <v>8000</v>
       </c>
       <c r="O120" s="24">
@@ -13897,26 +13897,26 @@
         <v>5830</v>
       </c>
       <c r="Z120" s="24">
-        <f>SUM(J120:Y120)</f>
+        <f t="shared" si="35"/>
         <v>87040</v>
       </c>
       <c r="AA120" s="24">
         <v>0</v>
       </c>
       <c r="AB120" s="20">
-        <f>Z120-AA120</f>
+        <f t="shared" si="36"/>
         <v>87040</v>
       </c>
       <c r="AC120" s="24" t="str">
-        <f>IF(AND($T120=6000, ($T120+$W120-$AB120)&gt;=6000),T120,"")</f>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AD120" s="24" t="str">
-        <f>IF(AND($T120=8000, ($T120+$W120-$AB120)&gt;=8000),T120,"")</f>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AE120" s="24" t="str">
-        <f>IF(($T120+$W120-$AB120)&gt;=$T120+8000,W120,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -13946,31 +13946,31 @@
       <c r="W121" s="27"/>
       <c r="X121" s="27"/>
       <c r="Y121" s="27">
-        <f>SUM(Y2:Y120)</f>
+        <f t="shared" ref="Y121:AE121" si="40">SUM(Y2:Y120)</f>
         <v>188670</v>
       </c>
       <c r="Z121" s="27">
-        <f>SUM(Z2:Z120)</f>
+        <f t="shared" si="40"/>
         <v>7251495</v>
       </c>
       <c r="AA121" s="27">
-        <f>SUM(AA2:AA120)</f>
+        <f t="shared" si="40"/>
         <v>91000</v>
       </c>
       <c r="AB121" s="27">
-        <f>SUM(AB2:AB120)</f>
+        <f t="shared" si="40"/>
         <v>7160495</v>
       </c>
       <c r="AC121" s="27">
-        <f>SUM(AC2:AC120)</f>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AD121" s="27">
-        <f>SUM(AD2:AD120)</f>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AE121" s="27">
-        <f>SUM(AE2:AE120)</f>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
     </row>
@@ -22197,16 +22197,16 @@
         <v>166</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>246</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>247</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>139</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F1" s="4"/>
       <c r="G1" s="4"/>
@@ -22233,16 +22233,16 @@
         <v>46238</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D2" s="9">
         <v>48000</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="3" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -22250,16 +22250,16 @@
         <v>46255</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D3" s="9">
         <v>43000</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="4" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
